--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14T22:45</t>
+          <t>2026-09-14T23:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -539,16 +539,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:00</t>
+          <t>2026-09-14T23:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="E4" t="n">
         <v>81</v>
@@ -548,7 +548,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="District_Daily_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Telangana_State_Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +425,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>district</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>state</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -455,71 +456,86 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>weather_code</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>observation_time</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12T09:00</t>
+          <t>Adilabad</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.4</v>
+        <v>25.1</v>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>11.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-13T09:00</t>
+          <t>Bhadradri Kothagudem</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.1</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="H3" t="n">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -530,28 +546,1285 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:15</t>
+          <t>Hanumakonda</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>82</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>80</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>92</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>94</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>67</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>23</v>
+      </c>
+      <c r="E10" t="n">
+        <v>89</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>26</v>
+      </c>
+      <c r="E11" t="n">
+        <v>82</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>93</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>93</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>95</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>79</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>87</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>85</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>84</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>24</v>
+      </c>
+      <c r="E19" t="n">
+        <v>96</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>86</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>88</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" t="n">
+        <v>75</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>85</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>79</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>87</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>83</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>82</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>79</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>82</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>94</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E31" t="n">
+        <v>81</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>69</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>94</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>86</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>total_districts_monitored</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>state_avg_temp_C</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>hottest_district</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>max_temp_C</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>coolest_district</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>min_temp_C</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>state_avg_humidity_%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>total_state_rainfall_mm</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>rainiest_district</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>max_rainfall_mm</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>windiest_district</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>max_wind_speed_kmh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>23</v>
+      </c>
+      <c r="I2" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>12.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="District_Daily_Data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Telangana_State_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Monthly_Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1812,7 +1813,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Bhadradri Kothagudem</t>
+          <t>Jangaon</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -1825,6 +1826,948 @@
       </c>
       <c r="N2" t="n">
         <v>12.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>monthly_avg_temp_C</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>monthly_max_temp_C</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>monthly_min_temp_C</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>monthly_avg_humidity_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>monthly_total_rain_mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>87</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F3" t="n">
+        <v>96</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>94</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>82</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>80</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>92</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>94</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>67</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>23</v>
+      </c>
+      <c r="D10" t="n">
+        <v>23</v>
+      </c>
+      <c r="E10" t="n">
+        <v>23</v>
+      </c>
+      <c r="F10" t="n">
+        <v>89</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D11" t="n">
+        <v>26</v>
+      </c>
+      <c r="E11" t="n">
+        <v>26</v>
+      </c>
+      <c r="F11" t="n">
+        <v>82</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>93</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>93</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>95</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>79</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>87</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>85</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>84</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>24</v>
+      </c>
+      <c r="D19" t="n">
+        <v>24</v>
+      </c>
+      <c r="E19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" t="n">
+        <v>96</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F20" t="n">
+        <v>86</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>88</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" t="n">
+        <v>75</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>85</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D24" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>79</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D25" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="F25" t="n">
+        <v>87</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>83</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>82</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>79</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>82</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>94</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D31" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E31" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>81</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>69</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>94</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>86</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -1813,7 +1813,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Jangaon</t>
+          <t>Hanumakonda</t>
         </is>
       </c>
       <c r="L2" t="n">

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1683,6 +1683,1190 @@
       <c r="I34" t="inlineStr">
         <is>
           <t>2026-09-14T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>63</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>66</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>64</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>44</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>51</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>31</v>
+      </c>
+      <c r="E39" t="n">
+        <v>65</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>31</v>
+      </c>
+      <c r="E40" t="n">
+        <v>58</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>65</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E42" t="n">
+        <v>44</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E43" t="n">
+        <v>59</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>65</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E45" t="n">
+        <v>61</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E46" t="n">
+        <v>63</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E47" t="n">
+        <v>63</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E48" t="n">
+        <v>53</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>32</v>
+      </c>
+      <c r="E49" t="n">
+        <v>67</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>30</v>
+      </c>
+      <c r="E50" t="n">
+        <v>61</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E51" t="n">
+        <v>66</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H51" t="n">
+        <v>51</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>54</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E53" t="n">
+        <v>49</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E54" t="n">
+        <v>50</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E55" t="n">
+        <v>65</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>9</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>61</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>66</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>66</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E59" t="n">
+        <v>53</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H59" t="n">
+        <v>51</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>51</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H60" t="n">
+        <v>51</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E61" t="n">
+        <v>64</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H61" t="n">
+        <v>51</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E62" t="n">
+        <v>57</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E63" t="n">
+        <v>55</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E64" t="n">
+        <v>51</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E65" t="n">
+        <v>61</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E66" t="n">
+        <v>52</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-09-15T14:15</t>
         </is>
       </c>
     </row>
@@ -1697,7 +2881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1826,6 +3010,62 @@
       </c>
       <c r="N2" t="n">
         <v>12.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>11.2</v>
       </c>
     </row>
   </sheetData>
@@ -1891,16 +3131,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25.1</v>
+        <v>28.2</v>
       </c>
       <c r="D2" t="n">
-        <v>25.1</v>
+        <v>31.4</v>
       </c>
       <c r="E2" t="n">
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1918,16 +3158,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>28.2</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>31.5</v>
       </c>
       <c r="E3" t="n">
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1945,16 +3185,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24.9</v>
+        <v>28.2</v>
       </c>
       <c r="D4" t="n">
-        <v>24.9</v>
+        <v>31.5</v>
       </c>
       <c r="E4" t="n">
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1972,19 +3212,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24.8</v>
+        <v>28.4</v>
       </c>
       <c r="D5" t="n">
-        <v>24.8</v>
+        <v>32.1</v>
       </c>
       <c r="E5" t="n">
         <v>24.8</v>
       </c>
       <c r="F5" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
@@ -1999,16 +3239,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25.7</v>
+        <v>28.4</v>
       </c>
       <c r="D6" t="n">
-        <v>25.7</v>
+        <v>31</v>
       </c>
       <c r="E6" t="n">
         <v>25.7</v>
       </c>
       <c r="F6" t="n">
-        <v>80</v>
+        <v>72.5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2026,16 +3266,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24.4</v>
+        <v>27.7</v>
       </c>
       <c r="D7" t="n">
-        <v>24.4</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2053,16 +3293,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24.6</v>
+        <v>28.1</v>
       </c>
       <c r="D8" t="n">
-        <v>24.6</v>
+        <v>31.6</v>
       </c>
       <c r="E8" t="n">
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>94</v>
+        <v>79.5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -2080,16 +3320,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27.4</v>
+        <v>30.6</v>
       </c>
       <c r="D9" t="n">
-        <v>27.4</v>
+        <v>33.8</v>
       </c>
       <c r="E9" t="n">
         <v>27.4</v>
       </c>
       <c r="F9" t="n">
-        <v>67</v>
+        <v>55.5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2107,16 +3347,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>26.4</v>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>29.9</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2134,16 +3374,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>28.8</v>
       </c>
       <c r="D11" t="n">
-        <v>26</v>
+        <v>31.5</v>
       </c>
       <c r="E11" t="n">
         <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>82</v>
+        <v>73.5</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -2161,16 +3401,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.5</v>
+        <v>29</v>
       </c>
       <c r="D12" t="n">
-        <v>25.5</v>
+        <v>32.5</v>
       </c>
       <c r="E12" t="n">
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2188,16 +3428,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25.3</v>
+        <v>28.4</v>
       </c>
       <c r="D13" t="n">
-        <v>25.3</v>
+        <v>31.6</v>
       </c>
       <c r="E13" t="n">
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2215,16 +3455,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.9</v>
+        <v>28.3</v>
       </c>
       <c r="D14" t="n">
-        <v>24.9</v>
+        <v>31.7</v>
       </c>
       <c r="E14" t="n">
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -2242,16 +3482,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24.3</v>
+        <v>27.4</v>
       </c>
       <c r="D15" t="n">
-        <v>24.3</v>
+        <v>30.6</v>
       </c>
       <c r="E15" t="n">
         <v>24.3</v>
       </c>
       <c r="F15" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -2269,16 +3509,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26.8</v>
+        <v>29.4</v>
       </c>
       <c r="D16" t="n">
-        <v>26.8</v>
+        <v>32</v>
       </c>
       <c r="E16" t="n">
         <v>26.8</v>
       </c>
       <c r="F16" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -2296,16 +3536,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.3</v>
+        <v>27.2</v>
       </c>
       <c r="D17" t="n">
-        <v>24.3</v>
+        <v>30</v>
       </c>
       <c r="E17" t="n">
         <v>24.3</v>
       </c>
       <c r="F17" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -2350,19 +3590,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>27.4</v>
       </c>
       <c r="D19" t="n">
-        <v>24</v>
+        <v>30.9</v>
       </c>
       <c r="E19" t="n">
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="20">
@@ -2377,16 +3617,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.7</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>24.7</v>
+        <v>31.2</v>
       </c>
       <c r="E20" t="n">
         <v>24.7</v>
       </c>
       <c r="F20" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2404,16 +3644,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>25.7</v>
+        <v>29.6</v>
       </c>
       <c r="D21" t="n">
-        <v>25.7</v>
+        <v>33.6</v>
       </c>
       <c r="E21" t="n">
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>88</v>
+        <v>68.5</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2431,16 +3671,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>28.2</v>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>31.3</v>
       </c>
       <c r="E22" t="n">
         <v>25</v>
       </c>
       <c r="F22" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -2458,16 +3698,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.4</v>
+        <v>27.5</v>
       </c>
       <c r="D23" t="n">
-        <v>24.4</v>
+        <v>30.6</v>
       </c>
       <c r="E23" t="n">
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2485,16 +3725,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.7</v>
+        <v>27.4</v>
       </c>
       <c r="D24" t="n">
-        <v>24.7</v>
+        <v>30.2</v>
       </c>
       <c r="E24" t="n">
         <v>24.7</v>
       </c>
       <c r="F24" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2512,16 +3752,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.9</v>
+        <v>28.7</v>
       </c>
       <c r="D25" t="n">
-        <v>25.9</v>
+        <v>31.5</v>
       </c>
       <c r="E25" t="n">
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>87</v>
+        <v>76.5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2539,16 +3779,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.2</v>
+        <v>28.2</v>
       </c>
       <c r="D26" t="n">
-        <v>25.2</v>
+        <v>31.1</v>
       </c>
       <c r="E26" t="n">
         <v>25.2</v>
       </c>
       <c r="F26" t="n">
-        <v>83</v>
+        <v>74.5</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2566,19 +3806,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.2</v>
+        <v>27.4</v>
       </c>
       <c r="D27" t="n">
-        <v>24.2</v>
+        <v>30.5</v>
       </c>
       <c r="E27" t="n">
         <v>24.2</v>
       </c>
       <c r="F27" t="n">
-        <v>82</v>
+        <v>67.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="28">
@@ -2593,19 +3833,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.5</v>
+        <v>27.8</v>
       </c>
       <c r="D28" t="n">
-        <v>24.5</v>
+        <v>31.1</v>
       </c>
       <c r="E28" t="n">
         <v>24.5</v>
       </c>
       <c r="F28" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="29">
@@ -2620,19 +3860,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.4</v>
+        <v>27.1</v>
       </c>
       <c r="D29" t="n">
-        <v>24.4</v>
+        <v>29.8</v>
       </c>
       <c r="E29" t="n">
         <v>24.4</v>
       </c>
       <c r="F29" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="30">
@@ -2647,16 +3887,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25.4</v>
+        <v>29.1</v>
       </c>
       <c r="D30" t="n">
-        <v>25.4</v>
+        <v>32.8</v>
       </c>
       <c r="E30" t="n">
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>94</v>
+        <v>75.5</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2674,16 +3914,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>23.9</v>
+        <v>26.8</v>
       </c>
       <c r="D31" t="n">
-        <v>23.9</v>
+        <v>29.8</v>
       </c>
       <c r="E31" t="n">
         <v>23.9</v>
       </c>
       <c r="F31" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2701,16 +3941,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>26.4</v>
+        <v>29.2</v>
       </c>
       <c r="D32" t="n">
-        <v>26.4</v>
+        <v>31.9</v>
       </c>
       <c r="E32" t="n">
         <v>26.4</v>
       </c>
       <c r="F32" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -2728,16 +3968,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>24.7</v>
+        <v>28.2</v>
       </c>
       <c r="D33" t="n">
-        <v>24.7</v>
+        <v>31.7</v>
       </c>
       <c r="E33" t="n">
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>94</v>
+        <v>77.5</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2755,16 +3995,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>24.5</v>
+        <v>28</v>
       </c>
       <c r="D34" t="n">
-        <v>24.5</v>
+        <v>31.6</v>
       </c>
       <c r="E34" t="n">
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2867,6 +2867,1227 @@
       <c r="I66" t="inlineStr">
         <is>
           <t>2026-09-15T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E67" t="n">
+        <v>52</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H67" t="n">
+        <v>51</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E68" t="n">
+        <v>66</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E69" t="n">
+        <v>58</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>4</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E70" t="n">
+        <v>38</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>32</v>
+      </c>
+      <c r="E71" t="n">
+        <v>57</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E72" t="n">
+        <v>56</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E73" t="n">
+        <v>57</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="E74" t="n">
+        <v>39</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>8</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>31</v>
+      </c>
+      <c r="E75" t="n">
+        <v>52</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E76" t="n">
+        <v>58</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E77" t="n">
+        <v>54</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E78" t="n">
+        <v>53</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E79" t="n">
+        <v>60</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E80" t="n">
+        <v>49</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>58</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E82" t="n">
+        <v>54</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E83" t="n">
+        <v>45</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E84" t="n">
+        <v>65</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E85" t="n">
+        <v>48</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>9</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>35</v>
+      </c>
+      <c r="E86" t="n">
+        <v>41</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E87" t="n">
+        <v>48</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E88" t="n">
+        <v>58</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>58</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E90" t="n">
+        <v>62</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>32</v>
+      </c>
+      <c r="E91" t="n">
+        <v>55</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>31</v>
+      </c>
+      <c r="E92" t="n">
+        <v>50</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H92" t="n">
+        <v>51</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E93" t="n">
+        <v>45</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H93" t="n">
+        <v>51</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>54</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G94" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H94" t="n">
+        <v>51</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E95" t="n">
+        <v>49</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E96" t="n">
+        <v>50</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G96" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H96" t="n">
+        <v>51</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E97" t="n">
+        <v>43</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E98" t="n">
+        <v>56</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>4</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E99" t="n">
+        <v>50</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:15</t>
         </is>
       </c>
     </row>
@@ -2881,7 +4102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3066,6 +4287,62 @@
       </c>
       <c r="N3" t="n">
         <v>11.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>33</v>
+      </c>
+      <c r="D4" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3131,19 +4408,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.2</v>
+        <v>29.7</v>
       </c>
       <c r="D2" t="n">
-        <v>31.4</v>
+        <v>32.5</v>
       </c>
       <c r="E2" t="n">
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>67.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
@@ -3158,16 +4435,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.2</v>
+        <v>29.7</v>
       </c>
       <c r="D3" t="n">
-        <v>31.5</v>
+        <v>32.6</v>
       </c>
       <c r="E3" t="n">
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -3185,16 +4462,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.2</v>
+        <v>29.7</v>
       </c>
       <c r="D4" t="n">
-        <v>31.5</v>
+        <v>32.7</v>
       </c>
       <c r="E4" t="n">
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -3212,16 +4489,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.4</v>
+        <v>30.3</v>
       </c>
       <c r="D5" t="n">
-        <v>32.1</v>
+        <v>33.9</v>
       </c>
       <c r="E5" t="n">
         <v>24.8</v>
       </c>
       <c r="F5" t="n">
-        <v>63</v>
+        <v>54.7</v>
       </c>
       <c r="G5" t="n">
         <v>0.1</v>
@@ -3239,16 +4516,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.4</v>
+        <v>29.6</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
         <v>25.7</v>
       </c>
       <c r="F6" t="n">
-        <v>72.5</v>
+        <v>67.3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3266,16 +4543,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.7</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="E7" t="n">
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>68.7</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -3293,16 +4570,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.1</v>
+        <v>29.7</v>
       </c>
       <c r="D8" t="n">
-        <v>31.6</v>
+        <v>32.8</v>
       </c>
       <c r="E8" t="n">
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>79.5</v>
+        <v>72</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -3320,16 +4597,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30.6</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>33.8</v>
+        <v>34.9</v>
       </c>
       <c r="E9" t="n">
         <v>27.4</v>
       </c>
       <c r="F9" t="n">
-        <v>55.5</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -3347,16 +4624,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.4</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>29.9</v>
+        <v>31</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>74</v>
+        <v>66.7</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3374,16 +4651,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.8</v>
+        <v>29.9</v>
       </c>
       <c r="D11" t="n">
-        <v>31.5</v>
+        <v>32.2</v>
       </c>
       <c r="E11" t="n">
         <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>73.5</v>
+        <v>68.3</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -3401,16 +4678,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
+        <v>30.6</v>
       </c>
       <c r="D12" t="n">
-        <v>32.5</v>
+        <v>33.8</v>
       </c>
       <c r="E12" t="n">
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>77</v>
+        <v>69.3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -3428,16 +4705,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.4</v>
+        <v>29.9</v>
       </c>
       <c r="D13" t="n">
-        <v>31.6</v>
+        <v>32.9</v>
       </c>
       <c r="E13" t="n">
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>78</v>
+        <v>69.7</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -3455,16 +4732,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.3</v>
+        <v>29.8</v>
       </c>
       <c r="D14" t="n">
-        <v>31.7</v>
+        <v>32.8</v>
       </c>
       <c r="E14" t="n">
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>79</v>
+        <v>72.7</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -3482,16 +4759,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.4</v>
+        <v>28.7</v>
       </c>
       <c r="D15" t="n">
-        <v>30.6</v>
+        <v>31.3</v>
       </c>
       <c r="E15" t="n">
         <v>24.3</v>
       </c>
       <c r="F15" t="n">
-        <v>66</v>
+        <v>60.3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -3509,16 +4786,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.4</v>
+        <v>30.6</v>
       </c>
       <c r="D16" t="n">
-        <v>32</v>
+        <v>33.1</v>
       </c>
       <c r="E16" t="n">
         <v>26.8</v>
       </c>
       <c r="F16" t="n">
-        <v>77</v>
+        <v>70.7</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -3536,16 +4813,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.2</v>
+        <v>28.6</v>
       </c>
       <c r="D17" t="n">
-        <v>30</v>
+        <v>31.4</v>
       </c>
       <c r="E17" t="n">
         <v>24.3</v>
       </c>
       <c r="F17" t="n">
-        <v>73</v>
+        <v>66.7</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -3563,16 +4840,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.9</v>
+        <v>28</v>
       </c>
       <c r="D18" t="n">
-        <v>23.9</v>
+        <v>32.2</v>
       </c>
       <c r="E18" t="n">
         <v>23.9</v>
       </c>
       <c r="F18" t="n">
-        <v>84</v>
+        <v>64.5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -3590,16 +4867,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.4</v>
+        <v>28.9</v>
       </c>
       <c r="D19" t="n">
-        <v>30.9</v>
+        <v>31.8</v>
       </c>
       <c r="E19" t="n">
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>81</v>
+        <v>75.7</v>
       </c>
       <c r="G19" t="n">
         <v>0.1</v>
@@ -3617,16 +4894,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29.4</v>
       </c>
       <c r="D20" t="n">
-        <v>31.2</v>
+        <v>32.3</v>
       </c>
       <c r="E20" t="n">
         <v>24.7</v>
       </c>
       <c r="F20" t="n">
-        <v>70</v>
+        <v>62.7</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -3644,16 +4921,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>29.6</v>
+        <v>31.4</v>
       </c>
       <c r="D21" t="n">
-        <v>33.6</v>
+        <v>35</v>
       </c>
       <c r="E21" t="n">
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>68.5</v>
+        <v>59.3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -3671,16 +4948,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28.2</v>
+        <v>29.4</v>
       </c>
       <c r="D22" t="n">
-        <v>31.3</v>
+        <v>31.9</v>
       </c>
       <c r="E22" t="n">
         <v>25</v>
       </c>
       <c r="F22" t="n">
-        <v>62.5</v>
+        <v>57.7</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -3698,16 +4975,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.5</v>
+        <v>28.8</v>
       </c>
       <c r="D23" t="n">
-        <v>30.6</v>
+        <v>31.5</v>
       </c>
       <c r="E23" t="n">
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>75</v>
+        <v>69.3</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -3725,16 +5002,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.4</v>
+        <v>28.7</v>
       </c>
       <c r="D24" t="n">
-        <v>30.2</v>
+        <v>31.1</v>
       </c>
       <c r="E24" t="n">
         <v>24.7</v>
       </c>
       <c r="F24" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -3752,16 +5029,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.7</v>
+        <v>29.9</v>
       </c>
       <c r="D25" t="n">
-        <v>31.5</v>
+        <v>32.4</v>
       </c>
       <c r="E25" t="n">
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>76.5</v>
+        <v>71.7</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -3779,16 +5056,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.2</v>
+        <v>29.4</v>
       </c>
       <c r="D26" t="n">
-        <v>31.1</v>
+        <v>32</v>
       </c>
       <c r="E26" t="n">
         <v>25.2</v>
       </c>
       <c r="F26" t="n">
-        <v>74.5</v>
+        <v>68</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -3806,19 +5083,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.4</v>
+        <v>28.6</v>
       </c>
       <c r="D27" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="E27" t="n">
         <v>24.2</v>
       </c>
       <c r="F27" t="n">
-        <v>67.5</v>
+        <v>61.7</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28">
@@ -3833,19 +5110,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.8</v>
+        <v>29.3</v>
       </c>
       <c r="D28" t="n">
-        <v>31.1</v>
+        <v>32.4</v>
       </c>
       <c r="E28" t="n">
         <v>24.5</v>
       </c>
       <c r="F28" t="n">
-        <v>65</v>
+        <v>58.3</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29">
@@ -3860,19 +5137,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.1</v>
+        <v>28.4</v>
       </c>
       <c r="D29" t="n">
-        <v>29.8</v>
+        <v>31.1</v>
       </c>
       <c r="E29" t="n">
         <v>24.4</v>
       </c>
       <c r="F29" t="n">
-        <v>73</v>
+        <v>66.7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="30">
@@ -3887,16 +5164,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.1</v>
+        <v>30.7</v>
       </c>
       <c r="D30" t="n">
-        <v>32.8</v>
+        <v>33.8</v>
       </c>
       <c r="E30" t="n">
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>75.5</v>
+        <v>66.7</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -3914,19 +5191,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.8</v>
+        <v>28.2</v>
       </c>
       <c r="D31" t="n">
-        <v>29.8</v>
+        <v>30.8</v>
       </c>
       <c r="E31" t="n">
         <v>23.9</v>
       </c>
       <c r="F31" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32">
@@ -3941,16 +5218,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>29.2</v>
+        <v>30.6</v>
       </c>
       <c r="D32" t="n">
-        <v>31.9</v>
+        <v>33.5</v>
       </c>
       <c r="E32" t="n">
         <v>26.4</v>
       </c>
       <c r="F32" t="n">
-        <v>60</v>
+        <v>54.3</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -3968,16 +5245,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.2</v>
+        <v>29.7</v>
       </c>
       <c r="D33" t="n">
-        <v>31.7</v>
+        <v>32.8</v>
       </c>
       <c r="E33" t="n">
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>77.5</v>
+        <v>70.3</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3995,16 +5272,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>28</v>
+        <v>29.5</v>
       </c>
       <c r="D34" t="n">
-        <v>31.6</v>
+        <v>32.3</v>
       </c>
       <c r="E34" t="n">
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>69</v>
+        <v>62.7</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,23 +2887,23 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>32.5</v>
+        <v>28.7</v>
       </c>
       <c r="E67" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="H67" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -2924,23 +2924,23 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>32.6</v>
+        <v>29.7</v>
       </c>
       <c r="E68" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -2961,23 +2961,23 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>32.7</v>
+        <v>29.2</v>
       </c>
       <c r="E69" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -2998,23 +2998,23 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>33.9</v>
+        <v>30.8</v>
       </c>
       <c r="E70" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3035,23 +3035,23 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>32</v>
+        <v>27.9</v>
       </c>
       <c r="E71" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3072,23 +3072,23 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>31.5</v>
+        <v>28.6</v>
       </c>
       <c r="E72" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3109,23 +3109,23 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>32.8</v>
+        <v>28.2</v>
       </c>
       <c r="E73" t="n">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3146,23 +3146,23 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>34.9</v>
+        <v>31.2</v>
       </c>
       <c r="E74" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3183,23 +3183,23 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>31</v>
+        <v>26.5</v>
       </c>
       <c r="E75" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>6.3</v>
+        <v>4.8</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3220,23 +3220,23 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>32.2</v>
+        <v>28.8</v>
       </c>
       <c r="E76" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3257,23 +3257,23 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>33.8</v>
+        <v>30.1</v>
       </c>
       <c r="E77" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3294,23 +3294,23 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>32.9</v>
+        <v>29</v>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3331,23 +3331,23 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>32.8</v>
+        <v>29.1</v>
       </c>
       <c r="E79" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3368,23 +3368,23 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>31.3</v>
+        <v>27.6</v>
       </c>
       <c r="E80" t="n">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3405,23 +3405,23 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>33.1</v>
+        <v>29.2</v>
       </c>
       <c r="E81" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3442,23 +3442,23 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>31.4</v>
+        <v>27.3</v>
       </c>
       <c r="E82" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3479,23 +3479,23 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>32.2</v>
+        <v>27.9</v>
       </c>
       <c r="E83" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3516,23 +3516,23 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>31.8</v>
+        <v>28.7</v>
       </c>
       <c r="E84" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3553,23 +3553,23 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>32.3</v>
+        <v>28.3</v>
       </c>
       <c r="E85" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3590,23 +3590,23 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E86" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>5.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3627,23 +3627,23 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>31.9</v>
+        <v>27.9</v>
       </c>
       <c r="E87" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>8.699999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3664,23 +3664,23 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>31.5</v>
+        <v>28.4</v>
       </c>
       <c r="E88" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3701,23 +3701,23 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>31.1</v>
+        <v>28</v>
       </c>
       <c r="E89" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>6.5</v>
+        <v>0.7</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3738,23 +3738,23 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>32.4</v>
+        <v>28.6</v>
       </c>
       <c r="E90" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3775,23 +3775,23 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>32</v>
+        <v>28.4</v>
       </c>
       <c r="E91" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3812,23 +3812,23 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>31</v>
+        <v>26.9</v>
       </c>
       <c r="E92" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>7.3</v>
+        <v>6</v>
       </c>
       <c r="H92" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3849,23 +3849,23 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>32.4</v>
+        <v>27.7</v>
       </c>
       <c r="E93" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>6.7</v>
+        <v>4.6</v>
       </c>
       <c r="H93" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3886,23 +3886,23 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>31.1</v>
+        <v>27.2</v>
       </c>
       <c r="E94" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="H94" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3923,23 +3923,23 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>33.8</v>
+        <v>30.2</v>
       </c>
       <c r="E95" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3960,23 +3960,23 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>30.8</v>
+        <v>26.8</v>
       </c>
       <c r="E96" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="H96" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -3997,23 +3997,23 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>33.5</v>
+        <v>29.8</v>
       </c>
       <c r="E97" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -4034,23 +4034,23 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>32.8</v>
+        <v>29.1</v>
       </c>
       <c r="E98" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-09-16T14:15</t>
+          <t>2026-09-16T19:15</t>
         </is>
       </c>
     </row>
@@ -4071,23 +4071,1244 @@
         </is>
       </c>
       <c r="D99" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E99" t="n">
+        <v>72</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-09-16T19:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E100" t="n">
+        <v>63</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E101" t="n">
+        <v>63</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>6</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>32</v>
+      </c>
+      <c r="E102" t="n">
+        <v>57</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H102" t="n">
+        <v>51</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>40</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H103" t="n">
+        <v>51</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>31</v>
+      </c>
+      <c r="E104" t="n">
+        <v>63</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E105" t="n">
+        <v>64</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E106" t="n">
+        <v>60</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E107" t="n">
+        <v>47</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E108" t="n">
+        <v>62</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>5</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E109" t="n">
+        <v>61</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E110" t="n">
+        <v>58</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E111" t="n">
+        <v>60</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E112" t="n">
+        <v>62</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E113" t="n">
+        <v>60</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>9</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
         <v>32.3</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E114" t="n">
+        <v>62</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E115" t="n">
+        <v>63</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E116" t="n">
+        <v>48</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E117" t="n">
+        <v>64</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E118" t="n">
+        <v>55</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G118" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H118" t="n">
+        <v>51</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="E119" t="n">
+        <v>44</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H119" t="n">
+        <v>1</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>56</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E121" t="n">
+        <v>62</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>7</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E122" t="n">
+        <v>61</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E123" t="n">
+        <v>63</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E124" t="n">
+        <v>58</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E125" t="n">
+        <v>53</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E126" t="n">
         <v>50</v>
       </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2026-09-16T14:15</t>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E127" t="n">
+        <v>60</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E128" t="n">
+        <v>52</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E129" t="n">
+        <v>59</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G129" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H129" t="n">
+        <v>51</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E130" t="n">
+        <v>50</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E131" t="n">
+        <v>55</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E132" t="n">
+        <v>57</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-09-17T11:15</t>
         </is>
       </c>
     </row>
@@ -4102,7 +5323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4304,29 +5525,29 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>32.4</v>
+        <v>28.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nalgonda</t>
+          <t>Jogulamba Gadwal</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>31.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vikarabad</t>
+          <t>Kamareddy</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>30.8</v>
+        <v>26.5</v>
       </c>
       <c r="I4" t="n">
-        <v>52.7</v>
+        <v>71.3</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4334,15 +5555,71 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Nagarkurnool</t>
+          <t>Jogulamba Gadwal</t>
         </is>
       </c>
       <c r="N4" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>33</v>
+      </c>
+      <c r="D5" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>10.1</v>
       </c>
     </row>
   </sheetData>
@@ -4408,19 +5685,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="D2" t="n">
-        <v>32.5</v>
+        <v>31.5</v>
       </c>
       <c r="E2" t="n">
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>67.3</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4438,13 +5715,13 @@
         <v>29.7</v>
       </c>
       <c r="D3" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="E3" t="n">
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>75.2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4462,19 +5739,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.7</v>
+        <v>29.4</v>
       </c>
       <c r="D4" t="n">
-        <v>32.7</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>72</v>
+        <v>71.8</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
@@ -4489,19 +5766,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="D5" t="n">
-        <v>33.9</v>
+        <v>33.1</v>
       </c>
       <c r="E5" t="n">
         <v>24.8</v>
       </c>
       <c r="F5" t="n">
-        <v>54.7</v>
+        <v>53.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -4516,16 +5793,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29.6</v>
+        <v>28.9</v>
       </c>
       <c r="D6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" t="n">
         <v>25.7</v>
       </c>
       <c r="F6" t="n">
-        <v>67.3</v>
+        <v>72.8</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -4543,16 +5820,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>28.7</v>
       </c>
       <c r="D7" t="n">
-        <v>31.5</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>68.7</v>
+        <v>71.8</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -4570,16 +5847,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="D8" t="n">
-        <v>32.8</v>
+        <v>32.5</v>
       </c>
       <c r="E8" t="n">
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>72</v>
+        <v>76.2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4597,16 +5874,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>31.5</v>
       </c>
       <c r="D9" t="n">
-        <v>34.9</v>
+        <v>33.8</v>
       </c>
       <c r="E9" t="n">
         <v>27.4</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4624,16 +5901,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>27.4</v>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>30.2</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>66.7</v>
+        <v>72.5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4651,16 +5928,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29.9</v>
+        <v>29.5</v>
       </c>
       <c r="D11" t="n">
-        <v>32.2</v>
+        <v>31.8</v>
       </c>
       <c r="E11" t="n">
         <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>68.3</v>
+        <v>71.5</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -4678,16 +5955,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="D12" t="n">
-        <v>33.8</v>
+        <v>33.3</v>
       </c>
       <c r="E12" t="n">
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>69.3</v>
+        <v>70.8</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -4705,16 +5982,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29.9</v>
+        <v>29.5</v>
       </c>
       <c r="D13" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="E13" t="n">
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>69.7</v>
+        <v>73</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -4732,16 +6009,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.8</v>
+        <v>29.5</v>
       </c>
       <c r="D14" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
       <c r="E14" t="n">
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>72.7</v>
+        <v>75</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4759,16 +6036,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28.7</v>
+        <v>28.2</v>
       </c>
       <c r="D15" t="n">
-        <v>31.3</v>
+        <v>30.6</v>
       </c>
       <c r="E15" t="n">
         <v>24.3</v>
       </c>
       <c r="F15" t="n">
-        <v>60.3</v>
+        <v>65.8</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -4786,16 +6063,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30.6</v>
+        <v>30.1</v>
       </c>
       <c r="D16" t="n">
-        <v>33.1</v>
+        <v>32.3</v>
       </c>
       <c r="E16" t="n">
         <v>26.8</v>
       </c>
       <c r="F16" t="n">
-        <v>70.7</v>
+        <v>74</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -4813,16 +6090,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28.6</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>31.4</v>
+        <v>30.5</v>
       </c>
       <c r="E17" t="n">
         <v>24.3</v>
       </c>
       <c r="F17" t="n">
-        <v>66.7</v>
+        <v>71</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -4840,16 +6117,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D18" t="n">
-        <v>32.2</v>
+        <v>31.9</v>
       </c>
       <c r="E18" t="n">
         <v>23.9</v>
       </c>
       <c r="F18" t="n">
-        <v>64.5</v>
+        <v>64.7</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -4867,16 +6144,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="D19" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="E19" t="n">
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>75.7</v>
+        <v>76</v>
       </c>
       <c r="G19" t="n">
         <v>0.1</v>
@@ -4894,19 +6171,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>29.4</v>
+        <v>28.8</v>
       </c>
       <c r="D20" t="n">
-        <v>32.3</v>
+        <v>31.2</v>
       </c>
       <c r="E20" t="n">
         <v>24.7</v>
       </c>
       <c r="F20" t="n">
-        <v>62.7</v>
+        <v>65</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="21">
@@ -4921,16 +6198,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>34.6</v>
       </c>
       <c r="E21" t="n">
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>59.3</v>
+        <v>59.8</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -4948,16 +6225,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>29.4</v>
+        <v>28.8</v>
       </c>
       <c r="D22" t="n">
-        <v>31.9</v>
+        <v>31.3</v>
       </c>
       <c r="E22" t="n">
         <v>25</v>
       </c>
       <c r="F22" t="n">
-        <v>57.7</v>
+        <v>61</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -4975,16 +6252,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.8</v>
+        <v>28.5</v>
       </c>
       <c r="D23" t="n">
-        <v>31.5</v>
+        <v>30.6</v>
       </c>
       <c r="E23" t="n">
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>69.3</v>
+        <v>71.8</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -5002,7 +6279,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="D24" t="n">
         <v>31.1</v>
@@ -5011,7 +6288,7 @@
         <v>24.7</v>
       </c>
       <c r="F24" t="n">
-        <v>66</v>
+        <v>69.8</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5029,16 +6306,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>29.9</v>
+        <v>29.4</v>
       </c>
       <c r="D25" t="n">
-        <v>32.4</v>
+        <v>31.8</v>
       </c>
       <c r="E25" t="n">
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>71.7</v>
+        <v>74.8</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -5056,16 +6333,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="D26" t="n">
-        <v>32</v>
+        <v>31.7</v>
       </c>
       <c r="E26" t="n">
         <v>25.2</v>
       </c>
       <c r="F26" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -5083,19 +6360,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>28.6</v>
+        <v>28.1</v>
       </c>
       <c r="D27" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="E27" t="n">
         <v>24.2</v>
       </c>
       <c r="F27" t="n">
-        <v>61.7</v>
+        <v>64</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="28">
@@ -5110,19 +6387,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>29.3</v>
+        <v>28.8</v>
       </c>
       <c r="D28" t="n">
-        <v>32.4</v>
+        <v>31.8</v>
       </c>
       <c r="E28" t="n">
         <v>24.5</v>
       </c>
       <c r="F28" t="n">
-        <v>58.3</v>
+        <v>62</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="29">
@@ -5137,19 +6414,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>28.4</v>
+        <v>28</v>
       </c>
       <c r="D29" t="n">
-        <v>31.1</v>
+        <v>30.7</v>
       </c>
       <c r="E29" t="n">
         <v>24.4</v>
       </c>
       <c r="F29" t="n">
-        <v>66.7</v>
+        <v>71.2</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="30">
@@ -5164,16 +6441,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="D30" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="E30" t="n">
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>66.7</v>
+        <v>67</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -5191,16 +6468,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="D31" t="n">
-        <v>30.8</v>
+        <v>29.9</v>
       </c>
       <c r="E31" t="n">
         <v>23.9</v>
       </c>
       <c r="F31" t="n">
-        <v>62</v>
+        <v>65.8</v>
       </c>
       <c r="G31" t="n">
         <v>0.1</v>
@@ -5218,16 +6495,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>30.6</v>
+        <v>30.1</v>
       </c>
       <c r="D32" t="n">
-        <v>33.5</v>
+        <v>32.4</v>
       </c>
       <c r="E32" t="n">
         <v>26.4</v>
       </c>
       <c r="F32" t="n">
-        <v>54.3</v>
+        <v>55.8</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -5245,16 +6522,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.7</v>
+        <v>29.4</v>
       </c>
       <c r="D33" t="n">
-        <v>32.8</v>
+        <v>32.3</v>
       </c>
       <c r="E33" t="n">
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>70.3</v>
+        <v>70.8</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -5272,16 +6549,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>29.5</v>
+        <v>29</v>
       </c>
       <c r="D34" t="n">
-        <v>32.3</v>
+        <v>31.6</v>
       </c>
       <c r="E34" t="n">
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>62.7</v>
+        <v>66.8</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -4108,23 +4108,23 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>31.5</v>
+        <v>30.5</v>
       </c>
       <c r="E100" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4145,23 +4145,23 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>32.5</v>
+        <v>31.8</v>
       </c>
       <c r="E101" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4182,23 +4182,23 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>32</v>
+        <v>33.2</v>
       </c>
       <c r="E102" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>7.5</v>
+        <v>1.3</v>
       </c>
       <c r="H102" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4219,23 +4219,23 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>33.1</v>
+        <v>33.7</v>
       </c>
       <c r="E103" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F103" t="n">
         <v>0.1</v>
       </c>
       <c r="G103" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="H103" t="n">
         <v>51</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4256,23 +4256,23 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>31</v>
+        <v>32.1</v>
       </c>
       <c r="E104" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4293,23 +4293,23 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>30.9</v>
+        <v>31.9</v>
       </c>
       <c r="E105" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="H105" t="n">
         <v>1</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>32.5</v>
+        <v>31.2</v>
       </c>
       <c r="E106" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -4342,11 +4342,11 @@
         <v>5.2</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4367,23 +4367,23 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>33.5</v>
+        <v>35.6</v>
       </c>
       <c r="E107" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>8.9</v>
+        <v>10.6</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4404,23 +4404,23 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>30.2</v>
+        <v>30.8</v>
       </c>
       <c r="E108" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G108" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4441,23 +4441,23 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>31.8</v>
+        <v>32.3</v>
       </c>
       <c r="E109" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4478,23 +4478,23 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>33.3</v>
+        <v>34</v>
       </c>
       <c r="E110" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4515,23 +4515,23 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>32.1</v>
+        <v>33.4</v>
       </c>
       <c r="E111" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="H111" t="n">
         <v>1</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>32.2</v>
+        <v>32.7</v>
       </c>
       <c r="E112" t="n">
         <v>62</v>
@@ -4561,14 +4561,14 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>7.9</v>
+        <v>3.1</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4589,23 +4589,23 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>30.4</v>
+        <v>31.8</v>
       </c>
       <c r="E113" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4626,23 +4626,23 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>32.3</v>
+        <v>31.8</v>
       </c>
       <c r="E114" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4663,23 +4663,23 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>30.5</v>
+        <v>31.4</v>
       </c>
       <c r="E115" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4700,23 +4700,23 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>31.9</v>
+        <v>32.2</v>
       </c>
       <c r="E116" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>3.5</v>
+        <v>8.6</v>
       </c>
       <c r="H116" t="n">
         <v>1</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4737,23 +4737,23 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>31.7</v>
+        <v>31.3</v>
       </c>
       <c r="E117" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>6.6</v>
+        <v>2.7</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4774,23 +4774,23 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>31.2</v>
+        <v>32.8</v>
       </c>
       <c r="E118" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F118" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
       <c r="H118" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4811,23 +4811,23 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>34.6</v>
+        <v>36.2</v>
       </c>
       <c r="E119" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="H119" t="n">
         <v>1</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4848,23 +4848,23 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>31.1</v>
+        <v>32.6</v>
       </c>
       <c r="E120" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>9.4</v>
+        <v>10.1</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4885,23 +4885,23 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>30.5</v>
+        <v>30.7</v>
       </c>
       <c r="E121" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G121" t="n">
-        <v>7</v>
+        <v>10.2</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4922,23 +4922,23 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>31.1</v>
+        <v>31.8</v>
       </c>
       <c r="E122" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4962,20 +4962,20 @@
         <v>31.8</v>
       </c>
       <c r="E123" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>6.4</v>
+        <v>3.1</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -4996,23 +4996,23 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>31.7</v>
+        <v>32.3</v>
       </c>
       <c r="E124" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -5033,23 +5033,23 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>30.7</v>
+        <v>31.2</v>
       </c>
       <c r="E125" t="n">
         <v>53</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G125" t="n">
-        <v>8.4</v>
+        <v>10.3</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -5070,23 +5070,23 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>31.8</v>
+        <v>32.2</v>
       </c>
       <c r="E126" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G126" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H126" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -5107,23 +5107,23 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>30.7</v>
+        <v>31</v>
       </c>
       <c r="E127" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -5144,23 +5144,23 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>33.7</v>
+        <v>34.6</v>
       </c>
       <c r="E128" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -5181,23 +5181,23 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>29.9</v>
+        <v>30.8</v>
       </c>
       <c r="E129" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F129" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="H129" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -5218,23 +5218,23 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>32.4</v>
+        <v>34.1</v>
       </c>
       <c r="E130" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>8.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -5255,23 +5255,23 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>32.3</v>
+        <v>33.6</v>
       </c>
       <c r="E131" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>7.5</v>
+        <v>1.7</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -5292,23 +5292,23 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
       </c>
       <c r="E132" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-09-17T11:15</t>
+          <t>2026-09-17T14:15</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
         <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>31.8</v>
+        <v>32.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -5589,29 +5589,29 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>34.6</v>
+        <v>36.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vikarabad</t>
+          <t>Adilabad</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29.9</v>
+        <v>30.5</v>
       </c>
       <c r="I5" t="n">
-        <v>57.3</v>
+        <v>56.2</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Hanumakonda</t>
+          <t>Nirmal</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
     </row>
   </sheetData>
@@ -5685,16 +5685,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29.2</v>
+        <v>28.9</v>
       </c>
       <c r="D2" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="E2" t="n">
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -5712,16 +5712,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="D3" t="n">
-        <v>32.5</v>
+        <v>31.8</v>
       </c>
       <c r="E3" t="n">
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>75.2</v>
+        <v>76.5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -5739,19 +5739,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.4</v>
+        <v>29.7</v>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>33.2</v>
       </c>
       <c r="E4" t="n">
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>71.8</v>
+        <v>71.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -5766,16 +5766,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="D5" t="n">
-        <v>33.1</v>
+        <v>33.7</v>
       </c>
       <c r="E5" t="n">
         <v>24.8</v>
       </c>
       <c r="F5" t="n">
-        <v>53.2</v>
+        <v>53.5</v>
       </c>
       <c r="G5" t="n">
         <v>0.2</v>
@@ -5793,16 +5793,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>32.1</v>
       </c>
       <c r="E6" t="n">
         <v>25.7</v>
       </c>
       <c r="F6" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -5820,16 +5820,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.7</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>31.9</v>
       </c>
       <c r="E7" t="n">
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>71.8</v>
+        <v>70.8</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -5847,16 +5847,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.2</v>
+        <v>28.9</v>
       </c>
       <c r="D8" t="n">
-        <v>32.5</v>
+        <v>31.6</v>
       </c>
       <c r="E8" t="n">
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>76.2</v>
+        <v>77.5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -5874,16 +5874,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>33.8</v>
+        <v>35.6</v>
       </c>
       <c r="E9" t="n">
         <v>27.4</v>
       </c>
       <c r="F9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -5901,19 +5901,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="D10" t="n">
-        <v>30.2</v>
+        <v>30.8</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>72.5</v>
+        <v>71.2</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -5928,16 +5928,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="D11" t="n">
-        <v>31.8</v>
+        <v>32.3</v>
       </c>
       <c r="E11" t="n">
         <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>71.5</v>
+        <v>71.8</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -5955,16 +5955,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="D12" t="n">
-        <v>33.3</v>
+        <v>34</v>
       </c>
       <c r="E12" t="n">
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>70.8</v>
+        <v>69.5</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -5982,16 +5982,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29.5</v>
+        <v>29.8</v>
       </c>
       <c r="D13" t="n">
-        <v>32.1</v>
+        <v>33.4</v>
       </c>
       <c r="E13" t="n">
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -6009,10 +6009,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="D14" t="n">
-        <v>32.2</v>
+        <v>32.7</v>
       </c>
       <c r="E14" t="n">
         <v>24.9</v>
@@ -6036,16 +6036,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28.2</v>
+        <v>28.6</v>
       </c>
       <c r="D15" t="n">
-        <v>30.6</v>
+        <v>31.8</v>
       </c>
       <c r="E15" t="n">
         <v>24.3</v>
       </c>
       <c r="F15" t="n">
-        <v>65.8</v>
+        <v>63.5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -6063,16 +6063,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>32.3</v>
+        <v>32</v>
       </c>
       <c r="E16" t="n">
         <v>26.8</v>
       </c>
       <c r="F16" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -6090,16 +6090,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>28.2</v>
       </c>
       <c r="D17" t="n">
-        <v>30.5</v>
+        <v>31.4</v>
       </c>
       <c r="E17" t="n">
         <v>24.3</v>
       </c>
       <c r="F17" t="n">
-        <v>71</v>
+        <v>69.5</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -6117,16 +6117,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="D18" t="n">
-        <v>31.9</v>
+        <v>32.2</v>
       </c>
       <c r="E18" t="n">
         <v>23.9</v>
       </c>
       <c r="F18" t="n">
-        <v>64.7</v>
+        <v>64.3</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -6144,16 +6144,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="D19" t="n">
-        <v>31.7</v>
+        <v>31.3</v>
       </c>
       <c r="E19" t="n">
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>76</v>
+        <v>76.5</v>
       </c>
       <c r="G19" t="n">
         <v>0.1</v>
@@ -6171,19 +6171,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="D20" t="n">
-        <v>31.2</v>
+        <v>32.8</v>
       </c>
       <c r="E20" t="n">
         <v>24.7</v>
       </c>
       <c r="F20" t="n">
-        <v>65</v>
+        <v>63.5</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -6198,16 +6198,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="D21" t="n">
-        <v>34.6</v>
+        <v>36.2</v>
       </c>
       <c r="E21" t="n">
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>59.8</v>
+        <v>59.5</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -6225,16 +6225,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="D22" t="n">
-        <v>31.3</v>
+        <v>32.6</v>
       </c>
       <c r="E22" t="n">
         <v>25</v>
       </c>
       <c r="F22" t="n">
-        <v>61</v>
+        <v>59.2</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>28.5</v>
       </c>
       <c r="D23" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="E23" t="n">
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>71.8</v>
+        <v>72.8</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="24">
@@ -6279,16 +6279,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="D24" t="n">
-        <v>31.1</v>
+        <v>31.8</v>
       </c>
       <c r="E24" t="n">
         <v>24.7</v>
       </c>
       <c r="F24" t="n">
-        <v>69.8</v>
+        <v>69.5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -6315,7 +6315,7 @@
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>74.8</v>
+        <v>75.5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -6333,16 +6333,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="D26" t="n">
-        <v>31.7</v>
+        <v>32.3</v>
       </c>
       <c r="E26" t="n">
         <v>25.2</v>
       </c>
       <c r="F26" t="n">
-        <v>71</v>
+        <v>72.5</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="D27" t="n">
-        <v>30.7</v>
+        <v>31.2</v>
       </c>
       <c r="E27" t="n">
         <v>24.2</v>
@@ -6372,7 +6372,7 @@
         <v>64</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28">
@@ -6387,19 +6387,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="D28" t="n">
-        <v>31.8</v>
+        <v>32.2</v>
       </c>
       <c r="E28" t="n">
         <v>24.5</v>
       </c>
       <c r="F28" t="n">
-        <v>62</v>
+        <v>61.8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29">
@@ -6414,16 +6414,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="D29" t="n">
-        <v>30.7</v>
+        <v>31</v>
       </c>
       <c r="E29" t="n">
         <v>24.4</v>
       </c>
       <c r="F29" t="n">
-        <v>71.2</v>
+        <v>72</v>
       </c>
       <c r="G29" t="n">
         <v>0.1</v>
@@ -6441,16 +6441,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.5</v>
+        <v>30.8</v>
       </c>
       <c r="D30" t="n">
-        <v>33.7</v>
+        <v>34.6</v>
       </c>
       <c r="E30" t="n">
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>67</v>
+        <v>66.5</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -6468,19 +6468,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="D31" t="n">
-        <v>29.9</v>
+        <v>30.8</v>
       </c>
       <c r="E31" t="n">
         <v>23.9</v>
       </c>
       <c r="F31" t="n">
-        <v>65.8</v>
+        <v>65.2</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -6495,16 +6495,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>30.1</v>
+        <v>30.6</v>
       </c>
       <c r="D32" t="n">
-        <v>32.4</v>
+        <v>34.1</v>
       </c>
       <c r="E32" t="n">
         <v>26.4</v>
       </c>
       <c r="F32" t="n">
-        <v>55.8</v>
+        <v>54</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -6522,16 +6522,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.4</v>
+        <v>29.8</v>
       </c>
       <c r="D33" t="n">
-        <v>32.3</v>
+        <v>33.6</v>
       </c>
       <c r="E33" t="n">
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>70.8</v>
+        <v>70.2</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6549,16 +6549,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>29</v>
+        <v>29.3</v>
       </c>
       <c r="D34" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
       </c>
       <c r="E34" t="n">
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>66.8</v>
+        <v>65.2</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4108,23 +4108,23 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>30.5</v>
+        <v>25.3</v>
       </c>
       <c r="E100" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G100" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4145,23 +4145,23 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>31.8</v>
+        <v>28.5</v>
       </c>
       <c r="E101" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4182,23 +4182,23 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>33.2</v>
+        <v>28.7</v>
       </c>
       <c r="E102" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4219,23 +4219,23 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>33.7</v>
+        <v>29.7</v>
       </c>
       <c r="E103" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="H103" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4256,23 +4256,23 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>32.1</v>
+        <v>26.7</v>
       </c>
       <c r="E104" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4293,23 +4293,23 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>31.9</v>
+        <v>26.6</v>
       </c>
       <c r="E105" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4330,23 +4330,23 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>31.2</v>
+        <v>27.7</v>
       </c>
       <c r="E106" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="H106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4367,23 +4367,23 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>35.6</v>
+        <v>25.8</v>
       </c>
       <c r="E107" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G107" t="n">
-        <v>10.6</v>
+        <v>19.8</v>
       </c>
       <c r="H107" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4404,23 +4404,23 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>30.8</v>
+        <v>25.5</v>
       </c>
       <c r="E108" t="n">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F108" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="H108" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4441,23 +4441,23 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>32.3</v>
+        <v>27.2</v>
       </c>
       <c r="E109" t="n">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4478,23 +4478,23 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>34</v>
+        <v>29.4</v>
       </c>
       <c r="E110" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4515,23 +4515,23 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>33.4</v>
+        <v>26.7</v>
       </c>
       <c r="E111" t="n">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="H111" t="n">
         <v>1</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4552,23 +4552,23 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>32.7</v>
+        <v>28.5</v>
       </c>
       <c r="E112" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="H112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4589,23 +4589,23 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>31.8</v>
+        <v>26.6</v>
       </c>
       <c r="E113" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>9.5</v>
+        <v>4.2</v>
       </c>
       <c r="H113" t="n">
         <v>1</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4626,23 +4626,23 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>31.8</v>
+        <v>28.2</v>
       </c>
       <c r="E114" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4663,23 +4663,23 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>31.4</v>
+        <v>25.4</v>
       </c>
       <c r="E115" t="n">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G115" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4700,23 +4700,23 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>32.2</v>
+        <v>26.6</v>
       </c>
       <c r="E116" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>8.6</v>
+        <v>3.9</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4737,23 +4737,23 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>31.3</v>
+        <v>27.9</v>
       </c>
       <c r="E117" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4774,23 +4774,23 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>32.8</v>
+        <v>28</v>
       </c>
       <c r="E118" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>10.9</v>
+        <v>4.4</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4811,23 +4811,23 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>36.2</v>
+        <v>30.4</v>
       </c>
       <c r="E119" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="H119" t="n">
         <v>1</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4848,23 +4848,23 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>32.6</v>
+        <v>27.2</v>
       </c>
       <c r="E120" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G120" t="n">
-        <v>10.1</v>
+        <v>4.3</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4885,23 +4885,23 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>30.7</v>
+        <v>26.4</v>
       </c>
       <c r="E121" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="F121" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="G121" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="H121" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4922,23 +4922,23 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>31.8</v>
+        <v>24.2</v>
       </c>
       <c r="E122" t="n">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G122" t="n">
-        <v>4.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4959,23 +4959,23 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>31.8</v>
+        <v>27.2</v>
       </c>
       <c r="E123" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -4996,23 +4996,23 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>32.3</v>
+        <v>26.3</v>
       </c>
       <c r="E124" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="H124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -5033,23 +5033,23 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>31.2</v>
+        <v>26.3</v>
       </c>
       <c r="E125" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="F125" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>10.3</v>
+        <v>0.7</v>
       </c>
       <c r="H125" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -5070,23 +5070,23 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>32.2</v>
+        <v>26</v>
       </c>
       <c r="E126" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="F126" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="H126" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -5107,23 +5107,23 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E127" t="n">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="H127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -5144,23 +5144,23 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>34.6</v>
+        <v>29.7</v>
       </c>
       <c r="E128" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="H128" t="n">
         <v>1</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -5181,23 +5181,23 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>30.8</v>
+        <v>26.2</v>
       </c>
       <c r="E129" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -5218,23 +5218,23 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>34.1</v>
+        <v>28.1</v>
       </c>
       <c r="E130" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>9.4</v>
+        <v>1.1</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -5255,23 +5255,23 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>33.6</v>
+        <v>29</v>
       </c>
       <c r="E131" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="H131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15</t>
+          <t>2026-09-17T21:45</t>
         </is>
       </c>
     </row>
@@ -5292,23 +5292,1244 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>32.6</v>
+        <v>27.1</v>
       </c>
       <c r="E132" t="n">
+        <v>76</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H132" t="n">
+        <v>3</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-09-17T21:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E133" t="n">
+        <v>66</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G133" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E134" t="n">
+        <v>60</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G134" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H134" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E135" t="n">
+        <v>63</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G135" t="n">
+        <v>12</v>
+      </c>
+      <c r="H135" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E136" t="n">
+        <v>59</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G136" t="n">
+        <v>12</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>30</v>
+      </c>
+      <c r="E137" t="n">
+        <v>65</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G137" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E138" t="n">
+        <v>58</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G138" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>31</v>
+      </c>
+      <c r="E139" t="n">
+        <v>61</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G139" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E140" t="n">
+        <v>54</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G140" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E141" t="n">
+        <v>65</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E142" t="n">
+        <v>64</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>58</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G143" t="n">
+        <v>15</v>
+      </c>
+      <c r="H143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E144" t="n">
+        <v>68</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G144" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E145" t="n">
+        <v>60</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G145" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H145" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E146" t="n">
+        <v>56</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G146" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H146" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E147" t="n">
+        <v>66</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H147" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E148" t="n">
+        <v>62</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G148" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H148" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E149" t="n">
+        <v>61</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G149" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E150" t="n">
+        <v>66</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G150" t="n">
+        <v>11</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E151" t="n">
+        <v>57</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G151" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H151" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>57</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G152" t="n">
+        <v>14</v>
+      </c>
+      <c r="H152" t="n">
+        <v>1</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E153" t="n">
+        <v>59</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H153" t="n">
+        <v>1</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E154" t="n">
+        <v>70</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E155" t="n">
+        <v>76</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H155" t="n">
+        <v>2</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E156" t="n">
+        <v>70</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G156" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H156" t="n">
         <v>51</v>
       </c>
-      <c r="F132" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H132" t="n">
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E157" t="n">
+        <v>67</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H157" t="n">
+        <v>2</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E158" t="n">
+        <v>64</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H158" t="n">
         <v>1</v>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>2026-09-17T14:15</t>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E159" t="n">
+        <v>65</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H159" t="n">
+        <v>3</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E160" t="n">
+        <v>70</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
+        <v>11</v>
+      </c>
+      <c r="H160" t="n">
+        <v>2</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>55</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E162" t="n">
+        <v>66</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G162" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H162" t="n">
+        <v>51</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E163" t="n">
+        <v>54</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H163" t="n">
+        <v>2</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E164" t="n">
+        <v>63</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H164" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E165" t="n">
+        <v>62</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H165" t="n">
+        <v>2</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>2026-09-18T11:15</t>
         </is>
       </c>
     </row>
@@ -5323,7 +6544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5581,7 +6802,7 @@
         <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>32.4</v>
+        <v>27.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -5589,37 +6810,93 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>36.2</v>
+        <v>30.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Adilabad</t>
+          <t>Nizamabad</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30.5</v>
+        <v>24.2</v>
       </c>
       <c r="I5" t="n">
-        <v>56.2</v>
+        <v>80.8</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Nirmal</t>
+          <t>Jogulamba Gadwal</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Nagarkurnool</t>
+          <t>Jogulamba Gadwal</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>10.9</v>
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -5685,7 +6962,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.9</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
         <v>31.4</v>
@@ -5694,10 +6971,10 @@
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="3">
@@ -5712,19 +6989,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="D3" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="E3" t="n">
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>76.5</v>
+        <v>76.2</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -5739,19 +7016,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.7</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
       </c>
       <c r="E4" t="n">
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>71.5</v>
+        <v>75.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -5766,19 +7043,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.4</v>
+        <v>29.7</v>
       </c>
       <c r="D5" t="n">
-        <v>33.7</v>
+        <v>32.1</v>
       </c>
       <c r="E5" t="n">
         <v>24.8</v>
       </c>
       <c r="F5" t="n">
-        <v>53.5</v>
+        <v>58.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -5793,19 +7070,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29.2</v>
+        <v>28.3</v>
       </c>
       <c r="D6" t="n">
-        <v>32.1</v>
+        <v>31</v>
       </c>
       <c r="E6" t="n">
         <v>25.7</v>
       </c>
       <c r="F6" t="n">
-        <v>72.5</v>
+        <v>77.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7">
@@ -5820,19 +7097,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>28.4</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9</v>
+        <v>31.3</v>
       </c>
       <c r="E7" t="n">
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>70.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -5847,7 +7124,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.9</v>
+        <v>28.6</v>
       </c>
       <c r="D8" t="n">
         <v>31.6</v>
@@ -5856,10 +7133,10 @@
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>77.5</v>
+        <v>77.8</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -5874,19 +7151,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>29.8</v>
       </c>
       <c r="D9" t="n">
-        <v>35.6</v>
+        <v>33.8</v>
       </c>
       <c r="E9" t="n">
-        <v>27.4</v>
+        <v>25.8</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>58.2</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10">
@@ -5901,19 +7178,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27.6</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>30.8</v>
+        <v>29.9</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>71.2</v>
+        <v>76</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="11">
@@ -5928,19 +7205,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29.6</v>
+        <v>28.7</v>
       </c>
       <c r="D11" t="n">
-        <v>32.3</v>
+        <v>31.5</v>
       </c>
       <c r="E11" t="n">
         <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>71.8</v>
+        <v>76</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12">
@@ -5955,19 +7232,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.5</v>
+        <v>29.9</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>32.5</v>
       </c>
       <c r="E12" t="n">
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>69.5</v>
+        <v>71.8</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -5982,19 +7259,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29.8</v>
+        <v>28.3</v>
       </c>
       <c r="D13" t="n">
-        <v>33.4</v>
+        <v>31.6</v>
       </c>
       <c r="E13" t="n">
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>72</v>
+        <v>79.2</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="14">
@@ -6009,19 +7286,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.6</v>
+        <v>29.1</v>
       </c>
       <c r="D14" t="n">
-        <v>32.7</v>
+        <v>31.7</v>
       </c>
       <c r="E14" t="n">
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>75</v>
+        <v>76.2</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="15">
@@ -6036,19 +7313,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28.6</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>31.8</v>
+        <v>30.9</v>
       </c>
       <c r="E15" t="n">
         <v>24.3</v>
       </c>
       <c r="F15" t="n">
-        <v>63.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16">
@@ -6063,7 +7340,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29.2</v>
       </c>
       <c r="D16" t="n">
         <v>32</v>
@@ -6072,10 +7349,10 @@
         <v>26.8</v>
       </c>
       <c r="F16" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -6090,19 +7367,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28.2</v>
+        <v>27.5</v>
       </c>
       <c r="D17" t="n">
-        <v>31.4</v>
+        <v>30.7</v>
       </c>
       <c r="E17" t="n">
         <v>24.3</v>
       </c>
       <c r="F17" t="n">
-        <v>69.5</v>
+        <v>73.8</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="18">
@@ -6117,19 +7394,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="D18" t="n">
-        <v>32.2</v>
+        <v>30.6</v>
       </c>
       <c r="E18" t="n">
         <v>23.9</v>
       </c>
       <c r="F18" t="n">
-        <v>64.3</v>
+        <v>70</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
@@ -6144,19 +7421,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.7</v>
+        <v>28.4</v>
       </c>
       <c r="D19" t="n">
-        <v>31.3</v>
+        <v>30.9</v>
       </c>
       <c r="E19" t="n">
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>76.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -6171,19 +7448,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>29.2</v>
+        <v>28.5</v>
       </c>
       <c r="D20" t="n">
-        <v>32.8</v>
+        <v>31.2</v>
       </c>
       <c r="E20" t="n">
         <v>24.7</v>
       </c>
       <c r="F20" t="n">
-        <v>63.5</v>
+        <v>65.2</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="21">
@@ -6198,19 +7475,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31.6</v>
+        <v>30.4</v>
       </c>
       <c r="D21" t="n">
-        <v>36.2</v>
+        <v>33.6</v>
       </c>
       <c r="E21" t="n">
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>59.5</v>
+        <v>63</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="22">
@@ -6225,19 +7502,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>29.2</v>
+        <v>28.4</v>
       </c>
       <c r="D22" t="n">
-        <v>32.6</v>
+        <v>31.3</v>
       </c>
       <c r="E22" t="n">
         <v>25</v>
       </c>
       <c r="F22" t="n">
-        <v>59.2</v>
+        <v>64</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="23">
@@ -6252,19 +7529,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.5</v>
+        <v>27.9</v>
       </c>
       <c r="D23" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="E23" t="n">
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>72.8</v>
+        <v>76</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
@@ -6279,19 +7556,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>28.7</v>
+        <v>27</v>
       </c>
       <c r="D24" t="n">
-        <v>31.8</v>
+        <v>30.2</v>
       </c>
       <c r="E24" t="n">
-        <v>24.7</v>
+        <v>24.2</v>
       </c>
       <c r="F24" t="n">
-        <v>69.5</v>
+        <v>78.2</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="25">
@@ -6306,19 +7583,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>29.4</v>
+        <v>28.7</v>
       </c>
       <c r="D25" t="n">
-        <v>31.8</v>
+        <v>31.5</v>
       </c>
       <c r="E25" t="n">
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>75.5</v>
+        <v>79.8</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26">
@@ -6333,16 +7610,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>29.2</v>
+        <v>28.2</v>
       </c>
       <c r="D26" t="n">
-        <v>32.3</v>
+        <v>31.1</v>
       </c>
       <c r="E26" t="n">
         <v>25.2</v>
       </c>
       <c r="F26" t="n">
-        <v>72.5</v>
+        <v>76.2</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -6360,19 +7637,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>28.2</v>
+        <v>27.5</v>
       </c>
       <c r="D27" t="n">
-        <v>31.2</v>
+        <v>30.5</v>
       </c>
       <c r="E27" t="n">
         <v>24.2</v>
       </c>
       <c r="F27" t="n">
-        <v>64</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="28">
@@ -6387,19 +7664,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28.9</v>
+        <v>27.7</v>
       </c>
       <c r="D28" t="n">
-        <v>32.2</v>
+        <v>31.1</v>
       </c>
       <c r="E28" t="n">
         <v>24.5</v>
       </c>
       <c r="F28" t="n">
-        <v>61.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="29">
@@ -6414,16 +7691,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>28.1</v>
+        <v>27.3</v>
       </c>
       <c r="D29" t="n">
-        <v>31</v>
+        <v>29.8</v>
       </c>
       <c r="E29" t="n">
         <v>24.4</v>
       </c>
       <c r="F29" t="n">
-        <v>72</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0.1</v>
@@ -6441,16 +7718,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="D30" t="n">
-        <v>34.6</v>
+        <v>33.1</v>
       </c>
       <c r="E30" t="n">
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>66.5</v>
+        <v>68.2</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -6468,19 +7745,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.8</v>
+        <v>27.1</v>
       </c>
       <c r="D31" t="n">
-        <v>30.8</v>
+        <v>29.8</v>
       </c>
       <c r="E31" t="n">
         <v>23.9</v>
       </c>
       <c r="F31" t="n">
-        <v>65.2</v>
+        <v>68.8</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32">
@@ -6495,19 +7772,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>30.6</v>
+        <v>29.6</v>
       </c>
       <c r="D32" t="n">
-        <v>34.1</v>
+        <v>31.9</v>
       </c>
       <c r="E32" t="n">
         <v>26.4</v>
       </c>
       <c r="F32" t="n">
-        <v>54</v>
+        <v>58.4</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -6522,16 +7799,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.8</v>
+        <v>29.2</v>
       </c>
       <c r="D33" t="n">
-        <v>33.6</v>
+        <v>31.7</v>
       </c>
       <c r="E33" t="n">
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>70.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6549,16 +7826,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>29.3</v>
+        <v>28.5</v>
       </c>
       <c r="D34" t="n">
-        <v>32.6</v>
+        <v>31.6</v>
       </c>
       <c r="E34" t="n">
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>65.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -5329,23 +5329,23 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>29.4</v>
+        <v>31.7</v>
       </c>
       <c r="E133" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F133" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>10.6</v>
+        <v>7.7</v>
       </c>
       <c r="H133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5366,23 +5366,23 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>31.6</v>
+        <v>34.1</v>
       </c>
       <c r="E134" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F134" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>13.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5403,23 +5403,23 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>30.9</v>
+        <v>32.9</v>
       </c>
       <c r="E135" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F135" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="H135" t="n">
         <v>1</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5440,23 +5440,23 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>31.2</v>
+        <v>32.2</v>
       </c>
       <c r="E136" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F136" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="H136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5477,23 +5477,23 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E137" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F137" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>10.8</v>
+        <v>9.1</v>
       </c>
       <c r="H137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5514,23 +5514,23 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>31.3</v>
+        <v>31.8</v>
       </c>
       <c r="E138" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F138" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>13.1</v>
+        <v>11.1</v>
       </c>
       <c r="H138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5551,23 +5551,23 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>31</v>
+        <v>32.7</v>
       </c>
       <c r="E139" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F139" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>12.3</v>
+        <v>8.6</v>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5588,23 +5588,23 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>30.8</v>
+        <v>34.2</v>
       </c>
       <c r="E140" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="H140" t="n">
         <v>1</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5625,23 +5625,23 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>29.9</v>
+        <v>28.1</v>
       </c>
       <c r="E141" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F141" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="H141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5662,23 +5662,23 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>30.2</v>
+        <v>31.6</v>
       </c>
       <c r="E142" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F142" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>11.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5699,23 +5699,23 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>32.1</v>
+        <v>35.2</v>
       </c>
       <c r="E143" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F143" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5736,23 +5736,23 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>28.7</v>
+        <v>32.8</v>
       </c>
       <c r="E144" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F144" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="H144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5773,23 +5773,23 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>31.2</v>
+        <v>33.3</v>
       </c>
       <c r="E145" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F145" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>13.6</v>
+        <v>10.7</v>
       </c>
       <c r="H145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5810,23 +5810,23 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="E146" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F146" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>13.4</v>
+        <v>13.1</v>
       </c>
       <c r="H146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5847,23 +5847,23 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>29.7</v>
+        <v>32.6</v>
       </c>
       <c r="E147" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>10.3</v>
+        <v>6.4</v>
       </c>
       <c r="H147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5884,23 +5884,23 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>30.7</v>
+        <v>28</v>
       </c>
       <c r="E148" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F148" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
       <c r="H148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5921,23 +5921,23 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>30.6</v>
+        <v>29.5</v>
       </c>
       <c r="E149" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F149" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G149" t="n">
-        <v>12.8</v>
+        <v>13.8</v>
       </c>
       <c r="H149" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5958,23 +5958,23 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>30.4</v>
+        <v>31.9</v>
       </c>
       <c r="E150" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F150" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>11</v>
+        <v>11.7</v>
       </c>
       <c r="H150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -5995,23 +5995,23 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>30.5</v>
+        <v>32.2</v>
       </c>
       <c r="E151" t="n">
         <v>57</v>
       </c>
       <c r="F151" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="H151" t="n">
         <v>1</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6032,23 +6032,23 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>31.1</v>
+        <v>36.2</v>
       </c>
       <c r="E152" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="F152" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>14</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>30.5</v>
+        <v>31.2</v>
       </c>
       <c r="E153" t="n">
         <v>59</v>
@@ -6078,14 +6078,14 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="H153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6106,23 +6106,23 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>29.5</v>
+        <v>30.5</v>
       </c>
       <c r="E154" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6143,23 +6143,23 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>27.9</v>
+        <v>27.2</v>
       </c>
       <c r="E155" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="H155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6180,23 +6180,23 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>30.2</v>
+        <v>31.8</v>
       </c>
       <c r="E156" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F156" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>9.9</v>
+        <v>8.4</v>
       </c>
       <c r="H156" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6217,23 +6217,23 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>30.2</v>
+        <v>31</v>
       </c>
       <c r="E157" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>10.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6254,23 +6254,23 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>29.4</v>
+        <v>29.9</v>
       </c>
       <c r="E158" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="H158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6291,23 +6291,23 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>29.3</v>
+        <v>29.9</v>
       </c>
       <c r="E159" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>10.9</v>
+        <v>13.1</v>
       </c>
       <c r="H159" t="n">
         <v>3</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6328,23 +6328,23 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>29.3</v>
+        <v>29.9</v>
       </c>
       <c r="E160" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>11</v>
+        <v>12.4</v>
       </c>
       <c r="H160" t="n">
         <v>2</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6365,23 +6365,23 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>33.1</v>
+        <v>34.5</v>
       </c>
       <c r="E161" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6402,23 +6402,23 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>28.7</v>
+        <v>29.1</v>
       </c>
       <c r="E162" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F162" t="n">
         <v>0.1</v>
       </c>
       <c r="G162" t="n">
-        <v>10.9</v>
+        <v>14.2</v>
       </c>
       <c r="H162" t="n">
         <v>51</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6439,23 +6439,23 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>31.8</v>
+        <v>32.1</v>
       </c>
       <c r="E163" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>12.3</v>
+        <v>11.6</v>
       </c>
       <c r="H163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6476,23 +6476,23 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>31.5</v>
+        <v>33.3</v>
       </c>
       <c r="E164" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H164" t="n">
         <v>1</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6513,23 +6513,23 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>30.9</v>
+        <v>31.3</v>
       </c>
       <c r="E165" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G165" t="n">
-        <v>9.6</v>
+        <v>12.6</v>
       </c>
       <c r="H165" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-09-18T11:15</t>
+          <t>2026-09-18T13:45</t>
         </is>
       </c>
     </row>
@@ -6858,15 +6858,15 @@
         <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>30.4</v>
+        <v>31.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suryapet</t>
+          <t>Nalgonda</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>33.1</v>
+        <v>36.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -6874,29 +6874,29 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>27.9</v>
+        <v>27.2</v>
       </c>
       <c r="I6" t="n">
-        <v>62.6</v>
+        <v>60.5</v>
       </c>
       <c r="J6" t="n">
-        <v>13.7</v>
+        <v>0.3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Kumuram Bheem Asifabad</t>
+          <t>Medchal-Malkajgiri</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Khammam</t>
+          <t>Rangareddy</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
     </row>
   </sheetData>
@@ -6962,19 +6962,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="D2" t="n">
-        <v>31.4</v>
+        <v>31.7</v>
       </c>
       <c r="E2" t="n">
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>77</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
@@ -6989,19 +6989,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.3</v>
+        <v>29.8</v>
       </c>
       <c r="D3" t="n">
-        <v>31.6</v>
+        <v>34.1</v>
       </c>
       <c r="E3" t="n">
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -7016,19 +7016,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>29.4</v>
       </c>
       <c r="D4" t="n">
-        <v>31.5</v>
+        <v>32.9</v>
       </c>
       <c r="E4" t="n">
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>75.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7043,19 +7043,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.7</v>
+        <v>29.9</v>
       </c>
       <c r="D5" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="E5" t="n">
         <v>24.8</v>
       </c>
       <c r="F5" t="n">
-        <v>58.2</v>
+        <v>56.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.3</v>
+        <v>28.5</v>
       </c>
       <c r="D6" t="n">
         <v>31</v>
@@ -7079,10 +7079,10 @@
         <v>25.7</v>
       </c>
       <c r="F6" t="n">
-        <v>77.2</v>
+        <v>77.8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7097,19 +7097,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="D7" t="n">
-        <v>31.3</v>
+        <v>31.8</v>
       </c>
       <c r="E7" t="n">
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -7124,19 +7124,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.6</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>31.6</v>
+        <v>32.7</v>
       </c>
       <c r="E8" t="n">
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>77.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -7151,19 +7151,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29.8</v>
+        <v>30.5</v>
       </c>
       <c r="D9" t="n">
-        <v>33.8</v>
+        <v>34.2</v>
       </c>
       <c r="E9" t="n">
         <v>25.8</v>
       </c>
       <c r="F9" t="n">
-        <v>58.2</v>
+        <v>57.2</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="10">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>26.6</v>
       </c>
       <c r="D10" t="n">
         <v>29.9</v>
@@ -7187,10 +7187,10 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -7205,19 +7205,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.7</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="E11" t="n">
         <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -7232,19 +7232,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.9</v>
+        <v>30.5</v>
       </c>
       <c r="D12" t="n">
-        <v>32.5</v>
+        <v>35.2</v>
       </c>
       <c r="E12" t="n">
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>71.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7259,19 +7259,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.3</v>
+        <v>29.1</v>
       </c>
       <c r="D13" t="n">
-        <v>31.6</v>
+        <v>32.8</v>
       </c>
       <c r="E13" t="n">
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>79.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7286,19 +7286,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.1</v>
+        <v>29.5</v>
       </c>
       <c r="D14" t="n">
-        <v>31.7</v>
+        <v>33.3</v>
       </c>
       <c r="E14" t="n">
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>76.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -7316,16 +7316,16 @@
         <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="E15" t="n">
         <v>24.3</v>
       </c>
       <c r="F15" t="n">
-        <v>66.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -7340,19 +7340,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.2</v>
+        <v>29.8</v>
       </c>
       <c r="D16" t="n">
-        <v>32</v>
+        <v>32.6</v>
       </c>
       <c r="E16" t="n">
         <v>26.8</v>
       </c>
       <c r="F16" t="n">
-        <v>78</v>
+        <v>77.2</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -7367,19 +7367,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="D17" t="n">
-        <v>30.7</v>
+        <v>30</v>
       </c>
       <c r="E17" t="n">
         <v>24.3</v>
       </c>
       <c r="F17" t="n">
-        <v>73.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
@@ -7394,19 +7394,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>30.6</v>
+        <v>29.5</v>
       </c>
       <c r="E18" t="n">
         <v>23.9</v>
       </c>
       <c r="F18" t="n">
-        <v>70</v>
+        <v>70.8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="19">
@@ -7421,19 +7421,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.4</v>
+        <v>28.7</v>
       </c>
       <c r="D19" t="n">
-        <v>30.9</v>
+        <v>31.9</v>
       </c>
       <c r="E19" t="n">
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>77.59999999999999</v>
+        <v>77</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="20">
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.5</v>
+        <v>28.9</v>
       </c>
       <c r="D20" t="n">
-        <v>31.2</v>
+        <v>32.2</v>
       </c>
       <c r="E20" t="n">
         <v>24.7</v>
@@ -7460,7 +7460,7 @@
         <v>65.2</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -7475,19 +7475,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.4</v>
+        <v>31.4</v>
       </c>
       <c r="D21" t="n">
-        <v>33.6</v>
+        <v>36.2</v>
       </c>
       <c r="E21" t="n">
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>63</v>
+        <v>60.2</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -7502,7 +7502,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="D22" t="n">
         <v>31.3</v>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.9</v>
+        <v>28.1</v>
       </c>
       <c r="D23" t="n">
         <v>30.6</v>
@@ -7538,7 +7538,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>76</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="D24" t="n">
         <v>30.2</v>
@@ -7565,7 +7565,7 @@
         <v>24.2</v>
       </c>
       <c r="F24" t="n">
-        <v>78.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0.2</v>
@@ -7583,19 +7583,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.7</v>
+        <v>29</v>
       </c>
       <c r="D25" t="n">
-        <v>31.5</v>
+        <v>31.8</v>
       </c>
       <c r="E25" t="n">
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>79.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="D26" t="n">
         <v>31.1</v>
@@ -7619,7 +7619,7 @@
         <v>25.2</v>
       </c>
       <c r="F26" t="n">
-        <v>76.2</v>
+        <v>76</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="D27" t="n">
         <v>30.5</v>
@@ -7646,7 +7646,7 @@
         <v>24.2</v>
       </c>
       <c r="F27" t="n">
-        <v>68.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="G27" t="n">
         <v>0.1</v>
@@ -7664,7 +7664,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="D28" t="n">
         <v>31.1</v>
@@ -7673,7 +7673,7 @@
         <v>24.5</v>
       </c>
       <c r="F28" t="n">
-        <v>69.40000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G28" t="n">
         <v>0.1</v>
@@ -7691,16 +7691,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.3</v>
+        <v>27.5</v>
       </c>
       <c r="D29" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="E29" t="n">
         <v>24.4</v>
       </c>
       <c r="F29" t="n">
-        <v>76.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="G29" t="n">
         <v>0.1</v>
@@ -7718,16 +7718,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="D30" t="n">
-        <v>33.1</v>
+        <v>34.5</v>
       </c>
       <c r="E30" t="n">
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="D31" t="n">
         <v>29.8</v>
@@ -7754,7 +7754,7 @@
         <v>23.9</v>
       </c>
       <c r="F31" t="n">
-        <v>68.8</v>
+        <v>68.2</v>
       </c>
       <c r="G31" t="n">
         <v>0.1</v>
@@ -7772,16 +7772,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="D32" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="E32" t="n">
         <v>26.4</v>
       </c>
       <c r="F32" t="n">
-        <v>58.4</v>
+        <v>59</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -7799,16 +7799,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.2</v>
+        <v>29.6</v>
       </c>
       <c r="D33" t="n">
-        <v>31.7</v>
+        <v>33.3</v>
       </c>
       <c r="E33" t="n">
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>73.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="D34" t="n">
         <v>31.6</v>
@@ -7835,10 +7835,10 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>69.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:I198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6530,6 +6530,1227 @@
       <c r="I165" t="inlineStr">
         <is>
           <t>2026-09-18T13:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E166" t="n">
+        <v>65</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H166" t="n">
+        <v>2</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E167" t="n">
+        <v>58</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" t="n">
+        <v>9</v>
+      </c>
+      <c r="H167" t="n">
+        <v>3</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E168" t="n">
+        <v>64</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G168" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H168" t="n">
+        <v>51</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E169" t="n">
+        <v>50</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H169" t="n">
+        <v>3</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E170" t="n">
+        <v>74</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G170" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H170" t="n">
+        <v>95</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E171" t="n">
+        <v>65</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G171" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H171" t="n">
+        <v>51</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E172" t="n">
+        <v>80</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G172" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H172" t="n">
+        <v>51</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="E173" t="n">
+        <v>43</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E174" t="n">
+        <v>69</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H174" t="n">
+        <v>1</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E175" t="n">
+        <v>74</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G175" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>95</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="E176" t="n">
+        <v>51</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H176" t="n">
+        <v>3</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E177" t="n">
+        <v>74</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G177" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H177" t="n">
+        <v>95</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E178" t="n">
+        <v>63</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G178" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H178" t="n">
+        <v>53</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E179" t="n">
+        <v>55</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H179" t="n">
+        <v>3</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E180" t="n">
+        <v>74</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G180" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H180" t="n">
+        <v>95</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E181" t="n">
+        <v>71</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H181" t="n">
+        <v>3</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E182" t="n">
+        <v>56</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H182" t="n">
+        <v>3</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E183" t="n">
+        <v>80</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G183" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H183" t="n">
+        <v>51</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>33</v>
+      </c>
+      <c r="E184" t="n">
+        <v>52</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H184" t="n">
+        <v>3</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="E185" t="n">
+        <v>44</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H185" t="n">
+        <v>1</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E186" t="n">
+        <v>52</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H186" t="n">
+        <v>1</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E187" t="n">
+        <v>70</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H187" t="n">
+        <v>2</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E188" t="n">
+        <v>70</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H188" t="n">
+        <v>3</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E189" t="n">
+        <v>77</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G189" t="n">
+        <v>8</v>
+      </c>
+      <c r="H189" t="n">
+        <v>95</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E190" t="n">
+        <v>69</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H190" t="n">
+        <v>3</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>31</v>
+      </c>
+      <c r="E191" t="n">
+        <v>57</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="n">
+        <v>9</v>
+      </c>
+      <c r="H191" t="n">
+        <v>1</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E192" t="n">
+        <v>54</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H192" t="n">
+        <v>3</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>30</v>
+      </c>
+      <c r="E193" t="n">
+        <v>70</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H193" t="n">
+        <v>3</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E194" t="n">
+        <v>49</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H194" t="n">
+        <v>3</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>31</v>
+      </c>
+      <c r="E195" t="n">
+        <v>56</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H195" t="n">
+        <v>3</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E196" t="n">
+        <v>52</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E197" t="n">
+        <v>61</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G197" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H197" t="n">
+        <v>51</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E198" t="n">
+        <v>67</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G198" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H198" t="n">
+        <v>95</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>2026-09-19T13:30</t>
         </is>
       </c>
     </row>
@@ -6544,7 +7765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6897,6 +8118,62 @@
       </c>
       <c r="N6" t="n">
         <v>14.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>33</v>
+      </c>
+      <c r="D7" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>15.3</v>
       </c>
     </row>
   </sheetData>
@@ -6962,7 +8239,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.4</v>
+        <v>28.9</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -6971,7 +8248,7 @@
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>76.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -6989,7 +8266,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.8</v>
+        <v>30.4</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -6998,7 +8275,7 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>75.2</v>
+        <v>72.3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -7016,7 +8293,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.4</v>
+        <v>29.8</v>
       </c>
       <c r="D4" t="n">
         <v>32.9</v>
@@ -7025,10 +8302,10 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>73.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
@@ -7043,16 +8320,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.9</v>
+        <v>30.3</v>
       </c>
       <c r="D5" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="E5" t="n">
         <v>24.8</v>
       </c>
       <c r="F5" t="n">
-        <v>56.6</v>
+        <v>55.5</v>
       </c>
       <c r="G5" t="n">
         <v>0.1</v>
@@ -7070,7 +8347,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.5</v>
+        <v>28.8</v>
       </c>
       <c r="D6" t="n">
         <v>31</v>
@@ -7079,10 +8356,10 @@
         <v>25.7</v>
       </c>
       <c r="F6" t="n">
-        <v>77.8</v>
+        <v>77.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -7097,7 +8374,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.5</v>
+        <v>28.9</v>
       </c>
       <c r="D7" t="n">
         <v>31.8</v>
@@ -7106,10 +8383,10 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>72.8</v>
+        <v>71.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -7124,7 +8401,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="D8" t="n">
         <v>32.7</v>
@@ -7133,10 +8410,10 @@
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>77.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -7151,16 +8428,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30.5</v>
+        <v>31.3</v>
       </c>
       <c r="D9" t="n">
-        <v>34.2</v>
+        <v>35.2</v>
       </c>
       <c r="E9" t="n">
         <v>25.8</v>
       </c>
       <c r="F9" t="n">
-        <v>57.2</v>
+        <v>54.8</v>
       </c>
       <c r="G9" t="n">
         <v>1.6</v>
@@ -7178,7 +8455,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.6</v>
+        <v>27.1</v>
       </c>
       <c r="D10" t="n">
         <v>29.9</v>
@@ -7187,7 +8464,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>77.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -7205,7 +8482,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>29.3</v>
       </c>
       <c r="D11" t="n">
         <v>31.6</v>
@@ -7214,10 +8491,10 @@
         <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>76.2</v>
+        <v>75.8</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -7232,7 +8509,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.5</v>
+        <v>31.3</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -7241,7 +8518,7 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>69.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -7259,7 +8536,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -7268,10 +8545,10 @@
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>77.59999999999999</v>
+        <v>77</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
@@ -7286,7 +8563,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.5</v>
+        <v>29.8</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -7295,10 +8572,10 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>75.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15">
@@ -7313,16 +8590,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>28.7</v>
       </c>
       <c r="D15" t="n">
-        <v>31.1</v>
+        <v>31.8</v>
       </c>
       <c r="E15" t="n">
         <v>24.3</v>
       </c>
       <c r="F15" t="n">
-        <v>67.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -7340,7 +8617,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>32.6</v>
@@ -7349,10 +8626,10 @@
         <v>26.8</v>
       </c>
       <c r="F16" t="n">
-        <v>77.2</v>
+        <v>76.7</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="17">
@@ -7367,7 +8644,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>27.4</v>
       </c>
       <c r="D17" t="n">
         <v>30</v>
@@ -7376,7 +8653,7 @@
         <v>24.3</v>
       </c>
       <c r="F17" t="n">
-        <v>76.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="G17" t="n">
         <v>0.5</v>
@@ -7394,16 +8671,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>27.9</v>
       </c>
       <c r="D18" t="n">
-        <v>29.5</v>
+        <v>31.6</v>
       </c>
       <c r="E18" t="n">
         <v>23.9</v>
       </c>
       <c r="F18" t="n">
-        <v>70.8</v>
+        <v>67.8</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -7421,7 +8698,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="D19" t="n">
         <v>31.9</v>
@@ -7430,10 +8707,10 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>77</v>
+        <v>77.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20">
@@ -7448,16 +8725,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="D20" t="n">
-        <v>32.2</v>
+        <v>33</v>
       </c>
       <c r="E20" t="n">
         <v>24.7</v>
       </c>
       <c r="F20" t="n">
-        <v>65.2</v>
+        <v>63</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -7475,7 +8752,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31.4</v>
+        <v>32.1</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -7484,7 +8761,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>60.2</v>
+        <v>57.5</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -7502,16 +8779,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28.5</v>
+        <v>29.2</v>
       </c>
       <c r="D22" t="n">
-        <v>31.3</v>
+        <v>32.6</v>
       </c>
       <c r="E22" t="n">
         <v>25</v>
       </c>
       <c r="F22" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G22" t="n">
         <v>0.1</v>
@@ -7529,16 +8806,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.1</v>
+        <v>28.5</v>
       </c>
       <c r="D23" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="E23" t="n">
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>75.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
@@ -7556,16 +8833,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.9</v>
+        <v>27.5</v>
       </c>
       <c r="D24" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="E24" t="n">
         <v>24.2</v>
       </c>
       <c r="F24" t="n">
-        <v>79.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="G24" t="n">
         <v>0.2</v>
@@ -7583,7 +8860,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>29</v>
+        <v>29.3</v>
       </c>
       <c r="D25" t="n">
         <v>31.8</v>
@@ -7592,10 +8869,10 @@
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>78.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26">
@@ -7610,7 +8887,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.4</v>
+        <v>28.8</v>
       </c>
       <c r="D26" t="n">
         <v>31.1</v>
@@ -7619,7 +8896,7 @@
         <v>25.2</v>
       </c>
       <c r="F26" t="n">
-        <v>76</v>
+        <v>74.8</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -7637,16 +8914,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.6</v>
+        <v>28.1</v>
       </c>
       <c r="D27" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="E27" t="n">
         <v>24.2</v>
       </c>
       <c r="F27" t="n">
-        <v>68</v>
+        <v>66.2</v>
       </c>
       <c r="G27" t="n">
         <v>0.1</v>
@@ -7664,16 +8941,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.8</v>
+        <v>28.6</v>
       </c>
       <c r="D28" t="n">
-        <v>31.1</v>
+        <v>32.4</v>
       </c>
       <c r="E28" t="n">
         <v>24.5</v>
       </c>
       <c r="F28" t="n">
-        <v>68.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="G28" t="n">
         <v>0.1</v>
@@ -7691,16 +8968,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.5</v>
+        <v>27.9</v>
       </c>
       <c r="D29" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="E29" t="n">
         <v>24.4</v>
       </c>
       <c r="F29" t="n">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="G29" t="n">
         <v>0.1</v>
@@ -7718,16 +8995,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.5</v>
+        <v>31.2</v>
       </c>
       <c r="D30" t="n">
-        <v>34.5</v>
+        <v>34.8</v>
       </c>
       <c r="E30" t="n">
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>67.2</v>
+        <v>64.2</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -7745,16 +9022,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.2</v>
+        <v>27.8</v>
       </c>
       <c r="D31" t="n">
-        <v>29.8</v>
+        <v>31</v>
       </c>
       <c r="E31" t="n">
         <v>23.9</v>
       </c>
       <c r="F31" t="n">
-        <v>68.2</v>
+        <v>66.2</v>
       </c>
       <c r="G31" t="n">
         <v>0.1</v>
@@ -7772,16 +9049,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>29.7</v>
+        <v>30.3</v>
       </c>
       <c r="D32" t="n">
-        <v>32.1</v>
+        <v>33.3</v>
       </c>
       <c r="E32" t="n">
         <v>26.4</v>
       </c>
       <c r="F32" t="n">
-        <v>59</v>
+        <v>57.8</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -7799,7 +9076,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.6</v>
+        <v>29.9</v>
       </c>
       <c r="D33" t="n">
         <v>33.3</v>
@@ -7808,10 +9085,10 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>71.8</v>
+        <v>70</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="34">
@@ -7826,7 +9103,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="D34" t="n">
         <v>31.6</v>
@@ -7835,10 +9112,10 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>68.8</v>
+        <v>68.5</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I198"/>
+  <dimension ref="A1:I231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7751,6 +7751,1227 @@
       <c r="I198" t="inlineStr">
         <is>
           <t>2026-09-19T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E199" t="n">
+        <v>62</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H199" t="n">
+        <v>1</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E200" t="n">
+        <v>66</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G200" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H200" t="n">
+        <v>95</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E201" t="n">
+        <v>54</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G201" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H201" t="n">
+        <v>95</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>32</v>
+      </c>
+      <c r="E202" t="n">
+        <v>51</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H202" t="n">
+        <v>2</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E203" t="n">
+        <v>71</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G203" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H203" t="n">
+        <v>95</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>31</v>
+      </c>
+      <c r="E204" t="n">
+        <v>60</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G204" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H204" t="n">
+        <v>51</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E205" t="n">
+        <v>58</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H205" t="n">
+        <v>3</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E206" t="n">
+        <v>61</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="n">
+        <v>5</v>
+      </c>
+      <c r="H206" t="n">
+        <v>3</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>30</v>
+      </c>
+      <c r="E207" t="n">
+        <v>67</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H207" t="n">
+        <v>2</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E208" t="n">
+        <v>64</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H208" t="n">
+        <v>1</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E209" t="n">
+        <v>60</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G209" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H209" t="n">
+        <v>51</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E210" t="n">
+        <v>72</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G210" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H210" t="n">
+        <v>95</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E211" t="n">
+        <v>59</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H211" t="n">
+        <v>3</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E212" t="n">
+        <v>58</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>3</v>
+      </c>
+      <c r="H212" t="n">
+        <v>2</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="E213" t="n">
+        <v>59</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E214" t="n">
+        <v>67</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E215" t="n">
+        <v>57</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H215" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>32</v>
+      </c>
+      <c r="E216" t="n">
+        <v>62</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H216" t="n">
+        <v>2</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E217" t="n">
+        <v>54</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H217" t="n">
+        <v>3</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E218" t="n">
+        <v>46</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H218" t="n">
+        <v>3</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E219" t="n">
+        <v>59</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H219" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E220" t="n">
+        <v>68</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>5</v>
+      </c>
+      <c r="H220" t="n">
+        <v>3</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E221" t="n">
+        <v>66</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E222" t="n">
+        <v>63</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H222" t="n">
+        <v>1</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E223" t="n">
+        <v>81</v>
+      </c>
+      <c r="F223" t="n">
+        <v>2</v>
+      </c>
+      <c r="G223" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H223" t="n">
+        <v>96</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E224" t="n">
+        <v>60</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E225" t="n">
+        <v>57</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G225" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H225" t="n">
+        <v>51</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E226" t="n">
+        <v>63</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H226" t="n">
+        <v>2</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E227" t="n">
+        <v>52</v>
+      </c>
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H227" t="n">
+        <v>3</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E228" t="n">
+        <v>56</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H228" t="n">
+        <v>1</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E229" t="n">
+        <v>60</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H229" t="n">
+        <v>3</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E230" t="n">
+        <v>51</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G230" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H230" t="n">
+        <v>51</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E231" t="n">
+        <v>55</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
+        <v>9</v>
+      </c>
+      <c r="H231" t="n">
+        <v>3</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>2026-09-20T14:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +8986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8174,6 +9395,62 @@
       </c>
       <c r="N7" t="n">
         <v>15.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>33</v>
+      </c>
+      <c r="D8" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>10.1</v>
       </c>
     </row>
   </sheetData>
@@ -8239,7 +9516,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.9</v>
+        <v>29.3</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -8248,7 +9525,7 @@
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>74.5</v>
+        <v>72.7</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -8266,7 +9543,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -8275,10 +9552,10 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>72.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
@@ -8293,7 +9570,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.8</v>
+        <v>30.2</v>
       </c>
       <c r="D4" t="n">
         <v>32.9</v>
@@ -8302,10 +9579,10 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>71.8</v>
+        <v>69.3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -8320,7 +9597,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.3</v>
+        <v>30.6</v>
       </c>
       <c r="D5" t="n">
         <v>32.3</v>
@@ -8329,7 +9606,7 @@
         <v>24.8</v>
       </c>
       <c r="F5" t="n">
-        <v>55.5</v>
+        <v>54.9</v>
       </c>
       <c r="G5" t="n">
         <v>0.1</v>
@@ -8347,19 +9624,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="E6" t="n">
         <v>25.7</v>
       </c>
       <c r="F6" t="n">
-        <v>77.2</v>
+        <v>76.3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -8374,7 +9651,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="D7" t="n">
         <v>31.8</v>
@@ -8383,10 +9660,10 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>71.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
@@ -8401,16 +9678,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.1</v>
+        <v>29.6</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="E8" t="n">
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>77.8</v>
+        <v>75</v>
       </c>
       <c r="G8" t="n">
         <v>0.1</v>
@@ -8428,7 +9705,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="D9" t="n">
         <v>35.2</v>
@@ -8437,7 +9714,7 @@
         <v>25.8</v>
       </c>
       <c r="F9" t="n">
-        <v>54.8</v>
+        <v>55.7</v>
       </c>
       <c r="G9" t="n">
         <v>1.6</v>
@@ -8455,16 +9732,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27.1</v>
+        <v>27.5</v>
       </c>
       <c r="D10" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>76.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -8482,16 +9759,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29.3</v>
+        <v>29.8</v>
       </c>
       <c r="D11" t="n">
-        <v>31.6</v>
+        <v>32.3</v>
       </c>
       <c r="E11" t="n">
         <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>75.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>0.1</v>
@@ -8509,7 +9786,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -8518,10 +9795,10 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>66.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13">
@@ -8536,7 +9813,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29.4</v>
+        <v>29.7</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -8545,10 +9822,10 @@
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>77</v>
+        <v>76.3</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14">
@@ -8563,7 +9840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.8</v>
+        <v>30.2</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -8572,7 +9849,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>73.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>0.2</v>
@@ -8590,7 +9867,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="D15" t="n">
         <v>31.8</v>
@@ -8599,7 +9876,7 @@
         <v>24.3</v>
       </c>
       <c r="F15" t="n">
-        <v>65.3</v>
+        <v>64.3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -8617,16 +9894,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="D16" t="n">
-        <v>32.6</v>
+        <v>33.1</v>
       </c>
       <c r="E16" t="n">
         <v>26.8</v>
       </c>
       <c r="F16" t="n">
-        <v>76.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>0.1</v>
@@ -8644,16 +9921,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.4</v>
+        <v>27.9</v>
       </c>
       <c r="D17" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="E17" t="n">
         <v>24.3</v>
       </c>
       <c r="F17" t="n">
-        <v>75.5</v>
+        <v>74.3</v>
       </c>
       <c r="G17" t="n">
         <v>0.5</v>
@@ -8671,7 +9948,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27.9</v>
+        <v>28.4</v>
       </c>
       <c r="D18" t="n">
         <v>31.6</v>
@@ -8680,7 +9957,7 @@
         <v>23.9</v>
       </c>
       <c r="F18" t="n">
-        <v>67.8</v>
+        <v>66</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -8698,16 +9975,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="D19" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="E19" t="n">
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>77.5</v>
+        <v>75.3</v>
       </c>
       <c r="G19" t="n">
         <v>0.2</v>
@@ -8725,7 +10002,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>29.6</v>
+        <v>29.9</v>
       </c>
       <c r="D20" t="n">
         <v>33</v>
@@ -8734,7 +10011,7 @@
         <v>24.7</v>
       </c>
       <c r="F20" t="n">
-        <v>63</v>
+        <v>61.7</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -8752,7 +10029,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -8761,7 +10038,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>57.5</v>
+        <v>55.9</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -8779,7 +10056,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>29.2</v>
+        <v>29.4</v>
       </c>
       <c r="D22" t="n">
         <v>32.6</v>
@@ -8788,7 +10065,7 @@
         <v>25</v>
       </c>
       <c r="F22" t="n">
-        <v>62</v>
+        <v>61.6</v>
       </c>
       <c r="G22" t="n">
         <v>0.1</v>
@@ -8806,16 +10083,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.5</v>
+        <v>28.9</v>
       </c>
       <c r="D23" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="E23" t="n">
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>74.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
@@ -8833,16 +10110,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.5</v>
+        <v>27.9</v>
       </c>
       <c r="D24" t="n">
-        <v>30.5</v>
+        <v>30.7</v>
       </c>
       <c r="E24" t="n">
         <v>24.2</v>
       </c>
       <c r="F24" t="n">
-        <v>77.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0.2</v>
@@ -8860,16 +10137,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>29.3</v>
+        <v>29.7</v>
       </c>
       <c r="D25" t="n">
-        <v>31.8</v>
+        <v>32.2</v>
       </c>
       <c r="E25" t="n">
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>78.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0.1</v>
@@ -8887,7 +10164,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="D26" t="n">
         <v>31.1</v>
@@ -8896,10 +10173,10 @@
         <v>25.2</v>
       </c>
       <c r="F26" t="n">
-        <v>74.8</v>
+        <v>75.7</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -8914,7 +10191,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>28.1</v>
+        <v>28.5</v>
       </c>
       <c r="D27" t="n">
         <v>31</v>
@@ -8923,7 +10200,7 @@
         <v>24.2</v>
       </c>
       <c r="F27" t="n">
-        <v>66.2</v>
+        <v>65.3</v>
       </c>
       <c r="G27" t="n">
         <v>0.1</v>
@@ -8941,7 +10218,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28.6</v>
+        <v>29</v>
       </c>
       <c r="D28" t="n">
         <v>32.4</v>
@@ -8950,10 +10227,10 @@
         <v>24.5</v>
       </c>
       <c r="F28" t="n">
-        <v>66.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29">
@@ -8968,16 +10245,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.9</v>
+        <v>28.3</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
       <c r="E29" t="n">
         <v>24.4</v>
       </c>
       <c r="F29" t="n">
-        <v>75.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0.1</v>
@@ -8995,7 +10272,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>31.2</v>
+        <v>31.5</v>
       </c>
       <c r="D30" t="n">
         <v>34.8</v>
@@ -9004,7 +10281,7 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>64.2</v>
+        <v>62.4</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -9022,7 +10299,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="D31" t="n">
         <v>31</v>
@@ -9031,7 +10308,7 @@
         <v>23.9</v>
       </c>
       <c r="F31" t="n">
-        <v>66.2</v>
+        <v>64.7</v>
       </c>
       <c r="G31" t="n">
         <v>0.1</v>
@@ -9058,7 +10335,7 @@
         <v>26.4</v>
       </c>
       <c r="F32" t="n">
-        <v>57.8</v>
+        <v>58.1</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -9076,7 +10353,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.9</v>
+        <v>30.4</v>
       </c>
       <c r="D33" t="n">
         <v>33.3</v>
@@ -9085,10 +10362,10 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>70</v>
+        <v>67.3</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="34">
@@ -9103,16 +10380,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>28.7</v>
+        <v>29.2</v>
       </c>
       <c r="D34" t="n">
-        <v>31.6</v>
+        <v>31.9</v>
       </c>
       <c r="E34" t="n">
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>68.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G34" t="n">
         <v>0.3</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I231"/>
+  <dimension ref="A1:I330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Adilabad</t>
+          <t>Wanaparthy</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6550,23 +6550,23 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>31.2</v>
+        <v>27.5</v>
       </c>
       <c r="E166" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>3.8</v>
+        <v>10.4</v>
       </c>
       <c r="H166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Bhadradri Kothagudem</t>
+          <t>Warangal</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6587,23 +6587,23 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>33.4</v>
+        <v>26.5</v>
       </c>
       <c r="E167" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H167" t="n">
         <v>3</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Hanumakonda</t>
+          <t>Yadadri Bhuvanagiri</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6624,23 +6624,23 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>31.3</v>
+        <v>25.7</v>
       </c>
       <c r="E168" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="F168" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>10.6</v>
+        <v>8.1</v>
       </c>
       <c r="H168" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Adilabad</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6661,23 +6661,23 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>32.3</v>
+        <v>26.2</v>
       </c>
       <c r="E169" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="H169" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Jagtial</t>
+          <t>Bhadradri Kothagudem</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6698,23 +6698,23 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>30.5</v>
+        <v>27.2</v>
       </c>
       <c r="E170" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F170" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="H170" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Jangaon</t>
+          <t>Hanumakonda</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6735,23 +6735,23 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>30.9</v>
+        <v>26.5</v>
       </c>
       <c r="E171" t="n">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="F171" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>10.1</v>
+        <v>5.7</v>
       </c>
       <c r="H171" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -6763,7 +6763,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Jayashankar Bhupalpally</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6772,23 +6772,23 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>29.6</v>
+        <v>26.7</v>
       </c>
       <c r="E172" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F172" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="H172" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Jogulamba Gadwal</t>
+          <t>Jagtial</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6809,23 +6809,23 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>35.2</v>
+        <v>25.7</v>
       </c>
       <c r="E173" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>8.5</v>
+        <v>1.3</v>
       </c>
       <c r="H173" t="n">
         <v>1</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Kamareddy</t>
+          <t>Jangaon</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6846,23 +6846,23 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>29.7</v>
+        <v>25.7</v>
       </c>
       <c r="E174" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>7.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Karimnagar</t>
+          <t>Jayashankar Bhupalpally</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6883,23 +6883,23 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>30.9</v>
+        <v>25.4</v>
       </c>
       <c r="E175" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="F175" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="H175" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Khammam</t>
+          <t>Jogulamba Gadwal</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6920,23 +6920,23 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>35.1</v>
+        <v>24.6</v>
       </c>
       <c r="E176" t="n">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="F176" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G176" t="n">
-        <v>10.8</v>
+        <v>18.7</v>
       </c>
       <c r="H176" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Kumuram Bheem Asifabad</t>
+          <t>Kamareddy</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6957,23 +6957,23 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>31.1</v>
+        <v>24.6</v>
       </c>
       <c r="E177" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F177" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="H177" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Mahabubabad</t>
+          <t>Karimnagar</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6994,23 +6994,23 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>31.5</v>
+        <v>25.9</v>
       </c>
       <c r="E178" t="n">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="F178" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>15.3</v>
+        <v>2.1</v>
       </c>
       <c r="H178" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Mahbubnagar</t>
+          <t>Khammam</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -7031,23 +7031,23 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>31.8</v>
+        <v>27.9</v>
       </c>
       <c r="E179" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F179" t="n">
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Mancherial</t>
+          <t>Kumuram Bheem Asifabad</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7068,23 +7068,23 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>31.4</v>
+        <v>25.5</v>
       </c>
       <c r="E180" t="n">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="F180" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="H180" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Medak</t>
+          <t>Mahabubabad</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -7105,23 +7105,23 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>29.7</v>
+        <v>26.7</v>
       </c>
       <c r="E181" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="F181" t="n">
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="H181" t="n">
         <v>3</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Medchal-Malkajgiri</t>
+          <t>Mahbubnagar</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -7142,23 +7142,23 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>31.6</v>
+        <v>25.8</v>
       </c>
       <c r="E182" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="H182" t="n">
         <v>3</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mulugu</t>
+          <t>Mancherial</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7179,23 +7179,23 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>29.1</v>
+        <v>26.1</v>
       </c>
       <c r="E183" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="F183" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>12.2</v>
+        <v>4.4</v>
       </c>
       <c r="H183" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Nagarkurnool</t>
+          <t>Medak</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7216,23 +7216,23 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>33</v>
+        <v>25.2</v>
       </c>
       <c r="E184" t="n">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="F184" t="n">
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H184" t="n">
         <v>3</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Nalgonda</t>
+          <t>Medchal-Malkajgiri</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7253,23 +7253,23 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>35.6</v>
+        <v>25.3</v>
       </c>
       <c r="E185" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="F185" t="n">
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>11.5</v>
+        <v>4.7</v>
       </c>
       <c r="H185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Narayanpet</t>
+          <t>Mulugu</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7290,23 +7290,23 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>32.6</v>
+        <v>25.7</v>
       </c>
       <c r="E186" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="F186" t="n">
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Nirmal</t>
+          <t>Nagarkurnool</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7327,23 +7327,23 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>30.8</v>
+        <v>25.9</v>
       </c>
       <c r="E187" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F187" t="n">
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>4.1</v>
+        <v>7.3</v>
       </c>
       <c r="H187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Nizamabad</t>
+          <t>Nalgonda</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7364,23 +7364,23 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>30.5</v>
+        <v>28.2</v>
       </c>
       <c r="E188" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F188" t="n">
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="H188" t="n">
         <v>3</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Peddapalli</t>
+          <t>Narayanpet</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7401,23 +7401,23 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>30.8</v>
+        <v>23.5</v>
       </c>
       <c r="E189" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F189" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G189" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H189" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Rajanna Sircilla</t>
+          <t>Nirmal</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7438,23 +7438,23 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>30.8</v>
+        <v>25.5</v>
       </c>
       <c r="E190" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="F190" t="n">
         <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="H190" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Rangareddy</t>
+          <t>Nizamabad</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7475,23 +7475,23 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>31</v>
+        <v>25.4</v>
       </c>
       <c r="E191" t="n">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>9</v>
+        <v>2.9</v>
       </c>
       <c r="H191" t="n">
         <v>1</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Sangareddy</t>
+          <t>Peddapalli</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7512,23 +7512,23 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>32.4</v>
+        <v>26.1</v>
       </c>
       <c r="E192" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="H192" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Siddipet</t>
+          <t>Rajanna Sircilla</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7549,23 +7549,23 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>30</v>
+        <v>25.6</v>
       </c>
       <c r="E193" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>8.4</v>
+        <v>1.9</v>
       </c>
       <c r="H193" t="n">
         <v>3</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Suryapet</t>
+          <t>Rangareddy</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7586,23 +7586,23 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>34.8</v>
+        <v>24.9</v>
       </c>
       <c r="E194" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="F194" t="n">
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>10.6</v>
+        <v>6.8</v>
       </c>
       <c r="H194" t="n">
         <v>3</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Vikarabad</t>
+          <t>Sangareddy</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7623,23 +7623,23 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>31</v>
+        <v>25.7</v>
       </c>
       <c r="E195" t="n">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F195" t="n">
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>8.4</v>
+        <v>6.3</v>
       </c>
       <c r="H195" t="n">
         <v>3</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Wanaparthy</t>
+          <t>Siddipet</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7660,23 +7660,23 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>33.3</v>
+        <v>24.8</v>
       </c>
       <c r="E196" t="n">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="F196" t="n">
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>6.7</v>
+        <v>4.1</v>
       </c>
       <c r="H196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Warangal</t>
+          <t>Suryapet</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7697,23 +7697,23 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>31.6</v>
+        <v>27.9</v>
       </c>
       <c r="E197" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="F197" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G197" t="n">
-        <v>10.8</v>
+        <v>8.6</v>
       </c>
       <c r="H197" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Yadadri Bhuvanagiri</t>
+          <t>Vikarabad</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7734,30 +7734,30 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>29.5</v>
+        <v>25</v>
       </c>
       <c r="E198" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F198" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>14.8</v>
+        <v>10.2</v>
       </c>
       <c r="H198" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-09-19T13:30</t>
+          <t>2026-09-19T23:30</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7771,30 +7771,30 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>31.5</v>
+        <v>26.1</v>
       </c>
       <c r="E199" t="n">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F199" t="n">
         <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="H199" t="n">
         <v>1</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7808,30 +7808,30 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>31.7</v>
+        <v>27.2</v>
       </c>
       <c r="E200" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="F200" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="H200" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7845,30 +7845,30 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>32.9</v>
+        <v>26.4</v>
       </c>
       <c r="E201" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F201" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="H201" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7882,30 +7882,30 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>32</v>
+        <v>26.6</v>
       </c>
       <c r="E202" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="F202" t="n">
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="H202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7919,30 +7919,30 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>31.2</v>
+        <v>25.6</v>
       </c>
       <c r="E203" t="n">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="F203" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="H203" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7956,30 +7956,30 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>31</v>
+        <v>25.6</v>
       </c>
       <c r="E204" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="F204" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>10.1</v>
+        <v>8.5</v>
       </c>
       <c r="H204" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7993,30 +7993,30 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>32.9</v>
+        <v>25.3</v>
       </c>
       <c r="E205" t="n">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="F205" t="n">
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="H205" t="n">
         <v>3</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -8030,30 +8030,30 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>30.6</v>
+        <v>24.4</v>
       </c>
       <c r="E206" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="F206" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G206" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H206" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -8067,30 +8067,30 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>30</v>
+        <v>24.5</v>
       </c>
       <c r="E207" t="n">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="F207" t="n">
         <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="H207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -8104,30 +8104,30 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>32.3</v>
+        <v>25.8</v>
       </c>
       <c r="E208" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="F208" t="n">
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>7.4</v>
+        <v>2.2</v>
       </c>
       <c r="H208" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -8141,30 +8141,30 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>32.3</v>
+        <v>27.8</v>
       </c>
       <c r="E209" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F209" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H209" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -8178,30 +8178,30 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>31.1</v>
+        <v>25.4</v>
       </c>
       <c r="E210" t="n">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="F210" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G210" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="H210" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -8215,30 +8215,30 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>32.6</v>
+        <v>26.6</v>
       </c>
       <c r="E211" t="n">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="F211" t="n">
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="H211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -8252,30 +8252,30 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>30.4</v>
+        <v>25.4</v>
       </c>
       <c r="E212" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="F212" t="n">
         <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>3</v>
+        <v>6.1</v>
       </c>
       <c r="H212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -8289,30 +8289,30 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>33.1</v>
+        <v>26</v>
       </c>
       <c r="E213" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="F213" t="n">
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="H213" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -8326,30 +8326,30 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>30.3</v>
+        <v>25.2</v>
       </c>
       <c r="E214" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F214" t="n">
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="H214" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -8363,30 +8363,30 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>31.1</v>
+        <v>25.2</v>
       </c>
       <c r="E215" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="F215" t="n">
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>8.5</v>
+        <v>4.7</v>
       </c>
       <c r="H215" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -8400,30 +8400,30 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>32</v>
+        <v>25.6</v>
       </c>
       <c r="E216" t="n">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="F216" t="n">
         <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="H216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -8437,30 +8437,30 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>31.9</v>
+        <v>25.9</v>
       </c>
       <c r="E217" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F217" t="n">
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="H217" t="n">
         <v>3</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -8474,30 +8474,30 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>34.4</v>
+        <v>28.1</v>
       </c>
       <c r="E218" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="F218" t="n">
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>9.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H218" t="n">
         <v>3</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -8511,30 +8511,30 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>30.9</v>
+        <v>23.3</v>
       </c>
       <c r="E219" t="n">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="F219" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G219" t="n">
-        <v>3.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H219" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -8548,30 +8548,30 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>30.9</v>
+        <v>25.5</v>
       </c>
       <c r="E220" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="F220" t="n">
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="H220" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -8585,30 +8585,30 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>30.7</v>
+        <v>25.3</v>
       </c>
       <c r="E221" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="F221" t="n">
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="H221" t="n">
         <v>1</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -8622,30 +8622,30 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>32.2</v>
+        <v>26</v>
       </c>
       <c r="E222" t="n">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="F222" t="n">
         <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="H222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -8659,30 +8659,30 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>27.8</v>
+        <v>25.5</v>
       </c>
       <c r="E223" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="F223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>7.1</v>
+        <v>1.4</v>
       </c>
       <c r="H223" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -8696,30 +8696,30 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>30.5</v>
+        <v>24.9</v>
       </c>
       <c r="E224" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="F224" t="n">
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="H224" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -8733,30 +8733,30 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>31.6</v>
+        <v>25.6</v>
       </c>
       <c r="E225" t="n">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="F225" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
       <c r="H225" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -8770,30 +8770,30 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>30.6</v>
+        <v>24.7</v>
       </c>
       <c r="E226" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F226" t="n">
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>6.7</v>
+        <v>3.9</v>
       </c>
       <c r="H226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -8807,10 +8807,10 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>33.4</v>
+        <v>27.8</v>
       </c>
       <c r="E227" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="F227" t="n">
         <v>0</v>
@@ -8823,14 +8823,14 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -8844,30 +8844,30 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>30.8</v>
+        <v>24.9</v>
       </c>
       <c r="E228" t="n">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="F228" t="n">
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>6.2</v>
+        <v>11.1</v>
       </c>
       <c r="H228" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -8881,30 +8881,30 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>30.6</v>
+        <v>26.6</v>
       </c>
       <c r="E229" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F229" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G229" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="H229" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -8918,60 +8918,3723 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>33.3</v>
+        <v>26.4</v>
       </c>
       <c r="E230" t="n">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="F230" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H230" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00</t>
+          <t>2026-09-19T23:45</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E231" t="n">
+        <v>89</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
+        <v>8</v>
+      </c>
+      <c r="H231" t="n">
+        <v>3</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>2026-09-19T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E232" t="n">
+        <v>94</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H232" t="n">
+        <v>1</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E233" t="n">
+        <v>91</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H233" t="n">
+        <v>3</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E234" t="n">
+        <v>87</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H234" t="n">
+        <v>3</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>26</v>
+      </c>
+      <c r="E235" t="n">
+        <v>79</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H235" t="n">
+        <v>3</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E236" t="n">
+        <v>97</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H236" t="n">
+        <v>3</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E237" t="n">
+        <v>85</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H237" t="n">
+        <v>3</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E238" t="n">
+        <v>94</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H238" t="n">
+        <v>3</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E239" t="n">
+        <v>94</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G239" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H239" t="n">
+        <v>51</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>24</v>
+      </c>
+      <c r="E240" t="n">
+        <v>90</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H240" t="n">
+        <v>1</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E241" t="n">
+        <v>92</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H241" t="n">
+        <v>2</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E242" t="n">
+        <v>87</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H242" t="n">
+        <v>3</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E243" t="n">
+        <v>97</v>
+      </c>
+      <c r="F243" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H243" t="n">
+        <v>3</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E244" t="n">
+        <v>86</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H244" t="n">
+        <v>3</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E245" t="n">
+        <v>88</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G245" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H245" t="n">
+        <v>51</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E246" t="n">
+        <v>90</v>
+      </c>
+      <c r="F246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H246" t="n">
+        <v>1</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>24</v>
+      </c>
+      <c r="E247" t="n">
+        <v>93</v>
+      </c>
+      <c r="F247" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H247" t="n">
+        <v>3</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E248" t="n">
+        <v>86</v>
+      </c>
+      <c r="F248" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H248" t="n">
+        <v>3</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E249" t="n">
+        <v>90</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H249" t="n">
+        <v>3</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E250" t="n">
+        <v>88</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G250" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H250" t="n">
+        <v>80</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E251" t="n">
+        <v>79</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H251" t="n">
+        <v>3</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E252" t="n">
+        <v>94</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G252" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H252" t="n">
+        <v>95</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E253" t="n">
+        <v>92</v>
+      </c>
+      <c r="F253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E254" t="n">
+        <v>96</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H254" t="n">
+        <v>0</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E255" t="n">
+        <v>90</v>
+      </c>
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H255" t="n">
+        <v>0</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E256" t="n">
+        <v>96</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H256" t="n">
+        <v>3</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E257" t="n">
+        <v>86</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H257" t="n">
+        <v>3</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E258" t="n">
+        <v>88</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H258" t="n">
+        <v>3</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E259" t="n">
+        <v>89</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H259" t="n">
+        <v>3</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>27</v>
+      </c>
+      <c r="E260" t="n">
+        <v>83</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H260" t="n">
+        <v>3</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E261" t="n">
+        <v>87</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H261" t="n">
+        <v>3</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E262" t="n">
+        <v>95</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G262" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H262" t="n">
+        <v>53</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E263" t="n">
+        <v>85</v>
+      </c>
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H263" t="n">
+        <v>3</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
         <is>
           <t>Yadadri Bhuvanagiri</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E231" t="n">
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E264" t="n">
+        <v>85</v>
+      </c>
+      <c r="F264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H264" t="n">
+        <v>3</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E265" t="n">
+        <v>63</v>
+      </c>
+      <c r="F265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H265" t="n">
+        <v>1</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E266" t="n">
+        <v>63</v>
+      </c>
+      <c r="F266" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H266" t="n">
+        <v>3</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E267" t="n">
+        <v>52</v>
+      </c>
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H267" t="n">
+        <v>3</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E268" t="n">
+        <v>52</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G268" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H268" t="n">
+        <v>51</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E269" t="n">
+        <v>70</v>
+      </c>
+      <c r="F269" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G269" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H269" t="n">
+        <v>95</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>32</v>
+      </c>
+      <c r="E270" t="n">
+        <v>56</v>
+      </c>
+      <c r="F270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="n">
+        <v>9</v>
+      </c>
+      <c r="H270" t="n">
+        <v>3</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>33</v>
+      </c>
+      <c r="E271" t="n">
+        <v>59</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H271" t="n">
+        <v>3</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E272" t="n">
+        <v>63</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H272" t="n">
+        <v>3</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E273" t="n">
+        <v>67</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="n">
+        <v>4</v>
+      </c>
+      <c r="H273" t="n">
+        <v>3</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>32</v>
+      </c>
+      <c r="E274" t="n">
+        <v>65</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H274" t="n">
+        <v>1</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="E275" t="n">
+        <v>56</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H275" t="n">
+        <v>3</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E276" t="n">
+        <v>69</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G276" t="n">
+        <v>3</v>
+      </c>
+      <c r="H276" t="n">
+        <v>51</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E277" t="n">
+        <v>61</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H277" t="n">
+        <v>3</v>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E278" t="n">
+        <v>59</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H278" t="n">
+        <v>2</v>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E279" t="n">
+        <v>61</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H279" t="n">
+        <v>0</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E280" t="n">
+        <v>67</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H280" t="n">
+        <v>1</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E281" t="n">
+        <v>57</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H281" t="n">
+        <v>0</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>32</v>
+      </c>
+      <c r="E282" t="n">
+        <v>62</v>
+      </c>
+      <c r="F282" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H282" t="n">
+        <v>1</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E283" t="n">
         <v>55</v>
       </c>
-      <c r="F231" t="n">
-        <v>0</v>
-      </c>
-      <c r="G231" t="n">
-        <v>9</v>
-      </c>
-      <c r="H231" t="n">
-        <v>3</v>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>2026-09-20T14:00</t>
+      <c r="F283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H283" t="n">
+        <v>3</v>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E284" t="n">
+        <v>44</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H284" t="n">
+        <v>3</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E285" t="n">
+        <v>59</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H285" t="n">
+        <v>0</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E286" t="n">
+        <v>69</v>
+      </c>
+      <c r="F286" t="n">
+        <v>0</v>
+      </c>
+      <c r="G286" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H286" t="n">
+        <v>3</v>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E287" t="n">
+        <v>66</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0</v>
+      </c>
+      <c r="G287" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H287" t="n">
+        <v>2</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>32</v>
+      </c>
+      <c r="E288" t="n">
+        <v>65</v>
+      </c>
+      <c r="F288" t="n">
+        <v>0</v>
+      </c>
+      <c r="G288" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H288" t="n">
+        <v>1</v>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E289" t="n">
+        <v>69</v>
+      </c>
+      <c r="F289" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G289" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H289" t="n">
+        <v>95</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E290" t="n">
+        <v>61</v>
+      </c>
+      <c r="F290" t="n">
+        <v>0</v>
+      </c>
+      <c r="G290" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H290" t="n">
+        <v>0</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E291" t="n">
+        <v>57</v>
+      </c>
+      <c r="F291" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G291" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H291" t="n">
+        <v>51</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E292" t="n">
+        <v>64</v>
+      </c>
+      <c r="F292" t="n">
+        <v>0</v>
+      </c>
+      <c r="G292" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H292" t="n">
+        <v>2</v>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E293" t="n">
+        <v>52</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H293" t="n">
+        <v>3</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E294" t="n">
+        <v>56</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G294" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H294" t="n">
+        <v>51</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E295" t="n">
+        <v>61</v>
+      </c>
+      <c r="F295" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H295" t="n">
+        <v>3</v>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E296" t="n">
+        <v>47</v>
+      </c>
+      <c r="F296" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H296" t="n">
+        <v>3</v>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>32</v>
+      </c>
+      <c r="E297" t="n">
+        <v>55</v>
+      </c>
+      <c r="F297" t="n">
+        <v>0</v>
+      </c>
+      <c r="G297" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H297" t="n">
+        <v>3</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E298" t="n">
+        <v>97</v>
+      </c>
+      <c r="F298" t="n">
+        <v>0</v>
+      </c>
+      <c r="G298" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H298" t="n">
+        <v>2</v>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E299" t="n">
+        <v>97</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H299" t="n">
+        <v>1</v>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>27</v>
+      </c>
+      <c r="E300" t="n">
+        <v>85</v>
+      </c>
+      <c r="F300" t="n">
+        <v>0</v>
+      </c>
+      <c r="G300" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H300" t="n">
+        <v>3</v>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E301" t="n">
+        <v>74</v>
+      </c>
+      <c r="F301" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H301" t="n">
+        <v>3</v>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E302" t="n">
+        <v>100</v>
+      </c>
+      <c r="F302" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H302" t="n">
+        <v>3</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E303" t="n">
+        <v>87</v>
+      </c>
+      <c r="F303" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H303" t="n">
+        <v>3</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E304" t="n">
+        <v>97</v>
+      </c>
+      <c r="F304" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" t="n">
+        <v>5</v>
+      </c>
+      <c r="H304" t="n">
+        <v>3</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E305" t="n">
+        <v>74</v>
+      </c>
+      <c r="F305" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H305" t="n">
+        <v>2</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E306" t="n">
+        <v>95</v>
+      </c>
+      <c r="F306" t="n">
+        <v>0</v>
+      </c>
+      <c r="G306" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H306" t="n">
+        <v>3</v>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>26</v>
+      </c>
+      <c r="E307" t="n">
+        <v>92</v>
+      </c>
+      <c r="F307" t="n">
+        <v>0</v>
+      </c>
+      <c r="G307" t="n">
+        <v>5</v>
+      </c>
+      <c r="H307" t="n">
+        <v>3</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E308" t="n">
+        <v>89</v>
+      </c>
+      <c r="F308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H308" t="n">
+        <v>1</v>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E309" t="n">
+        <v>96</v>
+      </c>
+      <c r="F309" t="n">
+        <v>0</v>
+      </c>
+      <c r="G309" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H309" t="n">
+        <v>3</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E310" t="n">
+        <v>83</v>
+      </c>
+      <c r="F310" t="n">
+        <v>0</v>
+      </c>
+      <c r="G310" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H310" t="n">
+        <v>1</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E311" t="n">
+        <v>80</v>
+      </c>
+      <c r="F311" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H311" t="n">
+        <v>2</v>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E312" t="n">
+        <v>92</v>
+      </c>
+      <c r="F312" t="n">
+        <v>0</v>
+      </c>
+      <c r="G312" t="n">
+        <v>5</v>
+      </c>
+      <c r="H312" t="n">
+        <v>3</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E313" t="n">
+        <v>91</v>
+      </c>
+      <c r="F313" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H313" t="n">
+        <v>3</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E314" t="n">
+        <v>85</v>
+      </c>
+      <c r="F314" t="n">
+        <v>0</v>
+      </c>
+      <c r="G314" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H314" t="n">
+        <v>3</v>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E315" t="n">
+        <v>94</v>
+      </c>
+      <c r="F315" t="n">
+        <v>0</v>
+      </c>
+      <c r="G315" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H315" t="n">
+        <v>3</v>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>26</v>
+      </c>
+      <c r="E316" t="n">
+        <v>86</v>
+      </c>
+      <c r="F316" t="n">
+        <v>0</v>
+      </c>
+      <c r="G316" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H316" t="n">
+        <v>3</v>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E317" t="n">
+        <v>72</v>
+      </c>
+      <c r="F317" t="n">
+        <v>0</v>
+      </c>
+      <c r="G317" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H317" t="n">
+        <v>3</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E318" t="n">
+        <v>79</v>
+      </c>
+      <c r="F318" t="n">
+        <v>0</v>
+      </c>
+      <c r="G318" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H318" t="n">
+        <v>2</v>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>26</v>
+      </c>
+      <c r="E319" t="n">
+        <v>89</v>
+      </c>
+      <c r="F319" t="n">
+        <v>0</v>
+      </c>
+      <c r="G319" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H319" t="n">
+        <v>3</v>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E320" t="n">
+        <v>92</v>
+      </c>
+      <c r="F320" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H320" t="n">
+        <v>3</v>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>26</v>
+      </c>
+      <c r="E321" t="n">
+        <v>91</v>
+      </c>
+      <c r="F321" t="n">
+        <v>0</v>
+      </c>
+      <c r="G321" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H321" t="n">
+        <v>3</v>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E322" t="n">
+        <v>96</v>
+      </c>
+      <c r="F322" t="n">
+        <v>0</v>
+      </c>
+      <c r="G322" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H322" t="n">
+        <v>3</v>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E323" t="n">
+        <v>82</v>
+      </c>
+      <c r="F323" t="n">
+        <v>0</v>
+      </c>
+      <c r="G323" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H323" t="n">
+        <v>2</v>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E324" t="n">
+        <v>78</v>
+      </c>
+      <c r="F324" t="n">
+        <v>0</v>
+      </c>
+      <c r="G324" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H324" t="n">
+        <v>3</v>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>25</v>
+      </c>
+      <c r="E325" t="n">
+        <v>94</v>
+      </c>
+      <c r="F325" t="n">
+        <v>0</v>
+      </c>
+      <c r="G325" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H325" t="n">
+        <v>2</v>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E326" t="n">
+        <v>76</v>
+      </c>
+      <c r="F326" t="n">
+        <v>0</v>
+      </c>
+      <c r="G326" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H326" t="n">
+        <v>2</v>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E327" t="n">
+        <v>76</v>
+      </c>
+      <c r="F327" t="n">
+        <v>0</v>
+      </c>
+      <c r="G327" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H327" t="n">
+        <v>3</v>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E328" t="n">
+        <v>73</v>
+      </c>
+      <c r="F328" t="n">
+        <v>0</v>
+      </c>
+      <c r="G328" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H328" t="n">
+        <v>2</v>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E329" t="n">
+        <v>83</v>
+      </c>
+      <c r="F329" t="n">
+        <v>0</v>
+      </c>
+      <c r="G329" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H329" t="n">
+        <v>3</v>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E330" t="n">
+        <v>84</v>
+      </c>
+      <c r="F330" t="n">
+        <v>0</v>
+      </c>
+      <c r="G330" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H330" t="n">
+        <v>3</v>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
         </is>
       </c>
     </row>
@@ -8986,7 +12649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9060,6 +12723,11 @@
           <t>max_wind_speed_kmh</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>observation_time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9116,6 +12784,7 @@
       <c r="N2" t="n">
         <v>12.3</v>
       </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9172,6 +12841,7 @@
       <c r="N3" t="n">
         <v>11.2</v>
       </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9228,6 +12898,7 @@
       <c r="N4" t="n">
         <v>9</v>
       </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9284,6 +12955,7 @@
       <c r="N5" t="n">
         <v>19.8</v>
       </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9340,6 +13012,7 @@
       <c r="N6" t="n">
         <v>14.5</v>
       </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9356,7 +13029,7 @@
         <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>31.6</v>
+        <v>25.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -9364,43 +13037,44 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>35.6</v>
+        <v>28.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mulugu</t>
+          <t>Narayanpet</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>29.1</v>
+        <v>23.5</v>
       </c>
       <c r="I7" t="n">
-        <v>62.6</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Mahabubabad</t>
+          <t>Jogulamba Gadwal</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Mahabubabad</t>
+          <t>Jogulamba Gadwal</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>15.3</v>
-      </c>
+        <v>18.7</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -9412,7 +13086,7 @@
         <v>33</v>
       </c>
       <c r="D8" t="n">
-        <v>31.5</v>
+        <v>25.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -9420,37 +13094,286 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>34.4</v>
+        <v>28.2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rajanna Sircilla</t>
+          <t>Narayanpet</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>27.8</v>
+        <v>23.5</v>
       </c>
       <c r="I8" t="n">
-        <v>60.6</v>
+        <v>89.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Rajanna Sircilla</t>
+          <t>Wanaparthy</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Jangaon</t>
+          <t>Jogulamba Gadwal</t>
         </is>
       </c>
       <c r="N8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-09-19T23:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>33</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>18</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-09-19T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>33</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D11" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
         <v>10.1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-09-20T13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>33</v>
+      </c>
+      <c r="D12" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2026-09-20T22:15</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -9516,7 +13439,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29.3</v>
+        <v>27.7</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -9525,7 +13448,7 @@
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>72.7</v>
+        <v>83</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -9543,7 +13466,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30.6</v>
+        <v>28.9</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -9552,10 +13475,10 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>71.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -9570,19 +13493,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.2</v>
+        <v>28.7</v>
       </c>
       <c r="D4" t="n">
-        <v>32.9</v>
+        <v>33.5</v>
       </c>
       <c r="E4" t="n">
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>69.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -9597,19 +13520,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.6</v>
+        <v>28.8</v>
       </c>
       <c r="D5" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="E5" t="n">
         <v>24.8</v>
       </c>
       <c r="F5" t="n">
-        <v>54.9</v>
+        <v>65.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -9624,19 +13547,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29.1</v>
+        <v>27.6</v>
       </c>
       <c r="D6" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="E6" t="n">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>76.3</v>
+        <v>85.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -9651,19 +13574,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29.2</v>
+        <v>27.8</v>
       </c>
       <c r="D7" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>69.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9678,19 +13601,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.6</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>75</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -9705,19 +13628,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>31.2</v>
+        <v>28.3</v>
       </c>
       <c r="D9" t="n">
-        <v>35.2</v>
+        <v>34.2</v>
       </c>
       <c r="E9" t="n">
-        <v>25.8</v>
+        <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>55.7</v>
+        <v>69.7</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -9732,16 +13655,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27.5</v>
+        <v>26.1</v>
       </c>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>74.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -9759,19 +13682,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29.8</v>
+        <v>28.1</v>
       </c>
       <c r="D11" t="n">
-        <v>32.3</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>74.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -9786,7 +13709,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>31.4</v>
+        <v>29.6</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -9795,10 +13718,10 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>65.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -9813,7 +13736,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29.7</v>
+        <v>28.1</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -9822,10 +13745,10 @@
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>76.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
@@ -9840,7 +13763,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>30.2</v>
+        <v>28.7</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -9849,10 +13772,10 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>71.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -9867,19 +13790,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28.9</v>
+        <v>27.2</v>
       </c>
       <c r="D15" t="n">
-        <v>31.8</v>
+        <v>31.1</v>
       </c>
       <c r="E15" t="n">
-        <v>24.3</v>
+        <v>23.8</v>
       </c>
       <c r="F15" t="n">
-        <v>64.3</v>
+        <v>72.8</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -9894,19 +13817,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30.5</v>
+        <v>28.6</v>
       </c>
       <c r="D16" t="n">
-        <v>33.1</v>
+        <v>32.7</v>
       </c>
       <c r="E16" t="n">
-        <v>26.8</v>
+        <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>74.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -9921,16 +13844,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.9</v>
+        <v>26.5</v>
       </c>
       <c r="D17" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="E17" t="n">
-        <v>24.3</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>74.3</v>
+        <v>81.2</v>
       </c>
       <c r="G17" t="n">
         <v>0.5</v>
@@ -9948,16 +13871,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28.4</v>
+        <v>26.7</v>
       </c>
       <c r="D18" t="n">
-        <v>31.6</v>
+        <v>31.1</v>
       </c>
       <c r="E18" t="n">
         <v>23.9</v>
       </c>
       <c r="F18" t="n">
-        <v>66</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -9975,7 +13898,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>29.2</v>
+        <v>27.9</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -9984,10 +13907,10 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>75.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="20">
@@ -10002,19 +13925,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>29.9</v>
+        <v>27.8</v>
       </c>
       <c r="D20" t="n">
-        <v>33</v>
+        <v>32.2</v>
       </c>
       <c r="E20" t="n">
-        <v>24.7</v>
+        <v>24.1</v>
       </c>
       <c r="F20" t="n">
-        <v>61.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21">
@@ -10029,7 +13952,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>32.4</v>
+        <v>30.4</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -10038,7 +13961,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>55.9</v>
+        <v>65.2</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -10056,19 +13979,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>29.4</v>
+        <v>26.9</v>
       </c>
       <c r="D22" t="n">
-        <v>32.6</v>
+        <v>31.3</v>
       </c>
       <c r="E22" t="n">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>61.6</v>
+        <v>73.3</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="23">
@@ -10083,16 +14006,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.9</v>
+        <v>27.3</v>
       </c>
       <c r="D23" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="E23" t="n">
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>73.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
@@ -10110,16 +14033,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.9</v>
+        <v>26.5</v>
       </c>
       <c r="D24" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="E24" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>76.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="G24" t="n">
         <v>0.2</v>
@@ -10137,19 +14060,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>29.7</v>
+        <v>28.1</v>
       </c>
       <c r="D25" t="n">
-        <v>32.2</v>
+        <v>32</v>
       </c>
       <c r="E25" t="n">
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>76.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -10164,19 +14087,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.7</v>
+        <v>27.5</v>
       </c>
       <c r="D26" t="n">
         <v>31.1</v>
       </c>
       <c r="E26" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>75.7</v>
+        <v>83.5</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="27">
@@ -10191,16 +14114,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>28.5</v>
+        <v>26.8</v>
       </c>
       <c r="D27" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="E27" t="n">
         <v>24.2</v>
       </c>
       <c r="F27" t="n">
-        <v>65.3</v>
+        <v>73.5</v>
       </c>
       <c r="G27" t="n">
         <v>0.1</v>
@@ -10218,16 +14141,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>29</v>
+        <v>27.4</v>
       </c>
       <c r="D28" t="n">
-        <v>32.4</v>
+        <v>31.5</v>
       </c>
       <c r="E28" t="n">
         <v>24.5</v>
       </c>
       <c r="F28" t="n">
-        <v>64.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="G28" t="n">
         <v>0.2</v>
@@ -10245,16 +14168,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>28.3</v>
+        <v>26.7</v>
       </c>
       <c r="D29" t="n">
-        <v>30.6</v>
+        <v>30.2</v>
       </c>
       <c r="E29" t="n">
         <v>24.4</v>
       </c>
       <c r="F29" t="n">
-        <v>73.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0.1</v>
@@ -10272,16 +14195,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>31.5</v>
+        <v>29.7</v>
       </c>
       <c r="D30" t="n">
-        <v>34.8</v>
+        <v>34.5</v>
       </c>
       <c r="E30" t="n">
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>62.4</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -10299,19 +14222,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>28.2</v>
+        <v>26.6</v>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="E31" t="n">
         <v>23.9</v>
       </c>
       <c r="F31" t="n">
-        <v>64.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="32">
@@ -10326,19 +14249,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>30.3</v>
+        <v>28.4</v>
       </c>
       <c r="D32" t="n">
-        <v>33.3</v>
+        <v>32.1</v>
       </c>
       <c r="E32" t="n">
-        <v>26.4</v>
+        <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>58.1</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -10353,19 +14276,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>30.4</v>
+        <v>28.9</v>
       </c>
       <c r="D33" t="n">
-        <v>33.3</v>
+        <v>34.4</v>
       </c>
       <c r="E33" t="n">
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>67.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -10380,19 +14303,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>29.2</v>
+        <v>27.8</v>
       </c>
       <c r="D34" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="E34" t="n">
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>66.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I330"/>
+  <dimension ref="A1:I363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12635,6 +12635,1227 @@
       <c r="I330" t="inlineStr">
         <is>
           <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E331" t="n">
+        <v>90</v>
+      </c>
+      <c r="F331" t="n">
+        <v>0</v>
+      </c>
+      <c r="G331" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H331" t="n">
+        <v>3</v>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E332" t="n">
+        <v>78</v>
+      </c>
+      <c r="F332" t="n">
+        <v>0</v>
+      </c>
+      <c r="G332" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H332" t="n">
+        <v>3</v>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E333" t="n">
+        <v>88</v>
+      </c>
+      <c r="F333" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G333" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H333" t="n">
+        <v>53</v>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E334" t="n">
+        <v>75</v>
+      </c>
+      <c r="F334" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G334" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H334" t="n">
+        <v>51</v>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E335" t="n">
+        <v>93</v>
+      </c>
+      <c r="F335" t="n">
+        <v>0</v>
+      </c>
+      <c r="G335" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H335" t="n">
+        <v>3</v>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E336" t="n">
+        <v>86</v>
+      </c>
+      <c r="F336" t="n">
+        <v>0</v>
+      </c>
+      <c r="G336" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H336" t="n">
+        <v>3</v>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>28</v>
+      </c>
+      <c r="E337" t="n">
+        <v>87</v>
+      </c>
+      <c r="F337" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G337" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H337" t="n">
+        <v>95</v>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E338" t="n">
+        <v>49</v>
+      </c>
+      <c r="F338" t="n">
+        <v>0</v>
+      </c>
+      <c r="G338" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H338" t="n">
+        <v>3</v>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E339" t="n">
+        <v>89</v>
+      </c>
+      <c r="F339" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G339" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H339" t="n">
+        <v>95</v>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E340" t="n">
+        <v>81</v>
+      </c>
+      <c r="F340" t="n">
+        <v>0</v>
+      </c>
+      <c r="G340" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H340" t="n">
+        <v>3</v>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E341" t="n">
+        <v>70</v>
+      </c>
+      <c r="F341" t="n">
+        <v>0</v>
+      </c>
+      <c r="G341" t="n">
+        <v>11</v>
+      </c>
+      <c r="H341" t="n">
+        <v>3</v>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E342" t="n">
+        <v>80</v>
+      </c>
+      <c r="F342" t="n">
+        <v>0</v>
+      </c>
+      <c r="G342" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H342" t="n">
+        <v>3</v>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E343" t="n">
+        <v>76</v>
+      </c>
+      <c r="F343" t="n">
+        <v>0</v>
+      </c>
+      <c r="G343" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H343" t="n">
+        <v>3</v>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E344" t="n">
+        <v>80</v>
+      </c>
+      <c r="F344" t="n">
+        <v>0</v>
+      </c>
+      <c r="G344" t="n">
+        <v>9</v>
+      </c>
+      <c r="H344" t="n">
+        <v>3</v>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E345" t="n">
+        <v>81</v>
+      </c>
+      <c r="F345" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G345" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H345" t="n">
+        <v>51</v>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>26</v>
+      </c>
+      <c r="E346" t="n">
+        <v>91</v>
+      </c>
+      <c r="F346" t="n">
+        <v>0</v>
+      </c>
+      <c r="G346" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H346" t="n">
+        <v>3</v>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E347" t="n">
+        <v>80</v>
+      </c>
+      <c r="F347" t="n">
+        <v>0</v>
+      </c>
+      <c r="G347" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H347" t="n">
+        <v>3</v>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E348" t="n">
+        <v>85</v>
+      </c>
+      <c r="F348" t="n">
+        <v>0</v>
+      </c>
+      <c r="G348" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H348" t="n">
+        <v>2</v>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E349" t="n">
+        <v>70</v>
+      </c>
+      <c r="F349" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G349" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H349" t="n">
+        <v>51</v>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E350" t="n">
+        <v>73</v>
+      </c>
+      <c r="F350" t="n">
+        <v>0</v>
+      </c>
+      <c r="G350" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H350" t="n">
+        <v>2</v>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E351" t="n">
+        <v>72</v>
+      </c>
+      <c r="F351" t="n">
+        <v>0</v>
+      </c>
+      <c r="G351" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H351" t="n">
+        <v>3</v>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E352" t="n">
+        <v>85</v>
+      </c>
+      <c r="F352" t="n">
+        <v>0</v>
+      </c>
+      <c r="G352" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H352" t="n">
+        <v>3</v>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>27</v>
+      </c>
+      <c r="E353" t="n">
+        <v>85</v>
+      </c>
+      <c r="F353" t="n">
+        <v>0</v>
+      </c>
+      <c r="G353" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H353" t="n">
+        <v>2</v>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E354" t="n">
+        <v>89</v>
+      </c>
+      <c r="F354" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G354" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H354" t="n">
+        <v>51</v>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E355" t="n">
+        <v>87</v>
+      </c>
+      <c r="F355" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G355" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H355" t="n">
+        <v>51</v>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E356" t="n">
+        <v>78</v>
+      </c>
+      <c r="F356" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H356" t="n">
+        <v>0</v>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E357" t="n">
+        <v>79</v>
+      </c>
+      <c r="F357" t="n">
+        <v>0</v>
+      </c>
+      <c r="G357" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H357" t="n">
+        <v>3</v>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E358" t="n">
+        <v>85</v>
+      </c>
+      <c r="F358" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G358" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H358" t="n">
+        <v>55</v>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>30</v>
+      </c>
+      <c r="E359" t="n">
+        <v>71</v>
+      </c>
+      <c r="F359" t="n">
+        <v>0</v>
+      </c>
+      <c r="G359" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H359" t="n">
+        <v>3</v>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E360" t="n">
+        <v>85</v>
+      </c>
+      <c r="F360" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G360" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H360" t="n">
+        <v>51</v>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E361" t="n">
+        <v>70</v>
+      </c>
+      <c r="F361" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G361" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H361" t="n">
+        <v>51</v>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E362" t="n">
+        <v>82</v>
+      </c>
+      <c r="F362" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G362" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H362" t="n">
+        <v>51</v>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E363" t="n">
+        <v>85</v>
+      </c>
+      <c r="F363" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G363" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H363" t="n">
+        <v>95</v>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
         </is>
       </c>
     </row>
@@ -12649,7 +13870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13373,6 +14594,67 @@
       <c r="O12" t="inlineStr">
         <is>
           <t>2026-09-20T22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>33</v>
+      </c>
+      <c r="D13" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2026-09-21T17:30</t>
         </is>
       </c>
     </row>
@@ -13448,7 +14730,7 @@
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>83</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -13475,7 +14757,7 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>80.7</v>
+        <v>80.5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -13493,7 +14775,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -13502,10 +14784,10 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>76.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -13520,7 +14802,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -13529,10 +14811,10 @@
         <v>24.8</v>
       </c>
       <c r="F5" t="n">
-        <v>65.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
@@ -13547,7 +14829,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -13556,7 +14838,7 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>85.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>0.1</v>
@@ -13574,7 +14856,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -13583,7 +14865,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>77.7</v>
+        <v>78.5</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -13610,10 +14892,10 @@
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -13628,7 +14910,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.3</v>
+        <v>28.7</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -13637,7 +14919,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>69.7</v>
+        <v>67.8</v>
       </c>
       <c r="G9" t="n">
         <v>2.4</v>
@@ -13655,7 +14937,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
         <v>29.9</v>
@@ -13664,10 +14946,10 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>83.2</v>
+        <v>83.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11">
@@ -13691,7 +14973,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -13709,7 +14991,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -13718,7 +15000,7 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>74.7</v>
+        <v>74.3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -13745,7 +15027,7 @@
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>84.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="G13" t="n">
         <v>0.1</v>
@@ -13772,7 +15054,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>78.8</v>
+        <v>78.5</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -13799,7 +15081,7 @@
         <v>23.8</v>
       </c>
       <c r="F15" t="n">
-        <v>72.8</v>
+        <v>73.5</v>
       </c>
       <c r="G15" t="n">
         <v>0.1</v>
@@ -13826,10 +15108,10 @@
         <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="17">
@@ -13853,7 +15135,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>81.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>0.5</v>
@@ -13880,7 +15162,7 @@
         <v>23.9</v>
       </c>
       <c r="F18" t="n">
-        <v>76.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -13907,7 +15189,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>81.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="G19" t="n">
         <v>0.1</v>
@@ -13925,7 +15207,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -13934,10 +15216,10 @@
         <v>24.1</v>
       </c>
       <c r="F20" t="n">
-        <v>71.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
@@ -13961,7 +15243,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>65.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -13979,7 +15261,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="D22" t="n">
         <v>31.3</v>
@@ -13988,7 +15270,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>73.3</v>
+        <v>73.2</v>
       </c>
       <c r="G22" t="n">
         <v>1.7</v>
@@ -14006,7 +15288,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="D23" t="n">
         <v>30.7</v>
@@ -14015,7 +15297,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>81.5</v>
+        <v>81.8</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
@@ -14033,7 +15315,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -14042,7 +15324,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0.2</v>
@@ -14069,10 +15351,10 @@
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>83.3</v>
+        <v>83.8</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26">
@@ -14096,10 +15378,10 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>83.5</v>
+        <v>83.8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="27">
@@ -14114,7 +15396,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="D27" t="n">
         <v>30.5</v>
@@ -14123,7 +15405,7 @@
         <v>24.2</v>
       </c>
       <c r="F27" t="n">
-        <v>73.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>0.1</v>
@@ -14150,7 +15432,7 @@
         <v>24.5</v>
       </c>
       <c r="F28" t="n">
-        <v>74.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G28" t="n">
         <v>0.2</v>
@@ -14168,7 +15450,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
@@ -14177,10 +15459,10 @@
         <v>24.4</v>
       </c>
       <c r="F29" t="n">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="30">
@@ -14231,10 +15513,10 @@
         <v>23.9</v>
       </c>
       <c r="F31" t="n">
-        <v>73.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="32">
@@ -14258,10 +15540,10 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>67.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="33">
@@ -14276,7 +15558,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -14285,10 +15567,10 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>74.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="34">
@@ -14303,7 +15585,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -14312,10 +15594,10 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>74.5</v>
+        <v>75.5</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I363"/>
+  <dimension ref="A1:I396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13856,6 +13856,1227 @@
       <c r="I363" t="inlineStr">
         <is>
           <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E364" t="n">
+        <v>96</v>
+      </c>
+      <c r="F364" t="n">
+        <v>0</v>
+      </c>
+      <c r="G364" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H364" t="n">
+        <v>1</v>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E365" t="n">
+        <v>87</v>
+      </c>
+      <c r="F365" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H365" t="n">
+        <v>3</v>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E366" t="n">
+        <v>90</v>
+      </c>
+      <c r="F366" t="n">
+        <v>0</v>
+      </c>
+      <c r="G366" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H366" t="n">
+        <v>3</v>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E367" t="n">
+        <v>90</v>
+      </c>
+      <c r="F367" t="n">
+        <v>0</v>
+      </c>
+      <c r="G367" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H367" t="n">
+        <v>3</v>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E368" t="n">
+        <v>95</v>
+      </c>
+      <c r="F368" t="n">
+        <v>0</v>
+      </c>
+      <c r="G368" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H368" t="n">
+        <v>3</v>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D369" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E369" t="n">
+        <v>90</v>
+      </c>
+      <c r="F369" t="n">
+        <v>0</v>
+      </c>
+      <c r="G369" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H369" t="n">
+        <v>2</v>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D370" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E370" t="n">
+        <v>95</v>
+      </c>
+      <c r="F370" t="n">
+        <v>0</v>
+      </c>
+      <c r="G370" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H370" t="n">
+        <v>3</v>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D371" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E371" t="n">
+        <v>93</v>
+      </c>
+      <c r="F371" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G371" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H371" t="n">
+        <v>55</v>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D372" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E372" t="n">
+        <v>94</v>
+      </c>
+      <c r="F372" t="n">
+        <v>0</v>
+      </c>
+      <c r="G372" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H372" t="n">
+        <v>3</v>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D373" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E373" t="n">
+        <v>92</v>
+      </c>
+      <c r="F373" t="n">
+        <v>0</v>
+      </c>
+      <c r="G373" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H373" t="n">
+        <v>2</v>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D374" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E374" t="n">
+        <v>86</v>
+      </c>
+      <c r="F374" t="n">
+        <v>0</v>
+      </c>
+      <c r="G374" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H374" t="n">
+        <v>3</v>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E375" t="n">
+        <v>96</v>
+      </c>
+      <c r="F375" t="n">
+        <v>0</v>
+      </c>
+      <c r="G375" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H375" t="n">
+        <v>3</v>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D376" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E376" t="n">
+        <v>92</v>
+      </c>
+      <c r="F376" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H376" t="n">
+        <v>3</v>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D377" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="E377" t="n">
+        <v>99</v>
+      </c>
+      <c r="F377" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G377" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H377" t="n">
+        <v>51</v>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E378" t="n">
+        <v>92</v>
+      </c>
+      <c r="F378" t="n">
+        <v>0</v>
+      </c>
+      <c r="G378" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H378" t="n">
+        <v>3</v>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E379" t="n">
+        <v>98</v>
+      </c>
+      <c r="F379" t="n">
+        <v>0</v>
+      </c>
+      <c r="G379" t="n">
+        <v>4</v>
+      </c>
+      <c r="H379" t="n">
+        <v>2</v>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D380" t="n">
+        <v>24</v>
+      </c>
+      <c r="E380" t="n">
+        <v>93</v>
+      </c>
+      <c r="F380" t="n">
+        <v>0</v>
+      </c>
+      <c r="G380" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H380" t="n">
+        <v>3</v>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>26</v>
+      </c>
+      <c r="E381" t="n">
+        <v>92</v>
+      </c>
+      <c r="F381" t="n">
+        <v>0</v>
+      </c>
+      <c r="G381" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H381" t="n">
+        <v>3</v>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D382" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E382" t="n">
+        <v>97</v>
+      </c>
+      <c r="F382" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G382" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H382" t="n">
+        <v>55</v>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E383" t="n">
+        <v>83</v>
+      </c>
+      <c r="F383" t="n">
+        <v>0</v>
+      </c>
+      <c r="G383" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H383" t="n">
+        <v>3</v>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E384" t="n">
+        <v>96</v>
+      </c>
+      <c r="F384" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G384" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H384" t="n">
+        <v>55</v>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E385" t="n">
+        <v>88</v>
+      </c>
+      <c r="F385" t="n">
+        <v>0</v>
+      </c>
+      <c r="G385" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H385" t="n">
+        <v>1</v>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>25</v>
+      </c>
+      <c r="E386" t="n">
+        <v>96</v>
+      </c>
+      <c r="F386" t="n">
+        <v>0</v>
+      </c>
+      <c r="G386" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H386" t="n">
+        <v>0</v>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E387" t="n">
+        <v>96</v>
+      </c>
+      <c r="F387" t="n">
+        <v>0</v>
+      </c>
+      <c r="G387" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H387" t="n">
+        <v>3</v>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E388" t="n">
+        <v>94</v>
+      </c>
+      <c r="F388" t="n">
+        <v>0</v>
+      </c>
+      <c r="G388" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H388" t="n">
+        <v>3</v>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>24</v>
+      </c>
+      <c r="E389" t="n">
+        <v>92</v>
+      </c>
+      <c r="F389" t="n">
+        <v>0</v>
+      </c>
+      <c r="G389" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H389" t="n">
+        <v>3</v>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E390" t="n">
+        <v>95</v>
+      </c>
+      <c r="F390" t="n">
+        <v>0</v>
+      </c>
+      <c r="G390" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H390" t="n">
+        <v>3</v>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E391" t="n">
+        <v>93</v>
+      </c>
+      <c r="F391" t="n">
+        <v>0</v>
+      </c>
+      <c r="G391" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H391" t="n">
+        <v>3</v>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E392" t="n">
+        <v>88</v>
+      </c>
+      <c r="F392" t="n">
+        <v>0</v>
+      </c>
+      <c r="G392" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H392" t="n">
+        <v>3</v>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E393" t="n">
+        <v>98</v>
+      </c>
+      <c r="F393" t="n">
+        <v>0</v>
+      </c>
+      <c r="G393" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H393" t="n">
+        <v>3</v>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E394" t="n">
+        <v>96</v>
+      </c>
+      <c r="F394" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G394" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H394" t="n">
+        <v>55</v>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E395" t="n">
+        <v>88</v>
+      </c>
+      <c r="F395" t="n">
+        <v>0</v>
+      </c>
+      <c r="G395" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H395" t="n">
+        <v>3</v>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E396" t="n">
+        <v>94</v>
+      </c>
+      <c r="F396" t="n">
+        <v>0</v>
+      </c>
+      <c r="G396" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H396" t="n">
+        <v>3</v>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
         </is>
       </c>
     </row>
@@ -13870,7 +15091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14655,6 +15876,67 @@
       <c r="O13" t="inlineStr">
         <is>
           <t>2026-09-21T17:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>33</v>
+      </c>
+      <c r="D14" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:00</t>
         </is>
       </c>
     </row>
@@ -14721,7 +16003,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -14730,7 +16012,7 @@
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>83.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -14748,7 +16030,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -14757,7 +16039,7 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>80.5</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -14775,7 +16057,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -14784,7 +16066,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>77.5</v>
+        <v>78.5</v>
       </c>
       <c r="G4" t="n">
         <v>0.2</v>
@@ -14802,7 +16084,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.7</v>
+        <v>28.4</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -14811,7 +16093,7 @@
         <v>24.8</v>
       </c>
       <c r="F5" t="n">
-        <v>66.09999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>0.3</v>
@@ -14829,7 +16111,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -14838,7 +16120,7 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>85.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="G6" t="n">
         <v>0.1</v>
@@ -14856,7 +16138,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -14865,7 +16147,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>78.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -14883,7 +16165,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -14892,7 +16174,7 @@
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G8" t="n">
         <v>0.1</v>
@@ -14910,7 +16192,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.7</v>
+        <v>28.3</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -14919,10 +16201,10 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>67.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
@@ -14937,7 +16219,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="D10" t="n">
         <v>29.9</v>
@@ -14946,7 +16228,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>83.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>1.3</v>
@@ -14964,7 +16246,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -14973,7 +16255,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>82.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -14991,7 +16273,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -15000,7 +16282,7 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -15018,7 +16300,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -15027,7 +16309,7 @@
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>84.2</v>
+        <v>85.2</v>
       </c>
       <c r="G13" t="n">
         <v>0.1</v>
@@ -15045,7 +16327,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -15054,7 +16336,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>78.5</v>
+        <v>79.7</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -15072,19 +16354,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.2</v>
+        <v>26.8</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
       </c>
       <c r="E15" t="n">
-        <v>23.8</v>
+        <v>22.1</v>
       </c>
       <c r="F15" t="n">
-        <v>73.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16">
@@ -15099,7 +16381,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -15108,7 +16390,7 @@
         <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>82</v>
+        <v>82.8</v>
       </c>
       <c r="G16" t="n">
         <v>0.1</v>
@@ -15126,7 +16408,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="D17" t="n">
         <v>30.2</v>
@@ -15135,7 +16417,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>82.09999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>0.5</v>
@@ -15153,7 +16435,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.7</v>
+        <v>26.4</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -15162,7 +16444,7 @@
         <v>23.9</v>
       </c>
       <c r="F18" t="n">
-        <v>76.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -15180,7 +16462,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -15189,7 +16471,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>81.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0.1</v>
@@ -15207,19 +16489,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.9</v>
+        <v>27.4</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
       </c>
       <c r="E20" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="F20" t="n">
-        <v>71</v>
+        <v>73.2</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="21">
@@ -15234,7 +16516,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -15243,7 +16525,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>65.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -15261,7 +16543,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27</v>
+        <v>26.7</v>
       </c>
       <c r="D22" t="n">
         <v>31.3</v>
@@ -15270,10 +16552,10 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>73.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -15288,7 +16570,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D23" t="n">
         <v>30.7</v>
@@ -15297,7 +16579,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>81.8</v>
+        <v>82.3</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
@@ -15315,7 +16597,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -15324,7 +16606,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>84.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="G24" t="n">
         <v>0.2</v>
@@ -15342,7 +16624,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -15351,7 +16633,7 @@
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>83.8</v>
+        <v>84.8</v>
       </c>
       <c r="G25" t="n">
         <v>0.1</v>
@@ -15369,7 +16651,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="D26" t="n">
         <v>31.1</v>
@@ -15378,7 +16660,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>83.8</v>
+        <v>84.7</v>
       </c>
       <c r="G26" t="n">
         <v>0.2</v>
@@ -15396,16 +16678,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="D27" t="n">
         <v>30.5</v>
       </c>
       <c r="E27" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="F27" t="n">
-        <v>73.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>0.1</v>
@@ -15423,16 +16705,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.4</v>
+        <v>27.1</v>
       </c>
       <c r="D28" t="n">
         <v>31.5</v>
       </c>
       <c r="E28" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="F28" t="n">
-        <v>74.59999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="G28" t="n">
         <v>0.2</v>
@@ -15450,7 +16732,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
@@ -15459,7 +16741,7 @@
         <v>24.4</v>
       </c>
       <c r="F29" t="n">
-        <v>82.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="G29" t="n">
         <v>0.4</v>
@@ -15477,7 +16759,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -15486,7 +16768,7 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>70.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -15504,16 +16786,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.6</v>
+        <v>26.3</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
       </c>
       <c r="E31" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="F31" t="n">
-        <v>74.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>0.3</v>
@@ -15531,19 +16813,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28.4</v>
+        <v>28</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
       </c>
       <c r="E32" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="F32" t="n">
-        <v>67.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="G32" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="33">
@@ -15558,7 +16840,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -15567,7 +16849,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>75.3</v>
+        <v>76.3</v>
       </c>
       <c r="G33" t="n">
         <v>0.1</v>
@@ -15585,7 +16867,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.7</v>
+        <v>27.4</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -15594,7 +16876,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>75.5</v>
+        <v>77</v>
       </c>
       <c r="G34" t="n">
         <v>0.4</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I396"/>
+  <dimension ref="A1:I429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15077,6 +15077,1227 @@
       <c r="I396" t="inlineStr">
         <is>
           <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E397" t="n">
+        <v>93</v>
+      </c>
+      <c r="F397" t="n">
+        <v>0</v>
+      </c>
+      <c r="G397" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H397" t="n">
+        <v>3</v>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E398" t="n">
+        <v>83</v>
+      </c>
+      <c r="F398" t="n">
+        <v>0</v>
+      </c>
+      <c r="G398" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H398" t="n">
+        <v>3</v>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>26</v>
+      </c>
+      <c r="E399" t="n">
+        <v>85</v>
+      </c>
+      <c r="F399" t="n">
+        <v>0</v>
+      </c>
+      <c r="G399" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H399" t="n">
+        <v>3</v>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E400" t="n">
+        <v>91</v>
+      </c>
+      <c r="F400" t="n">
+        <v>0</v>
+      </c>
+      <c r="G400" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H400" t="n">
+        <v>2</v>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>25</v>
+      </c>
+      <c r="E401" t="n">
+        <v>94</v>
+      </c>
+      <c r="F401" t="n">
+        <v>0</v>
+      </c>
+      <c r="G401" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H401" t="n">
+        <v>3</v>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E402" t="n">
+        <v>86</v>
+      </c>
+      <c r="F402" t="n">
+        <v>0</v>
+      </c>
+      <c r="G402" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H402" t="n">
+        <v>3</v>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E403" t="n">
+        <v>93</v>
+      </c>
+      <c r="F403" t="n">
+        <v>0</v>
+      </c>
+      <c r="G403" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H403" t="n">
+        <v>3</v>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E404" t="n">
+        <v>91</v>
+      </c>
+      <c r="F404" t="n">
+        <v>0</v>
+      </c>
+      <c r="G404" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H404" t="n">
+        <v>2</v>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E405" t="n">
+        <v>94</v>
+      </c>
+      <c r="F405" t="n">
+        <v>0</v>
+      </c>
+      <c r="G405" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H405" t="n">
+        <v>2</v>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E406" t="n">
+        <v>87</v>
+      </c>
+      <c r="F406" t="n">
+        <v>0</v>
+      </c>
+      <c r="G406" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H406" t="n">
+        <v>3</v>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E407" t="n">
+        <v>80</v>
+      </c>
+      <c r="F407" t="n">
+        <v>0</v>
+      </c>
+      <c r="G407" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H407" t="n">
+        <v>3</v>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E408" t="n">
+        <v>93</v>
+      </c>
+      <c r="F408" t="n">
+        <v>0</v>
+      </c>
+      <c r="G408" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H408" t="n">
+        <v>3</v>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E409" t="n">
+        <v>86</v>
+      </c>
+      <c r="F409" t="n">
+        <v>0</v>
+      </c>
+      <c r="G409" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H409" t="n">
+        <v>3</v>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E410" t="n">
+        <v>90</v>
+      </c>
+      <c r="F410" t="n">
+        <v>0</v>
+      </c>
+      <c r="G410" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H410" t="n">
+        <v>2</v>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E411" t="n">
+        <v>94</v>
+      </c>
+      <c r="F411" t="n">
+        <v>0</v>
+      </c>
+      <c r="G411" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H411" t="n">
+        <v>3</v>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E412" t="n">
+        <v>97</v>
+      </c>
+      <c r="F412" t="n">
+        <v>0</v>
+      </c>
+      <c r="G412" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H412" t="n">
+        <v>2</v>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E413" t="n">
+        <v>94</v>
+      </c>
+      <c r="F413" t="n">
+        <v>0</v>
+      </c>
+      <c r="G413" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H413" t="n">
+        <v>2</v>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E414" t="n">
+        <v>91</v>
+      </c>
+      <c r="F414" t="n">
+        <v>0</v>
+      </c>
+      <c r="G414" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H414" t="n">
+        <v>3</v>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E415" t="n">
+        <v>90</v>
+      </c>
+      <c r="F415" t="n">
+        <v>0</v>
+      </c>
+      <c r="G415" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H415" t="n">
+        <v>3</v>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>27</v>
+      </c>
+      <c r="E416" t="n">
+        <v>80</v>
+      </c>
+      <c r="F416" t="n">
+        <v>0</v>
+      </c>
+      <c r="G416" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H416" t="n">
+        <v>3</v>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E417" t="n">
+        <v>85</v>
+      </c>
+      <c r="F417" t="n">
+        <v>0</v>
+      </c>
+      <c r="G417" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H417" t="n">
+        <v>2</v>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E418" t="n">
+        <v>91</v>
+      </c>
+      <c r="F418" t="n">
+        <v>0</v>
+      </c>
+      <c r="G418" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H418" t="n">
+        <v>3</v>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E419" t="n">
+        <v>98</v>
+      </c>
+      <c r="F419" t="n">
+        <v>0</v>
+      </c>
+      <c r="G419" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H419" t="n">
+        <v>2</v>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E420" t="n">
+        <v>91</v>
+      </c>
+      <c r="F420" t="n">
+        <v>0</v>
+      </c>
+      <c r="G420" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H420" t="n">
+        <v>3</v>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E421" t="n">
+        <v>91</v>
+      </c>
+      <c r="F421" t="n">
+        <v>0</v>
+      </c>
+      <c r="G421" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H421" t="n">
+        <v>3</v>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E422" t="n">
+        <v>92</v>
+      </c>
+      <c r="F422" t="n">
+        <v>0</v>
+      </c>
+      <c r="G422" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H422" t="n">
+        <v>3</v>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E423" t="n">
+        <v>89</v>
+      </c>
+      <c r="F423" t="n">
+        <v>0</v>
+      </c>
+      <c r="G423" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H423" t="n">
+        <v>1</v>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E424" t="n">
+        <v>91</v>
+      </c>
+      <c r="F424" t="n">
+        <v>0</v>
+      </c>
+      <c r="G424" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H424" t="n">
+        <v>3</v>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E425" t="n">
+        <v>80</v>
+      </c>
+      <c r="F425" t="n">
+        <v>0</v>
+      </c>
+      <c r="G425" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H425" t="n">
+        <v>3</v>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E426" t="n">
+        <v>96</v>
+      </c>
+      <c r="F426" t="n">
+        <v>0</v>
+      </c>
+      <c r="G426" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H426" t="n">
+        <v>2</v>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E427" t="n">
+        <v>93</v>
+      </c>
+      <c r="F427" t="n">
+        <v>0</v>
+      </c>
+      <c r="G427" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H427" t="n">
+        <v>3</v>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E428" t="n">
+        <v>84</v>
+      </c>
+      <c r="F428" t="n">
+        <v>0</v>
+      </c>
+      <c r="G428" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H428" t="n">
+        <v>3</v>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E429" t="n">
+        <v>87</v>
+      </c>
+      <c r="F429" t="n">
+        <v>0</v>
+      </c>
+      <c r="G429" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H429" t="n">
+        <v>3</v>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
         </is>
       </c>
     </row>
@@ -15091,7 +16312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15937,6 +17158,67 @@
       <c r="O14" t="inlineStr">
         <is>
           <t>2026-09-22T00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D15" t="n">
+        <v>25</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-09-22T03:45</t>
         </is>
       </c>
     </row>
@@ -16003,7 +17285,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -16012,7 +17294,7 @@
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>84.7</v>
+        <v>85.3</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -16030,7 +17312,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -16039,7 +17321,7 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>81.2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -16057,7 +17339,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -16066,7 +17348,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>78.5</v>
+        <v>79</v>
       </c>
       <c r="G4" t="n">
         <v>0.2</v>
@@ -16084,16 +17366,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
       </c>
       <c r="E5" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="F5" t="n">
-        <v>68.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="G5" t="n">
         <v>0.3</v>
@@ -16111,16 +17393,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>86.7</v>
+        <v>87.2</v>
       </c>
       <c r="G6" t="n">
         <v>0.1</v>
@@ -16138,7 +17420,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -16147,7 +17429,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>79.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -16165,7 +17447,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -16174,7 +17456,7 @@
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>84.7</v>
       </c>
       <c r="G8" t="n">
         <v>0.1</v>
@@ -16192,7 +17474,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.3</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -16201,7 +17483,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>69.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="G9" t="n">
         <v>2.7</v>
@@ -16219,7 +17501,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="D10" t="n">
         <v>29.9</v>
@@ -16228,7 +17510,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>84.59999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="G10" t="n">
         <v>1.3</v>
@@ -16246,7 +17528,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -16255,7 +17537,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>82.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -16273,7 +17555,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -16282,7 +17564,7 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>75.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -16300,7 +17582,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -16309,7 +17591,7 @@
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>85.2</v>
+        <v>85.8</v>
       </c>
       <c r="G13" t="n">
         <v>0.1</v>
@@ -16327,7 +17609,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -16336,7 +17618,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>79.7</v>
+        <v>80.2</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -16354,7 +17636,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.8</v>
+        <v>26.5</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -16363,7 +17645,7 @@
         <v>22.1</v>
       </c>
       <c r="F15" t="n">
-        <v>75.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="G15" t="n">
         <v>0.2</v>
@@ -16381,16 +17663,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
       </c>
       <c r="E16" t="n">
-        <v>26</v>
+        <v>25.7</v>
       </c>
       <c r="F16" t="n">
-        <v>82.8</v>
+        <v>83.7</v>
       </c>
       <c r="G16" t="n">
         <v>0.1</v>
@@ -16408,16 +17690,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="D17" t="n">
         <v>30.2</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>23.6</v>
       </c>
       <c r="F17" t="n">
-        <v>83.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="G17" t="n">
         <v>0.5</v>
@@ -16435,16 +17717,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
       </c>
       <c r="E18" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="F18" t="n">
-        <v>78.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -16462,7 +17744,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -16471,7 +17753,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>82.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="G19" t="n">
         <v>0.1</v>
@@ -16489,7 +17771,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -16498,7 +17780,7 @@
         <v>22.9</v>
       </c>
       <c r="F20" t="n">
-        <v>73.2</v>
+        <v>74.5</v>
       </c>
       <c r="G20" t="n">
         <v>0.8</v>
@@ -16516,7 +17798,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -16525,7 +17807,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>67.3</v>
+        <v>68.3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -16543,7 +17825,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="D22" t="n">
         <v>31.3</v>
@@ -16552,7 +17834,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>75.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -16570,7 +17852,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="D23" t="n">
         <v>30.7</v>
@@ -16579,7 +17861,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>82.3</v>
+        <v>83</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
@@ -16597,7 +17879,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -16606,7 +17888,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>85.3</v>
+        <v>86.3</v>
       </c>
       <c r="G24" t="n">
         <v>0.2</v>
@@ -16624,7 +17906,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -16633,7 +17915,7 @@
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>84.8</v>
+        <v>85.3</v>
       </c>
       <c r="G25" t="n">
         <v>0.1</v>
@@ -16651,16 +17933,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="D26" t="n">
         <v>31.1</v>
       </c>
       <c r="E26" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="F26" t="n">
-        <v>84.7</v>
+        <v>85.2</v>
       </c>
       <c r="G26" t="n">
         <v>0.2</v>
@@ -16678,16 +17960,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="D27" t="n">
         <v>30.5</v>
       </c>
       <c r="E27" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="F27" t="n">
-        <v>75.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="G27" t="n">
         <v>0.1</v>
@@ -16705,16 +17987,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="D28" t="n">
         <v>31.5</v>
       </c>
       <c r="E28" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="F28" t="n">
-        <v>76.3</v>
+        <v>77.3</v>
       </c>
       <c r="G28" t="n">
         <v>0.2</v>
@@ -16732,16 +18014,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
       </c>
       <c r="E29" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>83.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>0.4</v>
@@ -16759,7 +18041,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -16768,7 +18050,7 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>72.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -16786,16 +18068,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.3</v>
+        <v>26</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
       </c>
       <c r="E31" t="n">
-        <v>23.5</v>
+        <v>22.4</v>
       </c>
       <c r="F31" t="n">
-        <v>76.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>0.3</v>
@@ -16813,7 +18095,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28</v>
+        <v>27.7</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -16822,7 +18104,7 @@
         <v>23.7</v>
       </c>
       <c r="F32" t="n">
-        <v>70</v>
+        <v>71.8</v>
       </c>
       <c r="G32" t="n">
         <v>2.4</v>
@@ -16840,7 +18122,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -16849,7 +18131,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>76.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0.1</v>
@@ -16867,7 +18149,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -16876,7 +18158,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>77</v>
+        <v>77.8</v>
       </c>
       <c r="G34" t="n">
         <v>0.4</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I429"/>
+  <dimension ref="A1:I462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16298,6 +16298,1227 @@
       <c r="I429" t="inlineStr">
         <is>
           <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>24</v>
+      </c>
+      <c r="E430" t="n">
+        <v>99</v>
+      </c>
+      <c r="F430" t="n">
+        <v>0</v>
+      </c>
+      <c r="G430" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H430" t="n">
+        <v>3</v>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E431" t="n">
+        <v>83</v>
+      </c>
+      <c r="F431" t="n">
+        <v>0</v>
+      </c>
+      <c r="G431" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H431" t="n">
+        <v>3</v>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E432" t="n">
+        <v>85</v>
+      </c>
+      <c r="F432" t="n">
+        <v>0</v>
+      </c>
+      <c r="G432" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H432" t="n">
+        <v>3</v>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E433" t="n">
+        <v>88</v>
+      </c>
+      <c r="F433" t="n">
+        <v>0</v>
+      </c>
+      <c r="G433" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H433" t="n">
+        <v>3</v>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E434" t="n">
+        <v>94</v>
+      </c>
+      <c r="F434" t="n">
+        <v>0</v>
+      </c>
+      <c r="G434" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H434" t="n">
+        <v>1</v>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E435" t="n">
+        <v>84</v>
+      </c>
+      <c r="F435" t="n">
+        <v>0</v>
+      </c>
+      <c r="G435" t="n">
+        <v>13</v>
+      </c>
+      <c r="H435" t="n">
+        <v>3</v>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E436" t="n">
+        <v>90</v>
+      </c>
+      <c r="F436" t="n">
+        <v>0</v>
+      </c>
+      <c r="G436" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H436" t="n">
+        <v>3</v>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E437" t="n">
+        <v>89</v>
+      </c>
+      <c r="F437" t="n">
+        <v>0</v>
+      </c>
+      <c r="G437" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H437" t="n">
+        <v>3</v>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E438" t="n">
+        <v>91</v>
+      </c>
+      <c r="F438" t="n">
+        <v>0</v>
+      </c>
+      <c r="G438" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H438" t="n">
+        <v>2</v>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E439" t="n">
+        <v>86</v>
+      </c>
+      <c r="F439" t="n">
+        <v>0</v>
+      </c>
+      <c r="G439" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H439" t="n">
+        <v>3</v>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E440" t="n">
+        <v>81</v>
+      </c>
+      <c r="F440" t="n">
+        <v>0</v>
+      </c>
+      <c r="G440" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H440" t="n">
+        <v>3</v>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E441" t="n">
+        <v>87</v>
+      </c>
+      <c r="F441" t="n">
+        <v>0</v>
+      </c>
+      <c r="G441" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H441" t="n">
+        <v>2</v>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E442" t="n">
+        <v>86</v>
+      </c>
+      <c r="F442" t="n">
+        <v>0</v>
+      </c>
+      <c r="G442" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H442" t="n">
+        <v>3</v>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E443" t="n">
+        <v>89</v>
+      </c>
+      <c r="F443" t="n">
+        <v>0</v>
+      </c>
+      <c r="G443" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H443" t="n">
+        <v>3</v>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E444" t="n">
+        <v>87</v>
+      </c>
+      <c r="F444" t="n">
+        <v>0</v>
+      </c>
+      <c r="G444" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H444" t="n">
+        <v>3</v>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E445" t="n">
+        <v>95</v>
+      </c>
+      <c r="F445" t="n">
+        <v>0</v>
+      </c>
+      <c r="G445" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H445" t="n">
+        <v>3</v>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E446" t="n">
+        <v>93</v>
+      </c>
+      <c r="F446" t="n">
+        <v>0</v>
+      </c>
+      <c r="G446" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H446" t="n">
+        <v>3</v>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E447" t="n">
+        <v>90</v>
+      </c>
+      <c r="F447" t="n">
+        <v>0</v>
+      </c>
+      <c r="G447" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H447" t="n">
+        <v>3</v>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E448" t="n">
+        <v>91</v>
+      </c>
+      <c r="F448" t="n">
+        <v>0</v>
+      </c>
+      <c r="G448" t="n">
+        <v>13</v>
+      </c>
+      <c r="H448" t="n">
+        <v>3</v>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E449" t="n">
+        <v>79</v>
+      </c>
+      <c r="F449" t="n">
+        <v>0</v>
+      </c>
+      <c r="G449" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H449" t="n">
+        <v>3</v>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E450" t="n">
+        <v>86</v>
+      </c>
+      <c r="F450" t="n">
+        <v>0</v>
+      </c>
+      <c r="G450" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H450" t="n">
+        <v>2</v>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E451" t="n">
+        <v>88</v>
+      </c>
+      <c r="F451" t="n">
+        <v>0</v>
+      </c>
+      <c r="G451" t="n">
+        <v>8</v>
+      </c>
+      <c r="H451" t="n">
+        <v>0</v>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E452" t="n">
+        <v>95</v>
+      </c>
+      <c r="F452" t="n">
+        <v>0</v>
+      </c>
+      <c r="G452" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H452" t="n">
+        <v>2</v>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E453" t="n">
+        <v>89</v>
+      </c>
+      <c r="F453" t="n">
+        <v>0</v>
+      </c>
+      <c r="G453" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H453" t="n">
+        <v>3</v>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E454" t="n">
+        <v>89</v>
+      </c>
+      <c r="F454" t="n">
+        <v>0</v>
+      </c>
+      <c r="G454" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H454" t="n">
+        <v>3</v>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E455" t="n">
+        <v>91</v>
+      </c>
+      <c r="F455" t="n">
+        <v>0</v>
+      </c>
+      <c r="G455" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H455" t="n">
+        <v>2</v>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E456" t="n">
+        <v>87</v>
+      </c>
+      <c r="F456" t="n">
+        <v>0</v>
+      </c>
+      <c r="G456" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H456" t="n">
+        <v>2</v>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E457" t="n">
+        <v>89</v>
+      </c>
+      <c r="F457" t="n">
+        <v>0</v>
+      </c>
+      <c r="G457" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H457" t="n">
+        <v>1</v>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E458" t="n">
+        <v>79</v>
+      </c>
+      <c r="F458" t="n">
+        <v>0</v>
+      </c>
+      <c r="G458" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H458" t="n">
+        <v>3</v>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E459" t="n">
+        <v>94</v>
+      </c>
+      <c r="F459" t="n">
+        <v>0</v>
+      </c>
+      <c r="G459" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H459" t="n">
+        <v>2</v>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>24</v>
+      </c>
+      <c r="E460" t="n">
+        <v>91</v>
+      </c>
+      <c r="F460" t="n">
+        <v>0</v>
+      </c>
+      <c r="G460" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H460" t="n">
+        <v>3</v>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E461" t="n">
+        <v>83</v>
+      </c>
+      <c r="F461" t="n">
+        <v>0</v>
+      </c>
+      <c r="G461" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H461" t="n">
+        <v>3</v>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E462" t="n">
+        <v>88</v>
+      </c>
+      <c r="F462" t="n">
+        <v>0</v>
+      </c>
+      <c r="G462" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H462" t="n">
+        <v>3</v>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
         </is>
       </c>
     </row>
@@ -16312,7 +17533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17219,6 +18440,67 @@
       <c r="O15" t="inlineStr">
         <is>
           <t>2026-09-22T03:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>33</v>
+      </c>
+      <c r="D16" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:45</t>
         </is>
       </c>
     </row>
@@ -17285,16 +18567,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
       </c>
       <c r="E2" t="n">
-        <v>25.1</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>85.3</v>
+        <v>86.3</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -17312,7 +18594,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -17321,7 +18603,7 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -17339,7 +18621,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -17348,7 +18630,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.2</v>
@@ -17366,16 +18648,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.1</v>
+        <v>27.8</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
       </c>
       <c r="E5" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="F5" t="n">
-        <v>69.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>0.3</v>
@@ -17393,7 +18675,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -17402,7 +18684,7 @@
         <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>87.2</v>
+        <v>87.7</v>
       </c>
       <c r="G6" t="n">
         <v>0.1</v>
@@ -17420,7 +18702,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -17429,7 +18711,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>79.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -17447,7 +18729,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -17456,7 +18738,7 @@
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>84.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0.1</v>
@@ -17474,7 +18756,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -17483,7 +18765,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>71.5</v>
+        <v>72.8</v>
       </c>
       <c r="G9" t="n">
         <v>2.7</v>
@@ -17501,7 +18783,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="D10" t="n">
         <v>29.9</v>
@@ -17510,7 +18792,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>85.3</v>
+        <v>85.7</v>
       </c>
       <c r="G10" t="n">
         <v>1.3</v>
@@ -17528,7 +18810,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -17537,7 +18819,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -17555,7 +18837,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -17564,7 +18846,7 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -17582,7 +18864,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -17591,7 +18873,7 @@
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>0.1</v>
@@ -17609,7 +18891,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -17618,7 +18900,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>80.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -17636,7 +18918,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -17645,7 +18927,7 @@
         <v>22.1</v>
       </c>
       <c r="F15" t="n">
-        <v>76.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>0.2</v>
@@ -17663,7 +18945,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -17672,7 +18954,7 @@
         <v>25.7</v>
       </c>
       <c r="F16" t="n">
-        <v>83.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>0.1</v>
@@ -17690,7 +18972,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="D17" t="n">
         <v>30.2</v>
@@ -17699,7 +18981,7 @@
         <v>23.6</v>
       </c>
       <c r="F17" t="n">
-        <v>84.5</v>
+        <v>85.2</v>
       </c>
       <c r="G17" t="n">
         <v>0.5</v>
@@ -17717,7 +18999,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -17726,7 +19008,7 @@
         <v>23.6</v>
       </c>
       <c r="F18" t="n">
-        <v>79.7</v>
+        <v>80.7</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -17744,7 +19026,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -17753,7 +19035,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>83.2</v>
+        <v>83.7</v>
       </c>
       <c r="G19" t="n">
         <v>0.1</v>
@@ -17771,7 +19053,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.2</v>
+        <v>26.9</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -17780,7 +19062,7 @@
         <v>22.9</v>
       </c>
       <c r="F20" t="n">
-        <v>74.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>0.8</v>
@@ -17798,7 +19080,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -17807,7 +19089,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>68.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -17825,7 +19107,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="D22" t="n">
         <v>31.3</v>
@@ -17834,7 +19116,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>75.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -17852,7 +19134,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="D23" t="n">
         <v>30.7</v>
@@ -17861,7 +19143,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>83</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
@@ -17879,7 +19161,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -17888,7 +19170,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>86.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0.2</v>
@@ -17906,7 +19188,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -17915,7 +19197,7 @@
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>85.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0.1</v>
@@ -17933,7 +19215,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="D26" t="n">
         <v>31.1</v>
@@ -17942,7 +19224,7 @@
         <v>24.8</v>
       </c>
       <c r="F26" t="n">
-        <v>85.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>0.2</v>
@@ -17960,16 +19242,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="D27" t="n">
         <v>30.5</v>
       </c>
       <c r="E27" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="F27" t="n">
-        <v>76.7</v>
+        <v>77.7</v>
       </c>
       <c r="G27" t="n">
         <v>0.1</v>
@@ -17987,7 +19269,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="D28" t="n">
         <v>31.5</v>
@@ -17996,7 +19278,7 @@
         <v>24.3</v>
       </c>
       <c r="F28" t="n">
-        <v>77.3</v>
+        <v>78</v>
       </c>
       <c r="G28" t="n">
         <v>0.2</v>
@@ -18014,7 +19296,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
@@ -18023,7 +19305,7 @@
         <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>84.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0.4</v>
@@ -18041,7 +19323,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -18050,7 +19332,7 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>72.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -18068,7 +19350,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -18077,7 +19359,7 @@
         <v>22.4</v>
       </c>
       <c r="F31" t="n">
-        <v>77.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0.3</v>
@@ -18095,7 +19377,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>27.7</v>
+        <v>27.4</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -18104,7 +19386,7 @@
         <v>23.7</v>
       </c>
       <c r="F32" t="n">
-        <v>71.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>2.4</v>
@@ -18122,7 +19404,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -18131,7 +19413,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>76.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0.1</v>
@@ -18149,7 +19431,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -18158,7 +19440,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>77.8</v>
+        <v>78.5</v>
       </c>
       <c r="G34" t="n">
         <v>0.4</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I462"/>
+  <dimension ref="A1:I429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12655,23 +12655,23 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>27.4</v>
+        <v>29.9</v>
       </c>
       <c r="E331" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F331" t="n">
         <v>0</v>
       </c>
       <c r="G331" t="n">
-        <v>0.6</v>
+        <v>6.7</v>
       </c>
       <c r="H331" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -12692,23 +12692,23 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>29.1</v>
+        <v>32.1</v>
       </c>
       <c r="E332" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F332" t="n">
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="H332" t="n">
         <v>3</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -12729,23 +12729,23 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>27.2</v>
+        <v>32.2</v>
       </c>
       <c r="E333" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="F333" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G333" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="H333" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -12766,23 +12766,23 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>27.6</v>
+        <v>31</v>
       </c>
       <c r="E334" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="F334" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="H334" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -12803,23 +12803,23 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>26.6</v>
+        <v>30.1</v>
       </c>
       <c r="E335" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F335" t="n">
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H335" t="n">
         <v>3</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -12840,23 +12840,23 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>27.3</v>
+        <v>30.4</v>
       </c>
       <c r="E336" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F336" t="n">
         <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="H336" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -12877,23 +12877,23 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>28</v>
+        <v>31.3</v>
       </c>
       <c r="E337" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="F337" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="H337" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -12914,23 +12914,23 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>32.4</v>
+        <v>32.1</v>
       </c>
       <c r="E338" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F338" t="n">
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H338" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -12951,23 +12951,23 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>25.8</v>
+        <v>29.2</v>
       </c>
       <c r="E339" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F339" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H339" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -12988,23 +12988,23 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>28.1</v>
+        <v>30.4</v>
       </c>
       <c r="E340" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F340" t="n">
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>9.1</v>
+        <v>7.2</v>
       </c>
       <c r="H340" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13025,23 +13025,23 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>30.7</v>
+        <v>33.8</v>
       </c>
       <c r="E341" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F341" t="n">
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>11</v>
+        <v>7.9</v>
       </c>
       <c r="H341" t="n">
         <v>3</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13062,23 +13062,23 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>28.8</v>
+        <v>31</v>
       </c>
       <c r="E342" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F342" t="n">
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="H342" t="n">
         <v>3</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13099,23 +13099,23 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>29.2</v>
+        <v>32</v>
       </c>
       <c r="E343" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F343" t="n">
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="H343" t="n">
         <v>3</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13136,23 +13136,23 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>27.5</v>
+        <v>30.5</v>
       </c>
       <c r="E344" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="F344" t="n">
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="H344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13173,23 +13173,23 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>28.9</v>
+        <v>30.9</v>
       </c>
       <c r="E345" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F345" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="H345" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13210,23 +13210,23 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>26</v>
+        <v>29.9</v>
       </c>
       <c r="E346" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="F346" t="n">
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="H346" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13247,10 +13247,10 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>26.7</v>
+        <v>30.2</v>
       </c>
       <c r="E347" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="F347" t="n">
         <v>0</v>
@@ -13259,11 +13259,11 @@
         <v>7.6</v>
       </c>
       <c r="H347" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13284,23 +13284,23 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>28.2</v>
+        <v>30.8</v>
       </c>
       <c r="E348" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F348" t="n">
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>6.4</v>
+        <v>7.7</v>
       </c>
       <c r="H348" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13321,23 +13321,23 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>28.6</v>
+        <v>31.3</v>
       </c>
       <c r="E349" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F349" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G349" t="n">
-        <v>7.5</v>
+        <v>9.9</v>
       </c>
       <c r="H349" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13358,23 +13358,23 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>29.9</v>
+        <v>33.4</v>
       </c>
       <c r="E350" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F350" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G350" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="H350" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13395,23 +13395,23 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>28.2</v>
+        <v>31.2</v>
       </c>
       <c r="E351" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F351" t="n">
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>9.699999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="H351" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13432,23 +13432,23 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>27.1</v>
+        <v>30</v>
       </c>
       <c r="E352" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="F352" t="n">
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="H352" t="n">
         <v>3</v>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13469,23 +13469,23 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>27</v>
+        <v>29.4</v>
       </c>
       <c r="E353" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="F353" t="n">
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="H353" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13506,23 +13506,23 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>27.8</v>
+        <v>30.4</v>
       </c>
       <c r="E354" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="F354" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="H354" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13543,23 +13543,23 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>27.5</v>
+        <v>30.3</v>
       </c>
       <c r="E355" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="F355" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
       <c r="H355" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13580,23 +13580,23 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>26.4</v>
+        <v>29.7</v>
       </c>
       <c r="E356" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="F356" t="n">
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="H356" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13617,23 +13617,23 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>27.4</v>
+        <v>30.8</v>
       </c>
       <c r="E357" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="F357" t="n">
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="H357" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13654,23 +13654,23 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>26.2</v>
+        <v>29.3</v>
       </c>
       <c r="E358" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F358" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G358" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="H358" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13691,23 +13691,23 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>30</v>
+        <v>32.9</v>
       </c>
       <c r="E359" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F359" t="n">
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>14.4</v>
+        <v>7.8</v>
       </c>
       <c r="H359" t="n">
         <v>3</v>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13728,23 +13728,23 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>26.3</v>
+        <v>30.1</v>
       </c>
       <c r="E360" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="F360" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>5.1</v>
+        <v>9.1</v>
       </c>
       <c r="H360" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13765,23 +13765,23 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>28.8</v>
+        <v>31.4</v>
       </c>
       <c r="E361" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F361" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
       <c r="H361" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13802,23 +13802,23 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>27.9</v>
+        <v>32.8</v>
       </c>
       <c r="E362" t="n">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="F362" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G362" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H362" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13839,23 +13839,23 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>26.6</v>
+        <v>30.4</v>
       </c>
       <c r="E363" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="F363" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="G363" t="n">
-        <v>11.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H363" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -13876,23 +13876,23 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>25.6</v>
+        <v>30.1</v>
       </c>
       <c r="E364" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="F364" t="n">
         <v>0</v>
       </c>
       <c r="G364" t="n">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
       <c r="H364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -13913,23 +13913,23 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>27.1</v>
+        <v>32.2</v>
       </c>
       <c r="E365" t="n">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="F365" t="n">
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="H365" t="n">
         <v>3</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -13950,23 +13950,23 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>26.8</v>
+        <v>32.4</v>
       </c>
       <c r="E366" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F366" t="n">
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H366" t="n">
         <v>3</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -13987,23 +13987,23 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>25.1</v>
+        <v>31.1</v>
       </c>
       <c r="E367" t="n">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="F367" t="n">
         <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H367" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14024,23 +14024,23 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>25.5</v>
+        <v>30.2</v>
       </c>
       <c r="E368" t="n">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="F368" t="n">
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>6.3</v>
+        <v>4</v>
       </c>
       <c r="H368" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14061,23 +14061,23 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>25.4</v>
+        <v>30.7</v>
       </c>
       <c r="E369" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="F369" t="n">
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="H369" t="n">
         <v>2</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14098,23 +14098,23 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>25.9</v>
+        <v>31.5</v>
       </c>
       <c r="E370" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="F370" t="n">
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="H370" t="n">
         <v>3</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14135,23 +14135,23 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>24.3</v>
+        <v>32.3</v>
       </c>
       <c r="E371" t="n">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="F371" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G371" t="n">
-        <v>13.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H371" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14172,23 +14172,23 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>24.1</v>
+        <v>29.2</v>
       </c>
       <c r="E372" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="F372" t="n">
         <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="H372" t="n">
         <v>3</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14209,23 +14209,23 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>26.2</v>
+        <v>30.6</v>
       </c>
       <c r="E373" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="F373" t="n">
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="H373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14246,23 +14246,23 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>27.8</v>
+        <v>34</v>
       </c>
       <c r="E374" t="n">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="F374" t="n">
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H374" t="n">
         <v>3</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14283,23 +14283,23 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>26.1</v>
+        <v>30.9</v>
       </c>
       <c r="E375" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="F375" t="n">
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="H375" t="n">
         <v>3</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14320,23 +14320,23 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>26.7</v>
+        <v>32.2</v>
       </c>
       <c r="E376" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="F376" t="n">
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="H376" t="n">
         <v>3</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14357,23 +14357,23 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>22.1</v>
+        <v>30.7</v>
       </c>
       <c r="E377" t="n">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="F377" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>15.1</v>
+        <v>6.3</v>
       </c>
       <c r="H377" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14394,23 +14394,23 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>26.9</v>
+        <v>31</v>
       </c>
       <c r="E378" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F378" t="n">
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="H378" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14431,23 +14431,23 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>24.4</v>
+        <v>29.9</v>
       </c>
       <c r="E379" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="F379" t="n">
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>4</v>
+        <v>7.3</v>
       </c>
       <c r="H379" t="n">
         <v>2</v>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14468,23 +14468,23 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>24</v>
+        <v>30.4</v>
       </c>
       <c r="E380" t="n">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="F380" t="n">
         <v>0</v>
       </c>
       <c r="G380" t="n">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H380" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14505,23 +14505,23 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>26</v>
+        <v>30.8</v>
       </c>
       <c r="E381" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F381" t="n">
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>5.4</v>
+        <v>7.9</v>
       </c>
       <c r="H381" t="n">
         <v>3</v>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14542,23 +14542,23 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>22.9</v>
+        <v>31.5</v>
       </c>
       <c r="E382" t="n">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="F382" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>19.1</v>
+        <v>10.1</v>
       </c>
       <c r="H382" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14579,23 +14579,23 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>27.7</v>
+        <v>33.4</v>
       </c>
       <c r="E383" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="F383" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G383" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H383" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14616,23 +14616,23 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>23.3</v>
+        <v>31.4</v>
       </c>
       <c r="E384" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="F384" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>12.3</v>
+        <v>6.1</v>
       </c>
       <c r="H384" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14653,23 +14653,23 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>25.6</v>
+        <v>30.2</v>
       </c>
       <c r="E385" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="F385" t="n">
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H385" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14690,23 +14690,23 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>25</v>
+        <v>29.5</v>
       </c>
       <c r="E386" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="F386" t="n">
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="H386" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14727,23 +14727,23 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>26.3</v>
+        <v>30.5</v>
       </c>
       <c r="E387" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="F387" t="n">
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="H387" t="n">
         <v>3</v>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14764,23 +14764,23 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>25.6</v>
+        <v>30.3</v>
       </c>
       <c r="E388" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="F388" t="n">
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="H388" t="n">
         <v>3</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14801,23 +14801,23 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>24</v>
+        <v>29.9</v>
       </c>
       <c r="E389" t="n">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="F389" t="n">
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="H389" t="n">
         <v>3</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14838,23 +14838,23 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>24.4</v>
+        <v>31.2</v>
       </c>
       <c r="E390" t="n">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="F390" t="n">
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="H390" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14875,23 +14875,23 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>24.8</v>
+        <v>29.5</v>
       </c>
       <c r="E391" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="F391" t="n">
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>7.6</v>
+        <v>10.3</v>
       </c>
       <c r="H391" t="n">
         <v>3</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14912,23 +14912,23 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>27.5</v>
+        <v>33.1</v>
       </c>
       <c r="E392" t="n">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="F392" t="n">
         <v>0</v>
       </c>
       <c r="G392" t="n">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="H392" t="n">
         <v>3</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14949,23 +14949,23 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>23.5</v>
+        <v>30.4</v>
       </c>
       <c r="E393" t="n">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="F393" t="n">
         <v>0</v>
       </c>
       <c r="G393" t="n">
-        <v>7.6</v>
+        <v>9.5</v>
       </c>
       <c r="H393" t="n">
         <v>3</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -14986,23 +14986,23 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>23.7</v>
+        <v>31.7</v>
       </c>
       <c r="E394" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="F394" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>13.2</v>
+        <v>8.9</v>
       </c>
       <c r="H394" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -15023,23 +15023,23 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>27.1</v>
+        <v>33</v>
       </c>
       <c r="E395" t="n">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="F395" t="n">
         <v>0</v>
       </c>
       <c r="G395" t="n">
-        <v>6.2</v>
+        <v>8.5</v>
       </c>
       <c r="H395" t="n">
         <v>3</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
@@ -15060,30 +15060,30 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>24.9</v>
+        <v>30.4</v>
       </c>
       <c r="E396" t="n">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="F396" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G396" t="n">
-        <v>7.9</v>
+        <v>10.7</v>
       </c>
       <c r="H396" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15097,30 +15097,30 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>25.2</v>
+        <v>29.7</v>
       </c>
       <c r="E397" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F397" t="n">
         <v>0</v>
       </c>
       <c r="G397" t="n">
-        <v>3.4</v>
+        <v>7.1</v>
       </c>
       <c r="H397" t="n">
         <v>3</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15134,30 +15134,30 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>27.1</v>
+        <v>30.6</v>
       </c>
       <c r="E398" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F398" t="n">
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>8.699999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="H398" t="n">
         <v>3</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15171,30 +15171,30 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>26</v>
+        <v>31.5</v>
       </c>
       <c r="E399" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="F399" t="n">
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>10.2</v>
+        <v>15.6</v>
       </c>
       <c r="H399" t="n">
         <v>3</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15208,30 +15208,30 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>24.6</v>
+        <v>30.6</v>
       </c>
       <c r="E400" t="n">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="F400" t="n">
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>7.3</v>
+        <v>10.6</v>
       </c>
       <c r="H400" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15245,30 +15245,30 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E401" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="F401" t="n">
         <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>8.9</v>
+        <v>11</v>
       </c>
       <c r="H401" t="n">
         <v>3</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15282,30 +15282,30 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>24.9</v>
+        <v>30.8</v>
       </c>
       <c r="E402" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="F402" t="n">
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>12.4</v>
+        <v>17.9</v>
       </c>
       <c r="H402" t="n">
         <v>3</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15319,30 +15319,30 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>25.9</v>
+        <v>30.7</v>
       </c>
       <c r="E403" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F403" t="n">
         <v>0</v>
       </c>
       <c r="G403" t="n">
-        <v>8.6</v>
+        <v>12.4</v>
       </c>
       <c r="H403" t="n">
         <v>3</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -15356,30 +15356,30 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>24.6</v>
+        <v>31.6</v>
       </c>
       <c r="E404" t="n">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="F404" t="n">
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>9.800000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="H404" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15393,30 +15393,30 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>23.8</v>
+        <v>28.6</v>
       </c>
       <c r="E405" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="F405" t="n">
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>7.6</v>
+        <v>12.6</v>
       </c>
       <c r="H405" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15430,30 +15430,30 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>25.8</v>
+        <v>30.9</v>
       </c>
       <c r="E406" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="F406" t="n">
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>8.6</v>
+        <v>13.1</v>
       </c>
       <c r="H406" t="n">
         <v>3</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15467,30 +15467,30 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>27.3</v>
+        <v>32.2</v>
       </c>
       <c r="E407" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F407" t="n">
         <v>0</v>
       </c>
       <c r="G407" t="n">
-        <v>12.2</v>
+        <v>18.4</v>
       </c>
       <c r="H407" t="n">
         <v>3</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15504,30 +15504,30 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>25.6</v>
+        <v>31.1</v>
       </c>
       <c r="E408" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="F408" t="n">
         <v>0</v>
       </c>
       <c r="G408" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="H408" t="n">
         <v>3</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15541,30 +15541,30 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>26.5</v>
+        <v>31.4</v>
       </c>
       <c r="E409" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="F409" t="n">
         <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>11.4</v>
+        <v>18.8</v>
       </c>
       <c r="H409" t="n">
         <v>3</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15578,30 +15578,30 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>23.4</v>
+        <v>30</v>
       </c>
       <c r="E410" t="n">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="F410" t="n">
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>10.2</v>
+        <v>14.4</v>
       </c>
       <c r="H410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15615,30 +15615,30 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>25.7</v>
+        <v>31.5</v>
       </c>
       <c r="E411" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="F411" t="n">
         <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="H411" t="n">
         <v>3</v>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15652,30 +15652,30 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>23.6</v>
+        <v>29</v>
       </c>
       <c r="E412" t="n">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="F412" t="n">
         <v>0</v>
       </c>
       <c r="G412" t="n">
-        <v>4.6</v>
+        <v>12.9</v>
       </c>
       <c r="H412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15689,30 +15689,30 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>23.6</v>
+        <v>29.6</v>
       </c>
       <c r="E413" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="F413" t="n">
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>8.6</v>
+        <v>14.1</v>
       </c>
       <c r="H413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15726,30 +15726,30 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>25.7</v>
+        <v>30.1</v>
       </c>
       <c r="E414" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F414" t="n">
         <v>0</v>
       </c>
       <c r="G414" t="n">
-        <v>11.1</v>
+        <v>15.5</v>
       </c>
       <c r="H414" t="n">
         <v>3</v>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15763,30 +15763,30 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>23.7</v>
+        <v>30.6</v>
       </c>
       <c r="E415" t="n">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="F415" t="n">
         <v>0</v>
       </c>
       <c r="G415" t="n">
-        <v>12.6</v>
+        <v>15.4</v>
       </c>
       <c r="H415" t="n">
         <v>3</v>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15800,30 +15800,30 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>27</v>
+        <v>33.4</v>
       </c>
       <c r="E416" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F416" t="n">
         <v>0</v>
       </c>
       <c r="G416" t="n">
-        <v>10.2</v>
+        <v>17.1</v>
       </c>
       <c r="H416" t="n">
         <v>3</v>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -15837,30 +15837,30 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>23.9</v>
+        <v>30.7</v>
       </c>
       <c r="E417" t="n">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="F417" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G417" t="n">
-        <v>11.5</v>
+        <v>13.6</v>
       </c>
       <c r="H417" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -15874,30 +15874,30 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>25.1</v>
+        <v>30</v>
       </c>
       <c r="E418" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="F418" t="n">
         <v>0</v>
       </c>
       <c r="G418" t="n">
-        <v>6.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H418" t="n">
         <v>3</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -15911,30 +15911,30 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>24.3</v>
+        <v>29.3</v>
       </c>
       <c r="E419" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="F419" t="n">
         <v>0</v>
       </c>
       <c r="G419" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="H419" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -15948,30 +15948,30 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>25.9</v>
+        <v>30.8</v>
       </c>
       <c r="E420" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="F420" t="n">
         <v>0</v>
       </c>
       <c r="G420" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="H420" t="n">
         <v>3</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -15985,30 +15985,30 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>24.8</v>
+        <v>30.1</v>
       </c>
       <c r="E421" t="n">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="F421" t="n">
         <v>0</v>
       </c>
       <c r="G421" t="n">
-        <v>7.7</v>
+        <v>12.6</v>
       </c>
       <c r="H421" t="n">
         <v>3</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -16022,30 +16022,30 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>23.5</v>
+        <v>29.6</v>
       </c>
       <c r="E422" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="F422" t="n">
         <v>0</v>
       </c>
       <c r="G422" t="n">
-        <v>9.6</v>
+        <v>14.9</v>
       </c>
       <c r="H422" t="n">
         <v>3</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -16059,30 +16059,30 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>24.3</v>
+        <v>30.7</v>
       </c>
       <c r="E423" t="n">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="F423" t="n">
         <v>0</v>
       </c>
       <c r="G423" t="n">
-        <v>6.9</v>
+        <v>14.5</v>
       </c>
       <c r="H423" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -16096,30 +16096,30 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>24.2</v>
+        <v>29</v>
       </c>
       <c r="E424" t="n">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="F424" t="n">
         <v>0</v>
       </c>
       <c r="G424" t="n">
-        <v>10.4</v>
+        <v>15.9</v>
       </c>
       <c r="H424" t="n">
         <v>3</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -16133,30 +16133,30 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>26.9</v>
+        <v>33.4</v>
       </c>
       <c r="E425" t="n">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="F425" t="n">
         <v>0</v>
       </c>
       <c r="G425" t="n">
-        <v>11.1</v>
+        <v>17</v>
       </c>
       <c r="H425" t="n">
         <v>3</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -16170,30 +16170,30 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>22.4</v>
+        <v>29.6</v>
       </c>
       <c r="E426" t="n">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="F426" t="n">
         <v>0</v>
       </c>
       <c r="G426" t="n">
-        <v>9.4</v>
+        <v>13.2</v>
       </c>
       <c r="H426" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -16207,30 +16207,30 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>23.8</v>
+        <v>30.8</v>
       </c>
       <c r="E427" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="F427" t="n">
         <v>0</v>
       </c>
       <c r="G427" t="n">
-        <v>8.300000000000001</v>
+        <v>14.4</v>
       </c>
       <c r="H427" t="n">
         <v>3</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -16244,30 +16244,30 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>26.2</v>
+        <v>31.8</v>
       </c>
       <c r="E428" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="F428" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G428" t="n">
-        <v>10.8</v>
+        <v>16.2</v>
       </c>
       <c r="H428" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -16281,1244 +16281,23 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>24.8</v>
+        <v>29.5</v>
       </c>
       <c r="E429" t="n">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="F429" t="n">
         <v>0</v>
       </c>
       <c r="G429" t="n">
-        <v>11.2</v>
+        <v>17.3</v>
       </c>
       <c r="H429" t="n">
         <v>3</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>Adilabad</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D430" t="n">
-        <v>24</v>
-      </c>
-      <c r="E430" t="n">
-        <v>99</v>
-      </c>
-      <c r="F430" t="n">
-        <v>0</v>
-      </c>
-      <c r="G430" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H430" t="n">
-        <v>3</v>
-      </c>
-      <c r="I430" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>Bhadradri Kothagudem</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D431" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E431" t="n">
-        <v>83</v>
-      </c>
-      <c r="F431" t="n">
-        <v>0</v>
-      </c>
-      <c r="G431" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H431" t="n">
-        <v>3</v>
-      </c>
-      <c r="I431" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>Hanumakonda</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D432" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E432" t="n">
-        <v>85</v>
-      </c>
-      <c r="F432" t="n">
-        <v>0</v>
-      </c>
-      <c r="G432" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H432" t="n">
-        <v>3</v>
-      </c>
-      <c r="I432" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D433" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E433" t="n">
-        <v>88</v>
-      </c>
-      <c r="F433" t="n">
-        <v>0</v>
-      </c>
-      <c r="G433" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="H433" t="n">
-        <v>3</v>
-      </c>
-      <c r="I433" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>Jagtial</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D434" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E434" t="n">
-        <v>94</v>
-      </c>
-      <c r="F434" t="n">
-        <v>0</v>
-      </c>
-      <c r="G434" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H434" t="n">
-        <v>1</v>
-      </c>
-      <c r="I434" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>Jangaon</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D435" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E435" t="n">
-        <v>84</v>
-      </c>
-      <c r="F435" t="n">
-        <v>0</v>
-      </c>
-      <c r="G435" t="n">
-        <v>13</v>
-      </c>
-      <c r="H435" t="n">
-        <v>3</v>
-      </c>
-      <c r="I435" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>Jayashankar Bhupalpally</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D436" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E436" t="n">
-        <v>90</v>
-      </c>
-      <c r="F436" t="n">
-        <v>0</v>
-      </c>
-      <c r="G436" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H436" t="n">
-        <v>3</v>
-      </c>
-      <c r="I436" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>Jogulamba Gadwal</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D437" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="E437" t="n">
-        <v>89</v>
-      </c>
-      <c r="F437" t="n">
-        <v>0</v>
-      </c>
-      <c r="G437" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="H437" t="n">
-        <v>3</v>
-      </c>
-      <c r="I437" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>Kamareddy</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D438" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E438" t="n">
-        <v>91</v>
-      </c>
-      <c r="F438" t="n">
-        <v>0</v>
-      </c>
-      <c r="G438" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H438" t="n">
-        <v>2</v>
-      </c>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>Karimnagar</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D439" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E439" t="n">
-        <v>86</v>
-      </c>
-      <c r="F439" t="n">
-        <v>0</v>
-      </c>
-      <c r="G439" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H439" t="n">
-        <v>3</v>
-      </c>
-      <c r="I439" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>Khammam</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D440" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="E440" t="n">
-        <v>81</v>
-      </c>
-      <c r="F440" t="n">
-        <v>0</v>
-      </c>
-      <c r="G440" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="H440" t="n">
-        <v>3</v>
-      </c>
-      <c r="I440" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>Kumuram Bheem Asifabad</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D441" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E441" t="n">
-        <v>87</v>
-      </c>
-      <c r="F441" t="n">
-        <v>0</v>
-      </c>
-      <c r="G441" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H441" t="n">
-        <v>2</v>
-      </c>
-      <c r="I441" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>Mahabubabad</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D442" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E442" t="n">
-        <v>86</v>
-      </c>
-      <c r="F442" t="n">
-        <v>0</v>
-      </c>
-      <c r="G442" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H442" t="n">
-        <v>3</v>
-      </c>
-      <c r="I442" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>Mahbubnagar</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D443" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E443" t="n">
-        <v>89</v>
-      </c>
-      <c r="F443" t="n">
-        <v>0</v>
-      </c>
-      <c r="G443" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="H443" t="n">
-        <v>3</v>
-      </c>
-      <c r="I443" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>Mancherial</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D444" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E444" t="n">
-        <v>87</v>
-      </c>
-      <c r="F444" t="n">
-        <v>0</v>
-      </c>
-      <c r="G444" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H444" t="n">
-        <v>3</v>
-      </c>
-      <c r="I444" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>Medak</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D445" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E445" t="n">
-        <v>95</v>
-      </c>
-      <c r="F445" t="n">
-        <v>0</v>
-      </c>
-      <c r="G445" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H445" t="n">
-        <v>3</v>
-      </c>
-      <c r="I445" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>Medchal-Malkajgiri</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D446" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E446" t="n">
-        <v>93</v>
-      </c>
-      <c r="F446" t="n">
-        <v>0</v>
-      </c>
-      <c r="G446" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H446" t="n">
-        <v>3</v>
-      </c>
-      <c r="I446" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>Mulugu</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D447" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E447" t="n">
-        <v>90</v>
-      </c>
-      <c r="F447" t="n">
-        <v>0</v>
-      </c>
-      <c r="G447" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H447" t="n">
-        <v>3</v>
-      </c>
-      <c r="I447" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>Nagarkurnool</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D448" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E448" t="n">
-        <v>91</v>
-      </c>
-      <c r="F448" t="n">
-        <v>0</v>
-      </c>
-      <c r="G448" t="n">
-        <v>13</v>
-      </c>
-      <c r="H448" t="n">
-        <v>3</v>
-      </c>
-      <c r="I448" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>Nalgonda</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D449" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="E449" t="n">
-        <v>79</v>
-      </c>
-      <c r="F449" t="n">
-        <v>0</v>
-      </c>
-      <c r="G449" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H449" t="n">
-        <v>3</v>
-      </c>
-      <c r="I449" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>Narayanpet</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D450" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E450" t="n">
-        <v>86</v>
-      </c>
-      <c r="F450" t="n">
-        <v>0</v>
-      </c>
-      <c r="G450" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="H450" t="n">
-        <v>2</v>
-      </c>
-      <c r="I450" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>Nirmal</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D451" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E451" t="n">
-        <v>88</v>
-      </c>
-      <c r="F451" t="n">
-        <v>0</v>
-      </c>
-      <c r="G451" t="n">
-        <v>8</v>
-      </c>
-      <c r="H451" t="n">
-        <v>0</v>
-      </c>
-      <c r="I451" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>Nizamabad</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D452" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="E452" t="n">
-        <v>95</v>
-      </c>
-      <c r="F452" t="n">
-        <v>0</v>
-      </c>
-      <c r="G452" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H452" t="n">
-        <v>2</v>
-      </c>
-      <c r="I452" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>Peddapalli</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D453" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E453" t="n">
-        <v>89</v>
-      </c>
-      <c r="F453" t="n">
-        <v>0</v>
-      </c>
-      <c r="G453" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H453" t="n">
-        <v>3</v>
-      </c>
-      <c r="I453" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>Rajanna Sircilla</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D454" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="E454" t="n">
-        <v>89</v>
-      </c>
-      <c r="F454" t="n">
-        <v>0</v>
-      </c>
-      <c r="G454" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H454" t="n">
-        <v>3</v>
-      </c>
-      <c r="I454" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>Rangareddy</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D455" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E455" t="n">
-        <v>91</v>
-      </c>
-      <c r="F455" t="n">
-        <v>0</v>
-      </c>
-      <c r="G455" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H455" t="n">
-        <v>2</v>
-      </c>
-      <c r="I455" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>Sangareddy</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D456" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E456" t="n">
-        <v>87</v>
-      </c>
-      <c r="F456" t="n">
-        <v>0</v>
-      </c>
-      <c r="G456" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H456" t="n">
-        <v>2</v>
-      </c>
-      <c r="I456" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>Siddipet</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D457" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E457" t="n">
-        <v>89</v>
-      </c>
-      <c r="F457" t="n">
-        <v>0</v>
-      </c>
-      <c r="G457" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="H457" t="n">
-        <v>1</v>
-      </c>
-      <c r="I457" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>Suryapet</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D458" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E458" t="n">
-        <v>79</v>
-      </c>
-      <c r="F458" t="n">
-        <v>0</v>
-      </c>
-      <c r="G458" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H458" t="n">
-        <v>3</v>
-      </c>
-      <c r="I458" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>Vikarabad</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D459" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E459" t="n">
-        <v>94</v>
-      </c>
-      <c r="F459" t="n">
-        <v>0</v>
-      </c>
-      <c r="G459" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H459" t="n">
-        <v>2</v>
-      </c>
-      <c r="I459" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>Wanaparthy</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D460" t="n">
-        <v>24</v>
-      </c>
-      <c r="E460" t="n">
-        <v>91</v>
-      </c>
-      <c r="F460" t="n">
-        <v>0</v>
-      </c>
-      <c r="G460" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H460" t="n">
-        <v>3</v>
-      </c>
-      <c r="I460" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>Warangal</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D461" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="E461" t="n">
-        <v>83</v>
-      </c>
-      <c r="F461" t="n">
-        <v>0</v>
-      </c>
-      <c r="G461" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H461" t="n">
-        <v>3</v>
-      </c>
-      <c r="I461" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>Yadadri Bhuvanagiri</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D462" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E462" t="n">
-        <v>88</v>
-      </c>
-      <c r="F462" t="n">
-        <v>0</v>
-      </c>
-      <c r="G462" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H462" t="n">
-        <v>3</v>
-      </c>
-      <c r="I462" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
@@ -17533,7 +16312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18275,15 +17054,15 @@
         <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>27.9</v>
+        <v>30.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jogulamba Gadwal</t>
+          <t>Khammam</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>32.4</v>
+        <v>33.8</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -18291,33 +17070,33 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>25.8</v>
+        <v>29.2</v>
       </c>
       <c r="I13" t="n">
-        <v>80.5</v>
+        <v>63.8</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Kamareddy</t>
+          <t>Nalgonda</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Suryapet</t>
+          <t>Jangaon</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>14.4</v>
+        <v>10.5</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-09-21T17:30</t>
+          <t>2026-09-21T11:45</t>
         </is>
       </c>
     </row>
@@ -18336,7 +17115,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="n">
-        <v>25.3</v>
+        <v>31.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -18344,48 +17123,48 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>27.8</v>
+        <v>34</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Mahbubnagar</t>
+          <t>Kamareddy</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.1</v>
+        <v>29.2</v>
       </c>
       <c r="I14" t="n">
-        <v>92.8</v>
+        <v>63.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Jogulamba Gadwal</t>
+          <t>Nalgonda</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Nagarkurnool</t>
+          <t>Yadadri Bhuvanagiri</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>19.1</v>
+        <v>10.7</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-09-22T00:00</t>
+          <t>2026-09-21T12:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -18397,110 +17176,49 @@
         <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>30.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Khammam</t>
+          <t>Nalgonda</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>27.3</v>
+        <v>33.4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Vikarabad</t>
+          <t>Kamareddy</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>22.4</v>
+        <v>28.6</v>
       </c>
       <c r="I15" t="n">
-        <v>89.7</v>
+        <v>65.5</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Adilabad</t>
+          <t>Narayanpet</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Nagarkurnool</t>
+          <t>Mahabubabad</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>12.6</v>
+        <v>18.8</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-09-22T03:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>33</v>
-      </c>
-      <c r="D16" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Khammam</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Vikarabad</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I16" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Adilabad</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Jogulamba Gadwal</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2026-09-22T06:45</t>
+          <t>2026-09-22T11:00</t>
         </is>
       </c>
     </row>
@@ -18567,16 +17285,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.1</v>
+        <v>28.2</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>86.3</v>
+        <v>81.2</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -18594,7 +17312,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -18603,7 +17321,7 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>81.3</v>
+        <v>77.8</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -18621,7 +17339,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.1</v>
+        <v>29.5</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -18630,10 +17348,10 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>79.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -18648,19 +17366,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27.8</v>
+        <v>29.3</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
       </c>
       <c r="E5" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="F5" t="n">
-        <v>71.09999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -18675,16 +17393,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>28.2</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>87.7</v>
+        <v>82.8</v>
       </c>
       <c r="G6" t="n">
         <v>0.1</v>
@@ -18702,7 +17420,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.2</v>
+        <v>28.4</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -18711,7 +17429,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>80.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -18729,7 +17447,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -18738,10 +17456,10 @@
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>85.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -18756,7 +17474,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27.8</v>
+        <v>29.2</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -18765,10 +17483,10 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>72.8</v>
+        <v>66.3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -18783,7 +17501,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25.6</v>
+        <v>26.7</v>
       </c>
       <c r="D10" t="n">
         <v>29.9</v>
@@ -18792,10 +17510,10 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>85.7</v>
+        <v>80.5</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -18810,7 +17528,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -18819,7 +17537,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>83.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -18837,7 +17555,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.2</v>
+        <v>30.5</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -18846,7 +17564,7 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>76</v>
+        <v>70.8</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -18864,7 +17582,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -18873,7 +17591,7 @@
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>85.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="G13" t="n">
         <v>0.1</v>
@@ -18891,7 +17609,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.3</v>
+        <v>29.4</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -18900,7 +17618,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>80.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -18918,19 +17636,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.3</v>
+        <v>27.9</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
       </c>
       <c r="E15" t="n">
-        <v>22.1</v>
+        <v>23.8</v>
       </c>
       <c r="F15" t="n">
-        <v>77.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -18945,19 +17663,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.2</v>
+        <v>29.2</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
       </c>
       <c r="E16" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>83.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -18972,16 +17690,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.9</v>
+        <v>27.2</v>
       </c>
       <c r="D17" t="n">
         <v>30.2</v>
       </c>
       <c r="E17" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>85.2</v>
+        <v>78.7</v>
       </c>
       <c r="G17" t="n">
         <v>0.5</v>
@@ -18999,16 +17717,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27.5</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
       </c>
       <c r="E18" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="F18" t="n">
-        <v>80.7</v>
+        <v>72.8</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -19026,7 +17744,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -19035,7 +17753,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>83.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0.1</v>
@@ -19053,19 +17771,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>26.9</v>
+        <v>28.6</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
       </c>
       <c r="E20" t="n">
-        <v>22.9</v>
+        <v>24.1</v>
       </c>
       <c r="F20" t="n">
-        <v>75.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21">
@@ -19080,7 +17798,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>29.7</v>
+        <v>31.1</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -19089,10 +17807,10 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>69.09999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22">
@@ -19107,19 +17825,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>26.3</v>
+        <v>27.9</v>
       </c>
       <c r="D22" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="E22" t="n">
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>76.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="23">
@@ -19134,7 +17852,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26.8</v>
+        <v>27.9</v>
       </c>
       <c r="D23" t="n">
         <v>30.7</v>
@@ -19143,7 +17861,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>83.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
@@ -19161,7 +17879,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.1</v>
+        <v>27.2</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -19170,7 +17888,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>86.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="G24" t="n">
         <v>0.2</v>
@@ -19188,7 +17906,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27.7</v>
+        <v>28.7</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -19197,10 +17915,10 @@
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>85.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -19215,19 +17933,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>28.1</v>
       </c>
       <c r="D26" t="n">
         <v>31.1</v>
       </c>
       <c r="E26" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>85.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="27">
@@ -19242,16 +17960,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.1</v>
+        <v>27.4</v>
       </c>
       <c r="D27" t="n">
         <v>30.5</v>
       </c>
       <c r="E27" t="n">
-        <v>23.3</v>
+        <v>24.2</v>
       </c>
       <c r="F27" t="n">
-        <v>77.7</v>
+        <v>70.3</v>
       </c>
       <c r="G27" t="n">
         <v>0.1</v>
@@ -19269,16 +17987,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26.7</v>
+        <v>28.2</v>
       </c>
       <c r="D28" t="n">
         <v>31.5</v>
       </c>
       <c r="E28" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="F28" t="n">
-        <v>78</v>
+        <v>70.3</v>
       </c>
       <c r="G28" t="n">
         <v>0.2</v>
@@ -19296,19 +18014,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.2</v>
+        <v>27.3</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
       </c>
       <c r="E29" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="F29" t="n">
-        <v>84.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="30">
@@ -19323,7 +18041,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.2</v>
+        <v>30.5</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -19332,7 +18050,7 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>73.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -19350,19 +18068,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.8</v>
+        <v>27.4</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
       </c>
       <c r="E31" t="n">
-        <v>22.4</v>
+        <v>23.9</v>
       </c>
       <c r="F31" t="n">
-        <v>79.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="32">
@@ -19377,19 +18095,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>27.4</v>
+        <v>29.1</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
       </c>
       <c r="E32" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>73.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -19404,7 +18122,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.3</v>
+        <v>29.7</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -19413,7 +18131,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>77.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0.1</v>
@@ -19431,7 +18149,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.1</v>
+        <v>28.3</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -19440,10 +18158,10 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>78.5</v>
+        <v>71.7</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I429"/>
+  <dimension ref="A1:I462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16298,6 +16298,1227 @@
       <c r="I429" t="inlineStr">
         <is>
           <t>2026-09-22T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E430" t="n">
+        <v>73</v>
+      </c>
+      <c r="F430" t="n">
+        <v>0</v>
+      </c>
+      <c r="G430" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H430" t="n">
+        <v>3</v>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E431" t="n">
+        <v>68</v>
+      </c>
+      <c r="F431" t="n">
+        <v>0</v>
+      </c>
+      <c r="G431" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H431" t="n">
+        <v>3</v>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E432" t="n">
+        <v>58</v>
+      </c>
+      <c r="F432" t="n">
+        <v>0</v>
+      </c>
+      <c r="G432" t="n">
+        <v>15</v>
+      </c>
+      <c r="H432" t="n">
+        <v>3</v>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E433" t="n">
+        <v>55</v>
+      </c>
+      <c r="F433" t="n">
+        <v>0</v>
+      </c>
+      <c r="G433" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H433" t="n">
+        <v>3</v>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E434" t="n">
+        <v>69</v>
+      </c>
+      <c r="F434" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G434" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H434" t="n">
+        <v>95</v>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E435" t="n">
+        <v>62</v>
+      </c>
+      <c r="F435" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G435" t="n">
+        <v>18</v>
+      </c>
+      <c r="H435" t="n">
+        <v>95</v>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E436" t="n">
+        <v>68</v>
+      </c>
+      <c r="F436" t="n">
+        <v>0</v>
+      </c>
+      <c r="G436" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H436" t="n">
+        <v>3</v>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E437" t="n">
+        <v>49</v>
+      </c>
+      <c r="F437" t="n">
+        <v>0</v>
+      </c>
+      <c r="G437" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H437" t="n">
+        <v>3</v>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E438" t="n">
+        <v>66</v>
+      </c>
+      <c r="F438" t="n">
+        <v>0</v>
+      </c>
+      <c r="G438" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H438" t="n">
+        <v>3</v>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E439" t="n">
+        <v>61</v>
+      </c>
+      <c r="F439" t="n">
+        <v>0</v>
+      </c>
+      <c r="G439" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H439" t="n">
+        <v>3</v>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E440" t="n">
+        <v>59</v>
+      </c>
+      <c r="F440" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G440" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H440" t="n">
+        <v>95</v>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E441" t="n">
+        <v>64</v>
+      </c>
+      <c r="F441" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G441" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H441" t="n">
+        <v>95</v>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E442" t="n">
+        <v>66</v>
+      </c>
+      <c r="F442" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G442" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H442" t="n">
+        <v>95</v>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E443" t="n">
+        <v>54</v>
+      </c>
+      <c r="F443" t="n">
+        <v>0</v>
+      </c>
+      <c r="G443" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H443" t="n">
+        <v>3</v>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E444" t="n">
+        <v>64</v>
+      </c>
+      <c r="F444" t="n">
+        <v>0</v>
+      </c>
+      <c r="G444" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H444" t="n">
+        <v>3</v>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E445" t="n">
+        <v>64</v>
+      </c>
+      <c r="F445" t="n">
+        <v>0</v>
+      </c>
+      <c r="G445" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H445" t="n">
+        <v>3</v>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E446" t="n">
+        <v>58</v>
+      </c>
+      <c r="F446" t="n">
+        <v>0</v>
+      </c>
+      <c r="G446" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H446" t="n">
+        <v>3</v>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E447" t="n">
+        <v>74</v>
+      </c>
+      <c r="F447" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G447" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H447" t="n">
+        <v>95</v>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E448" t="n">
+        <v>52</v>
+      </c>
+      <c r="F448" t="n">
+        <v>0</v>
+      </c>
+      <c r="G448" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H448" t="n">
+        <v>3</v>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E449" t="n">
+        <v>49</v>
+      </c>
+      <c r="F449" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G449" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H449" t="n">
+        <v>53</v>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E450" t="n">
+        <v>55</v>
+      </c>
+      <c r="F450" t="n">
+        <v>0</v>
+      </c>
+      <c r="G450" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H450" t="n">
+        <v>3</v>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E451" t="n">
+        <v>66</v>
+      </c>
+      <c r="F451" t="n">
+        <v>0</v>
+      </c>
+      <c r="G451" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H451" t="n">
+        <v>3</v>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E452" t="n">
+        <v>67</v>
+      </c>
+      <c r="F452" t="n">
+        <v>0</v>
+      </c>
+      <c r="G452" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H452" t="n">
+        <v>3</v>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E453" t="n">
+        <v>70</v>
+      </c>
+      <c r="F453" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G453" t="n">
+        <v>12</v>
+      </c>
+      <c r="H453" t="n">
+        <v>96</v>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E454" t="n">
+        <v>64</v>
+      </c>
+      <c r="F454" t="n">
+        <v>0</v>
+      </c>
+      <c r="G454" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H454" t="n">
+        <v>3</v>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E455" t="n">
+        <v>56</v>
+      </c>
+      <c r="F455" t="n">
+        <v>0</v>
+      </c>
+      <c r="G455" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H455" t="n">
+        <v>3</v>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E456" t="n">
+        <v>53</v>
+      </c>
+      <c r="F456" t="n">
+        <v>0</v>
+      </c>
+      <c r="G456" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H456" t="n">
+        <v>3</v>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E457" t="n">
+        <v>66</v>
+      </c>
+      <c r="F457" t="n">
+        <v>0</v>
+      </c>
+      <c r="G457" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H457" t="n">
+        <v>3</v>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E458" t="n">
+        <v>62</v>
+      </c>
+      <c r="F458" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G458" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H458" t="n">
+        <v>53</v>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E459" t="n">
+        <v>54</v>
+      </c>
+      <c r="F459" t="n">
+        <v>0</v>
+      </c>
+      <c r="G459" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H459" t="n">
+        <v>3</v>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E460" t="n">
+        <v>56</v>
+      </c>
+      <c r="F460" t="n">
+        <v>0</v>
+      </c>
+      <c r="G460" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H460" t="n">
+        <v>3</v>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E461" t="n">
+        <v>55</v>
+      </c>
+      <c r="F461" t="n">
+        <v>0</v>
+      </c>
+      <c r="G461" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H461" t="n">
+        <v>3</v>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E462" t="n">
+        <v>61</v>
+      </c>
+      <c r="F462" t="n">
+        <v>0</v>
+      </c>
+      <c r="G462" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H462" t="n">
+        <v>3</v>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
         </is>
       </c>
     </row>
@@ -16312,7 +17533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17219,6 +18440,67 @@
       <c r="O15" t="inlineStr">
         <is>
           <t>2026-09-22T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>33</v>
+      </c>
+      <c r="D16" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:45</t>
         </is>
       </c>
     </row>
@@ -17285,7 +18567,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -17294,7 +18576,7 @@
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>81.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -17312,7 +18594,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -17321,7 +18603,7 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>77.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -17339,7 +18621,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -17348,7 +18630,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>73.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -17366,7 +18648,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -17375,7 +18657,7 @@
         <v>24.8</v>
       </c>
       <c r="F5" t="n">
-        <v>62.9</v>
+        <v>62.4</v>
       </c>
       <c r="G5" t="n">
         <v>0.2</v>
@@ -17393,7 +18675,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -17402,10 +18684,10 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>82.8</v>
+        <v>81.8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -17420,7 +18702,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.4</v>
+        <v>28.6</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -17429,10 +18711,10 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>74.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -17447,7 +18729,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -17456,7 +18738,7 @@
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>79.3</v>
+        <v>78.5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -17474,7 +18756,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29.2</v>
+        <v>29.5</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -17483,7 +18765,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>66.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>2.4</v>
@@ -17501,7 +18783,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.7</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
         <v>29.9</v>
@@ -17510,7 +18792,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>80.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -17528,7 +18810,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -17537,7 +18819,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>79.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -17555,7 +18837,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -17564,10 +18846,10 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>70.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13">
@@ -17582,7 +18864,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -17591,10 +18873,10 @@
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>81.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14">
@@ -17609,7 +18891,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -17618,10 +18900,10 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="15">
@@ -17636,16 +18918,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.9</v>
+        <v>28.1</v>
       </c>
       <c r="D15" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="E15" t="n">
         <v>23.8</v>
       </c>
       <c r="F15" t="n">
-        <v>69.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>0.1</v>
@@ -17663,7 +18945,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.2</v>
+        <v>29.4</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -17672,7 +18954,7 @@
         <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>79</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -17690,7 +18972,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="D17" t="n">
         <v>30.2</v>
@@ -17699,7 +18981,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>78.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>0.5</v>
@@ -17717,7 +18999,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -17726,7 +19008,7 @@
         <v>23.9</v>
       </c>
       <c r="F18" t="n">
-        <v>72.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -17744,7 +19026,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -17753,10 +19035,10 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>79.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="20">
@@ -17771,7 +19053,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -17780,7 +19062,7 @@
         <v>24.1</v>
       </c>
       <c r="F20" t="n">
-        <v>67.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>0.4</v>
@@ -17798,7 +19080,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -17807,10 +19089,10 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>61.7</v>
+        <v>60.8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22">
@@ -17825,16 +19107,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.9</v>
+        <v>28.2</v>
       </c>
       <c r="D22" t="n">
-        <v>31.4</v>
+        <v>32.2</v>
       </c>
       <c r="E22" t="n">
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>69.3</v>
+        <v>68.3</v>
       </c>
       <c r="G22" t="n">
         <v>1.8</v>
@@ -17852,16 +19134,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.9</v>
+        <v>28.1</v>
       </c>
       <c r="D23" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="E23" t="n">
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>78.7</v>
+        <v>77.8</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
@@ -17879,7 +19161,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -17888,7 +19170,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>81.5</v>
+        <v>80.5</v>
       </c>
       <c r="G24" t="n">
         <v>0.2</v>
@@ -17906,7 +19188,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -17915,10 +19197,10 @@
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>80.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="26">
@@ -17933,7 +19215,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.1</v>
+        <v>28.3</v>
       </c>
       <c r="D26" t="n">
         <v>31.1</v>
@@ -17942,7 +19224,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>80.5</v>
+        <v>79.3</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -17960,16 +19242,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.4</v>
+        <v>27.7</v>
       </c>
       <c r="D27" t="n">
-        <v>30.5</v>
+        <v>30.7</v>
       </c>
       <c r="E27" t="n">
         <v>24.2</v>
       </c>
       <c r="F27" t="n">
-        <v>70.3</v>
+        <v>69.3</v>
       </c>
       <c r="G27" t="n">
         <v>0.1</v>
@@ -17987,7 +19269,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="D28" t="n">
         <v>31.5</v>
@@ -17996,7 +19278,7 @@
         <v>24.5</v>
       </c>
       <c r="F28" t="n">
-        <v>70.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G28" t="n">
         <v>0.2</v>
@@ -18014,7 +19296,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.3</v>
+        <v>27.5</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
@@ -18023,7 +19305,7 @@
         <v>24.4</v>
       </c>
       <c r="F29" t="n">
-        <v>79.90000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0.1</v>
@@ -18050,10 +19332,10 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>67</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31">
@@ -18068,16 +19350,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.4</v>
+        <v>27.7</v>
       </c>
       <c r="D31" t="n">
-        <v>30.5</v>
+        <v>30.9</v>
       </c>
       <c r="E31" t="n">
         <v>23.9</v>
       </c>
       <c r="F31" t="n">
-        <v>69.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0.2</v>
@@ -18095,16 +19377,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="D32" t="n">
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
       <c r="E32" t="n">
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>64.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
@@ -18122,7 +19404,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.7</v>
+        <v>29.9</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -18131,7 +19413,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>70.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="G33" t="n">
         <v>0.1</v>
@@ -18149,7 +19431,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>28.3</v>
+        <v>28.5</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -18158,7 +19440,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>71.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G34" t="n">
         <v>0.3</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -16318,23 +16318,23 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>30.4</v>
+        <v>31.3</v>
       </c>
       <c r="E430" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F430" t="n">
         <v>0</v>
       </c>
       <c r="G430" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H430" t="n">
         <v>3</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16355,23 +16355,23 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E431" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F431" t="n">
         <v>0</v>
       </c>
       <c r="G431" t="n">
-        <v>13.3</v>
+        <v>12.6</v>
       </c>
       <c r="H431" t="n">
         <v>3</v>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16392,23 +16392,23 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>31.8</v>
+        <v>30.5</v>
       </c>
       <c r="E432" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F432" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G432" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="H432" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>31.3</v>
+        <v>31</v>
       </c>
       <c r="E433" t="n">
         <v>55</v>
@@ -16438,14 +16438,14 @@
         <v>0</v>
       </c>
       <c r="G433" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="H433" t="n">
         <v>3</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16466,23 +16466,23 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="E434" t="n">
         <v>69</v>
       </c>
       <c r="F434" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G434" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="H434" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16503,23 +16503,23 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="E435" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F435" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G435" t="n">
-        <v>18</v>
+        <v>17.3</v>
       </c>
       <c r="H435" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16540,7 +16540,7 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>31.3</v>
+        <v>31</v>
       </c>
       <c r="E436" t="n">
         <v>68</v>
@@ -16549,14 +16549,14 @@
         <v>0</v>
       </c>
       <c r="G436" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="H436" t="n">
         <v>3</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16577,7 @@
         </is>
       </c>
       <c r="D437" t="n">
-        <v>33.7</v>
+        <v>33.1</v>
       </c>
       <c r="E437" t="n">
         <v>49</v>
@@ -16586,14 +16586,14 @@
         <v>0</v>
       </c>
       <c r="G437" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="H437" t="n">
         <v>3</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16614,7 +16614,7 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>29.8</v>
+        <v>30.1</v>
       </c>
       <c r="E438" t="n">
         <v>66</v>
@@ -16623,14 +16623,14 @@
         <v>0</v>
       </c>
       <c r="G438" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="H438" t="n">
         <v>3</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16651,23 +16651,23 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>31.5</v>
+        <v>30.8</v>
       </c>
       <c r="E439" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F439" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G439" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="H439" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16688,23 +16688,23 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>32.7</v>
+        <v>32.4</v>
       </c>
       <c r="E440" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F440" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G440" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="H440" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16725,23 +16725,23 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
       <c r="E441" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F441" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G441" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="H441" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16762,23 +16762,23 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="E442" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F442" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G442" t="n">
-        <v>19.5</v>
+        <v>18.3</v>
       </c>
       <c r="H442" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16799,23 +16799,23 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>31.2</v>
+        <v>29.6</v>
       </c>
       <c r="E443" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F443" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G443" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="H443" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16836,23 +16836,23 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>31.9</v>
+        <v>30.9</v>
       </c>
       <c r="E444" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F444" t="n">
         <v>0</v>
       </c>
       <c r="G444" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="H444" t="n">
         <v>3</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16873,23 +16873,23 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>29.9</v>
+        <v>30.4</v>
       </c>
       <c r="E445" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F445" t="n">
         <v>0</v>
       </c>
       <c r="G445" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="H445" t="n">
         <v>3</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16910,23 +16910,23 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="E446" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F446" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G446" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="H446" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16947,23 +16947,23 @@
         </is>
       </c>
       <c r="D447" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="E447" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F447" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G447" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="H447" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -16984,23 +16984,23 @@
         </is>
       </c>
       <c r="D448" t="n">
-        <v>32.2</v>
+        <v>30.5</v>
       </c>
       <c r="E448" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F448" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G448" t="n">
-        <v>13.4</v>
+        <v>14.3</v>
       </c>
       <c r="H448" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -17021,23 +17021,23 @@
         </is>
       </c>
       <c r="D449" t="n">
-        <v>33.8</v>
+        <v>34.6</v>
       </c>
       <c r="E449" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F449" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G449" t="n">
-        <v>16.5</v>
+        <v>15.7</v>
       </c>
       <c r="H449" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -17058,23 +17058,23 @@
         </is>
       </c>
       <c r="D450" t="n">
-        <v>32.2</v>
+        <v>31.1</v>
       </c>
       <c r="E450" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F450" t="n">
         <v>0</v>
       </c>
       <c r="G450" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="H450" t="n">
         <v>3</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -17095,23 +17095,23 @@
         </is>
       </c>
       <c r="D451" t="n">
-        <v>30.8</v>
+        <v>31.6</v>
       </c>
       <c r="E451" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F451" t="n">
         <v>0</v>
       </c>
       <c r="G451" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H451" t="n">
         <v>3</v>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -17132,23 +17132,23 @@
         </is>
       </c>
       <c r="D452" t="n">
-        <v>30.2</v>
+        <v>30.6</v>
       </c>
       <c r="E452" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F452" t="n">
         <v>0</v>
       </c>
       <c r="G452" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="H452" t="n">
         <v>3</v>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -17169,23 +17169,23 @@
         </is>
       </c>
       <c r="D453" t="n">
-        <v>30.9</v>
+        <v>29.8</v>
       </c>
       <c r="E453" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F453" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="G453" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="H453" t="n">
         <v>96</v>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
         </is>
       </c>
       <c r="D454" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="E454" t="n">
         <v>64</v>
@@ -17215,14 +17215,14 @@
         <v>0</v>
       </c>
       <c r="G454" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="H454" t="n">
         <v>3</v>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -17243,23 +17243,23 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="E455" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F455" t="n">
         <v>0</v>
       </c>
       <c r="G455" t="n">
-        <v>15.1</v>
+        <v>15.5</v>
       </c>
       <c r="H455" t="n">
         <v>3</v>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -17280,23 +17280,23 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>31.5</v>
+        <v>31.9</v>
       </c>
       <c r="E456" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F456" t="n">
         <v>0</v>
       </c>
       <c r="G456" t="n">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="H456" t="n">
         <v>3</v>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -17320,20 +17320,20 @@
         <v>29.9</v>
       </c>
       <c r="E457" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F457" t="n">
         <v>0</v>
       </c>
       <c r="G457" t="n">
-        <v>15.4</v>
+        <v>14.8</v>
       </c>
       <c r="H457" t="n">
         <v>3</v>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -17354,23 +17354,23 @@
         </is>
       </c>
       <c r="D458" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="E458" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F458" t="n">
         <v>0.2</v>
       </c>
       <c r="G458" t="n">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="H458" t="n">
         <v>53</v>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -17391,23 +17391,23 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>30.9</v>
+        <v>30.1</v>
       </c>
       <c r="E459" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F459" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G459" t="n">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="H459" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -17428,23 +17428,23 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>32.4</v>
+        <v>31</v>
       </c>
       <c r="E460" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F460" t="n">
         <v>0</v>
       </c>
       <c r="G460" t="n">
-        <v>13.9</v>
+        <v>12.6</v>
       </c>
       <c r="H460" t="n">
         <v>3</v>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -17465,23 +17465,23 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>32.3</v>
+        <v>31.7</v>
       </c>
       <c r="E461" t="n">
         <v>55</v>
       </c>
       <c r="F461" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G461" t="n">
-        <v>15.9</v>
+        <v>16.4</v>
       </c>
       <c r="H461" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -17502,23 +17502,23 @@
         </is>
       </c>
       <c r="D462" t="n">
-        <v>30.5</v>
+        <v>31.3</v>
       </c>
       <c r="E462" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F462" t="n">
         <v>0</v>
       </c>
       <c r="G462" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="H462" t="n">
         <v>3</v>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -18458,7 +18458,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -18466,29 +18466,29 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>33.8</v>
+        <v>34.6</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kamareddy</t>
+          <t>Mahbubnagar</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="I16" t="n">
-        <v>61.2</v>
+        <v>61.6</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Kumuram Bheem Asifabad</t>
+          <t>Peddapalli</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -18496,11 +18496,11 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>19.5</v>
+        <v>18.3</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-09-22T12:45</t>
+          <t>2026-09-22T13:45</t>
         </is>
       </c>
     </row>
@@ -18576,7 +18576,7 @@
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -18603,7 +18603,7 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -18630,10 +18630,10 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>72.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -18675,7 +18675,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -18687,7 +18687,7 @@
         <v>81.8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -18711,10 +18711,10 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>73.8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -18786,7 +18786,7 @@
         <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
@@ -18810,7 +18810,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -18819,10 +18819,10 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -18846,10 +18846,10 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>69.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -18873,10 +18873,10 @@
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
@@ -18900,10 +18900,10 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>75.3</v>
+        <v>75.2</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -18918,19 +18918,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="E15" t="n">
         <v>23.8</v>
       </c>
       <c r="F15" t="n">
-        <v>68.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16">
@@ -18945,7 +18945,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -18954,7 +18954,7 @@
         <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>77.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -18975,13 +18975,13 @@
         <v>27.4</v>
       </c>
       <c r="D17" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="E17" t="n">
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="G17" t="n">
         <v>0.5</v>
@@ -19008,10 +19008,10 @@
         <v>23.9</v>
       </c>
       <c r="F18" t="n">
-        <v>71.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="19">
@@ -19035,10 +19035,10 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="20">
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -19062,10 +19062,10 @@
         <v>24.1</v>
       </c>
       <c r="F20" t="n">
-        <v>66.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
@@ -19080,7 +19080,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -19089,10 +19089,10 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>60.8</v>
+        <v>60.6</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22">
@@ -19107,16 +19107,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D22" t="n">
-        <v>32.2</v>
+        <v>31.4</v>
       </c>
       <c r="E22" t="n">
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>1.8</v>
@@ -19134,16 +19134,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="D23" t="n">
-        <v>30.8</v>
+        <v>31.6</v>
       </c>
       <c r="E23" t="n">
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>77.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
@@ -19170,7 +19170,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0.2</v>
@@ -19197,10 +19197,10 @@
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>80.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="26">
@@ -19218,7 +19218,7 @@
         <v>28.3</v>
       </c>
       <c r="D26" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="E26" t="n">
         <v>25.1</v>
@@ -19245,13 +19245,13 @@
         <v>27.7</v>
       </c>
       <c r="D27" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="E27" t="n">
         <v>24.2</v>
       </c>
       <c r="F27" t="n">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
       <c r="G27" t="n">
         <v>0.1</v>
@@ -19272,13 +19272,13 @@
         <v>28.4</v>
       </c>
       <c r="D28" t="n">
-        <v>31.5</v>
+        <v>31.9</v>
       </c>
       <c r="E28" t="n">
         <v>24.5</v>
       </c>
       <c r="F28" t="n">
-        <v>69.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G28" t="n">
         <v>0.2</v>
@@ -19323,7 +19323,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.5</v>
+        <v>30.7</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -19332,7 +19332,7 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>66.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="G30" t="n">
         <v>0.2</v>
@@ -19350,19 +19350,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="D31" t="n">
-        <v>30.9</v>
+        <v>30.5</v>
       </c>
       <c r="E31" t="n">
         <v>23.9</v>
       </c>
       <c r="F31" t="n">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="32">
@@ -19377,16 +19377,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="D32" t="n">
-        <v>32.4</v>
+        <v>32.1</v>
       </c>
       <c r="E32" t="n">
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>64.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
@@ -19416,7 +19416,7 @@
         <v>69.8</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="34">
@@ -19440,7 +19440,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>70.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="G34" t="n">
         <v>0.3</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I462"/>
+  <dimension ref="A1:I495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17519,6 +17519,1227 @@
       <c r="I462" t="inlineStr">
         <is>
           <t>2026-09-22T13:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E463" t="n">
+        <v>95</v>
+      </c>
+      <c r="F463" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G463" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H463" t="n">
+        <v>51</v>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E464" t="n">
+        <v>77</v>
+      </c>
+      <c r="F464" t="n">
+        <v>0</v>
+      </c>
+      <c r="G464" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H464" t="n">
+        <v>3</v>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E465" t="n">
+        <v>82</v>
+      </c>
+      <c r="F465" t="n">
+        <v>0</v>
+      </c>
+      <c r="G465" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H465" t="n">
+        <v>3</v>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E466" t="n">
+        <v>66</v>
+      </c>
+      <c r="F466" t="n">
+        <v>0</v>
+      </c>
+      <c r="G466" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H466" t="n">
+        <v>3</v>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E467" t="n">
+        <v>93</v>
+      </c>
+      <c r="F467" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G467" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H467" t="n">
+        <v>95</v>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>27</v>
+      </c>
+      <c r="E468" t="n">
+        <v>78</v>
+      </c>
+      <c r="F468" t="n">
+        <v>0</v>
+      </c>
+      <c r="G468" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H468" t="n">
+        <v>3</v>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E469" t="n">
+        <v>91</v>
+      </c>
+      <c r="F469" t="n">
+        <v>0</v>
+      </c>
+      <c r="G469" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H469" t="n">
+        <v>3</v>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E470" t="n">
+        <v>68</v>
+      </c>
+      <c r="F470" t="n">
+        <v>0</v>
+      </c>
+      <c r="G470" t="n">
+        <v>11</v>
+      </c>
+      <c r="H470" t="n">
+        <v>3</v>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E471" t="n">
+        <v>94</v>
+      </c>
+      <c r="F471" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G471" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H471" t="n">
+        <v>51</v>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E472" t="n">
+        <v>92</v>
+      </c>
+      <c r="F472" t="n">
+        <v>0</v>
+      </c>
+      <c r="G472" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H472" t="n">
+        <v>3</v>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E473" t="n">
+        <v>75</v>
+      </c>
+      <c r="F473" t="n">
+        <v>0</v>
+      </c>
+      <c r="G473" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H473" t="n">
+        <v>3</v>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E474" t="n">
+        <v>96</v>
+      </c>
+      <c r="F474" t="n">
+        <v>0</v>
+      </c>
+      <c r="G474" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H474" t="n">
+        <v>3</v>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E475" t="n">
+        <v>79</v>
+      </c>
+      <c r="F475" t="n">
+        <v>0</v>
+      </c>
+      <c r="G475" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H475" t="n">
+        <v>3</v>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E476" t="n">
+        <v>97</v>
+      </c>
+      <c r="F476" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G476" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H476" t="n">
+        <v>95</v>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>27</v>
+      </c>
+      <c r="E477" t="n">
+        <v>88</v>
+      </c>
+      <c r="F477" t="n">
+        <v>0</v>
+      </c>
+      <c r="G477" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H477" t="n">
+        <v>3</v>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E478" t="n">
+        <v>85</v>
+      </c>
+      <c r="F478" t="n">
+        <v>0</v>
+      </c>
+      <c r="G478" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H478" t="n">
+        <v>3</v>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E479" t="n">
+        <v>79</v>
+      </c>
+      <c r="F479" t="n">
+        <v>0</v>
+      </c>
+      <c r="G479" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H479" t="n">
+        <v>3</v>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E480" t="n">
+        <v>85</v>
+      </c>
+      <c r="F480" t="n">
+        <v>0</v>
+      </c>
+      <c r="G480" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H480" t="n">
+        <v>3</v>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>26</v>
+      </c>
+      <c r="E481" t="n">
+        <v>81</v>
+      </c>
+      <c r="F481" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G481" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H481" t="n">
+        <v>51</v>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E482" t="n">
+        <v>89</v>
+      </c>
+      <c r="F482" t="n">
+        <v>0</v>
+      </c>
+      <c r="G482" t="n">
+        <v>8</v>
+      </c>
+      <c r="H482" t="n">
+        <v>3</v>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E483" t="n">
+        <v>89</v>
+      </c>
+      <c r="F483" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G483" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H483" t="n">
+        <v>53</v>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E484" t="n">
+        <v>91</v>
+      </c>
+      <c r="F484" t="n">
+        <v>0</v>
+      </c>
+      <c r="G484" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H484" t="n">
+        <v>3</v>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E485" t="n">
+        <v>94</v>
+      </c>
+      <c r="F485" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G485" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H485" t="n">
+        <v>53</v>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E486" t="n">
+        <v>90</v>
+      </c>
+      <c r="F486" t="n">
+        <v>0</v>
+      </c>
+      <c r="G486" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H486" t="n">
+        <v>3</v>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E487" t="n">
+        <v>90</v>
+      </c>
+      <c r="F487" t="n">
+        <v>0</v>
+      </c>
+      <c r="G487" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H487" t="n">
+        <v>3</v>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E488" t="n">
+        <v>90</v>
+      </c>
+      <c r="F488" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G488" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H488" t="n">
+        <v>80</v>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E489" t="n">
+        <v>72</v>
+      </c>
+      <c r="F489" t="n">
+        <v>0</v>
+      </c>
+      <c r="G489" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H489" t="n">
+        <v>3</v>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E490" t="n">
+        <v>94</v>
+      </c>
+      <c r="F490" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G490" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H490" t="n">
+        <v>51</v>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>29</v>
+      </c>
+      <c r="E491" t="n">
+        <v>73</v>
+      </c>
+      <c r="F491" t="n">
+        <v>0</v>
+      </c>
+      <c r="G491" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H491" t="n">
+        <v>3</v>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E492" t="n">
+        <v>88</v>
+      </c>
+      <c r="F492" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G492" t="n">
+        <v>14</v>
+      </c>
+      <c r="H492" t="n">
+        <v>51</v>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E493" t="n">
+        <v>73</v>
+      </c>
+      <c r="F493" t="n">
+        <v>0</v>
+      </c>
+      <c r="G493" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H493" t="n">
+        <v>3</v>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E494" t="n">
+        <v>80</v>
+      </c>
+      <c r="F494" t="n">
+        <v>0</v>
+      </c>
+      <c r="G494" t="n">
+        <v>10</v>
+      </c>
+      <c r="H494" t="n">
+        <v>3</v>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E495" t="n">
+        <v>84</v>
+      </c>
+      <c r="F495" t="n">
+        <v>0</v>
+      </c>
+      <c r="G495" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H495" t="n">
+        <v>3</v>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
         </is>
       </c>
     </row>
@@ -17533,7 +18754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18501,6 +19722,67 @@
       <c r="O16" t="inlineStr">
         <is>
           <t>2026-09-22T13:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>33</v>
+      </c>
+      <c r="D17" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>14</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:30</t>
         </is>
       </c>
     </row>
@@ -18567,7 +19849,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -18576,10 +19858,10 @@
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>80.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -18594,7 +19876,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -18621,7 +19903,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.6</v>
+        <v>29.4</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -18630,7 +19912,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>72.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.2</v>
@@ -18648,7 +19930,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -18657,7 +19939,7 @@
         <v>24.8</v>
       </c>
       <c r="F5" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
       <c r="G5" t="n">
         <v>0.2</v>
@@ -18675,7 +19957,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -18684,10 +19966,10 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>81.8</v>
+        <v>82.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -18702,7 +19984,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -18711,7 +19993,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>73.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -18729,7 +20011,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -18738,7 +20020,7 @@
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>78.5</v>
+        <v>79.3</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -18756,7 +20038,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -18765,7 +20047,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>65.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="G9" t="n">
         <v>2.4</v>
@@ -18783,7 +20065,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -18792,10 +20074,10 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>79.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11">
@@ -18810,7 +20092,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -18819,7 +20101,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>78.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0.1</v>
@@ -18837,7 +20119,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -18846,7 +20128,7 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>70.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -18864,7 +20146,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -18873,7 +20155,7 @@
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>80.2</v>
+        <v>81.3</v>
       </c>
       <c r="G13" t="n">
         <v>0.1</v>
@@ -18900,7 +20182,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>75.2</v>
+        <v>75.5</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -18918,7 +20200,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -18927,10 +20209,10 @@
         <v>23.8</v>
       </c>
       <c r="F15" t="n">
-        <v>68.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="16">
@@ -18945,7 +20227,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -18954,7 +20236,7 @@
         <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>78.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -18972,7 +20254,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
@@ -18981,7 +20263,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>77.7</v>
+        <v>78.2</v>
       </c>
       <c r="G17" t="n">
         <v>0.5</v>
@@ -18999,7 +20281,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -19008,7 +20290,7 @@
         <v>23.9</v>
       </c>
       <c r="F18" t="n">
-        <v>71.8</v>
+        <v>72.3</v>
       </c>
       <c r="G18" t="n">
         <v>0.3</v>
@@ -19026,7 +20308,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -19035,7 +20317,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>78.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="G19" t="n">
         <v>0.1</v>
@@ -19053,7 +20335,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -19062,10 +20344,10 @@
         <v>24.1</v>
       </c>
       <c r="F20" t="n">
-        <v>66.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="21">
@@ -19080,7 +20362,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -19089,7 +20371,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>60.6</v>
+        <v>62.5</v>
       </c>
       <c r="G21" t="n">
         <v>0.2</v>
@@ -19107,7 +20389,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -19116,10 +20398,10 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>68.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="G22" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -19134,7 +20416,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -19143,7 +20425,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>77.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
@@ -19161,7 +20443,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -19170,10 +20452,10 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>80.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="25">
@@ -19188,7 +20470,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -19197,7 +20479,7 @@
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>80.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0.6</v>
@@ -19215,7 +20497,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
@@ -19224,7 +20506,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>79.3</v>
+        <v>80</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -19242,7 +20524,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -19251,10 +20533,10 @@
         <v>24.2</v>
       </c>
       <c r="F27" t="n">
-        <v>69.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="28">
@@ -19278,7 +20560,7 @@
         <v>24.5</v>
       </c>
       <c r="F28" t="n">
-        <v>68.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G28" t="n">
         <v>0.2</v>
@@ -19296,7 +20578,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
@@ -19305,10 +20587,10 @@
         <v>24.4</v>
       </c>
       <c r="F29" t="n">
-        <v>78.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="30">
@@ -19323,7 +20605,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -19332,7 +20614,7 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>66</v>
+        <v>66.5</v>
       </c>
       <c r="G30" t="n">
         <v>0.2</v>
@@ -19350,7 +20632,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -19359,10 +20641,10 @@
         <v>23.9</v>
       </c>
       <c r="F31" t="n">
-        <v>68.90000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32">
@@ -19377,7 +20659,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -19386,7 +20668,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>64.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
@@ -19404,7 +20686,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -19413,7 +20695,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>69.8</v>
+        <v>70.5</v>
       </c>
       <c r="G33" t="n">
         <v>0.2</v>
@@ -19431,7 +20713,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -19440,7 +20722,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>70.8</v>
+        <v>71.7</v>
       </c>
       <c r="G34" t="n">
         <v>0.3</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I495"/>
+  <dimension ref="A1:I528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18740,6 +18740,1227 @@
       <c r="I495" t="inlineStr">
         <is>
           <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E496" t="n">
+        <v>96</v>
+      </c>
+      <c r="F496" t="n">
+        <v>0</v>
+      </c>
+      <c r="G496" t="n">
+        <v>4</v>
+      </c>
+      <c r="H496" t="n">
+        <v>3</v>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E497" t="n">
+        <v>89</v>
+      </c>
+      <c r="F497" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G497" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H497" t="n">
+        <v>51</v>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E498" t="n">
+        <v>87</v>
+      </c>
+      <c r="F498" t="n">
+        <v>0</v>
+      </c>
+      <c r="G498" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H498" t="n">
+        <v>3</v>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E499" t="n">
+        <v>93</v>
+      </c>
+      <c r="F499" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G499" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H499" t="n">
+        <v>53</v>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E500" t="n">
+        <v>93</v>
+      </c>
+      <c r="F500" t="n">
+        <v>0</v>
+      </c>
+      <c r="G500" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H500" t="n">
+        <v>3</v>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E501" t="n">
+        <v>83</v>
+      </c>
+      <c r="F501" t="n">
+        <v>0</v>
+      </c>
+      <c r="G501" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H501" t="n">
+        <v>3</v>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E502" t="n">
+        <v>94</v>
+      </c>
+      <c r="F502" t="n">
+        <v>0</v>
+      </c>
+      <c r="G502" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H502" t="n">
+        <v>3</v>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E503" t="n">
+        <v>94</v>
+      </c>
+      <c r="F503" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G503" t="n">
+        <v>16</v>
+      </c>
+      <c r="H503" t="n">
+        <v>51</v>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E504" t="n">
+        <v>96</v>
+      </c>
+      <c r="F504" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G504" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H504" t="n">
+        <v>53</v>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E505" t="n">
+        <v>89</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0</v>
+      </c>
+      <c r="G505" t="n">
+        <v>10</v>
+      </c>
+      <c r="H505" t="n">
+        <v>3</v>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E506" t="n">
+        <v>82</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0</v>
+      </c>
+      <c r="G506" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H506" t="n">
+        <v>3</v>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E507" t="n">
+        <v>96</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0</v>
+      </c>
+      <c r="G507" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H507" t="n">
+        <v>3</v>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E508" t="n">
+        <v>88</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0</v>
+      </c>
+      <c r="G508" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H508" t="n">
+        <v>3</v>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E509" t="n">
+        <v>96</v>
+      </c>
+      <c r="F509" t="n">
+        <v>0</v>
+      </c>
+      <c r="G509" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H509" t="n">
+        <v>3</v>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E510" t="n">
+        <v>89</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0</v>
+      </c>
+      <c r="G510" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H510" t="n">
+        <v>3</v>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E511" t="n">
+        <v>95</v>
+      </c>
+      <c r="F511" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G511" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H511" t="n">
+        <v>95</v>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E512" t="n">
+        <v>97</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G512" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H512" t="n">
+        <v>53</v>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E513" t="n">
+        <v>92</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0</v>
+      </c>
+      <c r="G513" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H513" t="n">
+        <v>3</v>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E514" t="n">
+        <v>94</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0</v>
+      </c>
+      <c r="G514" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H514" t="n">
+        <v>3</v>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E515" t="n">
+        <v>81</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0</v>
+      </c>
+      <c r="G515" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H515" t="n">
+        <v>3</v>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E516" t="n">
+        <v>96</v>
+      </c>
+      <c r="F516" t="n">
+        <v>0</v>
+      </c>
+      <c r="G516" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H516" t="n">
+        <v>3</v>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E517" t="n">
+        <v>92</v>
+      </c>
+      <c r="F517" t="n">
+        <v>0</v>
+      </c>
+      <c r="G517" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H517" t="n">
+        <v>3</v>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E518" t="n">
+        <v>98</v>
+      </c>
+      <c r="F518" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G518" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H518" t="n">
+        <v>53</v>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>26</v>
+      </c>
+      <c r="E519" t="n">
+        <v>96</v>
+      </c>
+      <c r="F519" t="n">
+        <v>0</v>
+      </c>
+      <c r="G519" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H519" t="n">
+        <v>3</v>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>25</v>
+      </c>
+      <c r="E520" t="n">
+        <v>90</v>
+      </c>
+      <c r="F520" t="n">
+        <v>0</v>
+      </c>
+      <c r="G520" t="n">
+        <v>9</v>
+      </c>
+      <c r="H520" t="n">
+        <v>3</v>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E521" t="n">
+        <v>96</v>
+      </c>
+      <c r="F521" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G521" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H521" t="n">
+        <v>51</v>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E522" t="n">
+        <v>95</v>
+      </c>
+      <c r="F522" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G522" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H522" t="n">
+        <v>53</v>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E523" t="n">
+        <v>92</v>
+      </c>
+      <c r="F523" t="n">
+        <v>0</v>
+      </c>
+      <c r="G523" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H523" t="n">
+        <v>3</v>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E524" t="n">
+        <v>80</v>
+      </c>
+      <c r="F524" t="n">
+        <v>0</v>
+      </c>
+      <c r="G524" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H524" t="n">
+        <v>3</v>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E525" t="n">
+        <v>98</v>
+      </c>
+      <c r="F525" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G525" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H525" t="n">
+        <v>51</v>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E526" t="n">
+        <v>96</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G526" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H526" t="n">
+        <v>51</v>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E527" t="n">
+        <v>85</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0</v>
+      </c>
+      <c r="G527" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H527" t="n">
+        <v>3</v>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E528" t="n">
+        <v>87</v>
+      </c>
+      <c r="F528" t="n">
+        <v>0</v>
+      </c>
+      <c r="G528" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H528" t="n">
+        <v>3</v>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
         </is>
       </c>
     </row>
@@ -18754,7 +19975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19783,6 +21004,67 @@
       <c r="O17" t="inlineStr">
         <is>
           <t>2026-09-22T18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>33</v>
+      </c>
+      <c r="D18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:15</t>
         </is>
       </c>
     </row>
@@ -19849,7 +21131,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -19858,7 +21140,7 @@
         <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>81.3</v>
+        <v>82.2</v>
       </c>
       <c r="G2" t="n">
         <v>0.2</v>
@@ -19876,7 +21158,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -19885,10 +21167,10 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>77.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
@@ -19903,7 +21185,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -19912,7 +21194,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>72.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="G4" t="n">
         <v>0.2</v>
@@ -19930,19 +21212,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.3</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
       </c>
       <c r="E5" t="n">
-        <v>24.8</v>
+        <v>23.7</v>
       </c>
       <c r="F5" t="n">
-        <v>62.6</v>
+        <v>64.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6">
@@ -19957,7 +21239,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -19966,7 +21248,7 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>82.5</v>
+        <v>83.2</v>
       </c>
       <c r="G6" t="n">
         <v>0.2</v>
@@ -19984,7 +21266,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -19993,7 +21275,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>74.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -20011,7 +21293,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -20020,7 +21302,7 @@
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>79.3</v>
+        <v>80.2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -20038,7 +21320,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29.4</v>
+        <v>29.1</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -20047,10 +21329,10 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>65.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -20065,7 +21347,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -20074,10 +21356,10 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>80.40000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11">
@@ -20092,16 +21374,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="F11" t="n">
-        <v>79.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="G11" t="n">
         <v>0.1</v>
@@ -20119,7 +21401,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -20128,7 +21410,7 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>70.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -20146,7 +21428,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -20155,7 +21437,7 @@
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>81.3</v>
+        <v>82.2</v>
       </c>
       <c r="G13" t="n">
         <v>0.1</v>
@@ -20173,7 +21455,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -20182,7 +21464,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>75.5</v>
+        <v>76.2</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -20200,16 +21482,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.8</v>
+        <v>27.4</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
       </c>
       <c r="E15" t="n">
-        <v>23.8</v>
+        <v>22.9</v>
       </c>
       <c r="F15" t="n">
-        <v>70.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>1.9</v>
@@ -20227,7 +21509,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -20236,7 +21518,7 @@
         <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>78.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -20254,19 +21536,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>23.6</v>
       </c>
       <c r="F17" t="n">
-        <v>78.2</v>
+        <v>79.2</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -20281,19 +21563,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27.6</v>
+        <v>27.3</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
       </c>
       <c r="E18" t="n">
-        <v>23.9</v>
+        <v>22.7</v>
       </c>
       <c r="F18" t="n">
-        <v>72.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
@@ -20308,7 +21590,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -20317,7 +21599,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>79</v>
+        <v>79.8</v>
       </c>
       <c r="G19" t="n">
         <v>0.1</v>
@@ -20335,16 +21617,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.5</v>
+        <v>28.2</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
       </c>
       <c r="E20" t="n">
-        <v>24.1</v>
+        <v>23.1</v>
       </c>
       <c r="F20" t="n">
-        <v>67.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="G20" t="n">
         <v>0.6</v>
@@ -20362,7 +21644,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -20371,7 +21653,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>62.5</v>
+        <v>63.7</v>
       </c>
       <c r="G21" t="n">
         <v>0.2</v>
@@ -20389,7 +21671,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.9</v>
+        <v>27.6</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -20398,7 +21680,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>70</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -20416,7 +21698,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -20425,7 +21707,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>78.5</v>
+        <v>79.3</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
@@ -20443,19 +21725,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
       </c>
       <c r="E24" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="F24" t="n">
-        <v>81.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="25">
@@ -20470,7 +21752,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -20479,7 +21761,7 @@
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>81.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="G25" t="n">
         <v>0.6</v>
@@ -20497,16 +21779,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
       </c>
       <c r="E26" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>80</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -20524,19 +21806,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
       </c>
       <c r="E27" t="n">
-        <v>24.2</v>
+        <v>22.8</v>
       </c>
       <c r="F27" t="n">
-        <v>70.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="28">
@@ -20551,19 +21833,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
       </c>
       <c r="E28" t="n">
-        <v>24.5</v>
+        <v>23.7</v>
       </c>
       <c r="F28" t="n">
-        <v>69.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="29">
@@ -20578,16 +21860,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
       </c>
       <c r="E29" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="F29" t="n">
-        <v>79.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>0.2</v>
@@ -20605,7 +21887,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -20614,7 +21896,7 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>66.5</v>
+        <v>67.3</v>
       </c>
       <c r="G30" t="n">
         <v>0.2</v>
@@ -20632,19 +21914,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.4</v>
+        <v>27.1</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
       </c>
       <c r="E31" t="n">
-        <v>23.9</v>
+        <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>70.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="32">
@@ -20659,7 +21941,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>29.1</v>
+        <v>28.8</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -20668,10 +21950,10 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>65.09999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="33">
@@ -20686,7 +21968,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -20695,7 +21977,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>70.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0.2</v>
@@ -20713,7 +21995,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -20722,7 +22004,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>71.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="G34" t="n">
         <v>0.3</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I528"/>
+  <dimension ref="A1:I561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19961,6 +19961,1227 @@
       <c r="I528" t="inlineStr">
         <is>
           <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E529" t="n">
+        <v>94</v>
+      </c>
+      <c r="F529" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G529" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H529" t="n">
+        <v>51</v>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E530" t="n">
+        <v>96</v>
+      </c>
+      <c r="F530" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G530" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H530" t="n">
+        <v>81</v>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E531" t="n">
+        <v>80</v>
+      </c>
+      <c r="F531" t="n">
+        <v>0</v>
+      </c>
+      <c r="G531" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H531" t="n">
+        <v>3</v>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E532" t="n">
+        <v>89</v>
+      </c>
+      <c r="F532" t="n">
+        <v>0</v>
+      </c>
+      <c r="G532" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H532" t="n">
+        <v>3</v>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E533" t="n">
+        <v>90</v>
+      </c>
+      <c r="F533" t="n">
+        <v>0</v>
+      </c>
+      <c r="G533" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H533" t="n">
+        <v>3</v>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E534" t="n">
+        <v>87</v>
+      </c>
+      <c r="F534" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G534" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H534" t="n">
+        <v>51</v>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E535" t="n">
+        <v>91</v>
+      </c>
+      <c r="F535" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G535" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H535" t="n">
+        <v>51</v>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E536" t="n">
+        <v>89</v>
+      </c>
+      <c r="F536" t="n">
+        <v>0</v>
+      </c>
+      <c r="G536" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H536" t="n">
+        <v>3</v>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E537" t="n">
+        <v>94</v>
+      </c>
+      <c r="F537" t="n">
+        <v>0</v>
+      </c>
+      <c r="G537" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H537" t="n">
+        <v>3</v>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E538" t="n">
+        <v>84</v>
+      </c>
+      <c r="F538" t="n">
+        <v>0</v>
+      </c>
+      <c r="G538" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H538" t="n">
+        <v>3</v>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E539" t="n">
+        <v>95</v>
+      </c>
+      <c r="F539" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G539" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H539" t="n">
+        <v>51</v>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E540" t="n">
+        <v>90</v>
+      </c>
+      <c r="F540" t="n">
+        <v>0</v>
+      </c>
+      <c r="G540" t="n">
+        <v>9</v>
+      </c>
+      <c r="H540" t="n">
+        <v>3</v>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E541" t="n">
+        <v>95</v>
+      </c>
+      <c r="F541" t="n">
+        <v>0</v>
+      </c>
+      <c r="G541" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H541" t="n">
+        <v>3</v>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E542" t="n">
+        <v>96</v>
+      </c>
+      <c r="F542" t="n">
+        <v>0</v>
+      </c>
+      <c r="G542" t="n">
+        <v>16</v>
+      </c>
+      <c r="H542" t="n">
+        <v>3</v>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>26</v>
+      </c>
+      <c r="E543" t="n">
+        <v>90</v>
+      </c>
+      <c r="F543" t="n">
+        <v>0</v>
+      </c>
+      <c r="G543" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H543" t="n">
+        <v>3</v>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>23</v>
+      </c>
+      <c r="E544" t="n">
+        <v>97</v>
+      </c>
+      <c r="F544" t="n">
+        <v>0</v>
+      </c>
+      <c r="G544" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H544" t="n">
+        <v>3</v>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E545" t="n">
+        <v>93</v>
+      </c>
+      <c r="F545" t="n">
+        <v>0</v>
+      </c>
+      <c r="G545" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H545" t="n">
+        <v>3</v>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E546" t="n">
+        <v>93</v>
+      </c>
+      <c r="F546" t="n">
+        <v>0</v>
+      </c>
+      <c r="G546" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H546" t="n">
+        <v>3</v>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E547" t="n">
+        <v>94</v>
+      </c>
+      <c r="F547" t="n">
+        <v>0</v>
+      </c>
+      <c r="G547" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H547" t="n">
+        <v>3</v>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E548" t="n">
+        <v>87</v>
+      </c>
+      <c r="F548" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G548" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H548" t="n">
+        <v>51</v>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E549" t="n">
+        <v>95</v>
+      </c>
+      <c r="F549" t="n">
+        <v>0</v>
+      </c>
+      <c r="G549" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H549" t="n">
+        <v>3</v>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E550" t="n">
+        <v>96</v>
+      </c>
+      <c r="F550" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G550" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H550" t="n">
+        <v>53</v>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E551" t="n">
+        <v>98</v>
+      </c>
+      <c r="F551" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G551" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H551" t="n">
+        <v>51</v>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E552" t="n">
+        <v>89</v>
+      </c>
+      <c r="F552" t="n">
+        <v>0</v>
+      </c>
+      <c r="G552" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H552" t="n">
+        <v>3</v>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E553" t="n">
+        <v>88</v>
+      </c>
+      <c r="F553" t="n">
+        <v>0</v>
+      </c>
+      <c r="G553" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H553" t="n">
+        <v>3</v>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E554" t="n">
+        <v>95</v>
+      </c>
+      <c r="F554" t="n">
+        <v>0</v>
+      </c>
+      <c r="G554" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H554" t="n">
+        <v>3</v>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E555" t="n">
+        <v>92</v>
+      </c>
+      <c r="F555" t="n">
+        <v>0</v>
+      </c>
+      <c r="G555" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H555" t="n">
+        <v>3</v>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E556" t="n">
+        <v>92</v>
+      </c>
+      <c r="F556" t="n">
+        <v>0</v>
+      </c>
+      <c r="G556" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H556" t="n">
+        <v>3</v>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E557" t="n">
+        <v>85</v>
+      </c>
+      <c r="F557" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G557" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H557" t="n">
+        <v>51</v>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E558" t="n">
+        <v>98</v>
+      </c>
+      <c r="F558" t="n">
+        <v>0</v>
+      </c>
+      <c r="G558" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H558" t="n">
+        <v>3</v>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E559" t="n">
+        <v>95</v>
+      </c>
+      <c r="F559" t="n">
+        <v>0</v>
+      </c>
+      <c r="G559" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H559" t="n">
+        <v>3</v>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E560" t="n">
+        <v>79</v>
+      </c>
+      <c r="F560" t="n">
+        <v>0</v>
+      </c>
+      <c r="G560" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H560" t="n">
+        <v>3</v>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>24</v>
+      </c>
+      <c r="E561" t="n">
+        <v>89</v>
+      </c>
+      <c r="F561" t="n">
+        <v>0</v>
+      </c>
+      <c r="G561" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H561" t="n">
+        <v>3</v>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
         </is>
       </c>
     </row>
@@ -19975,7 +21196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21065,6 +22286,67 @@
       <c r="O18" t="inlineStr">
         <is>
           <t>2026-09-22T23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>33</v>
+      </c>
+      <c r="D19" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:30</t>
         </is>
       </c>
     </row>
@@ -21131,19 +22413,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
       </c>
       <c r="E2" t="n">
-        <v>25.1</v>
+        <v>24.3</v>
       </c>
       <c r="F2" t="n">
-        <v>82.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3">
@@ -21158,19 +22440,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.3</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>24.7</v>
       </c>
       <c r="F3" t="n">
-        <v>77.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
@@ -21185,7 +22467,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -21194,7 +22476,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>73.8</v>
+        <v>74.2</v>
       </c>
       <c r="G4" t="n">
         <v>0.2</v>
@@ -21212,7 +22494,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>28.7</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -21221,7 +22503,7 @@
         <v>23.7</v>
       </c>
       <c r="F5" t="n">
-        <v>64.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>0.4</v>
@@ -21239,16 +22521,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" t="n">
-        <v>25.1</v>
+        <v>24.2</v>
       </c>
       <c r="F6" t="n">
-        <v>83.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.2</v>
@@ -21266,7 +22548,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -21275,10 +22557,10 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>74.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -21293,7 +22575,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -21302,10 +22584,10 @@
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>80.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -21320,7 +22602,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29.1</v>
+        <v>28.8</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -21329,7 +22611,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>67.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>2.5</v>
@@ -21347,16 +22629,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="F10" t="n">
-        <v>81.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>1.3</v>
@@ -21374,16 +22656,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>25.6</v>
+        <v>25.2</v>
       </c>
       <c r="F11" t="n">
-        <v>80</v>
+        <v>80.2</v>
       </c>
       <c r="G11" t="n">
         <v>0.1</v>
@@ -21401,7 +22683,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -21410,10 +22692,10 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>71.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13">
@@ -21428,7 +22710,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -21437,7 +22719,7 @@
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>82.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>0.1</v>
@@ -21455,7 +22737,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -21464,7 +22746,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>76.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -21482,16 +22764,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
       </c>
       <c r="E15" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="F15" t="n">
-        <v>72.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="G15" t="n">
         <v>1.9</v>
@@ -21509,7 +22791,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -21518,7 +22800,7 @@
         <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>79.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -21536,16 +22818,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
       </c>
       <c r="E17" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="F17" t="n">
-        <v>79.2</v>
+        <v>80.3</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
@@ -21563,7 +22845,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27.3</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -21572,7 +22854,7 @@
         <v>22.7</v>
       </c>
       <c r="F18" t="n">
-        <v>73.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>0.5</v>
@@ -21590,7 +22872,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -21599,7 +22881,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>79.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0.1</v>
@@ -21617,7 +22899,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.2</v>
+        <v>27.9</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -21626,7 +22908,7 @@
         <v>23.1</v>
       </c>
       <c r="F20" t="n">
-        <v>69.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>0.6</v>
@@ -21644,19 +22926,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
       </c>
       <c r="E21" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="F21" t="n">
-        <v>63.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="22">
@@ -21671,7 +22953,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -21680,7 +22962,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>71.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -21698,19 +22980,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.9</v>
+        <v>27.6</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
       </c>
       <c r="E23" t="n">
-        <v>24.4</v>
+        <v>23.8</v>
       </c>
       <c r="F23" t="n">
-        <v>79.3</v>
+        <v>80.3</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="24">
@@ -21725,19 +23007,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
       </c>
       <c r="E24" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="F24" t="n">
-        <v>82.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="25">
@@ -21752,7 +23034,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -21761,7 +23043,7 @@
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>82</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0.6</v>
@@ -21779,16 +23061,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="F26" t="n">
-        <v>80.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -21806,16 +23088,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.2</v>
+        <v>26.9</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
       </c>
       <c r="E27" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="F27" t="n">
-        <v>72.2</v>
+        <v>73.5</v>
       </c>
       <c r="G27" t="n">
         <v>0.7</v>
@@ -21833,7 +23115,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28.1</v>
+        <v>27.8</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -21842,7 +23124,7 @@
         <v>23.7</v>
       </c>
       <c r="F28" t="n">
-        <v>70.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G28" t="n">
         <v>0.4</v>
@@ -21860,16 +23142,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
       </c>
       <c r="E29" t="n">
-        <v>24.3</v>
+        <v>23.5</v>
       </c>
       <c r="F29" t="n">
-        <v>80.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="G29" t="n">
         <v>0.2</v>
@@ -21887,7 +23169,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -21896,10 +23178,10 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>67.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31">
@@ -21914,16 +23196,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
       </c>
       <c r="E31" t="n">
-        <v>22.6</v>
+        <v>22.3</v>
       </c>
       <c r="F31" t="n">
-        <v>71.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="G31" t="n">
         <v>0.5</v>
@@ -21941,7 +23223,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28.8</v>
+        <v>28.5</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -21950,7 +23232,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>67.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="G32" t="n">
         <v>2.1</v>
@@ -21968,7 +23250,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -21977,7 +23259,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>71.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="G33" t="n">
         <v>0.2</v>
@@ -21995,16 +23277,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>28.2</v>
+        <v>27.9</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
       </c>
       <c r="E34" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="F34" t="n">
-        <v>72.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G34" t="n">
         <v>0.3</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I561"/>
+  <dimension ref="A1:I594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21182,6 +21182,1227 @@
       <c r="I561" t="inlineStr">
         <is>
           <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E562" t="n">
+        <v>94</v>
+      </c>
+      <c r="F562" t="n">
+        <v>0</v>
+      </c>
+      <c r="G562" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H562" t="n">
+        <v>3</v>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E563" t="n">
+        <v>96</v>
+      </c>
+      <c r="F563" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G563" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H563" t="n">
+        <v>80</v>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E564" t="n">
+        <v>89</v>
+      </c>
+      <c r="F564" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G564" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H564" t="n">
+        <v>51</v>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E565" t="n">
+        <v>88</v>
+      </c>
+      <c r="F565" t="n">
+        <v>0</v>
+      </c>
+      <c r="G565" t="n">
+        <v>13</v>
+      </c>
+      <c r="H565" t="n">
+        <v>3</v>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E566" t="n">
+        <v>93</v>
+      </c>
+      <c r="F566" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G566" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H566" t="n">
+        <v>51</v>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E567" t="n">
+        <v>85</v>
+      </c>
+      <c r="F567" t="n">
+        <v>0</v>
+      </c>
+      <c r="G567" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="H567" t="n">
+        <v>3</v>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E568" t="n">
+        <v>97</v>
+      </c>
+      <c r="F568" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G568" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H568" t="n">
+        <v>61</v>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E569" t="n">
+        <v>89</v>
+      </c>
+      <c r="F569" t="n">
+        <v>0</v>
+      </c>
+      <c r="G569" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H569" t="n">
+        <v>3</v>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E570" t="n">
+        <v>96</v>
+      </c>
+      <c r="F570" t="n">
+        <v>0</v>
+      </c>
+      <c r="G570" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H570" t="n">
+        <v>3</v>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E571" t="n">
+        <v>91</v>
+      </c>
+      <c r="F571" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G571" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H571" t="n">
+        <v>51</v>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E572" t="n">
+        <v>93</v>
+      </c>
+      <c r="F572" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G572" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H572" t="n">
+        <v>51</v>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E573" t="n">
+        <v>87</v>
+      </c>
+      <c r="F573" t="n">
+        <v>0</v>
+      </c>
+      <c r="G573" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H573" t="n">
+        <v>3</v>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E574" t="n">
+        <v>93</v>
+      </c>
+      <c r="F574" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G574" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H574" t="n">
+        <v>51</v>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E575" t="n">
+        <v>94</v>
+      </c>
+      <c r="F575" t="n">
+        <v>0</v>
+      </c>
+      <c r="G575" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H575" t="n">
+        <v>3</v>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E576" t="n">
+        <v>91</v>
+      </c>
+      <c r="F576" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G576" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H576" t="n">
+        <v>53</v>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>23</v>
+      </c>
+      <c r="E577" t="n">
+        <v>97</v>
+      </c>
+      <c r="F577" t="n">
+        <v>0</v>
+      </c>
+      <c r="G577" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H577" t="n">
+        <v>3</v>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>23</v>
+      </c>
+      <c r="E578" t="n">
+        <v>92</v>
+      </c>
+      <c r="F578" t="n">
+        <v>0</v>
+      </c>
+      <c r="G578" t="n">
+        <v>17</v>
+      </c>
+      <c r="H578" t="n">
+        <v>3</v>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E579" t="n">
+        <v>97</v>
+      </c>
+      <c r="F579" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G579" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H579" t="n">
+        <v>53</v>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E580" t="n">
+        <v>94</v>
+      </c>
+      <c r="F580" t="n">
+        <v>0</v>
+      </c>
+      <c r="G580" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H580" t="n">
+        <v>3</v>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E581" t="n">
+        <v>83</v>
+      </c>
+      <c r="F581" t="n">
+        <v>0</v>
+      </c>
+      <c r="G581" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H581" t="n">
+        <v>3</v>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E582" t="n">
+        <v>95</v>
+      </c>
+      <c r="F582" t="n">
+        <v>0</v>
+      </c>
+      <c r="G582" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H582" t="n">
+        <v>3</v>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E583" t="n">
+        <v>95</v>
+      </c>
+      <c r="F583" t="n">
+        <v>0</v>
+      </c>
+      <c r="G583" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H583" t="n">
+        <v>3</v>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D584" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E584" t="n">
+        <v>97</v>
+      </c>
+      <c r="F584" t="n">
+        <v>0</v>
+      </c>
+      <c r="G584" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H584" t="n">
+        <v>3</v>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D585" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E585" t="n">
+        <v>92</v>
+      </c>
+      <c r="F585" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G585" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H585" t="n">
+        <v>53</v>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D586" t="n">
+        <v>24</v>
+      </c>
+      <c r="E586" t="n">
+        <v>93</v>
+      </c>
+      <c r="F586" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G586" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H586" t="n">
+        <v>51</v>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E587" t="n">
+        <v>92</v>
+      </c>
+      <c r="F587" t="n">
+        <v>0</v>
+      </c>
+      <c r="G587" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H587" t="n">
+        <v>3</v>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E588" t="n">
+        <v>90</v>
+      </c>
+      <c r="F588" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G588" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H588" t="n">
+        <v>51</v>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E589" t="n">
+        <v>93</v>
+      </c>
+      <c r="F589" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G589" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H589" t="n">
+        <v>51</v>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E590" t="n">
+        <v>85</v>
+      </c>
+      <c r="F590" t="n">
+        <v>0</v>
+      </c>
+      <c r="G590" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H590" t="n">
+        <v>3</v>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E591" t="n">
+        <v>96</v>
+      </c>
+      <c r="F591" t="n">
+        <v>0</v>
+      </c>
+      <c r="G591" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H591" t="n">
+        <v>3</v>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>24</v>
+      </c>
+      <c r="E592" t="n">
+        <v>95</v>
+      </c>
+      <c r="F592" t="n">
+        <v>0</v>
+      </c>
+      <c r="G592" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H592" t="n">
+        <v>3</v>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E593" t="n">
+        <v>89</v>
+      </c>
+      <c r="F593" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G593" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H593" t="n">
+        <v>51</v>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E594" t="n">
+        <v>87</v>
+      </c>
+      <c r="F594" t="n">
+        <v>0</v>
+      </c>
+      <c r="G594" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="H594" t="n">
+        <v>3</v>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
         </is>
       </c>
     </row>
@@ -21196,7 +22417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22347,6 +23568,67 @@
       <c r="O19" t="inlineStr">
         <is>
           <t>2026-09-23T02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>33</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:30</t>
         </is>
       </c>
     </row>
@@ -22413,16 +23695,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
       </c>
       <c r="E2" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="F2" t="n">
-        <v>82.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>0.3</v>
@@ -22440,7 +23722,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -22449,10 +23731,10 @@
         <v>24.7</v>
       </c>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="4">
@@ -22467,19 +23749,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
       </c>
       <c r="E4" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="F4" t="n">
-        <v>74.2</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5">
@@ -22494,7 +23776,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.7</v>
+        <v>28.4</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -22503,7 +23785,7 @@
         <v>23.7</v>
       </c>
       <c r="F5" t="n">
-        <v>65.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="G5" t="n">
         <v>0.4</v>
@@ -22521,19 +23803,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="F6" t="n">
-        <v>83.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -22548,16 +23830,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="F7" t="n">
-        <v>75.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>0.1</v>
@@ -22575,19 +23857,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="F8" t="n">
-        <v>80.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
@@ -22602,7 +23884,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -22611,7 +23893,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>68.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="G9" t="n">
         <v>2.5</v>
@@ -22629,16 +23911,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
       </c>
       <c r="E10" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="F10" t="n">
-        <v>82.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>1.3</v>
@@ -22656,19 +23938,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>25.2</v>
+        <v>24.4</v>
       </c>
       <c r="F11" t="n">
-        <v>80.2</v>
+        <v>80.8</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -22683,19 +23965,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
       </c>
       <c r="E12" t="n">
-        <v>25.5</v>
+        <v>25.3</v>
       </c>
       <c r="F12" t="n">
-        <v>72.5</v>
+        <v>73.7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13">
@@ -22710,16 +23992,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
       </c>
       <c r="E13" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="F13" t="n">
-        <v>82.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>0.1</v>
@@ -22737,19 +24019,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.1</v>
+        <v>28.8</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
       </c>
       <c r="E14" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="F14" t="n">
-        <v>77.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="15">
@@ -22764,7 +24046,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.2</v>
+        <v>26.9</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -22773,7 +24055,7 @@
         <v>22.8</v>
       </c>
       <c r="F15" t="n">
-        <v>73.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>1.9</v>
@@ -22791,19 +24073,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
       </c>
       <c r="E16" t="n">
-        <v>26</v>
+        <v>24.8</v>
       </c>
       <c r="F16" t="n">
-        <v>80.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="17">
@@ -22818,7 +24100,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
@@ -22827,7 +24109,7 @@
         <v>23</v>
       </c>
       <c r="F17" t="n">
-        <v>80.3</v>
+        <v>81.2</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
@@ -22845,7 +24127,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -22854,7 +24136,7 @@
         <v>22.7</v>
       </c>
       <c r="F18" t="n">
-        <v>75.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>0.5</v>
@@ -22872,7 +24154,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.2</v>
+        <v>27.9</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -22881,10 +24163,10 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>80.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="20">
@@ -22899,7 +24181,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.9</v>
+        <v>27.6</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -22908,7 +24190,7 @@
         <v>23.1</v>
       </c>
       <c r="F20" t="n">
-        <v>70.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="G20" t="n">
         <v>0.6</v>
@@ -22926,7 +24208,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.5</v>
+        <v>30.2</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -22935,7 +24217,7 @@
         <v>25.6</v>
       </c>
       <c r="F21" t="n">
-        <v>65.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0.3</v>
@@ -22953,7 +24235,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -22962,7 +24244,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>73</v>
+        <v>74.2</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -22980,16 +24262,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
       </c>
       <c r="E23" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="F23" t="n">
-        <v>80.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>0.3</v>
@@ -23007,16 +24289,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
       </c>
       <c r="E24" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="F24" t="n">
-        <v>83.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0.7</v>
@@ -23034,19 +24316,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>25.9</v>
+        <v>24.3</v>
       </c>
       <c r="F25" t="n">
-        <v>82.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
@@ -23061,19 +24343,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
       </c>
       <c r="E26" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
-        <v>81.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="27">
@@ -23088,7 +24370,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -23097,7 +24379,7 @@
         <v>22.7</v>
       </c>
       <c r="F27" t="n">
-        <v>73.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0.7</v>
@@ -23115,7 +24397,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -23124,10 +24406,10 @@
         <v>23.7</v>
       </c>
       <c r="F28" t="n">
-        <v>71.90000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="29">
@@ -23142,19 +24424,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.9</v>
+        <v>26.6</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
       </c>
       <c r="E29" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="F29" t="n">
-        <v>81.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30">
@@ -23169,7 +24451,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -23178,7 +24460,7 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>68.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="G30" t="n">
         <v>0.3</v>
@@ -23196,7 +24478,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -23205,7 +24487,7 @@
         <v>22.3</v>
       </c>
       <c r="F31" t="n">
-        <v>73.5</v>
+        <v>74.7</v>
       </c>
       <c r="G31" t="n">
         <v>0.5</v>
@@ -23223,7 +24505,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -23232,7 +24514,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>68.7</v>
+        <v>70.2</v>
       </c>
       <c r="G32" t="n">
         <v>2.1</v>
@@ -23250,7 +24532,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -23259,10 +24541,10 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>71.8</v>
+        <v>72.8</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="34">
@@ -23277,16 +24559,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
       </c>
       <c r="E34" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="F34" t="n">
-        <v>73.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="G34" t="n">
         <v>0.3</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I594"/>
+  <dimension ref="A1:I627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22403,6 +22403,1227 @@
       <c r="I594" t="inlineStr">
         <is>
           <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>30</v>
+      </c>
+      <c r="E595" t="n">
+        <v>74</v>
+      </c>
+      <c r="F595" t="n">
+        <v>0</v>
+      </c>
+      <c r="G595" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H595" t="n">
+        <v>3</v>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>26</v>
+      </c>
+      <c r="E596" t="n">
+        <v>95</v>
+      </c>
+      <c r="F596" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G596" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H596" t="n">
+        <v>80</v>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D597" t="n">
+        <v>28</v>
+      </c>
+      <c r="E597" t="n">
+        <v>78</v>
+      </c>
+      <c r="F597" t="n">
+        <v>0</v>
+      </c>
+      <c r="G597" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H597" t="n">
+        <v>3</v>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E598" t="n">
+        <v>68</v>
+      </c>
+      <c r="F598" t="n">
+        <v>0</v>
+      </c>
+      <c r="G598" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H598" t="n">
+        <v>3</v>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E599" t="n">
+        <v>77</v>
+      </c>
+      <c r="F599" t="n">
+        <v>0</v>
+      </c>
+      <c r="G599" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H599" t="n">
+        <v>3</v>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E600" t="n">
+        <v>74</v>
+      </c>
+      <c r="F600" t="n">
+        <v>0</v>
+      </c>
+      <c r="G600" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H600" t="n">
+        <v>3</v>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E601" t="n">
+        <v>91</v>
+      </c>
+      <c r="F601" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G601" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H601" t="n">
+        <v>51</v>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E602" t="n">
+        <v>74</v>
+      </c>
+      <c r="F602" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G602" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="H602" t="n">
+        <v>51</v>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E603" t="n">
+        <v>75</v>
+      </c>
+      <c r="F603" t="n">
+        <v>0</v>
+      </c>
+      <c r="G603" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H603" t="n">
+        <v>3</v>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E604" t="n">
+        <v>73</v>
+      </c>
+      <c r="F604" t="n">
+        <v>0</v>
+      </c>
+      <c r="G604" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H604" t="n">
+        <v>3</v>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D605" t="n">
+        <v>27</v>
+      </c>
+      <c r="E605" t="n">
+        <v>90</v>
+      </c>
+      <c r="F605" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G605" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H605" t="n">
+        <v>53</v>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E606" t="n">
+        <v>72</v>
+      </c>
+      <c r="F606" t="n">
+        <v>0</v>
+      </c>
+      <c r="G606" t="n">
+        <v>16</v>
+      </c>
+      <c r="H606" t="n">
+        <v>3</v>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>26</v>
+      </c>
+      <c r="E607" t="n">
+        <v>91</v>
+      </c>
+      <c r="F607" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G607" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H607" t="n">
+        <v>55</v>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E608" t="n">
+        <v>94</v>
+      </c>
+      <c r="F608" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G608" t="n">
+        <v>17</v>
+      </c>
+      <c r="H608" t="n">
+        <v>95</v>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E609" t="n">
+        <v>70</v>
+      </c>
+      <c r="F609" t="n">
+        <v>0</v>
+      </c>
+      <c r="G609" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H609" t="n">
+        <v>3</v>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D610" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E610" t="n">
+        <v>77</v>
+      </c>
+      <c r="F610" t="n">
+        <v>0</v>
+      </c>
+      <c r="G610" t="n">
+        <v>20</v>
+      </c>
+      <c r="H610" t="n">
+        <v>3</v>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E611" t="n">
+        <v>74</v>
+      </c>
+      <c r="F611" t="n">
+        <v>0</v>
+      </c>
+      <c r="G611" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H611" t="n">
+        <v>3</v>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E612" t="n">
+        <v>95</v>
+      </c>
+      <c r="F612" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G612" t="n">
+        <v>16</v>
+      </c>
+      <c r="H612" t="n">
+        <v>95</v>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E613" t="n">
+        <v>88</v>
+      </c>
+      <c r="F613" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G613" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H613" t="n">
+        <v>95</v>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E614" t="n">
+        <v>88</v>
+      </c>
+      <c r="F614" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G614" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H614" t="n">
+        <v>51</v>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>27</v>
+      </c>
+      <c r="E615" t="n">
+        <v>77</v>
+      </c>
+      <c r="F615" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G615" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H615" t="n">
+        <v>51</v>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E616" t="n">
+        <v>71</v>
+      </c>
+      <c r="F616" t="n">
+        <v>0</v>
+      </c>
+      <c r="G616" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="H616" t="n">
+        <v>3</v>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E617" t="n">
+        <v>75</v>
+      </c>
+      <c r="F617" t="n">
+        <v>0</v>
+      </c>
+      <c r="G617" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H617" t="n">
+        <v>3</v>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>30</v>
+      </c>
+      <c r="E618" t="n">
+        <v>73</v>
+      </c>
+      <c r="F618" t="n">
+        <v>0</v>
+      </c>
+      <c r="G618" t="n">
+        <v>19</v>
+      </c>
+      <c r="H618" t="n">
+        <v>3</v>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D619" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E619" t="n">
+        <v>75</v>
+      </c>
+      <c r="F619" t="n">
+        <v>0</v>
+      </c>
+      <c r="G619" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H619" t="n">
+        <v>3</v>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>27</v>
+      </c>
+      <c r="E620" t="n">
+        <v>76</v>
+      </c>
+      <c r="F620" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G620" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="H620" t="n">
+        <v>51</v>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E621" t="n">
+        <v>67</v>
+      </c>
+      <c r="F621" t="n">
+        <v>0</v>
+      </c>
+      <c r="G621" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="H621" t="n">
+        <v>3</v>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E622" t="n">
+        <v>76</v>
+      </c>
+      <c r="F622" t="n">
+        <v>0</v>
+      </c>
+      <c r="G622" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="H622" t="n">
+        <v>3</v>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E623" t="n">
+        <v>88</v>
+      </c>
+      <c r="F623" t="n">
+        <v>0</v>
+      </c>
+      <c r="G623" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H623" t="n">
+        <v>3</v>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E624" t="n">
+        <v>81</v>
+      </c>
+      <c r="F624" t="n">
+        <v>0</v>
+      </c>
+      <c r="G624" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H624" t="n">
+        <v>3</v>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E625" t="n">
+        <v>86</v>
+      </c>
+      <c r="F625" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G625" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H625" t="n">
+        <v>55</v>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E626" t="n">
+        <v>78</v>
+      </c>
+      <c r="F626" t="n">
+        <v>0</v>
+      </c>
+      <c r="G626" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H626" t="n">
+        <v>3</v>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E627" t="n">
+        <v>73</v>
+      </c>
+      <c r="F627" t="n">
+        <v>0</v>
+      </c>
+      <c r="G627" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H627" t="n">
+        <v>3</v>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
@@ -22417,7 +23638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23629,6 +24850,67 @@
       <c r="O20" t="inlineStr">
         <is>
           <t>2026-09-23T05:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>33</v>
+      </c>
+      <c r="D21" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
@@ -23695,7 +24977,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -23704,7 +24986,7 @@
         <v>24.1</v>
       </c>
       <c r="F2" t="n">
-        <v>83.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>0.3</v>
@@ -23722,7 +25004,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -23731,10 +25013,10 @@
         <v>24.7</v>
       </c>
       <c r="F3" t="n">
-        <v>79.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="4">
@@ -23749,7 +25031,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -23758,7 +25040,7 @@
         <v>24.6</v>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>75.2</v>
       </c>
       <c r="G4" t="n">
         <v>0.3</v>
@@ -23803,7 +25085,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -23812,7 +25094,7 @@
         <v>24.1</v>
       </c>
       <c r="F6" t="n">
-        <v>84.09999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="G6" t="n">
         <v>0.3</v>
@@ -23839,7 +25121,7 @@
         <v>24.3</v>
       </c>
       <c r="F7" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="G7" t="n">
         <v>0.1</v>
@@ -23866,10 +25148,10 @@
         <v>24.2</v>
       </c>
       <c r="F8" t="n">
-        <v>81.8</v>
+        <v>82.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9">
@@ -23893,10 +25175,10 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>69.5</v>
+        <v>69.7</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
@@ -23911,7 +25193,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -23920,7 +25202,7 @@
         <v>22.5</v>
       </c>
       <c r="F10" t="n">
-        <v>82.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="G10" t="n">
         <v>1.3</v>
@@ -23947,7 +25229,7 @@
         <v>24.4</v>
       </c>
       <c r="F11" t="n">
-        <v>80.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0.2</v>
@@ -23965,7 +25247,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -23974,10 +25256,10 @@
         <v>25.3</v>
       </c>
       <c r="F12" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13">
@@ -23992,7 +25274,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -24001,7 +25283,7 @@
         <v>25.1</v>
       </c>
       <c r="F13" t="n">
-        <v>82.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="G13" t="n">
         <v>0.1</v>
@@ -24019,7 +25301,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -24028,10 +25310,10 @@
         <v>24.7</v>
       </c>
       <c r="F14" t="n">
-        <v>78.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
@@ -24046,7 +25328,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -24055,10 +25337,10 @@
         <v>22.8</v>
       </c>
       <c r="F15" t="n">
-        <v>74.90000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="16">
@@ -24073,7 +25355,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -24082,7 +25364,7 @@
         <v>24.8</v>
       </c>
       <c r="F16" t="n">
-        <v>80.7</v>
+        <v>80.2</v>
       </c>
       <c r="G16" t="n">
         <v>0.2</v>
@@ -24109,7 +25391,7 @@
         <v>23</v>
       </c>
       <c r="F17" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
@@ -24136,7 +25418,7 @@
         <v>22.7</v>
       </c>
       <c r="F18" t="n">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="G18" t="n">
         <v>0.5</v>
@@ -24154,7 +25436,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -24163,10 +25445,10 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>81.5</v>
+        <v>82.2</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -24181,7 +25463,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -24190,10 +25472,10 @@
         <v>23.1</v>
       </c>
       <c r="F20" t="n">
-        <v>72.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="21">
@@ -24208,7 +25490,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -24217,10 +25499,10 @@
         <v>25.6</v>
       </c>
       <c r="F21" t="n">
-        <v>66.09999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22">
@@ -24244,10 +25526,10 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>74.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23">
@@ -24262,7 +25544,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -24271,7 +25553,7 @@
         <v>23.7</v>
       </c>
       <c r="F23" t="n">
-        <v>81.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>0.3</v>
@@ -24289,7 +25571,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -24298,7 +25580,7 @@
         <v>23.4</v>
       </c>
       <c r="F24" t="n">
-        <v>84.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0.7</v>
@@ -24316,7 +25598,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -24325,7 +25607,7 @@
         <v>24.3</v>
       </c>
       <c r="F25" t="n">
-        <v>82.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0.8</v>
@@ -24352,7 +25634,7 @@
         <v>24</v>
       </c>
       <c r="F26" t="n">
-        <v>81.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>0.2</v>
@@ -24382,7 +25664,7 @@
         <v>74.59999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="28">
@@ -24397,7 +25679,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -24406,7 +25688,7 @@
         <v>23.7</v>
       </c>
       <c r="F28" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="G28" t="n">
         <v>0.5</v>
@@ -24424,7 +25706,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
@@ -24433,7 +25715,7 @@
         <v>23.1</v>
       </c>
       <c r="F29" t="n">
-        <v>81.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>0.3</v>
@@ -24451,7 +25733,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -24460,7 +25742,7 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>69.3</v>
+        <v>70.3</v>
       </c>
       <c r="G30" t="n">
         <v>0.3</v>
@@ -24487,7 +25769,7 @@
         <v>22.3</v>
       </c>
       <c r="F31" t="n">
-        <v>74.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0.5</v>
@@ -24505,7 +25787,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -24514,10 +25796,10 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>70.2</v>
+        <v>71</v>
       </c>
       <c r="G32" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="33">
@@ -24532,7 +25814,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -24541,7 +25823,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>72.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G33" t="n">
         <v>0.3</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I627"/>
+  <dimension ref="A1:I528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17539,23 +17539,23 @@
         </is>
       </c>
       <c r="D463" t="n">
-        <v>26.2</v>
+        <v>25.8</v>
       </c>
       <c r="E463" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F463" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G463" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="H463" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -17576,23 +17576,23 @@
         </is>
       </c>
       <c r="D464" t="n">
-        <v>28.4</v>
+        <v>26.8</v>
       </c>
       <c r="E464" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F464" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G464" t="n">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
       <c r="H464" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -17613,23 +17613,23 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>27.5</v>
+        <v>26.6</v>
       </c>
       <c r="E465" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F465" t="n">
         <v>0</v>
       </c>
       <c r="G465" t="n">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="H465" t="n">
         <v>3</v>
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -17650,23 +17650,23 @@
         </is>
       </c>
       <c r="D466" t="n">
-        <v>28.5</v>
+        <v>24.7</v>
       </c>
       <c r="E466" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="F466" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G466" t="n">
-        <v>7.9</v>
+        <v>11.2</v>
       </c>
       <c r="H466" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -17687,23 +17687,23 @@
         </is>
       </c>
       <c r="D467" t="n">
-        <v>26.6</v>
+        <v>25.2</v>
       </c>
       <c r="E467" t="n">
         <v>93</v>
       </c>
       <c r="F467" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G467" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="H467" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -17724,23 +17724,23 @@
         </is>
       </c>
       <c r="D468" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E468" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F468" t="n">
         <v>0</v>
       </c>
       <c r="G468" t="n">
-        <v>13.5</v>
+        <v>12.6</v>
       </c>
       <c r="H468" t="n">
         <v>3</v>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -17761,23 +17761,23 @@
         </is>
       </c>
       <c r="D469" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="E469" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F469" t="n">
         <v>0</v>
       </c>
       <c r="G469" t="n">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H469" t="n">
         <v>3</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -17798,23 +17798,23 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>28.8</v>
+        <v>24.1</v>
       </c>
       <c r="E470" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="F470" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G470" t="n">
-        <v>11</v>
+        <v>15.3</v>
       </c>
       <c r="H470" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -17841,17 +17841,17 @@
         <v>94</v>
       </c>
       <c r="F471" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G471" t="n">
-        <v>10.3</v>
+        <v>8.1</v>
       </c>
       <c r="H471" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -17872,23 +17872,23 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>26.6</v>
+        <v>25.8</v>
       </c>
       <c r="E472" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F472" t="n">
         <v>0</v>
       </c>
       <c r="G472" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="H472" t="n">
         <v>3</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -17909,23 +17909,23 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>29.4</v>
+        <v>28</v>
       </c>
       <c r="E473" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F473" t="n">
         <v>0</v>
       </c>
       <c r="G473" t="n">
-        <v>10.5</v>
+        <v>12.1</v>
       </c>
       <c r="H473" t="n">
         <v>3</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -17946,7 +17946,7 @@
         </is>
       </c>
       <c r="D474" t="n">
-        <v>25.8</v>
+        <v>26.1</v>
       </c>
       <c r="E474" t="n">
         <v>96</v>
@@ -17955,14 +17955,14 @@
         <v>0</v>
       </c>
       <c r="G474" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="H474" t="n">
         <v>3</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -17983,23 +17983,23 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>28.5</v>
+        <v>27.2</v>
       </c>
       <c r="E475" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F475" t="n">
         <v>0</v>
       </c>
       <c r="G475" t="n">
-        <v>10.7</v>
+        <v>11.7</v>
       </c>
       <c r="H475" t="n">
         <v>3</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18020,23 +18020,23 @@
         </is>
       </c>
       <c r="D476" t="n">
-        <v>23.9</v>
+        <v>23</v>
       </c>
       <c r="E476" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F476" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="G476" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="H476" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18057,23 +18057,23 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>27</v>
+        <v>26.4</v>
       </c>
       <c r="E477" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F477" t="n">
         <v>0</v>
       </c>
       <c r="G477" t="n">
-        <v>8.699999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="H477" t="n">
         <v>3</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18094,23 +18094,23 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>25.9</v>
+        <v>24.2</v>
       </c>
       <c r="E478" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F478" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G478" t="n">
-        <v>11.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H478" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18131,23 +18131,23 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>26.6</v>
+        <v>23.7</v>
       </c>
       <c r="E479" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="F479" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="G479" t="n">
-        <v>6.6</v>
+        <v>12.4</v>
       </c>
       <c r="H479" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18168,23 +18168,23 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>26.7</v>
+        <v>25.9</v>
       </c>
       <c r="E480" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F480" t="n">
         <v>0</v>
       </c>
       <c r="G480" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="H480" t="n">
         <v>3</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18205,23 +18205,23 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>26</v>
+        <v>23.4</v>
       </c>
       <c r="E481" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F481" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G481" t="n">
-        <v>13.1</v>
+        <v>16.3</v>
       </c>
       <c r="H481" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18242,23 +18242,23 @@
         </is>
       </c>
       <c r="D482" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="E482" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F482" t="n">
         <v>0</v>
       </c>
       <c r="G482" t="n">
-        <v>8</v>
+        <v>14.4</v>
       </c>
       <c r="H482" t="n">
         <v>3</v>
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18279,23 +18279,23 @@
         </is>
       </c>
       <c r="D483" t="n">
-        <v>25.3</v>
+        <v>23.7</v>
       </c>
       <c r="E483" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F483" t="n">
         <v>0.2</v>
       </c>
       <c r="G483" t="n">
-        <v>11.1</v>
+        <v>14.8</v>
       </c>
       <c r="H483" t="n">
         <v>53</v>
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18316,7 +18316,7 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>26.2</v>
+        <v>25.6</v>
       </c>
       <c r="E484" t="n">
         <v>91</v>
@@ -18325,14 +18325,14 @@
         <v>0</v>
       </c>
       <c r="G484" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="H484" t="n">
         <v>3</v>
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18353,23 +18353,23 @@
         </is>
       </c>
       <c r="D485" t="n">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
       <c r="E485" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F485" t="n">
         <v>0.2</v>
       </c>
       <c r="G485" t="n">
-        <v>7.3</v>
+        <v>12.6</v>
       </c>
       <c r="H485" t="n">
         <v>53</v>
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18390,23 +18390,23 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>27.2</v>
+        <v>26.1</v>
       </c>
       <c r="E486" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F486" t="n">
         <v>0</v>
       </c>
       <c r="G486" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="H486" t="n">
         <v>3</v>
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18427,23 +18427,23 @@
         </is>
       </c>
       <c r="D487" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="E487" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F487" t="n">
         <v>0</v>
       </c>
       <c r="G487" t="n">
-        <v>10.2</v>
+        <v>7.4</v>
       </c>
       <c r="H487" t="n">
         <v>3</v>
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18464,23 +18464,23 @@
         </is>
       </c>
       <c r="D488" t="n">
-        <v>24.3</v>
+        <v>22.9</v>
       </c>
       <c r="E488" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F488" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G488" t="n">
-        <v>12.1</v>
+        <v>16.5</v>
       </c>
       <c r="H488" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18501,23 +18501,23 @@
         </is>
       </c>
       <c r="D489" t="n">
-        <v>27.8</v>
+        <v>23.3</v>
       </c>
       <c r="E489" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F489" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G489" t="n">
-        <v>11.3</v>
+        <v>13.1</v>
       </c>
       <c r="H489" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18538,23 +18538,23 @@
         </is>
       </c>
       <c r="D490" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="E490" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F490" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G490" t="n">
-        <v>12.1</v>
+        <v>10.3</v>
       </c>
       <c r="H490" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18575,23 +18575,23 @@
         </is>
       </c>
       <c r="D491" t="n">
-        <v>29</v>
+        <v>28.2</v>
       </c>
       <c r="E491" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F491" t="n">
         <v>0</v>
       </c>
       <c r="G491" t="n">
-        <v>6.9</v>
+        <v>10.4</v>
       </c>
       <c r="H491" t="n">
         <v>3</v>
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18612,23 +18612,23 @@
         </is>
       </c>
       <c r="D492" t="n">
-        <v>24.4</v>
+        <v>22.6</v>
       </c>
       <c r="E492" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F492" t="n">
         <v>0.1</v>
       </c>
       <c r="G492" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="H492" t="n">
         <v>51</v>
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18649,23 +18649,23 @@
         </is>
       </c>
       <c r="D493" t="n">
-        <v>27.8</v>
+        <v>23.9</v>
       </c>
       <c r="E493" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="F493" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G493" t="n">
-        <v>6.5</v>
+        <v>13.5</v>
       </c>
       <c r="H493" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18686,23 +18686,23 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>27.7</v>
+        <v>26.7</v>
       </c>
       <c r="E494" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F494" t="n">
         <v>0</v>
       </c>
       <c r="G494" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H494" t="n">
         <v>3</v>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
@@ -18723,30 +18723,30 @@
         </is>
       </c>
       <c r="D495" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="E495" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F495" t="n">
         <v>0</v>
       </c>
       <c r="G495" t="n">
-        <v>8.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="H495" t="n">
         <v>3</v>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -18760,30 +18760,30 @@
         </is>
       </c>
       <c r="D496" t="n">
-        <v>25.7</v>
+        <v>30</v>
       </c>
       <c r="E496" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="F496" t="n">
         <v>0</v>
       </c>
       <c r="G496" t="n">
-        <v>4</v>
+        <v>16.3</v>
       </c>
       <c r="H496" t="n">
         <v>3</v>
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -18797,30 +18797,30 @@
         </is>
       </c>
       <c r="D497" t="n">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="E497" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F497" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="G497" t="n">
-        <v>11.2</v>
+        <v>17.8</v>
       </c>
       <c r="H497" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -18834,30 +18834,30 @@
         </is>
       </c>
       <c r="D498" t="n">
-        <v>26.3</v>
+        <v>28</v>
       </c>
       <c r="E498" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F498" t="n">
         <v>0</v>
       </c>
       <c r="G498" t="n">
-        <v>8.800000000000001</v>
+        <v>15.9</v>
       </c>
       <c r="H498" t="n">
         <v>3</v>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -18871,30 +18871,30 @@
         </is>
       </c>
       <c r="D499" t="n">
-        <v>23.7</v>
+        <v>28.1</v>
       </c>
       <c r="E499" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="F499" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G499" t="n">
-        <v>11.7</v>
+        <v>16.8</v>
       </c>
       <c r="H499" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -18908,30 +18908,30 @@
         </is>
       </c>
       <c r="D500" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="E500" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F500" t="n">
         <v>0</v>
       </c>
       <c r="G500" t="n">
-        <v>10.6</v>
+        <v>16.7</v>
       </c>
       <c r="H500" t="n">
         <v>3</v>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -18945,30 +18945,30 @@
         </is>
       </c>
       <c r="D501" t="n">
-        <v>25.8</v>
+        <v>27.7</v>
       </c>
       <c r="E501" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F501" t="n">
         <v>0</v>
       </c>
       <c r="G501" t="n">
-        <v>12.7</v>
+        <v>21.8</v>
       </c>
       <c r="H501" t="n">
         <v>3</v>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -18982,30 +18982,30 @@
         </is>
       </c>
       <c r="D502" t="n">
-        <v>25.6</v>
+        <v>27.1</v>
       </c>
       <c r="E502" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F502" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G502" t="n">
-        <v>9.4</v>
+        <v>13.7</v>
       </c>
       <c r="H502" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -19019,30 +19019,30 @@
         </is>
       </c>
       <c r="D503" t="n">
-        <v>24.1</v>
+        <v>27.6</v>
       </c>
       <c r="E503" t="n">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="F503" t="n">
         <v>0.1</v>
       </c>
       <c r="G503" t="n">
-        <v>16</v>
+        <v>24.1</v>
       </c>
       <c r="H503" t="n">
         <v>51</v>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19056,30 +19056,30 @@
         </is>
       </c>
       <c r="D504" t="n">
-        <v>23.5</v>
+        <v>28.3</v>
       </c>
       <c r="E504" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="F504" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G504" t="n">
-        <v>11.2</v>
+        <v>20.9</v>
       </c>
       <c r="H504" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -19093,30 +19093,30 @@
         </is>
       </c>
       <c r="D505" t="n">
-        <v>25.6</v>
+        <v>29.4</v>
       </c>
       <c r="E505" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F505" t="n">
         <v>0</v>
       </c>
       <c r="G505" t="n">
-        <v>10</v>
+        <v>18.6</v>
       </c>
       <c r="H505" t="n">
         <v>3</v>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -19130,30 +19130,30 @@
         </is>
       </c>
       <c r="D506" t="n">
-        <v>27.7</v>
+        <v>27</v>
       </c>
       <c r="E506" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F506" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G506" t="n">
-        <v>12.4</v>
+        <v>16.9</v>
       </c>
       <c r="H506" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -19167,30 +19167,30 @@
         </is>
       </c>
       <c r="D507" t="n">
-        <v>25.9</v>
+        <v>30.1</v>
       </c>
       <c r="E507" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F507" t="n">
         <v>0</v>
       </c>
       <c r="G507" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="H507" t="n">
         <v>3</v>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -19204,30 +19204,30 @@
         </is>
       </c>
       <c r="D508" t="n">
-        <v>26.8</v>
+        <v>26</v>
       </c>
       <c r="E508" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F508" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G508" t="n">
-        <v>10.7</v>
+        <v>18.4</v>
       </c>
       <c r="H508" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -19241,30 +19241,30 @@
         </is>
       </c>
       <c r="D509" t="n">
-        <v>22.9</v>
+        <v>24.6</v>
       </c>
       <c r="E509" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F509" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G509" t="n">
-        <v>14.4</v>
+        <v>17</v>
       </c>
       <c r="H509" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -19278,30 +19278,30 @@
         </is>
       </c>
       <c r="D510" t="n">
-        <v>26.4</v>
+        <v>30.7</v>
       </c>
       <c r="E510" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="F510" t="n">
         <v>0</v>
       </c>
       <c r="G510" t="n">
-        <v>5.2</v>
+        <v>14.6</v>
       </c>
       <c r="H510" t="n">
         <v>3</v>
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -19315,30 +19315,30 @@
         </is>
       </c>
       <c r="D511" t="n">
-        <v>23.6</v>
+        <v>28.4</v>
       </c>
       <c r="E511" t="n">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F511" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G511" t="n">
-        <v>8.1</v>
+        <v>20</v>
       </c>
       <c r="H511" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -19352,30 +19352,30 @@
         </is>
       </c>
       <c r="D512" t="n">
-        <v>22.7</v>
+        <v>27.3</v>
       </c>
       <c r="E512" t="n">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="F512" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G512" t="n">
-        <v>13.3</v>
+        <v>21.7</v>
       </c>
       <c r="H512" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -19389,30 +19389,30 @@
         </is>
       </c>
       <c r="D513" t="n">
-        <v>25.8</v>
+        <v>26.2</v>
       </c>
       <c r="E513" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F513" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G513" t="n">
-        <v>10.6</v>
+        <v>16</v>
       </c>
       <c r="H513" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -19426,30 +19426,30 @@
         </is>
       </c>
       <c r="D514" t="n">
-        <v>23.1</v>
+        <v>25.2</v>
       </c>
       <c r="E514" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F514" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="G514" t="n">
-        <v>17.5</v>
+        <v>18.1</v>
       </c>
       <c r="H514" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -19463,30 +19463,30 @@
         </is>
       </c>
       <c r="D515" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="E515" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F515" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G515" t="n">
-        <v>14.3</v>
+        <v>18.6</v>
       </c>
       <c r="H515" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -19500,30 +19500,30 @@
         </is>
       </c>
       <c r="D516" t="n">
-        <v>23.4</v>
+        <v>27</v>
       </c>
       <c r="E516" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="F516" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G516" t="n">
-        <v>12.9</v>
+        <v>19.5</v>
       </c>
       <c r="H516" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -19537,30 +19537,30 @@
         </is>
       </c>
       <c r="D517" t="n">
-        <v>25.4</v>
+        <v>29.9</v>
       </c>
       <c r="E517" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="F517" t="n">
         <v>0</v>
       </c>
       <c r="G517" t="n">
-        <v>8.5</v>
+        <v>18.3</v>
       </c>
       <c r="H517" t="n">
         <v>3</v>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -19574,30 +19574,30 @@
         </is>
       </c>
       <c r="D518" t="n">
-        <v>23.6</v>
+        <v>29.1</v>
       </c>
       <c r="E518" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="F518" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G518" t="n">
-        <v>9.6</v>
+        <v>16.4</v>
       </c>
       <c r="H518" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -19611,30 +19611,30 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E519" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="F519" t="n">
         <v>0</v>
       </c>
       <c r="G519" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="H519" t="n">
         <v>3</v>
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -19648,30 +19648,30 @@
         </is>
       </c>
       <c r="D520" t="n">
-        <v>25</v>
+        <v>28.4</v>
       </c>
       <c r="E520" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F520" t="n">
         <v>0</v>
       </c>
       <c r="G520" t="n">
-        <v>9</v>
+        <v>16.9</v>
       </c>
       <c r="H520" t="n">
         <v>3</v>
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -19685,30 +19685,30 @@
         </is>
       </c>
       <c r="D521" t="n">
-        <v>22.8</v>
+        <v>27</v>
       </c>
       <c r="E521" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="F521" t="n">
         <v>0.1</v>
       </c>
       <c r="G521" t="n">
-        <v>13.9</v>
+        <v>23.2</v>
       </c>
       <c r="H521" t="n">
         <v>51</v>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -19722,30 +19722,30 @@
         </is>
       </c>
       <c r="D522" t="n">
-        <v>23.7</v>
+        <v>29.3</v>
       </c>
       <c r="E522" t="n">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="F522" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G522" t="n">
-        <v>10.3</v>
+        <v>22.3</v>
       </c>
       <c r="H522" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -19759,30 +19759,30 @@
         </is>
       </c>
       <c r="D523" t="n">
-        <v>24.3</v>
+        <v>27.1</v>
       </c>
       <c r="E523" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F523" t="n">
         <v>0</v>
       </c>
       <c r="G523" t="n">
-        <v>11.2</v>
+        <v>22.4</v>
       </c>
       <c r="H523" t="n">
         <v>3</v>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -19796,30 +19796,30 @@
         </is>
       </c>
       <c r="D524" t="n">
-        <v>27.8</v>
+        <v>26.8</v>
       </c>
       <c r="E524" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F524" t="n">
         <v>0</v>
       </c>
       <c r="G524" t="n">
-        <v>12.1</v>
+        <v>16.3</v>
       </c>
       <c r="H524" t="n">
         <v>3</v>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -19833,30 +19833,30 @@
         </is>
       </c>
       <c r="D525" t="n">
-        <v>22.6</v>
+        <v>26.4</v>
       </c>
       <c r="E525" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="F525" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G525" t="n">
-        <v>14.3</v>
+        <v>18.5</v>
       </c>
       <c r="H525" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -19870,30 +19870,30 @@
         </is>
       </c>
       <c r="D526" t="n">
-        <v>23.9</v>
+        <v>26.1</v>
       </c>
       <c r="E526" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="F526" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G526" t="n">
-        <v>12.8</v>
+        <v>20.5</v>
       </c>
       <c r="H526" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -19907,30 +19907,30 @@
         </is>
       </c>
       <c r="D527" t="n">
-        <v>26.5</v>
+        <v>27.9</v>
       </c>
       <c r="E527" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F527" t="n">
         <v>0</v>
       </c>
       <c r="G527" t="n">
-        <v>8.9</v>
+        <v>15.6</v>
       </c>
       <c r="H527" t="n">
         <v>3</v>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>2026-09-22T23:15</t>
+          <t>2026-09-23T11:00</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -19944,3684 +19944,21 @@
         </is>
       </c>
       <c r="D528" t="n">
-        <v>24.9</v>
+        <v>27.6</v>
       </c>
       <c r="E528" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F528" t="n">
         <v>0</v>
       </c>
       <c r="G528" t="n">
-        <v>19.2</v>
+        <v>21.3</v>
       </c>
       <c r="H528" t="n">
         <v>3</v>
       </c>
       <c r="I528" t="inlineStr">
-        <is>
-          <t>2026-09-22T23:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>Adilabad</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D529" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E529" t="n">
-        <v>94</v>
-      </c>
-      <c r="F529" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G529" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H529" t="n">
-        <v>51</v>
-      </c>
-      <c r="I529" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>Bhadradri Kothagudem</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D530" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E530" t="n">
-        <v>96</v>
-      </c>
-      <c r="F530" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G530" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H530" t="n">
-        <v>81</v>
-      </c>
-      <c r="I530" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>Hanumakonda</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D531" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E531" t="n">
-        <v>80</v>
-      </c>
-      <c r="F531" t="n">
-        <v>0</v>
-      </c>
-      <c r="G531" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H531" t="n">
-        <v>3</v>
-      </c>
-      <c r="I531" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D532" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E532" t="n">
-        <v>89</v>
-      </c>
-      <c r="F532" t="n">
-        <v>0</v>
-      </c>
-      <c r="G532" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="H532" t="n">
-        <v>3</v>
-      </c>
-      <c r="I532" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>Jagtial</t>
-        </is>
-      </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D533" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E533" t="n">
-        <v>90</v>
-      </c>
-      <c r="F533" t="n">
-        <v>0</v>
-      </c>
-      <c r="G533" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H533" t="n">
-        <v>3</v>
-      </c>
-      <c r="I533" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>Jangaon</t>
-        </is>
-      </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D534" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="E534" t="n">
-        <v>87</v>
-      </c>
-      <c r="F534" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G534" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H534" t="n">
-        <v>51</v>
-      </c>
-      <c r="I534" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>Jayashankar Bhupalpally</t>
-        </is>
-      </c>
-      <c r="C535" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D535" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E535" t="n">
-        <v>91</v>
-      </c>
-      <c r="F535" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G535" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H535" t="n">
-        <v>51</v>
-      </c>
-      <c r="I535" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>Jogulamba Gadwal</t>
-        </is>
-      </c>
-      <c r="C536" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D536" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E536" t="n">
-        <v>89</v>
-      </c>
-      <c r="F536" t="n">
-        <v>0</v>
-      </c>
-      <c r="G536" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="H536" t="n">
-        <v>3</v>
-      </c>
-      <c r="I536" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>Kamareddy</t>
-        </is>
-      </c>
-      <c r="C537" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D537" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E537" t="n">
-        <v>94</v>
-      </c>
-      <c r="F537" t="n">
-        <v>0</v>
-      </c>
-      <c r="G537" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="H537" t="n">
-        <v>3</v>
-      </c>
-      <c r="I537" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>Karimnagar</t>
-        </is>
-      </c>
-      <c r="C538" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D538" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E538" t="n">
-        <v>84</v>
-      </c>
-      <c r="F538" t="n">
-        <v>0</v>
-      </c>
-      <c r="G538" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="H538" t="n">
-        <v>3</v>
-      </c>
-      <c r="I538" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t>Khammam</t>
-        </is>
-      </c>
-      <c r="C539" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D539" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E539" t="n">
-        <v>95</v>
-      </c>
-      <c r="F539" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G539" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H539" t="n">
-        <v>51</v>
-      </c>
-      <c r="I539" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>Kumuram Bheem Asifabad</t>
-        </is>
-      </c>
-      <c r="C540" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D540" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E540" t="n">
-        <v>90</v>
-      </c>
-      <c r="F540" t="n">
-        <v>0</v>
-      </c>
-      <c r="G540" t="n">
-        <v>9</v>
-      </c>
-      <c r="H540" t="n">
-        <v>3</v>
-      </c>
-      <c r="I540" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>Mahabubabad</t>
-        </is>
-      </c>
-      <c r="C541" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D541" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="E541" t="n">
-        <v>95</v>
-      </c>
-      <c r="F541" t="n">
-        <v>0</v>
-      </c>
-      <c r="G541" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H541" t="n">
-        <v>3</v>
-      </c>
-      <c r="I541" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>Mahbubnagar</t>
-        </is>
-      </c>
-      <c r="C542" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D542" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="E542" t="n">
-        <v>96</v>
-      </c>
-      <c r="F542" t="n">
-        <v>0</v>
-      </c>
-      <c r="G542" t="n">
-        <v>16</v>
-      </c>
-      <c r="H542" t="n">
-        <v>3</v>
-      </c>
-      <c r="I542" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>Mancherial</t>
-        </is>
-      </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D543" t="n">
-        <v>26</v>
-      </c>
-      <c r="E543" t="n">
-        <v>90</v>
-      </c>
-      <c r="F543" t="n">
-        <v>0</v>
-      </c>
-      <c r="G543" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H543" t="n">
-        <v>3</v>
-      </c>
-      <c r="I543" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>Medak</t>
-        </is>
-      </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D544" t="n">
-        <v>23</v>
-      </c>
-      <c r="E544" t="n">
-        <v>97</v>
-      </c>
-      <c r="F544" t="n">
-        <v>0</v>
-      </c>
-      <c r="G544" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H544" t="n">
-        <v>3</v>
-      </c>
-      <c r="I544" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>Medchal-Malkajgiri</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D545" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="E545" t="n">
-        <v>93</v>
-      </c>
-      <c r="F545" t="n">
-        <v>0</v>
-      </c>
-      <c r="G545" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H545" t="n">
-        <v>3</v>
-      </c>
-      <c r="I545" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>Mulugu</t>
-        </is>
-      </c>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D546" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E546" t="n">
-        <v>93</v>
-      </c>
-      <c r="F546" t="n">
-        <v>0</v>
-      </c>
-      <c r="G546" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="H546" t="n">
-        <v>3</v>
-      </c>
-      <c r="I546" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>Nagarkurnool</t>
-        </is>
-      </c>
-      <c r="C547" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D547" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E547" t="n">
-        <v>94</v>
-      </c>
-      <c r="F547" t="n">
-        <v>0</v>
-      </c>
-      <c r="G547" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="H547" t="n">
-        <v>3</v>
-      </c>
-      <c r="I547" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>Nalgonda</t>
-        </is>
-      </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D548" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E548" t="n">
-        <v>87</v>
-      </c>
-      <c r="F548" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G548" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H548" t="n">
-        <v>51</v>
-      </c>
-      <c r="I548" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>Narayanpet</t>
-        </is>
-      </c>
-      <c r="C549" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D549" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E549" t="n">
-        <v>95</v>
-      </c>
-      <c r="F549" t="n">
-        <v>0</v>
-      </c>
-      <c r="G549" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="H549" t="n">
-        <v>3</v>
-      </c>
-      <c r="I549" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>Nirmal</t>
-        </is>
-      </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D550" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E550" t="n">
-        <v>96</v>
-      </c>
-      <c r="F550" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G550" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="H550" t="n">
-        <v>53</v>
-      </c>
-      <c r="I550" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B551" t="inlineStr">
-        <is>
-          <t>Nizamabad</t>
-        </is>
-      </c>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D551" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E551" t="n">
-        <v>98</v>
-      </c>
-      <c r="F551" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G551" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H551" t="n">
-        <v>51</v>
-      </c>
-      <c r="I551" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>Peddapalli</t>
-        </is>
-      </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D552" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E552" t="n">
-        <v>89</v>
-      </c>
-      <c r="F552" t="n">
-        <v>0</v>
-      </c>
-      <c r="G552" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="H552" t="n">
-        <v>3</v>
-      </c>
-      <c r="I552" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>Rajanna Sircilla</t>
-        </is>
-      </c>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D553" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="E553" t="n">
-        <v>88</v>
-      </c>
-      <c r="F553" t="n">
-        <v>0</v>
-      </c>
-      <c r="G553" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="H553" t="n">
-        <v>3</v>
-      </c>
-      <c r="I553" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>Rangareddy</t>
-        </is>
-      </c>
-      <c r="C554" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D554" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="E554" t="n">
-        <v>95</v>
-      </c>
-      <c r="F554" t="n">
-        <v>0</v>
-      </c>
-      <c r="G554" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H554" t="n">
-        <v>3</v>
-      </c>
-      <c r="I554" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>Sangareddy</t>
-        </is>
-      </c>
-      <c r="C555" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D555" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E555" t="n">
-        <v>92</v>
-      </c>
-      <c r="F555" t="n">
-        <v>0</v>
-      </c>
-      <c r="G555" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="H555" t="n">
-        <v>3</v>
-      </c>
-      <c r="I555" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>Siddipet</t>
-        </is>
-      </c>
-      <c r="C556" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D556" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E556" t="n">
-        <v>92</v>
-      </c>
-      <c r="F556" t="n">
-        <v>0</v>
-      </c>
-      <c r="G556" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H556" t="n">
-        <v>3</v>
-      </c>
-      <c r="I556" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>Suryapet</t>
-        </is>
-      </c>
-      <c r="C557" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D557" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E557" t="n">
-        <v>85</v>
-      </c>
-      <c r="F557" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G557" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="H557" t="n">
-        <v>51</v>
-      </c>
-      <c r="I557" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>Vikarabad</t>
-        </is>
-      </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D558" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="E558" t="n">
-        <v>98</v>
-      </c>
-      <c r="F558" t="n">
-        <v>0</v>
-      </c>
-      <c r="G558" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H558" t="n">
-        <v>3</v>
-      </c>
-      <c r="I558" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>Wanaparthy</t>
-        </is>
-      </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D559" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E559" t="n">
-        <v>95</v>
-      </c>
-      <c r="F559" t="n">
-        <v>0</v>
-      </c>
-      <c r="G559" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="H559" t="n">
-        <v>3</v>
-      </c>
-      <c r="I559" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>Warangal</t>
-        </is>
-      </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D560" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E560" t="n">
-        <v>79</v>
-      </c>
-      <c r="F560" t="n">
-        <v>0</v>
-      </c>
-      <c r="G560" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H560" t="n">
-        <v>3</v>
-      </c>
-      <c r="I560" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>Yadadri Bhuvanagiri</t>
-        </is>
-      </c>
-      <c r="C561" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D561" t="n">
-        <v>24</v>
-      </c>
-      <c r="E561" t="n">
-        <v>89</v>
-      </c>
-      <c r="F561" t="n">
-        <v>0</v>
-      </c>
-      <c r="G561" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="H561" t="n">
-        <v>3</v>
-      </c>
-      <c r="I561" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>Adilabad</t>
-        </is>
-      </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D562" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E562" t="n">
-        <v>94</v>
-      </c>
-      <c r="F562" t="n">
-        <v>0</v>
-      </c>
-      <c r="G562" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H562" t="n">
-        <v>3</v>
-      </c>
-      <c r="I562" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>Bhadradri Kothagudem</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D563" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E563" t="n">
-        <v>96</v>
-      </c>
-      <c r="F563" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G563" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H563" t="n">
-        <v>80</v>
-      </c>
-      <c r="I563" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>Hanumakonda</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D564" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="E564" t="n">
-        <v>89</v>
-      </c>
-      <c r="F564" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G564" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="H564" t="n">
-        <v>51</v>
-      </c>
-      <c r="I564" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D565" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E565" t="n">
-        <v>88</v>
-      </c>
-      <c r="F565" t="n">
-        <v>0</v>
-      </c>
-      <c r="G565" t="n">
-        <v>13</v>
-      </c>
-      <c r="H565" t="n">
-        <v>3</v>
-      </c>
-      <c r="I565" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>Jagtial</t>
-        </is>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D566" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E566" t="n">
-        <v>93</v>
-      </c>
-      <c r="F566" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G566" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="H566" t="n">
-        <v>51</v>
-      </c>
-      <c r="I566" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>Jangaon</t>
-        </is>
-      </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D567" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E567" t="n">
-        <v>85</v>
-      </c>
-      <c r="F567" t="n">
-        <v>0</v>
-      </c>
-      <c r="G567" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="H567" t="n">
-        <v>3</v>
-      </c>
-      <c r="I567" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>Jayashankar Bhupalpally</t>
-        </is>
-      </c>
-      <c r="C568" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D568" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E568" t="n">
-        <v>97</v>
-      </c>
-      <c r="F568" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G568" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="H568" t="n">
-        <v>61</v>
-      </c>
-      <c r="I568" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t>Jogulamba Gadwal</t>
-        </is>
-      </c>
-      <c r="C569" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D569" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E569" t="n">
-        <v>89</v>
-      </c>
-      <c r="F569" t="n">
-        <v>0</v>
-      </c>
-      <c r="G569" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="H569" t="n">
-        <v>3</v>
-      </c>
-      <c r="I569" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>Kamareddy</t>
-        </is>
-      </c>
-      <c r="C570" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D570" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E570" t="n">
-        <v>96</v>
-      </c>
-      <c r="F570" t="n">
-        <v>0</v>
-      </c>
-      <c r="G570" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="H570" t="n">
-        <v>3</v>
-      </c>
-      <c r="I570" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B571" t="inlineStr">
-        <is>
-          <t>Karimnagar</t>
-        </is>
-      </c>
-      <c r="C571" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D571" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E571" t="n">
-        <v>91</v>
-      </c>
-      <c r="F571" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G571" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="H571" t="n">
-        <v>51</v>
-      </c>
-      <c r="I571" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>Khammam</t>
-        </is>
-      </c>
-      <c r="C572" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D572" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="E572" t="n">
-        <v>93</v>
-      </c>
-      <c r="F572" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G572" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H572" t="n">
-        <v>51</v>
-      </c>
-      <c r="I572" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B573" t="inlineStr">
-        <is>
-          <t>Kumuram Bheem Asifabad</t>
-        </is>
-      </c>
-      <c r="C573" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D573" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E573" t="n">
-        <v>87</v>
-      </c>
-      <c r="F573" t="n">
-        <v>0</v>
-      </c>
-      <c r="G573" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="H573" t="n">
-        <v>3</v>
-      </c>
-      <c r="I573" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B574" t="inlineStr">
-        <is>
-          <t>Mahabubabad</t>
-        </is>
-      </c>
-      <c r="C574" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D574" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E574" t="n">
-        <v>93</v>
-      </c>
-      <c r="F574" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G574" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H574" t="n">
-        <v>51</v>
-      </c>
-      <c r="I574" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B575" t="inlineStr">
-        <is>
-          <t>Mahbubnagar</t>
-        </is>
-      </c>
-      <c r="C575" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D575" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E575" t="n">
-        <v>94</v>
-      </c>
-      <c r="F575" t="n">
-        <v>0</v>
-      </c>
-      <c r="G575" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="H575" t="n">
-        <v>3</v>
-      </c>
-      <c r="I575" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B576" t="inlineStr">
-        <is>
-          <t>Mancherial</t>
-        </is>
-      </c>
-      <c r="C576" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D576" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E576" t="n">
-        <v>91</v>
-      </c>
-      <c r="F576" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G576" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H576" t="n">
-        <v>53</v>
-      </c>
-      <c r="I576" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B577" t="inlineStr">
-        <is>
-          <t>Medak</t>
-        </is>
-      </c>
-      <c r="C577" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D577" t="n">
-        <v>23</v>
-      </c>
-      <c r="E577" t="n">
-        <v>97</v>
-      </c>
-      <c r="F577" t="n">
-        <v>0</v>
-      </c>
-      <c r="G577" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="H577" t="n">
-        <v>3</v>
-      </c>
-      <c r="I577" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B578" t="inlineStr">
-        <is>
-          <t>Medchal-Malkajgiri</t>
-        </is>
-      </c>
-      <c r="C578" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D578" t="n">
-        <v>23</v>
-      </c>
-      <c r="E578" t="n">
-        <v>92</v>
-      </c>
-      <c r="F578" t="n">
-        <v>0</v>
-      </c>
-      <c r="G578" t="n">
-        <v>17</v>
-      </c>
-      <c r="H578" t="n">
-        <v>3</v>
-      </c>
-      <c r="I578" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>Mulugu</t>
-        </is>
-      </c>
-      <c r="C579" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D579" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E579" t="n">
-        <v>97</v>
-      </c>
-      <c r="F579" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G579" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="H579" t="n">
-        <v>53</v>
-      </c>
-      <c r="I579" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B580" t="inlineStr">
-        <is>
-          <t>Nagarkurnool</t>
-        </is>
-      </c>
-      <c r="C580" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D580" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E580" t="n">
-        <v>94</v>
-      </c>
-      <c r="F580" t="n">
-        <v>0</v>
-      </c>
-      <c r="G580" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="H580" t="n">
-        <v>3</v>
-      </c>
-      <c r="I580" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B581" t="inlineStr">
-        <is>
-          <t>Nalgonda</t>
-        </is>
-      </c>
-      <c r="C581" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D581" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E581" t="n">
-        <v>83</v>
-      </c>
-      <c r="F581" t="n">
-        <v>0</v>
-      </c>
-      <c r="G581" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="H581" t="n">
-        <v>3</v>
-      </c>
-      <c r="I581" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t>Narayanpet</t>
-        </is>
-      </c>
-      <c r="C582" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D582" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E582" t="n">
-        <v>95</v>
-      </c>
-      <c r="F582" t="n">
-        <v>0</v>
-      </c>
-      <c r="G582" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H582" t="n">
-        <v>3</v>
-      </c>
-      <c r="I582" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B583" t="inlineStr">
-        <is>
-          <t>Nirmal</t>
-        </is>
-      </c>
-      <c r="C583" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D583" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E583" t="n">
-        <v>95</v>
-      </c>
-      <c r="F583" t="n">
-        <v>0</v>
-      </c>
-      <c r="G583" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H583" t="n">
-        <v>3</v>
-      </c>
-      <c r="I583" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B584" t="inlineStr">
-        <is>
-          <t>Nizamabad</t>
-        </is>
-      </c>
-      <c r="C584" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D584" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E584" t="n">
-        <v>97</v>
-      </c>
-      <c r="F584" t="n">
-        <v>0</v>
-      </c>
-      <c r="G584" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H584" t="n">
-        <v>3</v>
-      </c>
-      <c r="I584" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B585" t="inlineStr">
-        <is>
-          <t>Peddapalli</t>
-        </is>
-      </c>
-      <c r="C585" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D585" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E585" t="n">
-        <v>92</v>
-      </c>
-      <c r="F585" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G585" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="H585" t="n">
-        <v>53</v>
-      </c>
-      <c r="I585" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B586" t="inlineStr">
-        <is>
-          <t>Rajanna Sircilla</t>
-        </is>
-      </c>
-      <c r="C586" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D586" t="n">
-        <v>24</v>
-      </c>
-      <c r="E586" t="n">
-        <v>93</v>
-      </c>
-      <c r="F586" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G586" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H586" t="n">
-        <v>51</v>
-      </c>
-      <c r="I586" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B587" t="inlineStr">
-        <is>
-          <t>Rangareddy</t>
-        </is>
-      </c>
-      <c r="C587" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D587" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E587" t="n">
-        <v>92</v>
-      </c>
-      <c r="F587" t="n">
-        <v>0</v>
-      </c>
-      <c r="G587" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="H587" t="n">
-        <v>3</v>
-      </c>
-      <c r="I587" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B588" t="inlineStr">
-        <is>
-          <t>Sangareddy</t>
-        </is>
-      </c>
-      <c r="C588" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D588" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E588" t="n">
-        <v>90</v>
-      </c>
-      <c r="F588" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G588" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="H588" t="n">
-        <v>51</v>
-      </c>
-      <c r="I588" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B589" t="inlineStr">
-        <is>
-          <t>Siddipet</t>
-        </is>
-      </c>
-      <c r="C589" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D589" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E589" t="n">
-        <v>93</v>
-      </c>
-      <c r="F589" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G589" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="H589" t="n">
-        <v>51</v>
-      </c>
-      <c r="I589" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>Suryapet</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D590" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="E590" t="n">
-        <v>85</v>
-      </c>
-      <c r="F590" t="n">
-        <v>0</v>
-      </c>
-      <c r="G590" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="H590" t="n">
-        <v>3</v>
-      </c>
-      <c r="I590" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B591" t="inlineStr">
-        <is>
-          <t>Vikarabad</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D591" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E591" t="n">
-        <v>96</v>
-      </c>
-      <c r="F591" t="n">
-        <v>0</v>
-      </c>
-      <c r="G591" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="H591" t="n">
-        <v>3</v>
-      </c>
-      <c r="I591" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B592" t="inlineStr">
-        <is>
-          <t>Wanaparthy</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D592" t="n">
-        <v>24</v>
-      </c>
-      <c r="E592" t="n">
-        <v>95</v>
-      </c>
-      <c r="F592" t="n">
-        <v>0</v>
-      </c>
-      <c r="G592" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="H592" t="n">
-        <v>3</v>
-      </c>
-      <c r="I592" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B593" t="inlineStr">
-        <is>
-          <t>Warangal</t>
-        </is>
-      </c>
-      <c r="C593" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D593" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E593" t="n">
-        <v>89</v>
-      </c>
-      <c r="F593" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G593" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="H593" t="n">
-        <v>51</v>
-      </c>
-      <c r="I593" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>Yadadri Bhuvanagiri</t>
-        </is>
-      </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D594" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E594" t="n">
-        <v>87</v>
-      </c>
-      <c r="F594" t="n">
-        <v>0</v>
-      </c>
-      <c r="G594" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="H594" t="n">
-        <v>3</v>
-      </c>
-      <c r="I594" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B595" t="inlineStr">
-        <is>
-          <t>Adilabad</t>
-        </is>
-      </c>
-      <c r="C595" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D595" t="n">
-        <v>30</v>
-      </c>
-      <c r="E595" t="n">
-        <v>74</v>
-      </c>
-      <c r="F595" t="n">
-        <v>0</v>
-      </c>
-      <c r="G595" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="H595" t="n">
-        <v>3</v>
-      </c>
-      <c r="I595" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B596" t="inlineStr">
-        <is>
-          <t>Bhadradri Kothagudem</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D596" t="n">
-        <v>26</v>
-      </c>
-      <c r="E596" t="n">
-        <v>95</v>
-      </c>
-      <c r="F596" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G596" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H596" t="n">
-        <v>80</v>
-      </c>
-      <c r="I596" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>Hanumakonda</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D597" t="n">
-        <v>28</v>
-      </c>
-      <c r="E597" t="n">
-        <v>78</v>
-      </c>
-      <c r="F597" t="n">
-        <v>0</v>
-      </c>
-      <c r="G597" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="H597" t="n">
-        <v>3</v>
-      </c>
-      <c r="I597" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D598" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E598" t="n">
-        <v>68</v>
-      </c>
-      <c r="F598" t="n">
-        <v>0</v>
-      </c>
-      <c r="G598" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="H598" t="n">
-        <v>3</v>
-      </c>
-      <c r="I598" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B599" t="inlineStr">
-        <is>
-          <t>Jagtial</t>
-        </is>
-      </c>
-      <c r="C599" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D599" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E599" t="n">
-        <v>77</v>
-      </c>
-      <c r="F599" t="n">
-        <v>0</v>
-      </c>
-      <c r="G599" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H599" t="n">
-        <v>3</v>
-      </c>
-      <c r="I599" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B600" t="inlineStr">
-        <is>
-          <t>Jangaon</t>
-        </is>
-      </c>
-      <c r="C600" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D600" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="E600" t="n">
-        <v>74</v>
-      </c>
-      <c r="F600" t="n">
-        <v>0</v>
-      </c>
-      <c r="G600" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H600" t="n">
-        <v>3</v>
-      </c>
-      <c r="I600" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B601" t="inlineStr">
-        <is>
-          <t>Jayashankar Bhupalpally</t>
-        </is>
-      </c>
-      <c r="C601" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D601" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="E601" t="n">
-        <v>91</v>
-      </c>
-      <c r="F601" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G601" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H601" t="n">
-        <v>51</v>
-      </c>
-      <c r="I601" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B602" t="inlineStr">
-        <is>
-          <t>Jogulamba Gadwal</t>
-        </is>
-      </c>
-      <c r="C602" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D602" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="E602" t="n">
-        <v>74</v>
-      </c>
-      <c r="F602" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G602" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H602" t="n">
-        <v>51</v>
-      </c>
-      <c r="I602" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>Kamareddy</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D603" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="E603" t="n">
-        <v>75</v>
-      </c>
-      <c r="F603" t="n">
-        <v>0</v>
-      </c>
-      <c r="G603" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="H603" t="n">
-        <v>3</v>
-      </c>
-      <c r="I603" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>Karimnagar</t>
-        </is>
-      </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D604" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E604" t="n">
-        <v>73</v>
-      </c>
-      <c r="F604" t="n">
-        <v>0</v>
-      </c>
-      <c r="G604" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H604" t="n">
-        <v>3</v>
-      </c>
-      <c r="I604" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B605" t="inlineStr">
-        <is>
-          <t>Khammam</t>
-        </is>
-      </c>
-      <c r="C605" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D605" t="n">
-        <v>27</v>
-      </c>
-      <c r="E605" t="n">
-        <v>90</v>
-      </c>
-      <c r="F605" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G605" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H605" t="n">
-        <v>53</v>
-      </c>
-      <c r="I605" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B606" t="inlineStr">
-        <is>
-          <t>Kumuram Bheem Asifabad</t>
-        </is>
-      </c>
-      <c r="C606" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D606" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E606" t="n">
-        <v>72</v>
-      </c>
-      <c r="F606" t="n">
-        <v>0</v>
-      </c>
-      <c r="G606" t="n">
-        <v>16</v>
-      </c>
-      <c r="H606" t="n">
-        <v>3</v>
-      </c>
-      <c r="I606" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B607" t="inlineStr">
-        <is>
-          <t>Mahabubabad</t>
-        </is>
-      </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D607" t="n">
-        <v>26</v>
-      </c>
-      <c r="E607" t="n">
-        <v>91</v>
-      </c>
-      <c r="F607" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G607" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="H607" t="n">
-        <v>55</v>
-      </c>
-      <c r="I607" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B608" t="inlineStr">
-        <is>
-          <t>Mahbubnagar</t>
-        </is>
-      </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D608" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="E608" t="n">
-        <v>94</v>
-      </c>
-      <c r="F608" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G608" t="n">
-        <v>17</v>
-      </c>
-      <c r="H608" t="n">
-        <v>95</v>
-      </c>
-      <c r="I608" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B609" t="inlineStr">
-        <is>
-          <t>Mancherial</t>
-        </is>
-      </c>
-      <c r="C609" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D609" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E609" t="n">
-        <v>70</v>
-      </c>
-      <c r="F609" t="n">
-        <v>0</v>
-      </c>
-      <c r="G609" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H609" t="n">
-        <v>3</v>
-      </c>
-      <c r="I609" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B610" t="inlineStr">
-        <is>
-          <t>Medak</t>
-        </is>
-      </c>
-      <c r="C610" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D610" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E610" t="n">
-        <v>77</v>
-      </c>
-      <c r="F610" t="n">
-        <v>0</v>
-      </c>
-      <c r="G610" t="n">
-        <v>20</v>
-      </c>
-      <c r="H610" t="n">
-        <v>3</v>
-      </c>
-      <c r="I610" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B611" t="inlineStr">
-        <is>
-          <t>Medchal-Malkajgiri</t>
-        </is>
-      </c>
-      <c r="C611" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D611" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="E611" t="n">
-        <v>74</v>
-      </c>
-      <c r="F611" t="n">
-        <v>0</v>
-      </c>
-      <c r="G611" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H611" t="n">
-        <v>3</v>
-      </c>
-      <c r="I611" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B612" t="inlineStr">
-        <is>
-          <t>Mulugu</t>
-        </is>
-      </c>
-      <c r="C612" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D612" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E612" t="n">
-        <v>95</v>
-      </c>
-      <c r="F612" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G612" t="n">
-        <v>16</v>
-      </c>
-      <c r="H612" t="n">
-        <v>95</v>
-      </c>
-      <c r="I612" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B613" t="inlineStr">
-        <is>
-          <t>Nagarkurnool</t>
-        </is>
-      </c>
-      <c r="C613" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D613" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E613" t="n">
-        <v>88</v>
-      </c>
-      <c r="F613" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G613" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="H613" t="n">
-        <v>95</v>
-      </c>
-      <c r="I613" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B614" t="inlineStr">
-        <is>
-          <t>Nalgonda</t>
-        </is>
-      </c>
-      <c r="C614" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D614" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E614" t="n">
-        <v>88</v>
-      </c>
-      <c r="F614" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G614" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H614" t="n">
-        <v>51</v>
-      </c>
-      <c r="I614" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>Narayanpet</t>
-        </is>
-      </c>
-      <c r="C615" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D615" t="n">
-        <v>27</v>
-      </c>
-      <c r="E615" t="n">
-        <v>77</v>
-      </c>
-      <c r="F615" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G615" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="H615" t="n">
-        <v>51</v>
-      </c>
-      <c r="I615" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>Nirmal</t>
-        </is>
-      </c>
-      <c r="C616" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D616" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E616" t="n">
-        <v>71</v>
-      </c>
-      <c r="F616" t="n">
-        <v>0</v>
-      </c>
-      <c r="G616" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="H616" t="n">
-        <v>3</v>
-      </c>
-      <c r="I616" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>Nizamabad</t>
-        </is>
-      </c>
-      <c r="C617" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D617" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E617" t="n">
-        <v>75</v>
-      </c>
-      <c r="F617" t="n">
-        <v>0</v>
-      </c>
-      <c r="G617" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="H617" t="n">
-        <v>3</v>
-      </c>
-      <c r="I617" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>Peddapalli</t>
-        </is>
-      </c>
-      <c r="C618" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D618" t="n">
-        <v>30</v>
-      </c>
-      <c r="E618" t="n">
-        <v>73</v>
-      </c>
-      <c r="F618" t="n">
-        <v>0</v>
-      </c>
-      <c r="G618" t="n">
-        <v>19</v>
-      </c>
-      <c r="H618" t="n">
-        <v>3</v>
-      </c>
-      <c r="I618" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>Rajanna Sircilla</t>
-        </is>
-      </c>
-      <c r="C619" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D619" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E619" t="n">
-        <v>75</v>
-      </c>
-      <c r="F619" t="n">
-        <v>0</v>
-      </c>
-      <c r="G619" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H619" t="n">
-        <v>3</v>
-      </c>
-      <c r="I619" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t>Rangareddy</t>
-        </is>
-      </c>
-      <c r="C620" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D620" t="n">
-        <v>27</v>
-      </c>
-      <c r="E620" t="n">
-        <v>76</v>
-      </c>
-      <c r="F620" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G620" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="H620" t="n">
-        <v>51</v>
-      </c>
-      <c r="I620" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B621" t="inlineStr">
-        <is>
-          <t>Sangareddy</t>
-        </is>
-      </c>
-      <c r="C621" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D621" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E621" t="n">
-        <v>67</v>
-      </c>
-      <c r="F621" t="n">
-        <v>0</v>
-      </c>
-      <c r="G621" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="H621" t="n">
-        <v>3</v>
-      </c>
-      <c r="I621" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B622" t="inlineStr">
-        <is>
-          <t>Siddipet</t>
-        </is>
-      </c>
-      <c r="C622" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D622" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="E622" t="n">
-        <v>76</v>
-      </c>
-      <c r="F622" t="n">
-        <v>0</v>
-      </c>
-      <c r="G622" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="H622" t="n">
-        <v>3</v>
-      </c>
-      <c r="I622" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B623" t="inlineStr">
-        <is>
-          <t>Suryapet</t>
-        </is>
-      </c>
-      <c r="C623" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D623" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E623" t="n">
-        <v>88</v>
-      </c>
-      <c r="F623" t="n">
-        <v>0</v>
-      </c>
-      <c r="G623" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="H623" t="n">
-        <v>3</v>
-      </c>
-      <c r="I623" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B624" t="inlineStr">
-        <is>
-          <t>Vikarabad</t>
-        </is>
-      </c>
-      <c r="C624" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D624" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E624" t="n">
-        <v>81</v>
-      </c>
-      <c r="F624" t="n">
-        <v>0</v>
-      </c>
-      <c r="G624" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H624" t="n">
-        <v>3</v>
-      </c>
-      <c r="I624" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B625" t="inlineStr">
-        <is>
-          <t>Wanaparthy</t>
-        </is>
-      </c>
-      <c r="C625" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D625" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E625" t="n">
-        <v>86</v>
-      </c>
-      <c r="F625" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G625" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="H625" t="n">
-        <v>55</v>
-      </c>
-      <c r="I625" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B626" t="inlineStr">
-        <is>
-          <t>Warangal</t>
-        </is>
-      </c>
-      <c r="C626" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D626" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="E626" t="n">
-        <v>78</v>
-      </c>
-      <c r="F626" t="n">
-        <v>0</v>
-      </c>
-      <c r="G626" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="H626" t="n">
-        <v>3</v>
-      </c>
-      <c r="I626" t="inlineStr">
-        <is>
-          <t>2026-09-23T11:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B627" t="inlineStr">
-        <is>
-          <t>Yadadri Bhuvanagiri</t>
-        </is>
-      </c>
-      <c r="C627" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D627" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="E627" t="n">
-        <v>73</v>
-      </c>
-      <c r="F627" t="n">
-        <v>0</v>
-      </c>
-      <c r="G627" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H627" t="n">
-        <v>3</v>
-      </c>
-      <c r="I627" t="inlineStr">
         <is>
           <t>2026-09-23T11:00</t>
         </is>
@@ -23638,7 +19975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24624,56 +20961,56 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>26.6</v>
+        <v>25.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Khammam</t>
+          <t>Suryapet</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>29.4</v>
+        <v>28.2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mahbubnagar</t>
+          <t>Vikarabad</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>23.9</v>
+        <v>22.6</v>
       </c>
       <c r="I17" t="n">
-        <v>84.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Mahbubnagar</t>
+          <t>Medchal-Malkajgiri</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Vikarabad</t>
+          <t>Rangareddy</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-09-22T18:30</t>
+          <t>2026-09-22T22:15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -24685,230 +21022,47 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>27.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Suryapet</t>
+          <t>Mancherial</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>27.8</v>
+        <v>30.7</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Vikarabad</t>
+          <t>Mahbubnagar</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>22.6</v>
+        <v>24.6</v>
       </c>
       <c r="I18" t="n">
-        <v>91.7</v>
+        <v>79.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Medak</t>
+          <t>Nagarkurnool</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Yadadri Bhuvanagiri</t>
+          <t>Jogulamba Gadwal</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>19.2</v>
+        <v>24.1</v>
       </c>
       <c r="O18" t="inlineStr">
-        <is>
-          <t>2026-09-22T23:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>33</v>
-      </c>
-      <c r="D19" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Khammam</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Vikarabad</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I19" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Bhadradri Kothagudem</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Siddipet</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>33</v>
-      </c>
-      <c r="D20" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Nalgonda</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Vikarabad</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="I20" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Bhadradri Kothagudem</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Yadadri Bhuvanagiri</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>33</v>
-      </c>
-      <c r="D21" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mancherial</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Mahbubnagar</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="I21" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Nagarkurnool</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Jogulamba Gadwal</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="O21" t="inlineStr">
         <is>
           <t>2026-09-23T11:00</t>
         </is>
@@ -24977,19 +21131,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.8</v>
+        <v>28.4</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
       </c>
       <c r="E2" t="n">
-        <v>24.1</v>
+        <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>83.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
@@ -25004,19 +21158,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.7</v>
+        <v>29.2</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
       </c>
       <c r="E3" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>80.7</v>
+        <v>79</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
@@ -25031,19 +21185,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.7</v>
+        <v>29.3</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
       </c>
       <c r="E4" t="n">
-        <v>24.6</v>
+        <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>75.2</v>
+        <v>73.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -25058,16 +21212,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.4</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
       </c>
       <c r="E5" t="n">
-        <v>23.7</v>
+        <v>24.7</v>
       </c>
       <c r="F5" t="n">
-        <v>67.2</v>
+        <v>64.3</v>
       </c>
       <c r="G5" t="n">
         <v>0.4</v>
@@ -25085,19 +21239,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.7</v>
+        <v>28.2</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" t="n">
-        <v>24.1</v>
+        <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>83.7</v>
+        <v>82.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -25112,19 +21266,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.9</v>
+        <v>28.4</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>75.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -25139,19 +21293,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.1</v>
+        <v>28.6</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>82.3</v>
+        <v>80.2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -25166,7 +21320,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.6</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -25175,10 +21329,10 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>69.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -25193,19 +21347,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.3</v>
+        <v>26.9</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
       </c>
       <c r="E10" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>82.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -25220,19 +21374,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>24.4</v>
+        <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>80.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -25247,19 +21401,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.7</v>
+        <v>30.2</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
       </c>
       <c r="E12" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>74.5</v>
+        <v>72</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13">
@@ -25274,16 +21428,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
       </c>
       <c r="E13" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>82.3</v>
+        <v>80.7</v>
       </c>
       <c r="G13" t="n">
         <v>0.1</v>
@@ -25301,19 +21455,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.7</v>
+        <v>29.2</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
       </c>
       <c r="E14" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>78.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -25328,19 +21482,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.8</v>
+        <v>27.5</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
       </c>
       <c r="E15" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>75.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="16">
@@ -25355,19 +21509,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.7</v>
+        <v>29.2</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
       </c>
       <c r="E16" t="n">
-        <v>24.8</v>
+        <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>80.2</v>
+        <v>78.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -25382,19 +21536,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.7</v>
+        <v>27.3</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
       </c>
       <c r="E17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>81</v>
+        <v>78.7</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="18">
@@ -25409,19 +21563,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.8</v>
+        <v>27.4</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
       </c>
       <c r="E18" t="n">
-        <v>22.7</v>
+        <v>23.7</v>
       </c>
       <c r="F18" t="n">
-        <v>76</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="19">
@@ -25436,7 +21590,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.8</v>
+        <v>28.3</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -25445,10 +21599,10 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>82.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="20">
@@ -25463,19 +21617,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.5</v>
+        <v>28.2</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
       </c>
       <c r="E20" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>73.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="21">
@@ -25490,19 +21644,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>30.8</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
       </c>
       <c r="E21" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>67.2</v>
+        <v>63.8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="22">
@@ -25517,7 +21671,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.2</v>
+        <v>27.8</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -25526,7 +21680,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>74.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="G22" t="n">
         <v>2.1</v>
@@ -25544,19 +21698,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.5</v>
+        <v>28.1</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
       </c>
       <c r="E23" t="n">
-        <v>23.7</v>
+        <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>80.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
@@ -25571,19 +21725,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.8</v>
+        <v>27.3</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
       </c>
       <c r="E24" t="n">
-        <v>23.4</v>
+        <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>83.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="25">
@@ -25598,19 +21752,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.2</v>
+        <v>28.7</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>24.3</v>
+        <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>82.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="26">
@@ -25625,19 +21779,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.6</v>
+        <v>28.1</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>81.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="27">
@@ -25652,19 +21806,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.7</v>
+        <v>27.3</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
       </c>
       <c r="E27" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>74.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28">
@@ -25679,19 +21833,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.7</v>
+        <v>28.2</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
       </c>
       <c r="E28" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="F28" t="n">
-        <v>72.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="29">
@@ -25706,19 +21860,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.7</v>
+        <v>27.2</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
       </c>
       <c r="E29" t="n">
-        <v>23.1</v>
+        <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>81.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="30">
@@ -25733,7 +21887,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.7</v>
+        <v>30.3</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -25742,10 +21896,10 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>70.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31">
@@ -25760,19 +21914,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.6</v>
+        <v>27.2</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
       </c>
       <c r="E31" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>75.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32">
@@ -25787,7 +21941,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -25796,7 +21950,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>71</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>2.4</v>
@@ -25814,7 +21968,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29</v>
+        <v>29.6</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -25823,10 +21977,10 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>73.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="34">
@@ -25841,16 +21995,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.7</v>
+        <v>28.3</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
       </c>
       <c r="E34" t="n">
-        <v>23.9</v>
+        <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>74.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G34" t="n">
         <v>0.3</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I528"/>
+  <dimension ref="A1:I561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19961,6 +19961,1227 @@
       <c r="I528" t="inlineStr">
         <is>
           <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E529" t="n">
+        <v>81</v>
+      </c>
+      <c r="F529" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G529" t="n">
+        <v>14</v>
+      </c>
+      <c r="H529" t="n">
+        <v>95</v>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>28</v>
+      </c>
+      <c r="E530" t="n">
+        <v>92</v>
+      </c>
+      <c r="F530" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G530" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H530" t="n">
+        <v>80</v>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E531" t="n">
+        <v>62</v>
+      </c>
+      <c r="F531" t="n">
+        <v>0</v>
+      </c>
+      <c r="G531" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H531" t="n">
+        <v>3</v>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E532" t="n">
+        <v>77</v>
+      </c>
+      <c r="F532" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G532" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H532" t="n">
+        <v>95</v>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E533" t="n">
+        <v>71</v>
+      </c>
+      <c r="F533" t="n">
+        <v>0</v>
+      </c>
+      <c r="G533" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H533" t="n">
+        <v>3</v>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E534" t="n">
+        <v>64</v>
+      </c>
+      <c r="F534" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G534" t="n">
+        <v>22</v>
+      </c>
+      <c r="H534" t="n">
+        <v>51</v>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E535" t="n">
+        <v>87</v>
+      </c>
+      <c r="F535" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G535" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H535" t="n">
+        <v>53</v>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>27</v>
+      </c>
+      <c r="E536" t="n">
+        <v>84</v>
+      </c>
+      <c r="F536" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G536" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H536" t="n">
+        <v>95</v>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E537" t="n">
+        <v>86</v>
+      </c>
+      <c r="F537" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G537" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H537" t="n">
+        <v>96</v>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E538" t="n">
+        <v>67</v>
+      </c>
+      <c r="F538" t="n">
+        <v>0</v>
+      </c>
+      <c r="G538" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H538" t="n">
+        <v>3</v>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>30</v>
+      </c>
+      <c r="E539" t="n">
+        <v>74</v>
+      </c>
+      <c r="F539" t="n">
+        <v>0</v>
+      </c>
+      <c r="G539" t="n">
+        <v>13</v>
+      </c>
+      <c r="H539" t="n">
+        <v>3</v>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E540" t="n">
+        <v>86</v>
+      </c>
+      <c r="F540" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G540" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H540" t="n">
+        <v>95</v>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E541" t="n">
+        <v>87</v>
+      </c>
+      <c r="F541" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G541" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H541" t="n">
+        <v>95</v>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E542" t="n">
+        <v>91</v>
+      </c>
+      <c r="F542" t="n">
+        <v>0</v>
+      </c>
+      <c r="G542" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H542" t="n">
+        <v>3</v>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E543" t="n">
+        <v>75</v>
+      </c>
+      <c r="F543" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G543" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H543" t="n">
+        <v>51</v>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E544" t="n">
+        <v>88</v>
+      </c>
+      <c r="F544" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G544" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="H544" t="n">
+        <v>95</v>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E545" t="n">
+        <v>90</v>
+      </c>
+      <c r="F545" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G545" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="H545" t="n">
+        <v>96</v>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E546" t="n">
+        <v>88</v>
+      </c>
+      <c r="F546" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G546" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H546" t="n">
+        <v>95</v>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E547" t="n">
+        <v>93</v>
+      </c>
+      <c r="F547" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G547" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H547" t="n">
+        <v>53</v>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E548" t="n">
+        <v>67</v>
+      </c>
+      <c r="F548" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G548" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H548" t="n">
+        <v>95</v>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E549" t="n">
+        <v>91</v>
+      </c>
+      <c r="F549" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G549" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H549" t="n">
+        <v>53</v>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E550" t="n">
+        <v>70</v>
+      </c>
+      <c r="F550" t="n">
+        <v>0</v>
+      </c>
+      <c r="G550" t="n">
+        <v>16</v>
+      </c>
+      <c r="H550" t="n">
+        <v>3</v>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E551" t="n">
+        <v>77</v>
+      </c>
+      <c r="F551" t="n">
+        <v>0</v>
+      </c>
+      <c r="G551" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H551" t="n">
+        <v>3</v>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E552" t="n">
+        <v>71</v>
+      </c>
+      <c r="F552" t="n">
+        <v>0</v>
+      </c>
+      <c r="G552" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H552" t="n">
+        <v>3</v>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E553" t="n">
+        <v>70</v>
+      </c>
+      <c r="F553" t="n">
+        <v>0</v>
+      </c>
+      <c r="G553" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H553" t="n">
+        <v>3</v>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E554" t="n">
+        <v>74</v>
+      </c>
+      <c r="F554" t="n">
+        <v>0</v>
+      </c>
+      <c r="G554" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H554" t="n">
+        <v>3</v>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E555" t="n">
+        <v>79</v>
+      </c>
+      <c r="F555" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G555" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H555" t="n">
+        <v>53</v>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E556" t="n">
+        <v>71</v>
+      </c>
+      <c r="F556" t="n">
+        <v>0</v>
+      </c>
+      <c r="G556" t="n">
+        <v>21</v>
+      </c>
+      <c r="H556" t="n">
+        <v>3</v>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E557" t="n">
+        <v>57</v>
+      </c>
+      <c r="F557" t="n">
+        <v>0</v>
+      </c>
+      <c r="G557" t="n">
+        <v>19</v>
+      </c>
+      <c r="H557" t="n">
+        <v>3</v>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E558" t="n">
+        <v>80</v>
+      </c>
+      <c r="F558" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G558" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="H558" t="n">
+        <v>53</v>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E559" t="n">
+        <v>92</v>
+      </c>
+      <c r="F559" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G559" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H559" t="n">
+        <v>81</v>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E560" t="n">
+        <v>59</v>
+      </c>
+      <c r="F560" t="n">
+        <v>0</v>
+      </c>
+      <c r="G560" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H560" t="n">
+        <v>3</v>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E561" t="n">
+        <v>76</v>
+      </c>
+      <c r="F561" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G561" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="H561" t="n">
+        <v>51</v>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
         </is>
       </c>
     </row>
@@ -19975,7 +21196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21065,6 +22286,67 @@
       <c r="O18" t="inlineStr">
         <is>
           <t>2026-09-23T11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>33</v>
+      </c>
+      <c r="D19" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:15</t>
         </is>
       </c>
     </row>
@@ -21143,7 +22425,7 @@
         <v>81</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -21158,7 +22440,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -21167,10 +22449,10 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>79.8</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4">
@@ -21185,7 +22467,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -21194,7 +22476,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>73.5</v>
+        <v>72.8</v>
       </c>
       <c r="G4" t="n">
         <v>0.2</v>
@@ -21212,7 +22494,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -21221,10 +22503,10 @@
         <v>24.7</v>
       </c>
       <c r="F5" t="n">
-        <v>64.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
@@ -21239,7 +22521,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -21248,7 +22530,7 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>82.2</v>
+        <v>81.5</v>
       </c>
       <c r="G6" t="n">
         <v>0.1</v>
@@ -21266,7 +22548,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -21275,10 +22557,10 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>74.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -21302,10 +22584,10 @@
         <v>24.6</v>
       </c>
       <c r="F8" t="n">
-        <v>80.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9">
@@ -21320,7 +22602,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -21329,10 +22611,10 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>67.40000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -21347,7 +22629,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -21356,10 +22638,10 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>80.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -21374,7 +22656,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -21383,7 +22665,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>78.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="G11" t="n">
         <v>0.1</v>
@@ -21410,7 +22692,7 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>0.2</v>
@@ -21437,10 +22719,10 @@
         <v>25.3</v>
       </c>
       <c r="F13" t="n">
-        <v>80.7</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
@@ -21455,7 +22737,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -21464,10 +22746,10 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>76.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15">
@@ -21482,7 +22764,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -21491,7 +22773,7 @@
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>72.2</v>
+        <v>73.3</v>
       </c>
       <c r="G15" t="n">
         <v>0.9</v>
@@ -21509,7 +22791,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -21518,10 +22800,10 @@
         <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>78.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="17">
@@ -21536,7 +22818,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
@@ -21545,10 +22827,10 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>78.7</v>
+        <v>79.2</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -21563,7 +22845,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -21572,10 +22854,10 @@
         <v>23.7</v>
       </c>
       <c r="F18" t="n">
-        <v>73.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="19">
@@ -21599,10 +22881,10 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>80.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20">
@@ -21617,7 +22899,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.2</v>
+        <v>27.9</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -21626,10 +22908,10 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>69.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -21653,10 +22935,10 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>63.8</v>
+        <v>64</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22">
@@ -21671,7 +22953,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -21680,10 +22962,10 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>70.8</v>
+        <v>72</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23">
@@ -21698,7 +22980,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -21707,7 +22989,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>78</v>
+        <v>77.5</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
@@ -21725,7 +23007,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -21734,7 +23016,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>81.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0.4</v>
@@ -21752,7 +23034,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -21761,7 +23043,7 @@
         <v>25.9</v>
       </c>
       <c r="F25" t="n">
-        <v>80.8</v>
+        <v>80.2</v>
       </c>
       <c r="G25" t="n">
         <v>0.6</v>
@@ -21779,7 +23061,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
@@ -21788,7 +23070,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>79.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -21806,7 +23088,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -21815,7 +23097,7 @@
         <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>0.2</v>
@@ -21833,7 +23115,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -21842,10 +23124,10 @@
         <v>23.3</v>
       </c>
       <c r="F28" t="n">
-        <v>70.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="29">
@@ -21860,7 +23142,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
@@ -21869,7 +23151,7 @@
         <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>79.5</v>
+        <v>79</v>
       </c>
       <c r="G29" t="n">
         <v>0.1</v>
@@ -21887,7 +23169,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -21896,7 +23178,7 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>68.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="G30" t="n">
         <v>0.2</v>
@@ -21923,10 +23205,10 @@
         <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>71.5</v>
+        <v>72</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="32">
@@ -21941,7 +23223,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -21950,10 +23232,10 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>67.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="G32" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="33">
@@ -21968,7 +23250,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -21977,7 +23259,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>71.2</v>
+        <v>70.5</v>
       </c>
       <c r="G33" t="n">
         <v>0.2</v>
@@ -22004,10 +23286,10 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>71.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I561"/>
+  <dimension ref="A1:I594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21182,6 +21182,1227 @@
       <c r="I561" t="inlineStr">
         <is>
           <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E562" t="n">
+        <v>94</v>
+      </c>
+      <c r="F562" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G562" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H562" t="n">
+        <v>53</v>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E563" t="n">
+        <v>95</v>
+      </c>
+      <c r="F563" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G563" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H563" t="n">
+        <v>95</v>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E564" t="n">
+        <v>94</v>
+      </c>
+      <c r="F564" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G564" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H564" t="n">
+        <v>80</v>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E565" t="n">
+        <v>81</v>
+      </c>
+      <c r="F565" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G565" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H565" t="n">
+        <v>51</v>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E566" t="n">
+        <v>95</v>
+      </c>
+      <c r="F566" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G566" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H566" t="n">
+        <v>51</v>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E567" t="n">
+        <v>89</v>
+      </c>
+      <c r="F567" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G567" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H567" t="n">
+        <v>51</v>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E568" t="n">
+        <v>98</v>
+      </c>
+      <c r="F568" t="n">
+        <v>1</v>
+      </c>
+      <c r="G568" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H568" t="n">
+        <v>95</v>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E569" t="n">
+        <v>88</v>
+      </c>
+      <c r="F569" t="n">
+        <v>0</v>
+      </c>
+      <c r="G569" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H569" t="n">
+        <v>3</v>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E570" t="n">
+        <v>88</v>
+      </c>
+      <c r="F570" t="n">
+        <v>0</v>
+      </c>
+      <c r="G570" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H570" t="n">
+        <v>3</v>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E571" t="n">
+        <v>92</v>
+      </c>
+      <c r="F571" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G571" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H571" t="n">
+        <v>55</v>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E572" t="n">
+        <v>93</v>
+      </c>
+      <c r="F572" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G572" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H572" t="n">
+        <v>95</v>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E573" t="n">
+        <v>93</v>
+      </c>
+      <c r="F573" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G573" t="n">
+        <v>18</v>
+      </c>
+      <c r="H573" t="n">
+        <v>55</v>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E574" t="n">
+        <v>94</v>
+      </c>
+      <c r="F574" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G574" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H574" t="n">
+        <v>95</v>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E575" t="n">
+        <v>92</v>
+      </c>
+      <c r="F575" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G575" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="H575" t="n">
+        <v>81</v>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>26</v>
+      </c>
+      <c r="E576" t="n">
+        <v>93</v>
+      </c>
+      <c r="F576" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G576" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H576" t="n">
+        <v>55</v>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E577" t="n">
+        <v>89</v>
+      </c>
+      <c r="F577" t="n">
+        <v>0</v>
+      </c>
+      <c r="G577" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H577" t="n">
+        <v>3</v>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>25</v>
+      </c>
+      <c r="E578" t="n">
+        <v>88</v>
+      </c>
+      <c r="F578" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G578" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H578" t="n">
+        <v>51</v>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E579" t="n">
+        <v>97</v>
+      </c>
+      <c r="F579" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G579" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H579" t="n">
+        <v>80</v>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E580" t="n">
+        <v>88</v>
+      </c>
+      <c r="F580" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G580" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="H580" t="n">
+        <v>51</v>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E581" t="n">
+        <v>88</v>
+      </c>
+      <c r="F581" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G581" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H581" t="n">
+        <v>51</v>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E582" t="n">
+        <v>94</v>
+      </c>
+      <c r="F582" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G582" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H582" t="n">
+        <v>55</v>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E583" t="n">
+        <v>87</v>
+      </c>
+      <c r="F583" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G583" t="n">
+        <v>15</v>
+      </c>
+      <c r="H583" t="n">
+        <v>51</v>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D584" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E584" t="n">
+        <v>88</v>
+      </c>
+      <c r="F584" t="n">
+        <v>0</v>
+      </c>
+      <c r="G584" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H584" t="n">
+        <v>3</v>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D585" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E585" t="n">
+        <v>94</v>
+      </c>
+      <c r="F585" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G585" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="H585" t="n">
+        <v>53</v>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D586" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E586" t="n">
+        <v>88</v>
+      </c>
+      <c r="F586" t="n">
+        <v>0</v>
+      </c>
+      <c r="G586" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H586" t="n">
+        <v>3</v>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E587" t="n">
+        <v>91</v>
+      </c>
+      <c r="F587" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G587" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H587" t="n">
+        <v>51</v>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E588" t="n">
+        <v>81</v>
+      </c>
+      <c r="F588" t="n">
+        <v>0</v>
+      </c>
+      <c r="G588" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H588" t="n">
+        <v>3</v>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E589" t="n">
+        <v>90</v>
+      </c>
+      <c r="F589" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G589" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H589" t="n">
+        <v>51</v>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E590" t="n">
+        <v>89</v>
+      </c>
+      <c r="F590" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G590" t="n">
+        <v>19</v>
+      </c>
+      <c r="H590" t="n">
+        <v>51</v>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E591" t="n">
+        <v>95</v>
+      </c>
+      <c r="F591" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G591" t="n">
+        <v>15</v>
+      </c>
+      <c r="H591" t="n">
+        <v>55</v>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E592" t="n">
+        <v>89</v>
+      </c>
+      <c r="F592" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G592" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H592" t="n">
+        <v>53</v>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E593" t="n">
+        <v>94</v>
+      </c>
+      <c r="F593" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G593" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H593" t="n">
+        <v>80</v>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E594" t="n">
+        <v>89</v>
+      </c>
+      <c r="F594" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G594" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H594" t="n">
+        <v>51</v>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
         </is>
       </c>
     </row>
@@ -21196,7 +22417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22347,6 +23568,67 @@
       <c r="O19" t="inlineStr">
         <is>
           <t>2026-09-23T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>33</v>
+      </c>
+      <c r="D20" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:45</t>
         </is>
       </c>
     </row>
@@ -22413,19 +23695,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
       </c>
       <c r="E2" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>81</v>
+        <v>81.7</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
@@ -22440,7 +23722,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -22449,10 +23731,10 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>79.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="4">
@@ -22467,7 +23749,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -22476,10 +23758,10 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>72.8</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -22494,7 +23776,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -22503,10 +23785,10 @@
         <v>24.7</v>
       </c>
       <c r="F5" t="n">
-        <v>65.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -22521,7 +23803,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -22530,10 +23812,10 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>81.5</v>
+        <v>82.3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -22548,7 +23830,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -22557,10 +23839,10 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
@@ -22575,19 +23857,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.6</v>
+        <v>28.3</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="F8" t="n">
-        <v>80.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="9">
@@ -22602,7 +23884,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -22611,7 +23893,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>68.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -22629,7 +23911,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -22638,7 +23920,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>80.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="G10" t="n">
         <v>2.2</v>
@@ -22656,7 +23938,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -22665,10 +23947,10 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>78.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
@@ -22683,7 +23965,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -22692,10 +23974,10 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>72.09999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="13">
@@ -22710,19 +23992,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
       </c>
       <c r="E13" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>81.7</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="14">
@@ -22737,7 +24019,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -22746,10 +24028,10 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>77.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="15">
@@ -22764,7 +24046,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.4</v>
+        <v>27.1</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -22773,10 +24055,10 @@
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>73.3</v>
+        <v>74.3</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="16">
@@ -22791,7 +24073,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -22800,10 +24082,10 @@
         <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>78.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17">
@@ -22818,7 +24100,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
@@ -22827,7 +24109,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>79.2</v>
+        <v>79.8</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -22845,7 +24127,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -22854,10 +24136,10 @@
         <v>23.7</v>
       </c>
       <c r="F18" t="n">
-        <v>74.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="19">
@@ -22872,7 +24154,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.3</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -22881,10 +24163,10 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>80.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="20">
@@ -22899,7 +24181,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -22908,10 +24190,10 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>71.2</v>
+        <v>72.2</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="21">
@@ -22926,7 +24208,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -22935,10 +24217,10 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>64</v>
+        <v>65.3</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="22">
@@ -22953,7 +24235,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -22962,10 +24244,10 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>72</v>
+        <v>73.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="23">
@@ -22980,7 +24262,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -22989,10 +24271,10 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>77.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24">
@@ -23007,7 +24289,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -23016,7 +24298,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>80.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="G24" t="n">
         <v>0.4</v>
@@ -23034,19 +24316,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>25.9</v>
+        <v>25.4</v>
       </c>
       <c r="F25" t="n">
-        <v>80.2</v>
+        <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
@@ -23061,7 +24343,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
@@ -23070,7 +24352,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>79.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -23088,7 +24370,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -23097,10 +24379,10 @@
         <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>71.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="28">
@@ -23115,7 +24397,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -23124,7 +24406,7 @@
         <v>23.3</v>
       </c>
       <c r="F28" t="n">
-        <v>70.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="G28" t="n">
         <v>0.8</v>
@@ -23142,7 +24424,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
@@ -23151,10 +24433,10 @@
         <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>79</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="30">
@@ -23169,7 +24451,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -23178,10 +24460,10 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>67.5</v>
+        <v>68.7</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31">
@@ -23196,7 +24478,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -23205,10 +24487,10 @@
         <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>72</v>
+        <v>73.3</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="32">
@@ -23223,7 +24505,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28.5</v>
+        <v>28.2</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -23232,10 +24514,10 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>69.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="33">
@@ -23250,7 +24532,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.7</v>
+        <v>29.4</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -23259,10 +24541,10 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>70.5</v>
+        <v>71.8</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="34">
@@ -23277,7 +24559,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -23286,10 +24568,10 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>72.09999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I594"/>
+  <dimension ref="A1:I627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22403,6 +22403,1227 @@
       <c r="I594" t="inlineStr">
         <is>
           <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E595" t="n">
+        <v>95</v>
+      </c>
+      <c r="F595" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G595" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H595" t="n">
+        <v>51</v>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E596" t="n">
+        <v>95</v>
+      </c>
+      <c r="F596" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G596" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H596" t="n">
+        <v>81</v>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D597" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E597" t="n">
+        <v>94</v>
+      </c>
+      <c r="F597" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G597" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H597" t="n">
+        <v>80</v>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E598" t="n">
+        <v>94</v>
+      </c>
+      <c r="F598" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G598" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H598" t="n">
+        <v>55</v>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E599" t="n">
+        <v>96</v>
+      </c>
+      <c r="F599" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G599" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H599" t="n">
+        <v>51</v>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E600" t="n">
+        <v>90</v>
+      </c>
+      <c r="F600" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G600" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="H600" t="n">
+        <v>80</v>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E601" t="n">
+        <v>99</v>
+      </c>
+      <c r="F601" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G601" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H601" t="n">
+        <v>53</v>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E602" t="n">
+        <v>89</v>
+      </c>
+      <c r="F602" t="n">
+        <v>0</v>
+      </c>
+      <c r="G602" t="n">
+        <v>20</v>
+      </c>
+      <c r="H602" t="n">
+        <v>3</v>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>23</v>
+      </c>
+      <c r="E603" t="n">
+        <v>96</v>
+      </c>
+      <c r="F603" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G603" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H603" t="n">
+        <v>53</v>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E604" t="n">
+        <v>94</v>
+      </c>
+      <c r="F604" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G604" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H604" t="n">
+        <v>53</v>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D605" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E605" t="n">
+        <v>94</v>
+      </c>
+      <c r="F605" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G605" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H605" t="n">
+        <v>95</v>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E606" t="n">
+        <v>94</v>
+      </c>
+      <c r="F606" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G606" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H606" t="n">
+        <v>51</v>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E607" t="n">
+        <v>94</v>
+      </c>
+      <c r="F607" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G607" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H607" t="n">
+        <v>53</v>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E608" t="n">
+        <v>97</v>
+      </c>
+      <c r="F608" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G608" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H608" t="n">
+        <v>51</v>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>25</v>
+      </c>
+      <c r="E609" t="n">
+        <v>95</v>
+      </c>
+      <c r="F609" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G609" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H609" t="n">
+        <v>51</v>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D610" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E610" t="n">
+        <v>96</v>
+      </c>
+      <c r="F610" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G610" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H610" t="n">
+        <v>95</v>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E611" t="n">
+        <v>96</v>
+      </c>
+      <c r="F611" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G611" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="H611" t="n">
+        <v>61</v>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E612" t="n">
+        <v>97</v>
+      </c>
+      <c r="F612" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G612" t="n">
+        <v>22</v>
+      </c>
+      <c r="H612" t="n">
+        <v>55</v>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E613" t="n">
+        <v>94</v>
+      </c>
+      <c r="F613" t="n">
+        <v>0</v>
+      </c>
+      <c r="G613" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H613" t="n">
+        <v>3</v>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E614" t="n">
+        <v>92</v>
+      </c>
+      <c r="F614" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G614" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H614" t="n">
+        <v>80</v>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E615" t="n">
+        <v>94</v>
+      </c>
+      <c r="F615" t="n">
+        <v>0</v>
+      </c>
+      <c r="G615" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H615" t="n">
+        <v>3</v>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E616" t="n">
+        <v>94</v>
+      </c>
+      <c r="F616" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G616" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H616" t="n">
+        <v>51</v>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E617" t="n">
+        <v>96</v>
+      </c>
+      <c r="F617" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G617" t="n">
+        <v>9</v>
+      </c>
+      <c r="H617" t="n">
+        <v>53</v>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E618" t="n">
+        <v>95</v>
+      </c>
+      <c r="F618" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G618" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H618" t="n">
+        <v>51</v>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D619" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E619" t="n">
+        <v>94</v>
+      </c>
+      <c r="F619" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G619" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H619" t="n">
+        <v>51</v>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E620" t="n">
+        <v>94</v>
+      </c>
+      <c r="F620" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G620" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H620" t="n">
+        <v>51</v>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E621" t="n">
+        <v>92</v>
+      </c>
+      <c r="F621" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G621" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H621" t="n">
+        <v>81</v>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E622" t="n">
+        <v>94</v>
+      </c>
+      <c r="F622" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G622" t="n">
+        <v>23</v>
+      </c>
+      <c r="H622" t="n">
+        <v>55</v>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E623" t="n">
+        <v>93</v>
+      </c>
+      <c r="F623" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G623" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H623" t="n">
+        <v>80</v>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E624" t="n">
+        <v>98</v>
+      </c>
+      <c r="F624" t="n">
+        <v>0</v>
+      </c>
+      <c r="G624" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H624" t="n">
+        <v>3</v>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E625" t="n">
+        <v>94</v>
+      </c>
+      <c r="F625" t="n">
+        <v>0</v>
+      </c>
+      <c r="G625" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H625" t="n">
+        <v>3</v>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E626" t="n">
+        <v>94</v>
+      </c>
+      <c r="F626" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G626" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="H626" t="n">
+        <v>80</v>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E627" t="n">
+        <v>93</v>
+      </c>
+      <c r="F627" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G627" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H627" t="n">
+        <v>80</v>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
         </is>
       </c>
     </row>
@@ -22417,7 +23638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23629,6 +24850,67 @@
       <c r="O20" t="inlineStr">
         <is>
           <t>2026-09-23T20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>33</v>
+      </c>
+      <c r="D21" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="I21" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>23</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:45</t>
         </is>
       </c>
     </row>
@@ -23695,19 +24977,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
       </c>
       <c r="E2" t="n">
-        <v>24.9</v>
+        <v>24.3</v>
       </c>
       <c r="F2" t="n">
-        <v>81.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="3">
@@ -23722,7 +25004,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -23731,10 +25013,10 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>80.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -23749,19 +25031,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.2</v>
+        <v>28.9</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
       </c>
       <c r="E4" t="n">
-        <v>24.9</v>
+        <v>24.2</v>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -23776,19 +25058,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.8</v>
+        <v>28.5</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
       </c>
       <c r="E5" t="n">
-        <v>24.7</v>
+        <v>23.1</v>
       </c>
       <c r="F5" t="n">
-        <v>65.90000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
@@ -23803,19 +25085,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" t="n">
-        <v>25.1</v>
+        <v>24.4</v>
       </c>
       <c r="F6" t="n">
-        <v>82.3</v>
+        <v>83</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -23830,19 +25112,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="F7" t="n">
-        <v>74.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
@@ -23857,19 +25139,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="F8" t="n">
-        <v>81.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -23884,7 +25166,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -23893,7 +25175,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>69.5</v>
+        <v>70.5</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -23911,7 +25193,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -23920,10 +25202,10 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>80.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -23938,19 +25220,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>25.8</v>
+        <v>24.4</v>
       </c>
       <c r="F11" t="n">
-        <v>78.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12">
@@ -23965,7 +25247,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -23974,10 +25256,10 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>73.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="13">
@@ -23992,19 +25274,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.6</v>
+        <v>28.3</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
       </c>
       <c r="E13" t="n">
-        <v>25.2</v>
+        <v>24.6</v>
       </c>
       <c r="F13" t="n">
-        <v>81.7</v>
+        <v>82.3</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="14">
@@ -24019,7 +25301,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -24028,10 +25310,10 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>78.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -24046,19 +25328,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="F15" t="n">
-        <v>74.3</v>
+        <v>75.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="16">
@@ -24073,19 +25355,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
       </c>
       <c r="E16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" t="n">
-        <v>78.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17">
@@ -24100,19 +25382,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>23.2</v>
       </c>
       <c r="F17" t="n">
-        <v>79.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18">
@@ -24127,19 +25409,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
       </c>
       <c r="E18" t="n">
-        <v>23.7</v>
+        <v>22.4</v>
       </c>
       <c r="F18" t="n">
-        <v>75.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -24154,19 +25436,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="F19" t="n">
-        <v>81.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="20">
@@ -24181,16 +25463,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
       </c>
       <c r="E20" t="n">
-        <v>23.4</v>
+        <v>22.9</v>
       </c>
       <c r="F20" t="n">
-        <v>72.2</v>
+        <v>73.3</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
@@ -24208,19 +25490,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.5</v>
+        <v>30.2</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
       </c>
       <c r="E21" t="n">
-        <v>25.7</v>
+        <v>24.7</v>
       </c>
       <c r="F21" t="n">
-        <v>65.3</v>
+        <v>66.7</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="22">
@@ -24235,7 +25517,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.4</v>
+        <v>27.1</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -24244,7 +25526,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>73.2</v>
+        <v>74.3</v>
       </c>
       <c r="G22" t="n">
         <v>2.6</v>
@@ -24262,19 +25544,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
       </c>
       <c r="E23" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="F23" t="n">
-        <v>78.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="24">
@@ -24289,19 +25571,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
       </c>
       <c r="E24" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="F24" t="n">
-        <v>81.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="25">
@@ -24316,19 +25598,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>25.4</v>
+        <v>24.3</v>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>81.7</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="26">
@@ -24343,19 +25625,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
       </c>
       <c r="E26" t="n">
-        <v>25.1</v>
+        <v>24.1</v>
       </c>
       <c r="F26" t="n">
-        <v>79.59999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="27">
@@ -24370,19 +25652,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
       </c>
       <c r="E27" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="F27" t="n">
-        <v>72.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28">
@@ -24397,7 +25679,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -24406,10 +25688,10 @@
         <v>23.3</v>
       </c>
       <c r="F28" t="n">
-        <v>71.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="29">
@@ -24424,19 +25706,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
       </c>
       <c r="E29" t="n">
-        <v>24.2</v>
+        <v>23.2</v>
       </c>
       <c r="F29" t="n">
-        <v>79.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30">
@@ -24451,19 +25733,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
       </c>
       <c r="E30" t="n">
-        <v>25.4</v>
+        <v>24.9</v>
       </c>
       <c r="F30" t="n">
-        <v>68.7</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="31">
@@ -24478,16 +25760,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27</v>
+        <v>26.7</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
       </c>
       <c r="E31" t="n">
-        <v>22.6</v>
+        <v>21.9</v>
       </c>
       <c r="F31" t="n">
-        <v>73.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0.9</v>
@@ -24505,16 +25787,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
       </c>
       <c r="E32" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="F32" t="n">
-        <v>70.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -24532,19 +25814,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
       </c>
       <c r="E33" t="n">
-        <v>24.7</v>
+        <v>24.2</v>
       </c>
       <c r="F33" t="n">
-        <v>71.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="34">
@@ -24559,19 +25841,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>28.1</v>
+        <v>27.8</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
       </c>
       <c r="E34" t="n">
-        <v>24.5</v>
+        <v>23.4</v>
       </c>
       <c r="F34" t="n">
-        <v>73.09999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I627"/>
+  <dimension ref="A1:I660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23624,6 +23624,1227 @@
       <c r="I627" t="inlineStr">
         <is>
           <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E628" t="n">
+        <v>94</v>
+      </c>
+      <c r="F628" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G628" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H628" t="n">
+        <v>51</v>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D629" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E629" t="n">
+        <v>96</v>
+      </c>
+      <c r="F629" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G629" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H629" t="n">
+        <v>80</v>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D630" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E630" t="n">
+        <v>94</v>
+      </c>
+      <c r="F630" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G630" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="H630" t="n">
+        <v>80</v>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D631" t="n">
+        <v>23</v>
+      </c>
+      <c r="E631" t="n">
+        <v>92</v>
+      </c>
+      <c r="F631" t="n">
+        <v>0</v>
+      </c>
+      <c r="G631" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H631" t="n">
+        <v>3</v>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D632" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E632" t="n">
+        <v>96</v>
+      </c>
+      <c r="F632" t="n">
+        <v>0</v>
+      </c>
+      <c r="G632" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H632" t="n">
+        <v>3</v>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D633" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E633" t="n">
+        <v>92</v>
+      </c>
+      <c r="F633" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G633" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="H633" t="n">
+        <v>80</v>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D634" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E634" t="n">
+        <v>99</v>
+      </c>
+      <c r="F634" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G634" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H634" t="n">
+        <v>95</v>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D635" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E635" t="n">
+        <v>82</v>
+      </c>
+      <c r="F635" t="n">
+        <v>0</v>
+      </c>
+      <c r="G635" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H635" t="n">
+        <v>3</v>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D636" t="n">
+        <v>23</v>
+      </c>
+      <c r="E636" t="n">
+        <v>95</v>
+      </c>
+      <c r="F636" t="n">
+        <v>0</v>
+      </c>
+      <c r="G636" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H636" t="n">
+        <v>3</v>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E637" t="n">
+        <v>94</v>
+      </c>
+      <c r="F637" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G637" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H637" t="n">
+        <v>53</v>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E638" t="n">
+        <v>94</v>
+      </c>
+      <c r="F638" t="n">
+        <v>1</v>
+      </c>
+      <c r="G638" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H638" t="n">
+        <v>81</v>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E639" t="n">
+        <v>94</v>
+      </c>
+      <c r="F639" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G639" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H639" t="n">
+        <v>53</v>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E640" t="n">
+        <v>95</v>
+      </c>
+      <c r="F640" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G640" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H640" t="n">
+        <v>81</v>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D641" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E641" t="n">
+        <v>94</v>
+      </c>
+      <c r="F641" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G641" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H641" t="n">
+        <v>51</v>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D642" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E642" t="n">
+        <v>96</v>
+      </c>
+      <c r="F642" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G642" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H642" t="n">
+        <v>55</v>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D643" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E643" t="n">
+        <v>96</v>
+      </c>
+      <c r="F643" t="n">
+        <v>0</v>
+      </c>
+      <c r="G643" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H643" t="n">
+        <v>3</v>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D644" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E644" t="n">
+        <v>95</v>
+      </c>
+      <c r="F644" t="n">
+        <v>0</v>
+      </c>
+      <c r="G644" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H644" t="n">
+        <v>3</v>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D645" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E645" t="n">
+        <v>99</v>
+      </c>
+      <c r="F645" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G645" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H645" t="n">
+        <v>95</v>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D646" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E646" t="n">
+        <v>94</v>
+      </c>
+      <c r="F646" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G646" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H646" t="n">
+        <v>53</v>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D647" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E647" t="n">
+        <v>91</v>
+      </c>
+      <c r="F647" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G647" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H647" t="n">
+        <v>80</v>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D648" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E648" t="n">
+        <v>88</v>
+      </c>
+      <c r="F648" t="n">
+        <v>0</v>
+      </c>
+      <c r="G648" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H648" t="n">
+        <v>3</v>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D649" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E649" t="n">
+        <v>94</v>
+      </c>
+      <c r="F649" t="n">
+        <v>0</v>
+      </c>
+      <c r="G649" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H649" t="n">
+        <v>3</v>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D650" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E650" t="n">
+        <v>96</v>
+      </c>
+      <c r="F650" t="n">
+        <v>0</v>
+      </c>
+      <c r="G650" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H650" t="n">
+        <v>3</v>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E651" t="n">
+        <v>96</v>
+      </c>
+      <c r="F651" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G651" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="H651" t="n">
+        <v>80</v>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E652" t="n">
+        <v>94</v>
+      </c>
+      <c r="F652" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G652" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="H652" t="n">
+        <v>51</v>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E653" t="n">
+        <v>95</v>
+      </c>
+      <c r="F653" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G653" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H653" t="n">
+        <v>51</v>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E654" t="n">
+        <v>92</v>
+      </c>
+      <c r="F654" t="n">
+        <v>0</v>
+      </c>
+      <c r="G654" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H654" t="n">
+        <v>3</v>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E655" t="n">
+        <v>96</v>
+      </c>
+      <c r="F655" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G655" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H655" t="n">
+        <v>80</v>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E656" t="n">
+        <v>92</v>
+      </c>
+      <c r="F656" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G656" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H656" t="n">
+        <v>80</v>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D657" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E657" t="n">
+        <v>96</v>
+      </c>
+      <c r="F657" t="n">
+        <v>0</v>
+      </c>
+      <c r="G657" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H657" t="n">
+        <v>3</v>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E658" t="n">
+        <v>90</v>
+      </c>
+      <c r="F658" t="n">
+        <v>0</v>
+      </c>
+      <c r="G658" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H658" t="n">
+        <v>3</v>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>24</v>
+      </c>
+      <c r="E659" t="n">
+        <v>95</v>
+      </c>
+      <c r="F659" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G659" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H659" t="n">
+        <v>80</v>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D660" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E660" t="n">
+        <v>92</v>
+      </c>
+      <c r="F660" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G660" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="H660" t="n">
+        <v>51</v>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
         </is>
       </c>
     </row>
@@ -23638,7 +24859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24911,6 +26132,67 @@
       <c r="O21" t="inlineStr">
         <is>
           <t>2026-09-24T00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>33</v>
+      </c>
+      <c r="D22" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="J22" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-09-24T04:00</t>
         </is>
       </c>
     </row>
@@ -24977,19 +26259,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
       </c>
       <c r="E2" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="F2" t="n">
-        <v>82.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3">
@@ -25004,19 +26286,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="F3" t="n">
-        <v>81.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -25031,19 +26313,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
       </c>
       <c r="E4" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="F4" t="n">
-        <v>75.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -25058,16 +26340,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.5</v>
+        <v>28.2</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
       </c>
       <c r="E5" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="F5" t="n">
-        <v>67.40000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>1.2</v>
@@ -25085,16 +26367,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" t="n">
-        <v>24.4</v>
+        <v>23.8</v>
       </c>
       <c r="F6" t="n">
-        <v>83</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.3</v>
@@ -25112,19 +26394,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="F7" t="n">
-        <v>75.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
@@ -25139,19 +26421,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="F8" t="n">
-        <v>82.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -25166,7 +26448,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -25175,7 +26457,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>70.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -25193,7 +26475,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -25202,7 +26484,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>81.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="G10" t="n">
         <v>2.4</v>
@@ -25220,19 +26502,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="F11" t="n">
-        <v>79.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12">
@@ -25247,19 +26529,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.8</v>
+        <v>29.5</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
       </c>
       <c r="E12" t="n">
-        <v>25.5</v>
+        <v>24.7</v>
       </c>
       <c r="F12" t="n">
-        <v>74.40000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -25274,7 +26556,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -25283,10 +26565,10 @@
         <v>24.6</v>
       </c>
       <c r="F13" t="n">
-        <v>82.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="14">
@@ -25301,19 +26583,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
       </c>
       <c r="E14" t="n">
-        <v>24.9</v>
+        <v>24.3</v>
       </c>
       <c r="F14" t="n">
-        <v>79.2</v>
+        <v>80</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -25328,7 +26610,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -25337,10 +26619,10 @@
         <v>22.4</v>
       </c>
       <c r="F15" t="n">
-        <v>75.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="16">
@@ -25355,19 +26637,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>24.7</v>
       </c>
       <c r="F16" t="n">
-        <v>79.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="17">
@@ -25382,16 +26664,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
       </c>
       <c r="E17" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="F17" t="n">
-        <v>80.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>1.7</v>
@@ -25409,16 +26691,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
       </c>
       <c r="E18" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="F18" t="n">
-        <v>76.40000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>2.3</v>
@@ -25436,19 +26718,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
       </c>
       <c r="E19" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="F19" t="n">
-        <v>82.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -25463,7 +26745,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -25472,10 +26754,10 @@
         <v>22.9</v>
       </c>
       <c r="F20" t="n">
-        <v>73.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
@@ -25490,7 +26772,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -25499,10 +26781,10 @@
         <v>24.7</v>
       </c>
       <c r="F21" t="n">
-        <v>66.7</v>
+        <v>68</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="22">
@@ -25517,7 +26799,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -25526,7 +26808,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>74.3</v>
+        <v>75</v>
       </c>
       <c r="G22" t="n">
         <v>2.6</v>
@@ -25544,16 +26826,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
       </c>
       <c r="E23" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="F23" t="n">
-        <v>78.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>0.3</v>
@@ -25571,16 +26853,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
       </c>
       <c r="E24" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="F24" t="n">
-        <v>82.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="G24" t="n">
         <v>0.6</v>
@@ -25598,19 +26880,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="F25" t="n">
-        <v>81.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="26">
@@ -25625,7 +26907,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
@@ -25634,10 +26916,10 @@
         <v>24.1</v>
       </c>
       <c r="F26" t="n">
-        <v>80.3</v>
+        <v>81</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="27">
@@ -25652,7 +26934,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>26.7</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -25661,10 +26943,10 @@
         <v>22.6</v>
       </c>
       <c r="F27" t="n">
-        <v>73.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="28">
@@ -25679,16 +26961,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
       </c>
       <c r="E28" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="F28" t="n">
-        <v>72.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G28" t="n">
         <v>1.5</v>
@@ -25706,19 +26988,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
       </c>
       <c r="E29" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="F29" t="n">
-        <v>80.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -25733,19 +27015,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
       </c>
       <c r="E30" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="F30" t="n">
-        <v>69.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="31">
@@ -25760,7 +27042,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -25769,7 +27051,7 @@
         <v>21.9</v>
       </c>
       <c r="F31" t="n">
-        <v>74.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0.9</v>
@@ -25787,7 +27069,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -25796,7 +27078,7 @@
         <v>23.8</v>
       </c>
       <c r="F32" t="n">
-        <v>71.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -25814,19 +27096,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.2</v>
+        <v>28.9</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
       </c>
       <c r="E33" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="F33" t="n">
-        <v>72.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="G33" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="34">
@@ -25841,7 +27123,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -25850,10 +27132,10 @@
         <v>23.4</v>
       </c>
       <c r="F34" t="n">
-        <v>74.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="G34" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I660"/>
+  <dimension ref="A1:I693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24845,6 +24845,1227 @@
       <c r="I660" t="inlineStr">
         <is>
           <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D661" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E661" t="n">
+        <v>94</v>
+      </c>
+      <c r="F661" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G661" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H661" t="n">
+        <v>80</v>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E662" t="n">
+        <v>96</v>
+      </c>
+      <c r="F662" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G662" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H662" t="n">
+        <v>55</v>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E663" t="n">
+        <v>95</v>
+      </c>
+      <c r="F663" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G663" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H663" t="n">
+        <v>81</v>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E664" t="n">
+        <v>90</v>
+      </c>
+      <c r="F664" t="n">
+        <v>0</v>
+      </c>
+      <c r="G664" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H664" t="n">
+        <v>3</v>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E665" t="n">
+        <v>96</v>
+      </c>
+      <c r="F665" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G665" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H665" t="n">
+        <v>80</v>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E666" t="n">
+        <v>91</v>
+      </c>
+      <c r="F666" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G666" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H666" t="n">
+        <v>80</v>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E667" t="n">
+        <v>99</v>
+      </c>
+      <c r="F667" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G667" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H667" t="n">
+        <v>53</v>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E668" t="n">
+        <v>87</v>
+      </c>
+      <c r="F668" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G668" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H668" t="n">
+        <v>53</v>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E669" t="n">
+        <v>92</v>
+      </c>
+      <c r="F669" t="n">
+        <v>0</v>
+      </c>
+      <c r="G669" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H669" t="n">
+        <v>3</v>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D670" t="n">
+        <v>24</v>
+      </c>
+      <c r="E670" t="n">
+        <v>94</v>
+      </c>
+      <c r="F670" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G670" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H670" t="n">
+        <v>53</v>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E671" t="n">
+        <v>94</v>
+      </c>
+      <c r="F671" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G671" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H671" t="n">
+        <v>80</v>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D672" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E672" t="n">
+        <v>95</v>
+      </c>
+      <c r="F672" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G672" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H672" t="n">
+        <v>51</v>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D673" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E673" t="n">
+        <v>95</v>
+      </c>
+      <c r="F673" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G673" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H673" t="n">
+        <v>80</v>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D674" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E674" t="n">
+        <v>92</v>
+      </c>
+      <c r="F674" t="n">
+        <v>0</v>
+      </c>
+      <c r="G674" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H674" t="n">
+        <v>3</v>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D675" t="n">
+        <v>25</v>
+      </c>
+      <c r="E675" t="n">
+        <v>95</v>
+      </c>
+      <c r="F675" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G675" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H675" t="n">
+        <v>51</v>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D676" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E676" t="n">
+        <v>93</v>
+      </c>
+      <c r="F676" t="n">
+        <v>0</v>
+      </c>
+      <c r="G676" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H676" t="n">
+        <v>3</v>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D677" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E677" t="n">
+        <v>94</v>
+      </c>
+      <c r="F677" t="n">
+        <v>0</v>
+      </c>
+      <c r="G677" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H677" t="n">
+        <v>3</v>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D678" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E678" t="n">
+        <v>98</v>
+      </c>
+      <c r="F678" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G678" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H678" t="n">
+        <v>53</v>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D679" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E679" t="n">
+        <v>93</v>
+      </c>
+      <c r="F679" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G679" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="H679" t="n">
+        <v>51</v>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D680" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E680" t="n">
+        <v>90</v>
+      </c>
+      <c r="F680" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G680" t="n">
+        <v>20</v>
+      </c>
+      <c r="H680" t="n">
+        <v>80</v>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D681" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E681" t="n">
+        <v>85</v>
+      </c>
+      <c r="F681" t="n">
+        <v>0</v>
+      </c>
+      <c r="G681" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H681" t="n">
+        <v>3</v>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D682" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E682" t="n">
+        <v>90</v>
+      </c>
+      <c r="F682" t="n">
+        <v>0</v>
+      </c>
+      <c r="G682" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H682" t="n">
+        <v>3</v>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D683" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E683" t="n">
+        <v>91</v>
+      </c>
+      <c r="F683" t="n">
+        <v>0</v>
+      </c>
+      <c r="G683" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H683" t="n">
+        <v>3</v>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E684" t="n">
+        <v>96</v>
+      </c>
+      <c r="F684" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G684" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="H684" t="n">
+        <v>55</v>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E685" t="n">
+        <v>94</v>
+      </c>
+      <c r="F685" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G685" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H685" t="n">
+        <v>53</v>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E686" t="n">
+        <v>92</v>
+      </c>
+      <c r="F686" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G686" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H686" t="n">
+        <v>51</v>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D687" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E687" t="n">
+        <v>87</v>
+      </c>
+      <c r="F687" t="n">
+        <v>0</v>
+      </c>
+      <c r="G687" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H687" t="n">
+        <v>3</v>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D688" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E688" t="n">
+        <v>94</v>
+      </c>
+      <c r="F688" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G688" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H688" t="n">
+        <v>55</v>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E689" t="n">
+        <v>91</v>
+      </c>
+      <c r="F689" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G689" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="H689" t="n">
+        <v>53</v>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E690" t="n">
+        <v>93</v>
+      </c>
+      <c r="F690" t="n">
+        <v>0</v>
+      </c>
+      <c r="G690" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="H690" t="n">
+        <v>3</v>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D691" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E691" t="n">
+        <v>90</v>
+      </c>
+      <c r="F691" t="n">
+        <v>0</v>
+      </c>
+      <c r="G691" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H691" t="n">
+        <v>3</v>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D692" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E692" t="n">
+        <v>96</v>
+      </c>
+      <c r="F692" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G692" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H692" t="n">
+        <v>81</v>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D693" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E693" t="n">
+        <v>91</v>
+      </c>
+      <c r="F693" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G693" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="H693" t="n">
+        <v>53</v>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
         </is>
       </c>
     </row>
@@ -24859,7 +26080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26193,6 +27414,67 @@
       <c r="O22" t="inlineStr">
         <is>
           <t>2026-09-24T04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>33</v>
+      </c>
+      <c r="D23" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>25</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-09-24T06:30</t>
         </is>
       </c>
     </row>
@@ -26259,19 +27541,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
       </c>
       <c r="E2" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="F2" t="n">
-        <v>83</v>
+        <v>83.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="3">
@@ -26286,7 +27568,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -26295,10 +27577,10 @@
         <v>24.2</v>
       </c>
       <c r="F3" t="n">
-        <v>82.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="4">
@@ -26313,19 +27595,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.7</v>
+        <v>28.4</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
       </c>
       <c r="E4" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="5">
@@ -26340,7 +27622,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -26349,7 +27631,7 @@
         <v>23</v>
       </c>
       <c r="F5" t="n">
-        <v>68.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="G5" t="n">
         <v>1.2</v>
@@ -26367,19 +27649,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="F6" t="n">
-        <v>83.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -26394,19 +27676,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="F7" t="n">
-        <v>76.2</v>
+        <v>77</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
@@ -26421,7 +27703,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -26430,10 +27712,10 @@
         <v>23.9</v>
       </c>
       <c r="F8" t="n">
-        <v>83.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -26448,7 +27730,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -26457,10 +27739,10 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>71.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="10">
@@ -26475,7 +27757,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -26484,7 +27766,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>82.3</v>
+        <v>82.8</v>
       </c>
       <c r="G10" t="n">
         <v>2.4</v>
@@ -26502,19 +27784,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>24.3</v>
+        <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>80.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -26529,7 +27811,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -26538,10 +27820,10 @@
         <v>24.7</v>
       </c>
       <c r="F12" t="n">
-        <v>75.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -26556,19 +27838,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
       </c>
       <c r="E13" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="F13" t="n">
-        <v>82.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="14">
@@ -26583,19 +27865,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
       </c>
       <c r="E14" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="F14" t="n">
-        <v>80</v>
+        <v>80.7</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="15">
@@ -26610,7 +27892,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -26619,7 +27901,7 @@
         <v>22.4</v>
       </c>
       <c r="F15" t="n">
-        <v>76.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="G15" t="n">
         <v>1.8</v>
@@ -26637,7 +27919,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -26646,10 +27928,10 @@
         <v>24.7</v>
       </c>
       <c r="F16" t="n">
-        <v>80.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -26664,7 +27946,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
@@ -26673,7 +27955,7 @@
         <v>22.8</v>
       </c>
       <c r="F17" t="n">
-        <v>81.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="G17" t="n">
         <v>1.7</v>
@@ -26691,7 +27973,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -26700,7 +27982,7 @@
         <v>22.3</v>
       </c>
       <c r="F18" t="n">
-        <v>77.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="G18" t="n">
         <v>2.3</v>
@@ -26718,19 +28000,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
       </c>
       <c r="E19" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="F19" t="n">
-        <v>83.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -26745,7 +28027,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -26754,10 +28036,10 @@
         <v>22.9</v>
       </c>
       <c r="F20" t="n">
-        <v>74.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -26772,7 +28054,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -26781,10 +28063,10 @@
         <v>24.7</v>
       </c>
       <c r="F21" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="22">
@@ -26799,7 +28081,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -26808,7 +28090,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>75</v>
+        <v>75.5</v>
       </c>
       <c r="G22" t="n">
         <v>2.6</v>
@@ -26826,7 +28108,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -26835,7 +28117,7 @@
         <v>23.7</v>
       </c>
       <c r="F23" t="n">
-        <v>79.59999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>0.3</v>
@@ -26853,7 +28135,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -26862,7 +28144,7 @@
         <v>23.5</v>
       </c>
       <c r="F24" t="n">
-        <v>82.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0.6</v>
@@ -26880,19 +28162,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="F25" t="n">
-        <v>82.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="26">
@@ -26907,19 +28189,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
       </c>
       <c r="E26" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="F26" t="n">
-        <v>81</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27">
@@ -26934,19 +28216,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
       </c>
       <c r="E27" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="F27" t="n">
-        <v>74.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="28">
@@ -26961,7 +28243,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -26970,7 +28252,7 @@
         <v>23.1</v>
       </c>
       <c r="F28" t="n">
-        <v>73.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="G28" t="n">
         <v>1.5</v>
@@ -26988,7 +28270,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
@@ -26997,10 +28279,10 @@
         <v>22.8</v>
       </c>
       <c r="F29" t="n">
-        <v>81.2</v>
+        <v>81.8</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="30">
@@ -27015,7 +28297,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.7</v>
+        <v>29.4</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -27024,10 +28306,10 @@
         <v>24.7</v>
       </c>
       <c r="F30" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G30" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="31">
@@ -27042,7 +28324,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -27051,7 +28333,7 @@
         <v>21.9</v>
       </c>
       <c r="F31" t="n">
-        <v>75.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="G31" t="n">
         <v>0.9</v>
@@ -27069,7 +28351,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -27078,7 +28360,7 @@
         <v>23.8</v>
       </c>
       <c r="F32" t="n">
-        <v>72.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -27096,19 +28378,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.9</v>
+        <v>28.6</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
       </c>
       <c r="E33" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="F33" t="n">
-        <v>74</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="34">
@@ -27123,7 +28405,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -27132,10 +28414,10 @@
         <v>23.4</v>
       </c>
       <c r="F34" t="n">
-        <v>75</v>
+        <v>75.8</v>
       </c>
       <c r="G34" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I693"/>
+  <dimension ref="A1:I628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22409,12 +22409,12 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Adilabad</t>
+          <t>Mahabubabad</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -22423,35 +22423,35 @@
         </is>
       </c>
       <c r="D595" t="n">
-        <v>24.3</v>
+        <v>31.2</v>
       </c>
       <c r="E595" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F595" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="G595" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="H595" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T12:00</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Bhadradri Kothagudem</t>
+          <t>Adilabad</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -22460,35 +22460,35 @@
         </is>
       </c>
       <c r="D596" t="n">
-        <v>25.2</v>
+        <v>29.7</v>
       </c>
       <c r="E596" t="n">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="F596" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G596" t="n">
-        <v>18.6</v>
+        <v>20</v>
       </c>
       <c r="H596" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Hanumakonda</t>
+          <t>Bhadradri Kothagudem</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -22497,35 +22497,35 @@
         </is>
       </c>
       <c r="D597" t="n">
-        <v>24.2</v>
+        <v>25.1</v>
       </c>
       <c r="E597" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F597" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G597" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="H597" t="n">
         <v>80</v>
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Hanumakonda</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -22534,35 +22534,35 @@
         </is>
       </c>
       <c r="D598" t="n">
-        <v>23.1</v>
+        <v>25.8</v>
       </c>
       <c r="E598" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F598" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="G598" t="n">
-        <v>14.4</v>
+        <v>17.9</v>
       </c>
       <c r="H598" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Jagtial</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -22571,35 +22571,35 @@
         </is>
       </c>
       <c r="D599" t="n">
-        <v>24.4</v>
+        <v>27.3</v>
       </c>
       <c r="E599" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="F599" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G599" t="n">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="H599" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Jangaon</t>
+          <t>Jagtial</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -22608,35 +22608,35 @@
         </is>
       </c>
       <c r="D600" t="n">
-        <v>24.2</v>
+        <v>28.1</v>
       </c>
       <c r="E600" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F600" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G600" t="n">
-        <v>22.4</v>
+        <v>18.6</v>
       </c>
       <c r="H600" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Jayashankar Bhupalpally</t>
+          <t>Jangaon</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -22645,35 +22645,35 @@
         </is>
       </c>
       <c r="D601" t="n">
-        <v>24.1</v>
+        <v>26.7</v>
       </c>
       <c r="E601" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="F601" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G601" t="n">
-        <v>15.8</v>
+        <v>26.7</v>
       </c>
       <c r="H601" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Jogulamba Gadwal</t>
+          <t>Jayashankar Bhupalpally</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -22682,35 +22682,35 @@
         </is>
       </c>
       <c r="D602" t="n">
-        <v>24.7</v>
+        <v>26.3</v>
       </c>
       <c r="E602" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F602" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G602" t="n">
-        <v>20</v>
+        <v>15.3</v>
       </c>
       <c r="H602" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Kamareddy</t>
+          <t>Jogulamba Gadwal</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -22719,35 +22719,35 @@
         </is>
       </c>
       <c r="D603" t="n">
-        <v>23</v>
+        <v>30.3</v>
       </c>
       <c r="E603" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="F603" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G603" t="n">
-        <v>19.2</v>
+        <v>26.6</v>
       </c>
       <c r="H603" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Karimnagar</t>
+          <t>Kamareddy</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -22756,35 +22756,35 @@
         </is>
       </c>
       <c r="D604" t="n">
-        <v>24.4</v>
+        <v>26.4</v>
       </c>
       <c r="E604" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="F604" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G604" t="n">
-        <v>14.9</v>
+        <v>22.3</v>
       </c>
       <c r="H604" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Khammam</t>
+          <t>Karimnagar</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -22793,35 +22793,35 @@
         </is>
       </c>
       <c r="D605" t="n">
-        <v>25.7</v>
+        <v>27.3</v>
       </c>
       <c r="E605" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F605" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G605" t="n">
-        <v>18.6</v>
+        <v>19.7</v>
       </c>
       <c r="H605" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Kumuram Bheem Asifabad</t>
+          <t>Khammam</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -22830,35 +22830,35 @@
         </is>
       </c>
       <c r="D606" t="n">
-        <v>24.6</v>
+        <v>26.3</v>
       </c>
       <c r="E606" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F606" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G606" t="n">
-        <v>15.1</v>
+        <v>21.1</v>
       </c>
       <c r="H606" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Mahabubabad</t>
+          <t>Kumuram Bheem Asifabad</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -22867,35 +22867,35 @@
         </is>
       </c>
       <c r="D607" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="E607" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="F607" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G607" t="n">
-        <v>20.8</v>
+        <v>19.6</v>
       </c>
       <c r="H607" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Mahbubnagar</t>
+          <t>Mahabubabad</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -22904,35 +22904,35 @@
         </is>
       </c>
       <c r="D608" t="n">
-        <v>22.4</v>
+        <v>25.4</v>
       </c>
       <c r="E608" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F608" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G608" t="n">
-        <v>15.3</v>
+        <v>23.4</v>
       </c>
       <c r="H608" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Mancherial</t>
+          <t>Mahbubnagar</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -22941,35 +22941,35 @@
         </is>
       </c>
       <c r="D609" t="n">
-        <v>25</v>
+        <v>28.2</v>
       </c>
       <c r="E609" t="n">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="F609" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G609" t="n">
-        <v>11.9</v>
+        <v>23.7</v>
       </c>
       <c r="H609" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Medak</t>
+          <t>Mancherial</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -22978,35 +22978,35 @@
         </is>
       </c>
       <c r="D610" t="n">
-        <v>23.2</v>
+        <v>28</v>
       </c>
       <c r="E610" t="n">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="F610" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G610" t="n">
-        <v>12.7</v>
+        <v>14.8</v>
       </c>
       <c r="H610" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Medchal-Malkajgiri</t>
+          <t>Medak</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -23015,35 +23015,35 @@
         </is>
       </c>
       <c r="D611" t="n">
-        <v>22.4</v>
+        <v>27.8</v>
       </c>
       <c r="E611" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="F611" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G611" t="n">
-        <v>18.3</v>
+        <v>22.6</v>
       </c>
       <c r="H611" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Mulugu</t>
+          <t>Medchal-Malkajgiri</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -23052,35 +23052,35 @@
         </is>
       </c>
       <c r="D612" t="n">
-        <v>23.9</v>
+        <v>26.2</v>
       </c>
       <c r="E612" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="F612" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G612" t="n">
-        <v>22</v>
+        <v>20.2</v>
       </c>
       <c r="H612" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Nagarkurnool</t>
+          <t>Mulugu</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -23089,35 +23089,35 @@
         </is>
       </c>
       <c r="D613" t="n">
-        <v>22.9</v>
+        <v>25.9</v>
       </c>
       <c r="E613" t="n">
         <v>94</v>
       </c>
       <c r="F613" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G613" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="H613" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Nalgonda</t>
+          <t>Nagarkurnool</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -23126,35 +23126,35 @@
         </is>
       </c>
       <c r="D614" t="n">
-        <v>24.7</v>
+        <v>28.1</v>
       </c>
       <c r="E614" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F614" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G614" t="n">
-        <v>17.2</v>
+        <v>25.8</v>
       </c>
       <c r="H614" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="I614" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Narayanpet</t>
+          <t>Nalgonda</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -23163,35 +23163,35 @@
         </is>
       </c>
       <c r="D615" t="n">
-        <v>23.4</v>
+        <v>27.1</v>
       </c>
       <c r="E615" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F615" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G615" t="n">
-        <v>14.9</v>
+        <v>18.5</v>
       </c>
       <c r="H615" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Nirmal</t>
+          <t>Narayanpet</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -23200,35 +23200,35 @@
         </is>
       </c>
       <c r="D616" t="n">
-        <v>24.1</v>
+        <v>29</v>
       </c>
       <c r="E616" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="F616" t="n">
         <v>0.1</v>
       </c>
       <c r="G616" t="n">
-        <v>15.9</v>
+        <v>24.4</v>
       </c>
       <c r="H616" t="n">
         <v>51</v>
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Nizamabad</t>
+          <t>Nirmal</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -23237,35 +23237,35 @@
         </is>
       </c>
       <c r="D617" t="n">
-        <v>23.8</v>
+        <v>29.3</v>
       </c>
       <c r="E617" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="F617" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G617" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H617" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="I617" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Peddapalli</t>
+          <t>Nizamabad</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -23274,35 +23274,35 @@
         </is>
       </c>
       <c r="D618" t="n">
-        <v>24.3</v>
+        <v>28.1</v>
       </c>
       <c r="E618" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="F618" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G618" t="n">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="H618" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Rajanna Sircilla</t>
+          <t>Peddapalli</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -23311,35 +23311,35 @@
         </is>
       </c>
       <c r="D619" t="n">
-        <v>24.1</v>
+        <v>27.1</v>
       </c>
       <c r="E619" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F619" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G619" t="n">
-        <v>15.1</v>
+        <v>20.4</v>
       </c>
       <c r="H619" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Rangareddy</t>
+          <t>Rajanna Sircilla</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -23348,35 +23348,35 @@
         </is>
       </c>
       <c r="D620" t="n">
-        <v>22.6</v>
+        <v>28</v>
       </c>
       <c r="E620" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="F620" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G620" t="n">
-        <v>19.6</v>
+        <v>18.3</v>
       </c>
       <c r="H620" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Sangareddy</t>
+          <t>Rangareddy</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -23385,35 +23385,35 @@
         </is>
       </c>
       <c r="D621" t="n">
-        <v>23.3</v>
+        <v>28.2</v>
       </c>
       <c r="E621" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="F621" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G621" t="n">
-        <v>17.1</v>
+        <v>26.7</v>
       </c>
       <c r="H621" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Siddipet</t>
+          <t>Sangareddy</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -23422,35 +23422,35 @@
         </is>
       </c>
       <c r="D622" t="n">
-        <v>23.2</v>
+        <v>28.9</v>
       </c>
       <c r="E622" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="F622" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="G622" t="n">
-        <v>23</v>
+        <v>26.4</v>
       </c>
       <c r="H622" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Suryapet</t>
+          <t>Siddipet</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -23459,35 +23459,35 @@
         </is>
       </c>
       <c r="D623" t="n">
-        <v>24.9</v>
+        <v>26.7</v>
       </c>
       <c r="E623" t="n">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="F623" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G623" t="n">
-        <v>22.5</v>
+        <v>23.8</v>
       </c>
       <c r="H623" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Vikarabad</t>
+          <t>Suryapet</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -23496,35 +23496,35 @@
         </is>
       </c>
       <c r="D624" t="n">
-        <v>21.9</v>
+        <v>26.5</v>
       </c>
       <c r="E624" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F624" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G624" t="n">
-        <v>16.3</v>
+        <v>21.1</v>
       </c>
       <c r="H624" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Wanaparthy</t>
+          <t>Vikarabad</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -23533,35 +23533,35 @@
         </is>
       </c>
       <c r="D625" t="n">
-        <v>23.8</v>
+        <v>28.1</v>
       </c>
       <c r="E625" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="F625" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G625" t="n">
-        <v>14.8</v>
+        <v>25.5</v>
       </c>
       <c r="H625" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Warangal</t>
+          <t>Wanaparthy</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -23570,35 +23570,35 @@
         </is>
       </c>
       <c r="D626" t="n">
-        <v>24.2</v>
+        <v>29.6</v>
       </c>
       <c r="E626" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="F626" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G626" t="n">
-        <v>21.9</v>
+        <v>26.1</v>
       </c>
       <c r="H626" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="I626" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Yadadri Bhuvanagiri</t>
+          <t>Warangal</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -23607,35 +23607,35 @@
         </is>
       </c>
       <c r="D627" t="n">
-        <v>23.4</v>
+        <v>25.6</v>
       </c>
       <c r="E627" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F627" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="G627" t="n">
-        <v>18.7</v>
+        <v>19.4</v>
       </c>
       <c r="H627" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Adilabad</t>
+          <t>Yadadri Bhuvanagiri</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -23644,2428 +23644,23 @@
         </is>
       </c>
       <c r="D628" t="n">
-        <v>24.2</v>
+        <v>25.8</v>
       </c>
       <c r="E628" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F628" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G628" t="n">
-        <v>13.2</v>
+        <v>20.1</v>
       </c>
       <c r="H628" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I628" t="inlineStr">
         <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B629" t="inlineStr">
-        <is>
-          <t>Bhadradri Kothagudem</t>
-        </is>
-      </c>
-      <c r="C629" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D629" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E629" t="n">
-        <v>96</v>
-      </c>
-      <c r="F629" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G629" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="H629" t="n">
-        <v>80</v>
-      </c>
-      <c r="I629" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B630" t="inlineStr">
-        <is>
-          <t>Hanumakonda</t>
-        </is>
-      </c>
-      <c r="C630" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D630" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E630" t="n">
-        <v>94</v>
-      </c>
-      <c r="F630" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G630" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="H630" t="n">
-        <v>80</v>
-      </c>
-      <c r="I630" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B631" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="C631" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D631" t="n">
-        <v>23</v>
-      </c>
-      <c r="E631" t="n">
-        <v>92</v>
-      </c>
-      <c r="F631" t="n">
-        <v>0</v>
-      </c>
-      <c r="G631" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="H631" t="n">
-        <v>3</v>
-      </c>
-      <c r="I631" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B632" t="inlineStr">
-        <is>
-          <t>Jagtial</t>
-        </is>
-      </c>
-      <c r="C632" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D632" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E632" t="n">
-        <v>96</v>
-      </c>
-      <c r="F632" t="n">
-        <v>0</v>
-      </c>
-      <c r="G632" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H632" t="n">
-        <v>3</v>
-      </c>
-      <c r="I632" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B633" t="inlineStr">
-        <is>
-          <t>Jangaon</t>
-        </is>
-      </c>
-      <c r="C633" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D633" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E633" t="n">
-        <v>92</v>
-      </c>
-      <c r="F633" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G633" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="H633" t="n">
-        <v>80</v>
-      </c>
-      <c r="I633" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B634" t="inlineStr">
-        <is>
-          <t>Jayashankar Bhupalpally</t>
-        </is>
-      </c>
-      <c r="C634" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D634" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E634" t="n">
-        <v>99</v>
-      </c>
-      <c r="F634" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G634" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H634" t="n">
-        <v>95</v>
-      </c>
-      <c r="I634" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t>Jogulamba Gadwal</t>
-        </is>
-      </c>
-      <c r="C635" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D635" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E635" t="n">
-        <v>82</v>
-      </c>
-      <c r="F635" t="n">
-        <v>0</v>
-      </c>
-      <c r="G635" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H635" t="n">
-        <v>3</v>
-      </c>
-      <c r="I635" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B636" t="inlineStr">
-        <is>
-          <t>Kamareddy</t>
-        </is>
-      </c>
-      <c r="C636" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D636" t="n">
-        <v>23</v>
-      </c>
-      <c r="E636" t="n">
-        <v>95</v>
-      </c>
-      <c r="F636" t="n">
-        <v>0</v>
-      </c>
-      <c r="G636" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="H636" t="n">
-        <v>3</v>
-      </c>
-      <c r="I636" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B637" t="inlineStr">
-        <is>
-          <t>Karimnagar</t>
-        </is>
-      </c>
-      <c r="C637" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D637" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E637" t="n">
-        <v>94</v>
-      </c>
-      <c r="F637" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G637" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H637" t="n">
-        <v>53</v>
-      </c>
-      <c r="I637" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B638" t="inlineStr">
-        <is>
-          <t>Khammam</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D638" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E638" t="n">
-        <v>94</v>
-      </c>
-      <c r="F638" t="n">
-        <v>1</v>
-      </c>
-      <c r="G638" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="H638" t="n">
-        <v>81</v>
-      </c>
-      <c r="I638" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B639" t="inlineStr">
-        <is>
-          <t>Kumuram Bheem Asifabad</t>
-        </is>
-      </c>
-      <c r="C639" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D639" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="E639" t="n">
-        <v>94</v>
-      </c>
-      <c r="F639" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G639" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="H639" t="n">
-        <v>53</v>
-      </c>
-      <c r="I639" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B640" t="inlineStr">
-        <is>
-          <t>Mahabubabad</t>
-        </is>
-      </c>
-      <c r="C640" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D640" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E640" t="n">
-        <v>95</v>
-      </c>
-      <c r="F640" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G640" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="H640" t="n">
-        <v>81</v>
-      </c>
-      <c r="I640" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B641" t="inlineStr">
-        <is>
-          <t>Mahbubnagar</t>
-        </is>
-      </c>
-      <c r="C641" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D641" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E641" t="n">
-        <v>94</v>
-      </c>
-      <c r="F641" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G641" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H641" t="n">
-        <v>51</v>
-      </c>
-      <c r="I641" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B642" t="inlineStr">
-        <is>
-          <t>Mancherial</t>
-        </is>
-      </c>
-      <c r="C642" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D642" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E642" t="n">
-        <v>96</v>
-      </c>
-      <c r="F642" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G642" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="H642" t="n">
-        <v>55</v>
-      </c>
-      <c r="I642" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B643" t="inlineStr">
-        <is>
-          <t>Medak</t>
-        </is>
-      </c>
-      <c r="C643" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D643" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="E643" t="n">
-        <v>96</v>
-      </c>
-      <c r="F643" t="n">
-        <v>0</v>
-      </c>
-      <c r="G643" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="H643" t="n">
-        <v>3</v>
-      </c>
-      <c r="I643" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B644" t="inlineStr">
-        <is>
-          <t>Medchal-Malkajgiri</t>
-        </is>
-      </c>
-      <c r="C644" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D644" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="E644" t="n">
-        <v>95</v>
-      </c>
-      <c r="F644" t="n">
-        <v>0</v>
-      </c>
-      <c r="G644" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="H644" t="n">
-        <v>3</v>
-      </c>
-      <c r="I644" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>Mulugu</t>
-        </is>
-      </c>
-      <c r="C645" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D645" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E645" t="n">
-        <v>99</v>
-      </c>
-      <c r="F645" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G645" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H645" t="n">
-        <v>95</v>
-      </c>
-      <c r="I645" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B646" t="inlineStr">
-        <is>
-          <t>Nagarkurnool</t>
-        </is>
-      </c>
-      <c r="C646" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D646" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E646" t="n">
-        <v>94</v>
-      </c>
-      <c r="F646" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G646" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="H646" t="n">
-        <v>53</v>
-      </c>
-      <c r="I646" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B647" t="inlineStr">
-        <is>
-          <t>Nalgonda</t>
-        </is>
-      </c>
-      <c r="C647" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D647" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E647" t="n">
-        <v>91</v>
-      </c>
-      <c r="F647" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G647" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H647" t="n">
-        <v>80</v>
-      </c>
-      <c r="I647" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B648" t="inlineStr">
-        <is>
-          <t>Narayanpet</t>
-        </is>
-      </c>
-      <c r="C648" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D648" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E648" t="n">
-        <v>88</v>
-      </c>
-      <c r="F648" t="n">
-        <v>0</v>
-      </c>
-      <c r="G648" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="H648" t="n">
-        <v>3</v>
-      </c>
-      <c r="I648" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B649" t="inlineStr">
-        <is>
-          <t>Nirmal</t>
-        </is>
-      </c>
-      <c r="C649" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D649" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E649" t="n">
-        <v>94</v>
-      </c>
-      <c r="F649" t="n">
-        <v>0</v>
-      </c>
-      <c r="G649" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="H649" t="n">
-        <v>3</v>
-      </c>
-      <c r="I649" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>Nizamabad</t>
-        </is>
-      </c>
-      <c r="C650" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D650" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E650" t="n">
-        <v>96</v>
-      </c>
-      <c r="F650" t="n">
-        <v>0</v>
-      </c>
-      <c r="G650" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="H650" t="n">
-        <v>3</v>
-      </c>
-      <c r="I650" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B651" t="inlineStr">
-        <is>
-          <t>Peddapalli</t>
-        </is>
-      </c>
-      <c r="C651" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D651" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E651" t="n">
-        <v>96</v>
-      </c>
-      <c r="F651" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G651" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="H651" t="n">
-        <v>80</v>
-      </c>
-      <c r="I651" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B652" t="inlineStr">
-        <is>
-          <t>Rajanna Sircilla</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D652" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E652" t="n">
-        <v>94</v>
-      </c>
-      <c r="F652" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G652" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="H652" t="n">
-        <v>51</v>
-      </c>
-      <c r="I652" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B653" t="inlineStr">
-        <is>
-          <t>Rangareddy</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D653" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E653" t="n">
-        <v>95</v>
-      </c>
-      <c r="F653" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G653" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="H653" t="n">
-        <v>51</v>
-      </c>
-      <c r="I653" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B654" t="inlineStr">
-        <is>
-          <t>Sangareddy</t>
-        </is>
-      </c>
-      <c r="C654" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D654" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E654" t="n">
-        <v>92</v>
-      </c>
-      <c r="F654" t="n">
-        <v>0</v>
-      </c>
-      <c r="G654" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="H654" t="n">
-        <v>3</v>
-      </c>
-      <c r="I654" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B655" t="inlineStr">
-        <is>
-          <t>Siddipet</t>
-        </is>
-      </c>
-      <c r="C655" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D655" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="E655" t="n">
-        <v>96</v>
-      </c>
-      <c r="F655" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G655" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="H655" t="n">
-        <v>80</v>
-      </c>
-      <c r="I655" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B656" t="inlineStr">
-        <is>
-          <t>Suryapet</t>
-        </is>
-      </c>
-      <c r="C656" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D656" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E656" t="n">
-        <v>92</v>
-      </c>
-      <c r="F656" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G656" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="H656" t="n">
-        <v>80</v>
-      </c>
-      <c r="I656" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B657" t="inlineStr">
-        <is>
-          <t>Vikarabad</t>
-        </is>
-      </c>
-      <c r="C657" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D657" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E657" t="n">
-        <v>96</v>
-      </c>
-      <c r="F657" t="n">
-        <v>0</v>
-      </c>
-      <c r="G657" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="H657" t="n">
-        <v>3</v>
-      </c>
-      <c r="I657" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B658" t="inlineStr">
-        <is>
-          <t>Wanaparthy</t>
-        </is>
-      </c>
-      <c r="C658" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D658" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E658" t="n">
-        <v>90</v>
-      </c>
-      <c r="F658" t="n">
-        <v>0</v>
-      </c>
-      <c r="G658" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H658" t="n">
-        <v>3</v>
-      </c>
-      <c r="I658" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B659" t="inlineStr">
-        <is>
-          <t>Warangal</t>
-        </is>
-      </c>
-      <c r="C659" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D659" t="n">
-        <v>24</v>
-      </c>
-      <c r="E659" t="n">
-        <v>95</v>
-      </c>
-      <c r="F659" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G659" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H659" t="n">
-        <v>80</v>
-      </c>
-      <c r="I659" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B660" t="inlineStr">
-        <is>
-          <t>Yadadri Bhuvanagiri</t>
-        </is>
-      </c>
-      <c r="C660" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D660" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E660" t="n">
-        <v>92</v>
-      </c>
-      <c r="F660" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G660" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="H660" t="n">
-        <v>51</v>
-      </c>
-      <c r="I660" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B661" t="inlineStr">
-        <is>
-          <t>Adilabad</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D661" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E661" t="n">
-        <v>94</v>
-      </c>
-      <c r="F661" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G661" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="H661" t="n">
-        <v>80</v>
-      </c>
-      <c r="I661" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B662" t="inlineStr">
-        <is>
-          <t>Bhadradri Kothagudem</t>
-        </is>
-      </c>
-      <c r="C662" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D662" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E662" t="n">
-        <v>96</v>
-      </c>
-      <c r="F662" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G662" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="H662" t="n">
-        <v>55</v>
-      </c>
-      <c r="I662" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B663" t="inlineStr">
-        <is>
-          <t>Hanumakonda</t>
-        </is>
-      </c>
-      <c r="C663" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D663" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E663" t="n">
-        <v>95</v>
-      </c>
-      <c r="F663" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G663" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H663" t="n">
-        <v>81</v>
-      </c>
-      <c r="I663" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B664" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="C664" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D664" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E664" t="n">
-        <v>90</v>
-      </c>
-      <c r="F664" t="n">
-        <v>0</v>
-      </c>
-      <c r="G664" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="H664" t="n">
-        <v>3</v>
-      </c>
-      <c r="I664" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B665" t="inlineStr">
-        <is>
-          <t>Jagtial</t>
-        </is>
-      </c>
-      <c r="C665" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D665" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E665" t="n">
-        <v>96</v>
-      </c>
-      <c r="F665" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G665" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H665" t="n">
-        <v>80</v>
-      </c>
-      <c r="I665" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B666" t="inlineStr">
-        <is>
-          <t>Jangaon</t>
-        </is>
-      </c>
-      <c r="C666" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D666" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E666" t="n">
-        <v>91</v>
-      </c>
-      <c r="F666" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G666" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="H666" t="n">
-        <v>80</v>
-      </c>
-      <c r="I666" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B667" t="inlineStr">
-        <is>
-          <t>Jayashankar Bhupalpally</t>
-        </is>
-      </c>
-      <c r="C667" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D667" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E667" t="n">
-        <v>99</v>
-      </c>
-      <c r="F667" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G667" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="H667" t="n">
-        <v>53</v>
-      </c>
-      <c r="I667" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B668" t="inlineStr">
-        <is>
-          <t>Jogulamba Gadwal</t>
-        </is>
-      </c>
-      <c r="C668" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D668" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E668" t="n">
-        <v>87</v>
-      </c>
-      <c r="F668" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G668" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H668" t="n">
-        <v>53</v>
-      </c>
-      <c r="I668" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B669" t="inlineStr">
-        <is>
-          <t>Kamareddy</t>
-        </is>
-      </c>
-      <c r="C669" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D669" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E669" t="n">
-        <v>92</v>
-      </c>
-      <c r="F669" t="n">
-        <v>0</v>
-      </c>
-      <c r="G669" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="H669" t="n">
-        <v>3</v>
-      </c>
-      <c r="I669" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>Karimnagar</t>
-        </is>
-      </c>
-      <c r="C670" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D670" t="n">
-        <v>24</v>
-      </c>
-      <c r="E670" t="n">
-        <v>94</v>
-      </c>
-      <c r="F670" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G670" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="H670" t="n">
-        <v>53</v>
-      </c>
-      <c r="I670" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>Khammam</t>
-        </is>
-      </c>
-      <c r="C671" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D671" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E671" t="n">
-        <v>94</v>
-      </c>
-      <c r="F671" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G671" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="H671" t="n">
-        <v>80</v>
-      </c>
-      <c r="I671" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B672" t="inlineStr">
-        <is>
-          <t>Kumuram Bheem Asifabad</t>
-        </is>
-      </c>
-      <c r="C672" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D672" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E672" t="n">
-        <v>95</v>
-      </c>
-      <c r="F672" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G672" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H672" t="n">
-        <v>51</v>
-      </c>
-      <c r="I672" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B673" t="inlineStr">
-        <is>
-          <t>Mahabubabad</t>
-        </is>
-      </c>
-      <c r="C673" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D673" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E673" t="n">
-        <v>95</v>
-      </c>
-      <c r="F673" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G673" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="H673" t="n">
-        <v>80</v>
-      </c>
-      <c r="I673" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B674" t="inlineStr">
-        <is>
-          <t>Mahbubnagar</t>
-        </is>
-      </c>
-      <c r="C674" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D674" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E674" t="n">
-        <v>92</v>
-      </c>
-      <c r="F674" t="n">
-        <v>0</v>
-      </c>
-      <c r="G674" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="H674" t="n">
-        <v>3</v>
-      </c>
-      <c r="I674" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B675" t="inlineStr">
-        <is>
-          <t>Mancherial</t>
-        </is>
-      </c>
-      <c r="C675" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D675" t="n">
-        <v>25</v>
-      </c>
-      <c r="E675" t="n">
-        <v>95</v>
-      </c>
-      <c r="F675" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G675" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="H675" t="n">
-        <v>51</v>
-      </c>
-      <c r="I675" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B676" t="inlineStr">
-        <is>
-          <t>Medak</t>
-        </is>
-      </c>
-      <c r="C676" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D676" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E676" t="n">
-        <v>93</v>
-      </c>
-      <c r="F676" t="n">
-        <v>0</v>
-      </c>
-      <c r="G676" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="H676" t="n">
-        <v>3</v>
-      </c>
-      <c r="I676" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B677" t="inlineStr">
-        <is>
-          <t>Medchal-Malkajgiri</t>
-        </is>
-      </c>
-      <c r="C677" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D677" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="E677" t="n">
-        <v>94</v>
-      </c>
-      <c r="F677" t="n">
-        <v>0</v>
-      </c>
-      <c r="G677" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="H677" t="n">
-        <v>3</v>
-      </c>
-      <c r="I677" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B678" t="inlineStr">
-        <is>
-          <t>Mulugu</t>
-        </is>
-      </c>
-      <c r="C678" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D678" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E678" t="n">
-        <v>98</v>
-      </c>
-      <c r="F678" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G678" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="H678" t="n">
-        <v>53</v>
-      </c>
-      <c r="I678" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B679" t="inlineStr">
-        <is>
-          <t>Nagarkurnool</t>
-        </is>
-      </c>
-      <c r="C679" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D679" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E679" t="n">
-        <v>93</v>
-      </c>
-      <c r="F679" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G679" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="H679" t="n">
-        <v>51</v>
-      </c>
-      <c r="I679" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B680" t="inlineStr">
-        <is>
-          <t>Nalgonda</t>
-        </is>
-      </c>
-      <c r="C680" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D680" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E680" t="n">
-        <v>90</v>
-      </c>
-      <c r="F680" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G680" t="n">
-        <v>20</v>
-      </c>
-      <c r="H680" t="n">
-        <v>80</v>
-      </c>
-      <c r="I680" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B681" t="inlineStr">
-        <is>
-          <t>Narayanpet</t>
-        </is>
-      </c>
-      <c r="C681" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D681" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E681" t="n">
-        <v>85</v>
-      </c>
-      <c r="F681" t="n">
-        <v>0</v>
-      </c>
-      <c r="G681" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="H681" t="n">
-        <v>3</v>
-      </c>
-      <c r="I681" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B682" t="inlineStr">
-        <is>
-          <t>Nirmal</t>
-        </is>
-      </c>
-      <c r="C682" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D682" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E682" t="n">
-        <v>90</v>
-      </c>
-      <c r="F682" t="n">
-        <v>0</v>
-      </c>
-      <c r="G682" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="H682" t="n">
-        <v>3</v>
-      </c>
-      <c r="I682" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B683" t="inlineStr">
-        <is>
-          <t>Nizamabad</t>
-        </is>
-      </c>
-      <c r="C683" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D683" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E683" t="n">
-        <v>91</v>
-      </c>
-      <c r="F683" t="n">
-        <v>0</v>
-      </c>
-      <c r="G683" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H683" t="n">
-        <v>3</v>
-      </c>
-      <c r="I683" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B684" t="inlineStr">
-        <is>
-          <t>Peddapalli</t>
-        </is>
-      </c>
-      <c r="C684" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D684" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E684" t="n">
-        <v>96</v>
-      </c>
-      <c r="F684" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G684" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="H684" t="n">
-        <v>55</v>
-      </c>
-      <c r="I684" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B685" t="inlineStr">
-        <is>
-          <t>Rajanna Sircilla</t>
-        </is>
-      </c>
-      <c r="C685" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D685" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E685" t="n">
-        <v>94</v>
-      </c>
-      <c r="F685" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G685" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H685" t="n">
-        <v>53</v>
-      </c>
-      <c r="I685" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B686" t="inlineStr">
-        <is>
-          <t>Rangareddy</t>
-        </is>
-      </c>
-      <c r="C686" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D686" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E686" t="n">
-        <v>92</v>
-      </c>
-      <c r="F686" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G686" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H686" t="n">
-        <v>51</v>
-      </c>
-      <c r="I686" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B687" t="inlineStr">
-        <is>
-          <t>Sangareddy</t>
-        </is>
-      </c>
-      <c r="C687" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D687" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E687" t="n">
-        <v>87</v>
-      </c>
-      <c r="F687" t="n">
-        <v>0</v>
-      </c>
-      <c r="G687" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="H687" t="n">
-        <v>3</v>
-      </c>
-      <c r="I687" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B688" t="inlineStr">
-        <is>
-          <t>Siddipet</t>
-        </is>
-      </c>
-      <c r="C688" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D688" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="E688" t="n">
-        <v>94</v>
-      </c>
-      <c r="F688" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G688" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H688" t="n">
-        <v>55</v>
-      </c>
-      <c r="I688" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B689" t="inlineStr">
-        <is>
-          <t>Suryapet</t>
-        </is>
-      </c>
-      <c r="C689" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D689" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E689" t="n">
-        <v>91</v>
-      </c>
-      <c r="F689" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G689" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="H689" t="n">
-        <v>53</v>
-      </c>
-      <c r="I689" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B690" t="inlineStr">
-        <is>
-          <t>Vikarabad</t>
-        </is>
-      </c>
-      <c r="C690" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D690" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E690" t="n">
-        <v>93</v>
-      </c>
-      <c r="F690" t="n">
-        <v>0</v>
-      </c>
-      <c r="G690" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="H690" t="n">
-        <v>3</v>
-      </c>
-      <c r="I690" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B691" t="inlineStr">
-        <is>
-          <t>Wanaparthy</t>
-        </is>
-      </c>
-      <c r="C691" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D691" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E691" t="n">
-        <v>90</v>
-      </c>
-      <c r="F691" t="n">
-        <v>0</v>
-      </c>
-      <c r="G691" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="H691" t="n">
-        <v>3</v>
-      </c>
-      <c r="I691" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B692" t="inlineStr">
-        <is>
-          <t>Warangal</t>
-        </is>
-      </c>
-      <c r="C692" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D692" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E692" t="n">
-        <v>96</v>
-      </c>
-      <c r="F692" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G692" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="H692" t="n">
-        <v>81</v>
-      </c>
-      <c r="I692" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B693" t="inlineStr">
-        <is>
-          <t>Yadadri Bhuvanagiri</t>
-        </is>
-      </c>
-      <c r="C693" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D693" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E693" t="n">
-        <v>91</v>
-      </c>
-      <c r="F693" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G693" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="H693" t="n">
-        <v>53</v>
-      </c>
-      <c r="I693" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
@@ -26080,7 +23675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27298,7 +24893,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -27310,29 +24905,29 @@
         <v>33</v>
       </c>
       <c r="D21" t="n">
-        <v>23.9</v>
+        <v>27.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Khammam</t>
+          <t>Jogulamba Gadwal</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>25.7</v>
+        <v>30.3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Vikarabad</t>
+          <t>Bhadradri Kothagudem</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>21.9</v>
+        <v>25.1</v>
       </c>
       <c r="I21" t="n">
-        <v>94.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>8.699999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -27340,141 +24935,19 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Siddipet</t>
+          <t>Jangaon</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>23</v>
+        <v>26.7</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-09-24T00:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>33</v>
-      </c>
-      <c r="D22" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Jogulamba Gadwal</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Medchal-Malkajgiri</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="I22" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="J22" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Khammam</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Jangaon</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>33</v>
-      </c>
-      <c r="D23" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Mancherial</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>25</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Vikarabad</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="I23" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="J23" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Hanumakonda</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Jangaon</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2026-09-24T06:30</t>
+          <t>2026-09-24T11:15</t>
         </is>
       </c>
     </row>
@@ -27541,19 +25014,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.6</v>
+        <v>28.3</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
       </c>
       <c r="E2" t="n">
-        <v>23.9</v>
+        <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>83.5</v>
+        <v>81.2</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
@@ -27568,19 +25041,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.3</v>
+        <v>28.7</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
       </c>
       <c r="E3" t="n">
-        <v>24.2</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>82.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4">
@@ -27595,19 +25068,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.4</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
       </c>
       <c r="E4" t="n">
-        <v>23.8</v>
+        <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>76.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
@@ -27622,19 +25095,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>28.7</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>24.7</v>
       </c>
       <c r="F5" t="n">
-        <v>69.7</v>
+        <v>66.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -27649,19 +25122,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.5</v>
+        <v>28.1</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
       </c>
       <c r="E6" t="n">
-        <v>23.6</v>
+        <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>84.2</v>
+        <v>82.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -27676,19 +25149,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.7</v>
+        <v>28.3</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>23.6</v>
+        <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8">
@@ -27703,19 +25176,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.7</v>
+        <v>28.2</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>23.9</v>
+        <v>24.4</v>
       </c>
       <c r="F8" t="n">
-        <v>84.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
@@ -27730,7 +25203,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.2</v>
+        <v>28.8</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -27739,10 +25212,10 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>71.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="G9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -27757,7 +25230,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.2</v>
+        <v>26.7</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -27766,10 +25239,10 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>82.8</v>
+        <v>80.7</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
@@ -27784,19 +25257,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>81.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
@@ -27811,19 +25284,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.3</v>
+        <v>29.8</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
       </c>
       <c r="E12" t="n">
-        <v>24.7</v>
+        <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>76.2</v>
+        <v>74.3</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13">
@@ -27838,19 +25311,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>28.6</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
       </c>
       <c r="E13" t="n">
-        <v>24.4</v>
+        <v>25.2</v>
       </c>
       <c r="F13" t="n">
-        <v>83.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="14">
@@ -27865,19 +25338,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.3</v>
+        <v>28.8</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
       </c>
       <c r="E14" t="n">
-        <v>24.1</v>
+        <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>80.7</v>
+        <v>78.2</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -27892,19 +25365,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.5</v>
+        <v>27.2</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
       </c>
       <c r="E15" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>77.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="16">
@@ -27919,19 +25392,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.5</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
       </c>
       <c r="E16" t="n">
-        <v>24.7</v>
+        <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>81.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17">
@@ -27946,19 +25419,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.6</v>
+        <v>27.2</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
       </c>
       <c r="E17" t="n">
-        <v>22.8</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>82</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="18">
@@ -27973,19 +25446,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.4</v>
+        <v>27.1</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
       </c>
       <c r="E18" t="n">
-        <v>22.3</v>
+        <v>23.7</v>
       </c>
       <c r="F18" t="n">
-        <v>78.2</v>
+        <v>75.3</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="19">
@@ -28000,19 +25473,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.4</v>
+        <v>27.9</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
       </c>
       <c r="E19" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>84.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="20">
@@ -28027,19 +25500,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.1</v>
+        <v>27.8</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
       </c>
       <c r="E20" t="n">
-        <v>22.9</v>
+        <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>75.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="21">
@@ -28054,19 +25527,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>29.7</v>
+        <v>30.4</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
       </c>
       <c r="E21" t="n">
-        <v>24.7</v>
+        <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>69</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="22">
@@ -28081,7 +25554,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>26.8</v>
+        <v>27.4</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -28090,10 +25563,10 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>75.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -28108,19 +25581,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.5</v>
+        <v>28.2</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
       </c>
       <c r="E23" t="n">
-        <v>23.7</v>
+        <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>80.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24">
@@ -28135,19 +25608,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.8</v>
+        <v>27.4</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
       </c>
       <c r="E24" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>83.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="25">
@@ -28162,19 +25635,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>24.1</v>
+        <v>25.4</v>
       </c>
       <c r="F25" t="n">
-        <v>83.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="G25" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
@@ -28189,19 +25662,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.5</v>
+        <v>28.1</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
       </c>
       <c r="E26" t="n">
-        <v>23.9</v>
+        <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>81.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="27">
@@ -28216,19 +25689,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.5</v>
+        <v>27.2</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
       </c>
       <c r="E27" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>75.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="28">
@@ -28243,19 +25716,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.4</v>
+        <v>28.1</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
       </c>
       <c r="E28" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="F28" t="n">
-        <v>74.2</v>
+        <v>71.2</v>
       </c>
       <c r="G28" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="29">
@@ -28270,19 +25743,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.6</v>
+        <v>27.2</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
       </c>
       <c r="E29" t="n">
-        <v>22.8</v>
+        <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>81.8</v>
+        <v>79.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="30">
@@ -28297,19 +25770,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.4</v>
+        <v>30</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
       </c>
       <c r="E30" t="n">
-        <v>24.7</v>
+        <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>72</v>
+        <v>69.8</v>
       </c>
       <c r="G30" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31">
@@ -28324,19 +25797,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.3</v>
+        <v>27</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
       </c>
       <c r="E31" t="n">
-        <v>21.9</v>
+        <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>76.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -28351,16 +25824,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>27.7</v>
+        <v>28.3</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
       </c>
       <c r="E32" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>73.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -28378,19 +25851,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.6</v>
+        <v>29.2</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
       </c>
       <c r="E33" t="n">
-        <v>23.7</v>
+        <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>75.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="G33" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="34">
@@ -28405,19 +25878,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.4</v>
+        <v>28</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
       </c>
       <c r="E34" t="n">
-        <v>23.4</v>
+        <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>75.8</v>
+        <v>73.7</v>
       </c>
       <c r="G34" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I628"/>
+  <dimension ref="A1:I661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23661,6 +23661,1227 @@
       <c r="I628" t="inlineStr">
         <is>
           <t>2026-09-24T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D629" t="n">
+        <v>30</v>
+      </c>
+      <c r="E629" t="n">
+        <v>70</v>
+      </c>
+      <c r="F629" t="n">
+        <v>0</v>
+      </c>
+      <c r="G629" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H629" t="n">
+        <v>3</v>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D630" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E630" t="n">
+        <v>91</v>
+      </c>
+      <c r="F630" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G630" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H630" t="n">
+        <v>51</v>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D631" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E631" t="n">
+        <v>83</v>
+      </c>
+      <c r="F631" t="n">
+        <v>0</v>
+      </c>
+      <c r="G631" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H631" t="n">
+        <v>3</v>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D632" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E632" t="n">
+        <v>69</v>
+      </c>
+      <c r="F632" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G632" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H632" t="n">
+        <v>51</v>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D633" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E633" t="n">
+        <v>75</v>
+      </c>
+      <c r="F633" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G633" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H633" t="n">
+        <v>51</v>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D634" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E634" t="n">
+        <v>79</v>
+      </c>
+      <c r="F634" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G634" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="H634" t="n">
+        <v>53</v>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D635" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E635" t="n">
+        <v>89</v>
+      </c>
+      <c r="F635" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G635" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H635" t="n">
+        <v>95</v>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D636" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E636" t="n">
+        <v>59</v>
+      </c>
+      <c r="F636" t="n">
+        <v>0</v>
+      </c>
+      <c r="G636" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H636" t="n">
+        <v>3</v>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E637" t="n">
+        <v>75</v>
+      </c>
+      <c r="F637" t="n">
+        <v>0</v>
+      </c>
+      <c r="G637" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H637" t="n">
+        <v>3</v>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E638" t="n">
+        <v>77</v>
+      </c>
+      <c r="F638" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G638" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="H638" t="n">
+        <v>95</v>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E639" t="n">
+        <v>92</v>
+      </c>
+      <c r="F639" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G639" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H639" t="n">
+        <v>51</v>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E640" t="n">
+        <v>93</v>
+      </c>
+      <c r="F640" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G640" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H640" t="n">
+        <v>51</v>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D641" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E641" t="n">
+        <v>90</v>
+      </c>
+      <c r="F641" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G641" t="n">
+        <v>21</v>
+      </c>
+      <c r="H641" t="n">
+        <v>51</v>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D642" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E642" t="n">
+        <v>63</v>
+      </c>
+      <c r="F642" t="n">
+        <v>0</v>
+      </c>
+      <c r="G642" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H642" t="n">
+        <v>3</v>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D643" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E643" t="n">
+        <v>76</v>
+      </c>
+      <c r="F643" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G643" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H643" t="n">
+        <v>96</v>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D644" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E644" t="n">
+        <v>76</v>
+      </c>
+      <c r="F644" t="n">
+        <v>0</v>
+      </c>
+      <c r="G644" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H644" t="n">
+        <v>3</v>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D645" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E645" t="n">
+        <v>72</v>
+      </c>
+      <c r="F645" t="n">
+        <v>0</v>
+      </c>
+      <c r="G645" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="H645" t="n">
+        <v>3</v>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D646" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E646" t="n">
+        <v>90</v>
+      </c>
+      <c r="F646" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G646" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H646" t="n">
+        <v>95</v>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D647" t="n">
+        <v>29</v>
+      </c>
+      <c r="E647" t="n">
+        <v>67</v>
+      </c>
+      <c r="F647" t="n">
+        <v>0</v>
+      </c>
+      <c r="G647" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H647" t="n">
+        <v>3</v>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D648" t="n">
+        <v>29</v>
+      </c>
+      <c r="E648" t="n">
+        <v>74</v>
+      </c>
+      <c r="F648" t="n">
+        <v>0</v>
+      </c>
+      <c r="G648" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H648" t="n">
+        <v>3</v>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D649" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E649" t="n">
+        <v>63</v>
+      </c>
+      <c r="F649" t="n">
+        <v>0</v>
+      </c>
+      <c r="G649" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H649" t="n">
+        <v>3</v>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D650" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E650" t="n">
+        <v>68</v>
+      </c>
+      <c r="F650" t="n">
+        <v>0</v>
+      </c>
+      <c r="G650" t="n">
+        <v>20</v>
+      </c>
+      <c r="H650" t="n">
+        <v>3</v>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E651" t="n">
+        <v>71</v>
+      </c>
+      <c r="F651" t="n">
+        <v>0</v>
+      </c>
+      <c r="G651" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H651" t="n">
+        <v>3</v>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E652" t="n">
+        <v>80</v>
+      </c>
+      <c r="F652" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G652" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H652" t="n">
+        <v>95</v>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E653" t="n">
+        <v>70</v>
+      </c>
+      <c r="F653" t="n">
+        <v>0</v>
+      </c>
+      <c r="G653" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H653" t="n">
+        <v>3</v>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E654" t="n">
+        <v>67</v>
+      </c>
+      <c r="F654" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G654" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H654" t="n">
+        <v>95</v>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E655" t="n">
+        <v>66</v>
+      </c>
+      <c r="F655" t="n">
+        <v>0</v>
+      </c>
+      <c r="G655" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="H655" t="n">
+        <v>3</v>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E656" t="n">
+        <v>74</v>
+      </c>
+      <c r="F656" t="n">
+        <v>0</v>
+      </c>
+      <c r="G656" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H656" t="n">
+        <v>3</v>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D657" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E657" t="n">
+        <v>89</v>
+      </c>
+      <c r="F657" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G657" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H657" t="n">
+        <v>55</v>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E658" t="n">
+        <v>64</v>
+      </c>
+      <c r="F658" t="n">
+        <v>0</v>
+      </c>
+      <c r="G658" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H658" t="n">
+        <v>3</v>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E659" t="n">
+        <v>63</v>
+      </c>
+      <c r="F659" t="n">
+        <v>0</v>
+      </c>
+      <c r="G659" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="H659" t="n">
+        <v>3</v>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D660" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E660" t="n">
+        <v>84</v>
+      </c>
+      <c r="F660" t="n">
+        <v>0</v>
+      </c>
+      <c r="G660" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H660" t="n">
+        <v>3</v>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D661" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E661" t="n">
+        <v>73</v>
+      </c>
+      <c r="F661" t="n">
+        <v>0</v>
+      </c>
+      <c r="G661" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H661" t="n">
+        <v>3</v>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
         </is>
       </c>
     </row>
@@ -23675,7 +24896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24948,6 +26169,67 @@
       <c r="O21" t="inlineStr">
         <is>
           <t>2026-09-24T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>33</v>
+      </c>
+      <c r="D22" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:45</t>
         </is>
       </c>
     </row>
@@ -25014,7 +26296,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -25023,7 +26305,7 @@
         <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>81.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>0.7</v>
@@ -25041,7 +26323,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -25050,10 +26332,10 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>81.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4">
@@ -25068,7 +26350,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -25077,7 +26359,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>74.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.7</v>
@@ -25095,7 +26377,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -25104,10 +26386,10 @@
         <v>24.7</v>
       </c>
       <c r="F5" t="n">
-        <v>66.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -25122,7 +26404,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -25131,10 +26413,10 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>82.2</v>
+        <v>81.8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -25149,7 +26431,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -25158,10 +26440,10 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>75.2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -25185,10 +26467,10 @@
         <v>24.4</v>
       </c>
       <c r="F8" t="n">
-        <v>82.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -25203,7 +26485,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -25212,7 +26494,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>69.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -25230,7 +26512,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -25239,7 +26521,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>80.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>2.3</v>
@@ -25257,7 +26539,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -25266,10 +26548,10 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12">
@@ -25284,7 +26566,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -25293,10 +26575,10 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -25311,7 +26593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -25320,10 +26602,10 @@
         <v>25.2</v>
       </c>
       <c r="F13" t="n">
-        <v>81.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -25338,7 +26620,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -25347,10 +26629,10 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>78.2</v>
+        <v>78.8</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -25365,7 +26647,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -25374,7 +26656,7 @@
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>73.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>1.6</v>
@@ -25401,10 +26683,10 @@
         <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -25428,7 +26710,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>1.1</v>
@@ -25455,7 +26737,7 @@
         <v>23.7</v>
       </c>
       <c r="F18" t="n">
-        <v>75.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>1.9</v>
@@ -25482,10 +26764,10 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>82.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="20">
@@ -25509,7 +26791,7 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>72.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
@@ -25527,7 +26809,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -25536,7 +26818,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="G21" t="n">
         <v>0.7</v>
@@ -25554,7 +26836,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -25563,7 +26845,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>72.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>2.7</v>
@@ -25581,7 +26863,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -25590,7 +26872,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>77.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="G23" t="n">
         <v>0.2</v>
@@ -25608,7 +26890,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -25617,7 +26899,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>80.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0.4</v>
@@ -25644,10 +26926,10 @@
         <v>25.4</v>
       </c>
       <c r="F25" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="26">
@@ -25662,7 +26944,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
@@ -25671,7 +26953,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>79.5</v>
+        <v>79</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -25689,7 +26971,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -25698,10 +26980,10 @@
         <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>72.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28">
@@ -25725,7 +27007,7 @@
         <v>23.3</v>
       </c>
       <c r="F28" t="n">
-        <v>71.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G28" t="n">
         <v>0.9</v>
@@ -25752,7 +27034,7 @@
         <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>79.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0.2</v>
@@ -25770,7 +27052,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -25779,10 +27061,10 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>69.8</v>
+        <v>70.8</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="31">
@@ -25797,7 +27079,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -25806,7 +27088,7 @@
         <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>72.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -25824,7 +27106,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -25833,7 +27115,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>70.2</v>
+        <v>69.8</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -25851,7 +27133,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -25860,7 +27142,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>72.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0.9</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I661"/>
+  <dimension ref="A1:I694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24882,6 +24882,1227 @@
       <c r="I661" t="inlineStr">
         <is>
           <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>26</v>
+      </c>
+      <c r="E662" t="n">
+        <v>90</v>
+      </c>
+      <c r="F662" t="n">
+        <v>0</v>
+      </c>
+      <c r="G662" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H662" t="n">
+        <v>3</v>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E663" t="n">
+        <v>95</v>
+      </c>
+      <c r="F663" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G663" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H663" t="n">
+        <v>80</v>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E664" t="n">
+        <v>90</v>
+      </c>
+      <c r="F664" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G664" t="n">
+        <v>17</v>
+      </c>
+      <c r="H664" t="n">
+        <v>51</v>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E665" t="n">
+        <v>77</v>
+      </c>
+      <c r="F665" t="n">
+        <v>0</v>
+      </c>
+      <c r="G665" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H665" t="n">
+        <v>3</v>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E666" t="n">
+        <v>92</v>
+      </c>
+      <c r="F666" t="n">
+        <v>0</v>
+      </c>
+      <c r="G666" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H666" t="n">
+        <v>3</v>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E667" t="n">
+        <v>90</v>
+      </c>
+      <c r="F667" t="n">
+        <v>0</v>
+      </c>
+      <c r="G667" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H667" t="n">
+        <v>3</v>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E668" t="n">
+        <v>91</v>
+      </c>
+      <c r="F668" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G668" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H668" t="n">
+        <v>51</v>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E669" t="n">
+        <v>64</v>
+      </c>
+      <c r="F669" t="n">
+        <v>0</v>
+      </c>
+      <c r="G669" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H669" t="n">
+        <v>3</v>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D670" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E670" t="n">
+        <v>93</v>
+      </c>
+      <c r="F670" t="n">
+        <v>0</v>
+      </c>
+      <c r="G670" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H670" t="n">
+        <v>3</v>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E671" t="n">
+        <v>86</v>
+      </c>
+      <c r="F671" t="n">
+        <v>0</v>
+      </c>
+      <c r="G671" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H671" t="n">
+        <v>3</v>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D672" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E672" t="n">
+        <v>83</v>
+      </c>
+      <c r="F672" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G672" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H672" t="n">
+        <v>51</v>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D673" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E673" t="n">
+        <v>89</v>
+      </c>
+      <c r="F673" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G673" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H673" t="n">
+        <v>51</v>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D674" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E674" t="n">
+        <v>89</v>
+      </c>
+      <c r="F674" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G674" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H674" t="n">
+        <v>55</v>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D675" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E675" t="n">
+        <v>82</v>
+      </c>
+      <c r="F675" t="n">
+        <v>0</v>
+      </c>
+      <c r="G675" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H675" t="n">
+        <v>3</v>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D676" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E676" t="n">
+        <v>89</v>
+      </c>
+      <c r="F676" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G676" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H676" t="n">
+        <v>53</v>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D677" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E677" t="n">
+        <v>92</v>
+      </c>
+      <c r="F677" t="n">
+        <v>0</v>
+      </c>
+      <c r="G677" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H677" t="n">
+        <v>3</v>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D678" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E678" t="n">
+        <v>86</v>
+      </c>
+      <c r="F678" t="n">
+        <v>0</v>
+      </c>
+      <c r="G678" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H678" t="n">
+        <v>3</v>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D679" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E679" t="n">
+        <v>95</v>
+      </c>
+      <c r="F679" t="n">
+        <v>0</v>
+      </c>
+      <c r="G679" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="H679" t="n">
+        <v>3</v>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D680" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E680" t="n">
+        <v>76</v>
+      </c>
+      <c r="F680" t="n">
+        <v>0</v>
+      </c>
+      <c r="G680" t="n">
+        <v>17</v>
+      </c>
+      <c r="H680" t="n">
+        <v>3</v>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D681" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E681" t="n">
+        <v>73</v>
+      </c>
+      <c r="F681" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G681" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H681" t="n">
+        <v>51</v>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D682" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E682" t="n">
+        <v>73</v>
+      </c>
+      <c r="F682" t="n">
+        <v>0</v>
+      </c>
+      <c r="G682" t="n">
+        <v>14</v>
+      </c>
+      <c r="H682" t="n">
+        <v>3</v>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D683" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E683" t="n">
+        <v>90</v>
+      </c>
+      <c r="F683" t="n">
+        <v>0</v>
+      </c>
+      <c r="G683" t="n">
+        <v>15</v>
+      </c>
+      <c r="H683" t="n">
+        <v>3</v>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E684" t="n">
+        <v>94</v>
+      </c>
+      <c r="F684" t="n">
+        <v>0</v>
+      </c>
+      <c r="G684" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H684" t="n">
+        <v>3</v>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
+        <v>26</v>
+      </c>
+      <c r="E685" t="n">
+        <v>90</v>
+      </c>
+      <c r="F685" t="n">
+        <v>0</v>
+      </c>
+      <c r="G685" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H685" t="n">
+        <v>3</v>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>25</v>
+      </c>
+      <c r="E686" t="n">
+        <v>90</v>
+      </c>
+      <c r="F686" t="n">
+        <v>0</v>
+      </c>
+      <c r="G686" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H686" t="n">
+        <v>3</v>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D687" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E687" t="n">
+        <v>79</v>
+      </c>
+      <c r="F687" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G687" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H687" t="n">
+        <v>51</v>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D688" t="n">
+        <v>27</v>
+      </c>
+      <c r="E688" t="n">
+        <v>74</v>
+      </c>
+      <c r="F688" t="n">
+        <v>0</v>
+      </c>
+      <c r="G688" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H688" t="n">
+        <v>3</v>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E689" t="n">
+        <v>90</v>
+      </c>
+      <c r="F689" t="n">
+        <v>0</v>
+      </c>
+      <c r="G689" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H689" t="n">
+        <v>3</v>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E690" t="n">
+        <v>88</v>
+      </c>
+      <c r="F690" t="n">
+        <v>0</v>
+      </c>
+      <c r="G690" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H690" t="n">
+        <v>3</v>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D691" t="n">
+        <v>26</v>
+      </c>
+      <c r="E691" t="n">
+        <v>80</v>
+      </c>
+      <c r="F691" t="n">
+        <v>0</v>
+      </c>
+      <c r="G691" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H691" t="n">
+        <v>3</v>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D692" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E692" t="n">
+        <v>73</v>
+      </c>
+      <c r="F692" t="n">
+        <v>0</v>
+      </c>
+      <c r="G692" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H692" t="n">
+        <v>3</v>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D693" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E693" t="n">
+        <v>90</v>
+      </c>
+      <c r="F693" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G693" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="H693" t="n">
+        <v>51</v>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D694" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E694" t="n">
+        <v>85</v>
+      </c>
+      <c r="F694" t="n">
+        <v>0</v>
+      </c>
+      <c r="G694" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H694" t="n">
+        <v>3</v>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
         </is>
       </c>
     </row>
@@ -24896,7 +26117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26230,6 +27451,67 @@
       <c r="O22" t="inlineStr">
         <is>
           <t>2026-09-24T12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>33</v>
+      </c>
+      <c r="D23" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-09-24T18:45</t>
         </is>
       </c>
     </row>
@@ -26296,7 +27578,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -26305,7 +27587,7 @@
         <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>80.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>0.7</v>
@@ -26323,7 +27605,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -26332,10 +27614,10 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>81.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="4">
@@ -26350,7 +27632,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -26359,10 +27641,10 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>75.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
@@ -26377,7 +27659,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -26386,7 +27668,7 @@
         <v>24.7</v>
       </c>
       <c r="F5" t="n">
-        <v>66.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -26404,7 +27686,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -26413,7 +27695,7 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>81.8</v>
+        <v>82.3</v>
       </c>
       <c r="G6" t="n">
         <v>0.3</v>
@@ -26431,7 +27713,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -26440,7 +27722,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>75.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>0.5</v>
@@ -26458,7 +27740,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -26467,10 +27749,10 @@
         <v>24.4</v>
       </c>
       <c r="F8" t="n">
-        <v>82.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="9">
@@ -26494,7 +27776,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>68.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -26512,7 +27794,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -26521,7 +27803,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>80.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="G10" t="n">
         <v>2.3</v>
@@ -26539,7 +27821,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -26548,7 +27830,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>79</v>
+        <v>79.3</v>
       </c>
       <c r="G11" t="n">
         <v>0.6</v>
@@ -26566,7 +27848,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -26575,10 +27857,10 @@
         <v>25.5</v>
       </c>
       <c r="F12" t="n">
-        <v>75.2</v>
+        <v>75.5</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="13">
@@ -26593,7 +27875,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -26602,10 +27884,10 @@
         <v>25.2</v>
       </c>
       <c r="F13" t="n">
-        <v>82.2</v>
+        <v>82.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="14">
@@ -26620,7 +27902,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -26629,10 +27911,10 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>78.8</v>
+        <v>79.3</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="15">
@@ -26656,7 +27938,7 @@
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>73.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="G15" t="n">
         <v>1.6</v>
@@ -26674,7 +27956,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -26683,10 +27965,10 @@
         <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>79</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -26701,7 +27983,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
@@ -26710,7 +27992,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>79.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="G17" t="n">
         <v>1.1</v>
@@ -26728,7 +28010,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -26737,7 +28019,7 @@
         <v>23.7</v>
       </c>
       <c r="F18" t="n">
-        <v>75.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>1.9</v>
@@ -26755,7 +28037,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -26764,7 +28046,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>82.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>1.4</v>
@@ -26791,7 +28073,7 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
@@ -26809,7 +28091,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -26818,10 +28100,10 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>66.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22">
@@ -26863,7 +28145,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -26872,7 +28154,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>77.2</v>
+        <v>77.8</v>
       </c>
       <c r="G23" t="n">
         <v>0.2</v>
@@ -26890,7 +28172,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -26899,7 +28181,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>80.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0.4</v>
@@ -26917,7 +28199,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -26926,7 +28208,7 @@
         <v>25.4</v>
       </c>
       <c r="F25" t="n">
-        <v>81.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0.9</v>
@@ -26944,16 +28226,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
       </c>
       <c r="E26" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>79</v>
+        <v>79.5</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -26980,10 +28262,10 @@
         <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>71.8</v>
+        <v>72.2</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="28">
@@ -27007,7 +28289,7 @@
         <v>23.3</v>
       </c>
       <c r="F28" t="n">
-        <v>70.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="G28" t="n">
         <v>0.9</v>
@@ -27025,7 +28307,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
@@ -27034,7 +28316,7 @@
         <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>79.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="G29" t="n">
         <v>0.2</v>
@@ -27052,7 +28334,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -27061,7 +28343,7 @@
         <v>25.4</v>
       </c>
       <c r="F30" t="n">
-        <v>70.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G30" t="n">
         <v>0.8</v>
@@ -27079,7 +28361,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -27088,7 +28370,7 @@
         <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -27115,7 +28397,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>69.8</v>
+        <v>70</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -27133,7 +28415,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -27142,10 +28424,10 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>73.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -27160,7 +28442,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -27169,7 +28451,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>73.7</v>
+        <v>74.2</v>
       </c>
       <c r="G34" t="n">
         <v>0.5</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I694"/>
+  <dimension ref="A1:I661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23681,23 +23681,23 @@
         </is>
       </c>
       <c r="D629" t="n">
-        <v>30</v>
+        <v>25.7</v>
       </c>
       <c r="E629" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="F629" t="n">
         <v>0</v>
       </c>
       <c r="G629" t="n">
-        <v>20.5</v>
+        <v>19.2</v>
       </c>
       <c r="H629" t="n">
         <v>3</v>
       </c>
       <c r="I629" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -23718,23 +23718,23 @@
         </is>
       </c>
       <c r="D630" t="n">
-        <v>26.9</v>
+        <v>25.1</v>
       </c>
       <c r="E630" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F630" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G630" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="H630" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I630" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -23755,23 +23755,23 @@
         </is>
       </c>
       <c r="D631" t="n">
-        <v>27.3</v>
+        <v>25.4</v>
       </c>
       <c r="E631" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F631" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G631" t="n">
-        <v>21.5</v>
+        <v>19.2</v>
       </c>
       <c r="H631" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I631" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -23792,23 +23792,23 @@
         </is>
       </c>
       <c r="D632" t="n">
-        <v>27.9</v>
+        <v>26.1</v>
       </c>
       <c r="E632" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F632" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G632" t="n">
-        <v>19.4</v>
+        <v>14.2</v>
       </c>
       <c r="H632" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I632" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -23829,23 +23829,23 @@
         </is>
       </c>
       <c r="D633" t="n">
-        <v>29.3</v>
+        <v>25.4</v>
       </c>
       <c r="E633" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="F633" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G633" t="n">
-        <v>19.6</v>
+        <v>17.8</v>
       </c>
       <c r="H633" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I633" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -23866,23 +23866,23 @@
         </is>
       </c>
       <c r="D634" t="n">
-        <v>27.7</v>
+        <v>26.7</v>
       </c>
       <c r="E634" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F634" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G634" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="H634" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="I634" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -23903,23 +23903,23 @@
         </is>
       </c>
       <c r="D635" t="n">
-        <v>27.4</v>
+        <v>24.5</v>
       </c>
       <c r="E635" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F635" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G635" t="n">
-        <v>20.9</v>
+        <v>17.9</v>
       </c>
       <c r="H635" t="n">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="I635" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -23940,23 +23940,23 @@
         </is>
       </c>
       <c r="D636" t="n">
-        <v>31.4</v>
+        <v>26.9</v>
       </c>
       <c r="E636" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="F636" t="n">
         <v>0</v>
       </c>
       <c r="G636" t="n">
-        <v>26.7</v>
+        <v>22.3</v>
       </c>
       <c r="H636" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I636" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -23977,23 +23977,23 @@
         </is>
       </c>
       <c r="D637" t="n">
-        <v>28.2</v>
+        <v>25.3</v>
       </c>
       <c r="E637" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F637" t="n">
         <v>0</v>
       </c>
       <c r="G637" t="n">
-        <v>23.5</v>
+        <v>21.1</v>
       </c>
       <c r="H637" t="n">
         <v>3</v>
       </c>
       <c r="I637" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24014,23 +24014,23 @@
         </is>
       </c>
       <c r="D638" t="n">
-        <v>29.1</v>
+        <v>26</v>
       </c>
       <c r="E638" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F638" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G638" t="n">
-        <v>20.4</v>
+        <v>16.6</v>
       </c>
       <c r="H638" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24051,23 +24051,23 @@
         </is>
       </c>
       <c r="D639" t="n">
-        <v>26.4</v>
+        <v>25.4</v>
       </c>
       <c r="E639" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F639" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G639" t="n">
-        <v>19.4</v>
+        <v>16.2</v>
       </c>
       <c r="H639" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I639" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24088,23 +24088,23 @@
         </is>
       </c>
       <c r="D640" t="n">
-        <v>26.9</v>
+        <v>24.8</v>
       </c>
       <c r="E640" t="n">
         <v>93</v>
       </c>
       <c r="F640" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G640" t="n">
-        <v>17.6</v>
+        <v>18.6</v>
       </c>
       <c r="H640" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24125,23 +24125,23 @@
         </is>
       </c>
       <c r="D641" t="n">
-        <v>26.3</v>
+        <v>25.3</v>
       </c>
       <c r="E641" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F641" t="n">
         <v>0.1</v>
       </c>
       <c r="G641" t="n">
-        <v>21</v>
+        <v>15.4</v>
       </c>
       <c r="H641" t="n">
         <v>51</v>
       </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24162,23 +24162,23 @@
         </is>
       </c>
       <c r="D642" t="n">
-        <v>29.8</v>
+        <v>25.8</v>
       </c>
       <c r="E642" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F642" t="n">
         <v>0</v>
       </c>
       <c r="G642" t="n">
-        <v>24.5</v>
+        <v>17</v>
       </c>
       <c r="H642" t="n">
         <v>3</v>
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24199,23 +24199,23 @@
         </is>
       </c>
       <c r="D643" t="n">
-        <v>29.5</v>
+        <v>25</v>
       </c>
       <c r="E643" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="F643" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="G643" t="n">
-        <v>16.6</v>
+        <v>15.6</v>
       </c>
       <c r="H643" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24236,23 +24236,23 @@
         </is>
       </c>
       <c r="D644" t="n">
-        <v>28.1</v>
+        <v>24.3</v>
       </c>
       <c r="E644" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F644" t="n">
         <v>0</v>
       </c>
       <c r="G644" t="n">
-        <v>23.1</v>
+        <v>11.7</v>
       </c>
       <c r="H644" t="n">
         <v>3</v>
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24273,23 +24273,23 @@
         </is>
       </c>
       <c r="D645" t="n">
-        <v>27.3</v>
+        <v>25.3</v>
       </c>
       <c r="E645" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F645" t="n">
         <v>0</v>
       </c>
       <c r="G645" t="n">
-        <v>22.4</v>
+        <v>17.5</v>
       </c>
       <c r="H645" t="n">
         <v>3</v>
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24310,23 +24310,23 @@
         </is>
       </c>
       <c r="D646" t="n">
-        <v>27.1</v>
+        <v>24.4</v>
       </c>
       <c r="E646" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F646" t="n">
         <v>0.1</v>
       </c>
       <c r="G646" t="n">
-        <v>20.7</v>
+        <v>19.6</v>
       </c>
       <c r="H646" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24347,23 +24347,23 @@
         </is>
       </c>
       <c r="D647" t="n">
-        <v>29</v>
+        <v>25.3</v>
       </c>
       <c r="E647" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F647" t="n">
         <v>0</v>
       </c>
       <c r="G647" t="n">
-        <v>25.6</v>
+        <v>20.2</v>
       </c>
       <c r="H647" t="n">
         <v>3</v>
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24384,23 +24384,23 @@
         </is>
       </c>
       <c r="D648" t="n">
-        <v>29</v>
+        <v>27.9</v>
       </c>
       <c r="E648" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F648" t="n">
         <v>0</v>
       </c>
       <c r="G648" t="n">
-        <v>19.1</v>
+        <v>14.6</v>
       </c>
       <c r="H648" t="n">
         <v>3</v>
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24421,7 +24421,7 @@
         </is>
       </c>
       <c r="D649" t="n">
-        <v>30.1</v>
+        <v>26.1</v>
       </c>
       <c r="E649" t="n">
         <v>63</v>
@@ -24430,14 +24430,14 @@
         <v>0</v>
       </c>
       <c r="G649" t="n">
-        <v>23.6</v>
+        <v>16.6</v>
       </c>
       <c r="H649" t="n">
         <v>3</v>
       </c>
       <c r="I649" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24458,23 +24458,23 @@
         </is>
       </c>
       <c r="D650" t="n">
-        <v>30.6</v>
+        <v>25.9</v>
       </c>
       <c r="E650" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F650" t="n">
         <v>0</v>
       </c>
       <c r="G650" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="H650" t="n">
         <v>3</v>
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24495,23 +24495,23 @@
         </is>
       </c>
       <c r="D651" t="n">
-        <v>29.5</v>
+        <v>25.6</v>
       </c>
       <c r="E651" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F651" t="n">
         <v>0</v>
       </c>
       <c r="G651" t="n">
-        <v>19.7</v>
+        <v>15.3</v>
       </c>
       <c r="H651" t="n">
         <v>3</v>
       </c>
       <c r="I651" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24532,23 +24532,23 @@
         </is>
       </c>
       <c r="D652" t="n">
-        <v>28.6</v>
+        <v>25.1</v>
       </c>
       <c r="E652" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F652" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G652" t="n">
-        <v>20.6</v>
+        <v>21.6</v>
       </c>
       <c r="H652" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24569,23 +24569,23 @@
         </is>
       </c>
       <c r="D653" t="n">
-        <v>29.6</v>
+        <v>26.3</v>
       </c>
       <c r="E653" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F653" t="n">
         <v>0</v>
       </c>
       <c r="G653" t="n">
-        <v>19.7</v>
+        <v>20.1</v>
       </c>
       <c r="H653" t="n">
         <v>3</v>
       </c>
       <c r="I653" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24606,23 +24606,23 @@
         </is>
       </c>
       <c r="D654" t="n">
-        <v>28.4</v>
+        <v>25.7</v>
       </c>
       <c r="E654" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F654" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G654" t="n">
-        <v>25.6</v>
+        <v>20.5</v>
       </c>
       <c r="H654" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24643,23 +24643,23 @@
         </is>
       </c>
       <c r="D655" t="n">
-        <v>29.4</v>
+        <v>26.8</v>
       </c>
       <c r="E655" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F655" t="n">
         <v>0</v>
       </c>
       <c r="G655" t="n">
-        <v>23.7</v>
+        <v>18.9</v>
       </c>
       <c r="H655" t="n">
         <v>3</v>
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24680,23 +24680,23 @@
         </is>
       </c>
       <c r="D656" t="n">
-        <v>28.5</v>
+        <v>25.6</v>
       </c>
       <c r="E656" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F656" t="n">
         <v>0</v>
       </c>
       <c r="G656" t="n">
-        <v>21.7</v>
+        <v>24.3</v>
       </c>
       <c r="H656" t="n">
         <v>3</v>
       </c>
       <c r="I656" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24717,23 +24717,23 @@
         </is>
       </c>
       <c r="D657" t="n">
-        <v>27.3</v>
+        <v>24.8</v>
       </c>
       <c r="E657" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F657" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G657" t="n">
-        <v>17.8</v>
+        <v>14.7</v>
       </c>
       <c r="H657" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24754,23 +24754,23 @@
         </is>
       </c>
       <c r="D658" t="n">
-        <v>29.3</v>
+        <v>25</v>
       </c>
       <c r="E658" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F658" t="n">
         <v>0</v>
       </c>
       <c r="G658" t="n">
-        <v>24.2</v>
+        <v>17.6</v>
       </c>
       <c r="H658" t="n">
         <v>3</v>
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24791,23 +24791,23 @@
         </is>
       </c>
       <c r="D659" t="n">
-        <v>30.4</v>
+        <v>25.6</v>
       </c>
       <c r="E659" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F659" t="n">
         <v>0</v>
       </c>
       <c r="G659" t="n">
-        <v>25.8</v>
+        <v>15.9</v>
       </c>
       <c r="H659" t="n">
         <v>3</v>
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24828,23 +24828,23 @@
         </is>
       </c>
       <c r="D660" t="n">
-        <v>27.1</v>
+        <v>25.4</v>
       </c>
       <c r="E660" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F660" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G660" t="n">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="H660" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -24865,1244 +24865,23 @@
         </is>
       </c>
       <c r="D661" t="n">
-        <v>27.8</v>
+        <v>26.4</v>
       </c>
       <c r="E661" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F661" t="n">
         <v>0</v>
       </c>
       <c r="G661" t="n">
-        <v>23.5</v>
+        <v>22.7</v>
       </c>
       <c r="H661" t="n">
         <v>3</v>
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B662" t="inlineStr">
-        <is>
-          <t>Adilabad</t>
-        </is>
-      </c>
-      <c r="C662" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D662" t="n">
-        <v>26</v>
-      </c>
-      <c r="E662" t="n">
-        <v>90</v>
-      </c>
-      <c r="F662" t="n">
-        <v>0</v>
-      </c>
-      <c r="G662" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="H662" t="n">
-        <v>3</v>
-      </c>
-      <c r="I662" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B663" t="inlineStr">
-        <is>
-          <t>Bhadradri Kothagudem</t>
-        </is>
-      </c>
-      <c r="C663" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D663" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="E663" t="n">
-        <v>95</v>
-      </c>
-      <c r="F663" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G663" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H663" t="n">
-        <v>80</v>
-      </c>
-      <c r="I663" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B664" t="inlineStr">
-        <is>
-          <t>Hanumakonda</t>
-        </is>
-      </c>
-      <c r="C664" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D664" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E664" t="n">
-        <v>90</v>
-      </c>
-      <c r="F664" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G664" t="n">
-        <v>17</v>
-      </c>
-      <c r="H664" t="n">
-        <v>51</v>
-      </c>
-      <c r="I664" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B665" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="C665" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D665" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E665" t="n">
-        <v>77</v>
-      </c>
-      <c r="F665" t="n">
-        <v>0</v>
-      </c>
-      <c r="G665" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H665" t="n">
-        <v>3</v>
-      </c>
-      <c r="I665" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B666" t="inlineStr">
-        <is>
-          <t>Jagtial</t>
-        </is>
-      </c>
-      <c r="C666" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D666" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E666" t="n">
-        <v>92</v>
-      </c>
-      <c r="F666" t="n">
-        <v>0</v>
-      </c>
-      <c r="G666" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="H666" t="n">
-        <v>3</v>
-      </c>
-      <c r="I666" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B667" t="inlineStr">
-        <is>
-          <t>Jangaon</t>
-        </is>
-      </c>
-      <c r="C667" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D667" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E667" t="n">
-        <v>90</v>
-      </c>
-      <c r="F667" t="n">
-        <v>0</v>
-      </c>
-      <c r="G667" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H667" t="n">
-        <v>3</v>
-      </c>
-      <c r="I667" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B668" t="inlineStr">
-        <is>
-          <t>Jayashankar Bhupalpally</t>
-        </is>
-      </c>
-      <c r="C668" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D668" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E668" t="n">
-        <v>91</v>
-      </c>
-      <c r="F668" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G668" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H668" t="n">
-        <v>51</v>
-      </c>
-      <c r="I668" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B669" t="inlineStr">
-        <is>
-          <t>Jogulamba Gadwal</t>
-        </is>
-      </c>
-      <c r="C669" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D669" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E669" t="n">
-        <v>64</v>
-      </c>
-      <c r="F669" t="n">
-        <v>0</v>
-      </c>
-      <c r="G669" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="H669" t="n">
-        <v>3</v>
-      </c>
-      <c r="I669" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>Kamareddy</t>
-        </is>
-      </c>
-      <c r="C670" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D670" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E670" t="n">
-        <v>93</v>
-      </c>
-      <c r="F670" t="n">
-        <v>0</v>
-      </c>
-      <c r="G670" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="H670" t="n">
-        <v>3</v>
-      </c>
-      <c r="I670" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>Karimnagar</t>
-        </is>
-      </c>
-      <c r="C671" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D671" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E671" t="n">
-        <v>86</v>
-      </c>
-      <c r="F671" t="n">
-        <v>0</v>
-      </c>
-      <c r="G671" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="H671" t="n">
-        <v>3</v>
-      </c>
-      <c r="I671" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B672" t="inlineStr">
-        <is>
-          <t>Khammam</t>
-        </is>
-      </c>
-      <c r="C672" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D672" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E672" t="n">
-        <v>83</v>
-      </c>
-      <c r="F672" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G672" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H672" t="n">
-        <v>51</v>
-      </c>
-      <c r="I672" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B673" t="inlineStr">
-        <is>
-          <t>Kumuram Bheem Asifabad</t>
-        </is>
-      </c>
-      <c r="C673" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D673" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E673" t="n">
-        <v>89</v>
-      </c>
-      <c r="F673" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G673" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H673" t="n">
-        <v>51</v>
-      </c>
-      <c r="I673" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B674" t="inlineStr">
-        <is>
-          <t>Mahabubabad</t>
-        </is>
-      </c>
-      <c r="C674" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D674" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E674" t="n">
-        <v>89</v>
-      </c>
-      <c r="F674" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G674" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H674" t="n">
-        <v>55</v>
-      </c>
-      <c r="I674" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B675" t="inlineStr">
-        <is>
-          <t>Mahbubnagar</t>
-        </is>
-      </c>
-      <c r="C675" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D675" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E675" t="n">
-        <v>82</v>
-      </c>
-      <c r="F675" t="n">
-        <v>0</v>
-      </c>
-      <c r="G675" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="H675" t="n">
-        <v>3</v>
-      </c>
-      <c r="I675" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B676" t="inlineStr">
-        <is>
-          <t>Mancherial</t>
-        </is>
-      </c>
-      <c r="C676" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D676" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E676" t="n">
-        <v>89</v>
-      </c>
-      <c r="F676" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G676" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="H676" t="n">
-        <v>53</v>
-      </c>
-      <c r="I676" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B677" t="inlineStr">
-        <is>
-          <t>Medak</t>
-        </is>
-      </c>
-      <c r="C677" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D677" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E677" t="n">
-        <v>92</v>
-      </c>
-      <c r="F677" t="n">
-        <v>0</v>
-      </c>
-      <c r="G677" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="H677" t="n">
-        <v>3</v>
-      </c>
-      <c r="I677" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B678" t="inlineStr">
-        <is>
-          <t>Medchal-Malkajgiri</t>
-        </is>
-      </c>
-      <c r="C678" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D678" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E678" t="n">
-        <v>86</v>
-      </c>
-      <c r="F678" t="n">
-        <v>0</v>
-      </c>
-      <c r="G678" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H678" t="n">
-        <v>3</v>
-      </c>
-      <c r="I678" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B679" t="inlineStr">
-        <is>
-          <t>Mulugu</t>
-        </is>
-      </c>
-      <c r="C679" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D679" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E679" t="n">
-        <v>95</v>
-      </c>
-      <c r="F679" t="n">
-        <v>0</v>
-      </c>
-      <c r="G679" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="H679" t="n">
-        <v>3</v>
-      </c>
-      <c r="I679" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B680" t="inlineStr">
-        <is>
-          <t>Nagarkurnool</t>
-        </is>
-      </c>
-      <c r="C680" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D680" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E680" t="n">
-        <v>76</v>
-      </c>
-      <c r="F680" t="n">
-        <v>0</v>
-      </c>
-      <c r="G680" t="n">
-        <v>17</v>
-      </c>
-      <c r="H680" t="n">
-        <v>3</v>
-      </c>
-      <c r="I680" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B681" t="inlineStr">
-        <is>
-          <t>Nalgonda</t>
-        </is>
-      </c>
-      <c r="C681" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D681" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E681" t="n">
-        <v>73</v>
-      </c>
-      <c r="F681" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G681" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H681" t="n">
-        <v>51</v>
-      </c>
-      <c r="I681" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B682" t="inlineStr">
-        <is>
-          <t>Narayanpet</t>
-        </is>
-      </c>
-      <c r="C682" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D682" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E682" t="n">
-        <v>73</v>
-      </c>
-      <c r="F682" t="n">
-        <v>0</v>
-      </c>
-      <c r="G682" t="n">
-        <v>14</v>
-      </c>
-      <c r="H682" t="n">
-        <v>3</v>
-      </c>
-      <c r="I682" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B683" t="inlineStr">
-        <is>
-          <t>Nirmal</t>
-        </is>
-      </c>
-      <c r="C683" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D683" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E683" t="n">
-        <v>90</v>
-      </c>
-      <c r="F683" t="n">
-        <v>0</v>
-      </c>
-      <c r="G683" t="n">
-        <v>15</v>
-      </c>
-      <c r="H683" t="n">
-        <v>3</v>
-      </c>
-      <c r="I683" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B684" t="inlineStr">
-        <is>
-          <t>Nizamabad</t>
-        </is>
-      </c>
-      <c r="C684" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D684" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E684" t="n">
-        <v>94</v>
-      </c>
-      <c r="F684" t="n">
-        <v>0</v>
-      </c>
-      <c r="G684" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H684" t="n">
-        <v>3</v>
-      </c>
-      <c r="I684" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B685" t="inlineStr">
-        <is>
-          <t>Peddapalli</t>
-        </is>
-      </c>
-      <c r="C685" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D685" t="n">
-        <v>26</v>
-      </c>
-      <c r="E685" t="n">
-        <v>90</v>
-      </c>
-      <c r="F685" t="n">
-        <v>0</v>
-      </c>
-      <c r="G685" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="H685" t="n">
-        <v>3</v>
-      </c>
-      <c r="I685" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B686" t="inlineStr">
-        <is>
-          <t>Rajanna Sircilla</t>
-        </is>
-      </c>
-      <c r="C686" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D686" t="n">
-        <v>25</v>
-      </c>
-      <c r="E686" t="n">
-        <v>90</v>
-      </c>
-      <c r="F686" t="n">
-        <v>0</v>
-      </c>
-      <c r="G686" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H686" t="n">
-        <v>3</v>
-      </c>
-      <c r="I686" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B687" t="inlineStr">
-        <is>
-          <t>Rangareddy</t>
-        </is>
-      </c>
-      <c r="C687" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D687" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E687" t="n">
-        <v>79</v>
-      </c>
-      <c r="F687" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G687" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H687" t="n">
-        <v>51</v>
-      </c>
-      <c r="I687" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B688" t="inlineStr">
-        <is>
-          <t>Sangareddy</t>
-        </is>
-      </c>
-      <c r="C688" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D688" t="n">
-        <v>27</v>
-      </c>
-      <c r="E688" t="n">
-        <v>74</v>
-      </c>
-      <c r="F688" t="n">
-        <v>0</v>
-      </c>
-      <c r="G688" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="H688" t="n">
-        <v>3</v>
-      </c>
-      <c r="I688" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B689" t="inlineStr">
-        <is>
-          <t>Siddipet</t>
-        </is>
-      </c>
-      <c r="C689" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D689" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="E689" t="n">
-        <v>90</v>
-      </c>
-      <c r="F689" t="n">
-        <v>0</v>
-      </c>
-      <c r="G689" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="H689" t="n">
-        <v>3</v>
-      </c>
-      <c r="I689" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B690" t="inlineStr">
-        <is>
-          <t>Suryapet</t>
-        </is>
-      </c>
-      <c r="C690" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D690" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E690" t="n">
-        <v>88</v>
-      </c>
-      <c r="F690" t="n">
-        <v>0</v>
-      </c>
-      <c r="G690" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="H690" t="n">
-        <v>3</v>
-      </c>
-      <c r="I690" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B691" t="inlineStr">
-        <is>
-          <t>Vikarabad</t>
-        </is>
-      </c>
-      <c r="C691" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D691" t="n">
-        <v>26</v>
-      </c>
-      <c r="E691" t="n">
-        <v>80</v>
-      </c>
-      <c r="F691" t="n">
-        <v>0</v>
-      </c>
-      <c r="G691" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="H691" t="n">
-        <v>3</v>
-      </c>
-      <c r="I691" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B692" t="inlineStr">
-        <is>
-          <t>Wanaparthy</t>
-        </is>
-      </c>
-      <c r="C692" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D692" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="E692" t="n">
-        <v>73</v>
-      </c>
-      <c r="F692" t="n">
-        <v>0</v>
-      </c>
-      <c r="G692" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H692" t="n">
-        <v>3</v>
-      </c>
-      <c r="I692" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B693" t="inlineStr">
-        <is>
-          <t>Warangal</t>
-        </is>
-      </c>
-      <c r="C693" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D693" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E693" t="n">
-        <v>90</v>
-      </c>
-      <c r="F693" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G693" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="H693" t="n">
-        <v>51</v>
-      </c>
-      <c r="I693" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B694" t="inlineStr">
-        <is>
-          <t>Yadadri Bhuvanagiri</t>
-        </is>
-      </c>
-      <c r="C694" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D694" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E694" t="n">
-        <v>85</v>
-      </c>
-      <c r="F694" t="n">
-        <v>0</v>
-      </c>
-      <c r="G694" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="H694" t="n">
-        <v>3</v>
-      </c>
-      <c r="I694" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -26117,7 +24896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27408,110 +26187,49 @@
         <v>33</v>
       </c>
       <c r="D22" t="n">
-        <v>28.5</v>
+        <v>25.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jogulamba Gadwal</t>
+          <t>Nalgonda</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>31.4</v>
+        <v>27.9</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mahabubabad</t>
+          <t>Medak</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>26.3</v>
+        <v>24.3</v>
       </c>
       <c r="I22" t="n">
-        <v>75.5</v>
+        <v>82</v>
       </c>
       <c r="J22" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Mancherial</t>
+          <t>Bhadradri Kothagudem</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Jogulamba Gadwal</t>
+          <t>Jangaon</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>26.7</v>
+        <v>24.5</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-09-24T12:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>33</v>
-      </c>
-      <c r="D23" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Jogulamba Gadwal</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Nizamabad</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Bhadradri Kothagudem</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Siddipet</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2026-09-24T18:45</t>
+          <t>2026-09-24T23:30</t>
         </is>
       </c>
     </row>
@@ -27578,7 +26296,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -27587,7 +26305,7 @@
         <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="G2" t="n">
         <v>0.7</v>
@@ -27614,10 +26332,10 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="4">
@@ -27632,7 +26350,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -27641,7 +26359,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>75.7</v>
       </c>
       <c r="G4" t="n">
         <v>0.8</v>
@@ -27668,10 +26386,10 @@
         <v>24.7</v>
       </c>
       <c r="F5" t="n">
-        <v>66.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -27686,7 +26404,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -27695,10 +26413,10 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -27713,7 +26431,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -27722,10 +26440,10 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>75.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8">
@@ -27740,7 +26458,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -27767,7 +26485,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -27776,7 +26494,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>68.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -27803,7 +26521,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>2.3</v>
@@ -27821,7 +26539,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -27830,10 +26548,10 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
@@ -27848,16 +26566,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
       </c>
       <c r="E12" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="F12" t="n">
-        <v>75.5</v>
+        <v>75.2</v>
       </c>
       <c r="G12" t="n">
         <v>1.1</v>
@@ -27881,13 +26599,13 @@
         <v>32.8</v>
       </c>
       <c r="E13" t="n">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
       <c r="F13" t="n">
-        <v>82.5</v>
+        <v>82.2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="14">
@@ -27911,10 +26629,10 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>79.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -27929,7 +26647,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -27956,19 +26674,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
       </c>
       <c r="E16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" t="n">
-        <v>79.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17">
@@ -27983,7 +26701,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
@@ -28019,7 +26737,7 @@
         <v>23.7</v>
       </c>
       <c r="F18" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="G18" t="n">
         <v>1.9</v>
@@ -28037,7 +26755,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -28046,7 +26764,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>83.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>1.4</v>
@@ -28064,7 +26782,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -28073,7 +26791,7 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>72</v>
+        <v>72.2</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
@@ -28100,10 +26818,10 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>67.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="22">
@@ -28118,7 +26836,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -28145,7 +26863,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -28181,7 +26899,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>81.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="G24" t="n">
         <v>0.4</v>
@@ -28199,19 +26917,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>25.4</v>
+        <v>25.1</v>
       </c>
       <c r="F25" t="n">
-        <v>81.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
@@ -28232,7 +26950,7 @@
         <v>31.2</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="F26" t="n">
         <v>79.5</v>
@@ -28253,7 +26971,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -28262,10 +26980,10 @@
         <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>72.2</v>
+        <v>72</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="28">
@@ -28280,7 +26998,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -28289,7 +27007,7 @@
         <v>23.3</v>
       </c>
       <c r="F28" t="n">
-        <v>71</v>
+        <v>70.7</v>
       </c>
       <c r="G28" t="n">
         <v>0.9</v>
@@ -28316,7 +27034,7 @@
         <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>80</v>
+        <v>79.8</v>
       </c>
       <c r="G29" t="n">
         <v>0.2</v>
@@ -28340,13 +27058,13 @@
         <v>34.5</v>
       </c>
       <c r="E30" t="n">
-        <v>25.4</v>
+        <v>24.8</v>
       </c>
       <c r="F30" t="n">
-        <v>71.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="31">
@@ -28361,7 +27079,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -28370,7 +27088,7 @@
         <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -28388,7 +27106,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -28397,7 +27115,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>70</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -28415,7 +27133,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -28424,7 +27142,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>74.2</v>
+        <v>73.7</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -28451,7 +27169,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>74.2</v>
+        <v>73.8</v>
       </c>
       <c r="G34" t="n">
         <v>0.5</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I661"/>
+  <dimension ref="A1:I694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24882,6 +24882,1227 @@
       <c r="I661" t="inlineStr">
         <is>
           <t>2026-09-24T23:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E662" t="n">
+        <v>82</v>
+      </c>
+      <c r="F662" t="n">
+        <v>0</v>
+      </c>
+      <c r="G662" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H662" t="n">
+        <v>3</v>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E663" t="n">
+        <v>95</v>
+      </c>
+      <c r="F663" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G663" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H663" t="n">
+        <v>55</v>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E664" t="n">
+        <v>90</v>
+      </c>
+      <c r="F664" t="n">
+        <v>0</v>
+      </c>
+      <c r="G664" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H664" t="n">
+        <v>3</v>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E665" t="n">
+        <v>71</v>
+      </c>
+      <c r="F665" t="n">
+        <v>0</v>
+      </c>
+      <c r="G665" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H665" t="n">
+        <v>3</v>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E666" t="n">
+        <v>88</v>
+      </c>
+      <c r="F666" t="n">
+        <v>0</v>
+      </c>
+      <c r="G666" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H666" t="n">
+        <v>3</v>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E667" t="n">
+        <v>75</v>
+      </c>
+      <c r="F667" t="n">
+        <v>0</v>
+      </c>
+      <c r="G667" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H667" t="n">
+        <v>3</v>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E668" t="n">
+        <v>97</v>
+      </c>
+      <c r="F668" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G668" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H668" t="n">
+        <v>51</v>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E669" t="n">
+        <v>72</v>
+      </c>
+      <c r="F669" t="n">
+        <v>0</v>
+      </c>
+      <c r="G669" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H669" t="n">
+        <v>2</v>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D670" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E670" t="n">
+        <v>77</v>
+      </c>
+      <c r="F670" t="n">
+        <v>0</v>
+      </c>
+      <c r="G670" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H670" t="n">
+        <v>3</v>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>26</v>
+      </c>
+      <c r="E671" t="n">
+        <v>86</v>
+      </c>
+      <c r="F671" t="n">
+        <v>0</v>
+      </c>
+      <c r="G671" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H671" t="n">
+        <v>3</v>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D672" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E672" t="n">
+        <v>94</v>
+      </c>
+      <c r="F672" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G672" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H672" t="n">
+        <v>51</v>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D673" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E673" t="n">
+        <v>92</v>
+      </c>
+      <c r="F673" t="n">
+        <v>0</v>
+      </c>
+      <c r="G673" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H673" t="n">
+        <v>3</v>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D674" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E674" t="n">
+        <v>92</v>
+      </c>
+      <c r="F674" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G674" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H674" t="n">
+        <v>51</v>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D675" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E675" t="n">
+        <v>69</v>
+      </c>
+      <c r="F675" t="n">
+        <v>0</v>
+      </c>
+      <c r="G675" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="H675" t="n">
+        <v>3</v>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D676" t="n">
+        <v>25</v>
+      </c>
+      <c r="E676" t="n">
+        <v>94</v>
+      </c>
+      <c r="F676" t="n">
+        <v>0</v>
+      </c>
+      <c r="G676" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H676" t="n">
+        <v>3</v>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D677" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E677" t="n">
+        <v>88</v>
+      </c>
+      <c r="F677" t="n">
+        <v>0</v>
+      </c>
+      <c r="G677" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H677" t="n">
+        <v>3</v>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D678" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E678" t="n">
+        <v>78</v>
+      </c>
+      <c r="F678" t="n">
+        <v>0</v>
+      </c>
+      <c r="G678" t="n">
+        <v>18</v>
+      </c>
+      <c r="H678" t="n">
+        <v>3</v>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D679" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E679" t="n">
+        <v>96</v>
+      </c>
+      <c r="F679" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G679" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H679" t="n">
+        <v>51</v>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D680" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E680" t="n">
+        <v>76</v>
+      </c>
+      <c r="F680" t="n">
+        <v>0</v>
+      </c>
+      <c r="G680" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H680" t="n">
+        <v>3</v>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D681" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E681" t="n">
+        <v>72</v>
+      </c>
+      <c r="F681" t="n">
+        <v>0</v>
+      </c>
+      <c r="G681" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H681" t="n">
+        <v>3</v>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D682" t="n">
+        <v>26</v>
+      </c>
+      <c r="E682" t="n">
+        <v>63</v>
+      </c>
+      <c r="F682" t="n">
+        <v>0</v>
+      </c>
+      <c r="G682" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H682" t="n">
+        <v>3</v>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D683" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E683" t="n">
+        <v>80</v>
+      </c>
+      <c r="F683" t="n">
+        <v>0</v>
+      </c>
+      <c r="G683" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H683" t="n">
+        <v>3</v>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E684" t="n">
+        <v>79</v>
+      </c>
+      <c r="F684" t="n">
+        <v>0</v>
+      </c>
+      <c r="G684" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H684" t="n">
+        <v>3</v>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
+        <v>25</v>
+      </c>
+      <c r="E685" t="n">
+        <v>93</v>
+      </c>
+      <c r="F685" t="n">
+        <v>0</v>
+      </c>
+      <c r="G685" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H685" t="n">
+        <v>3</v>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E686" t="n">
+        <v>80</v>
+      </c>
+      <c r="F686" t="n">
+        <v>0</v>
+      </c>
+      <c r="G686" t="n">
+        <v>20</v>
+      </c>
+      <c r="H686" t="n">
+        <v>3</v>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D687" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E687" t="n">
+        <v>70</v>
+      </c>
+      <c r="F687" t="n">
+        <v>0</v>
+      </c>
+      <c r="G687" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H687" t="n">
+        <v>3</v>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D688" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E688" t="n">
+        <v>61</v>
+      </c>
+      <c r="F688" t="n">
+        <v>0</v>
+      </c>
+      <c r="G688" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H688" t="n">
+        <v>3</v>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E689" t="n">
+        <v>80</v>
+      </c>
+      <c r="F689" t="n">
+        <v>0</v>
+      </c>
+      <c r="G689" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="H689" t="n">
+        <v>3</v>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E690" t="n">
+        <v>93</v>
+      </c>
+      <c r="F690" t="n">
+        <v>0</v>
+      </c>
+      <c r="G690" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H690" t="n">
+        <v>3</v>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D691" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E691" t="n">
+        <v>70</v>
+      </c>
+      <c r="F691" t="n">
+        <v>0</v>
+      </c>
+      <c r="G691" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H691" t="n">
+        <v>3</v>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D692" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E692" t="n">
+        <v>75</v>
+      </c>
+      <c r="F692" t="n">
+        <v>0</v>
+      </c>
+      <c r="G692" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H692" t="n">
+        <v>3</v>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D693" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E693" t="n">
+        <v>89</v>
+      </c>
+      <c r="F693" t="n">
+        <v>0</v>
+      </c>
+      <c r="G693" t="n">
+        <v>20</v>
+      </c>
+      <c r="H693" t="n">
+        <v>3</v>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D694" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E694" t="n">
+        <v>74</v>
+      </c>
+      <c r="F694" t="n">
+        <v>0</v>
+      </c>
+      <c r="G694" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="H694" t="n">
+        <v>3</v>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
         </is>
       </c>
     </row>
@@ -24896,7 +26117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26230,6 +27451,67 @@
       <c r="O22" t="inlineStr">
         <is>
           <t>2026-09-24T23:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>33</v>
+      </c>
+      <c r="D23" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-09-24T23:45</t>
         </is>
       </c>
     </row>
@@ -26296,7 +27578,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -26323,7 +27605,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -26332,10 +27614,10 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>82.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4">
@@ -26350,7 +27632,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -26359,7 +27641,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>75.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0.8</v>
@@ -26377,7 +27659,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -26386,7 +27668,7 @@
         <v>24.7</v>
       </c>
       <c r="F5" t="n">
-        <v>66.59999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="G5" t="n">
         <v>0.9</v>
@@ -26404,7 +27686,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -26413,7 +27695,7 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>82.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="G6" t="n">
         <v>0.2</v>
@@ -26431,7 +27713,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -26458,7 +27740,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -26467,10 +27749,10 @@
         <v>24.4</v>
       </c>
       <c r="F8" t="n">
-        <v>83</v>
+        <v>83.7</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9">
@@ -26485,7 +27767,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -26494,7 +27776,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>69.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -26512,7 +27794,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -26521,7 +27803,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>2.3</v>
@@ -26539,7 +27821,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -26548,7 +27830,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>79.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="G11" t="n">
         <v>0.5</v>
@@ -26566,19 +27848,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.6</v>
+        <v>29.4</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
       </c>
       <c r="E12" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="F12" t="n">
-        <v>75.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13">
@@ -26593,7 +27875,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -26602,7 +27884,7 @@
         <v>24.8</v>
       </c>
       <c r="F13" t="n">
-        <v>82.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>0.9</v>
@@ -26620,7 +27902,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -26629,10 +27911,10 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>78.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -26656,7 +27938,7 @@
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>73.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>1.6</v>
@@ -26674,7 +27956,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -26683,7 +27965,7 @@
         <v>25</v>
       </c>
       <c r="F16" t="n">
-        <v>79.8</v>
+        <v>80.5</v>
       </c>
       <c r="G16" t="n">
         <v>0.5</v>
@@ -26701,7 +27983,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
@@ -26710,7 +27992,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>80</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>1.1</v>
@@ -26728,7 +28010,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -26737,7 +28019,7 @@
         <v>23.7</v>
       </c>
       <c r="F18" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>1.9</v>
@@ -26755,7 +28037,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -26764,10 +28046,10 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>83.09999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="20">
@@ -26782,7 +28064,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -26791,7 +28073,7 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>72.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
@@ -26809,7 +28091,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -26818,7 +28100,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>66.8</v>
+        <v>67</v>
       </c>
       <c r="G21" t="n">
         <v>0.7</v>
@@ -26836,7 +28118,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -26845,7 +28127,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>72.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="G22" t="n">
         <v>2.7</v>
@@ -26863,7 +28145,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -26872,7 +28154,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0.2</v>
@@ -26890,7 +28172,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -26917,16 +28199,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="F25" t="n">
-        <v>81.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0.8</v>
@@ -26944,7 +28226,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
@@ -26971,7 +28253,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -26998,7 +28280,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -27007,7 +28289,7 @@
         <v>23.3</v>
       </c>
       <c r="F28" t="n">
-        <v>70.7</v>
+        <v>70.2</v>
       </c>
       <c r="G28" t="n">
         <v>0.9</v>
@@ -27025,7 +28307,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
@@ -27052,16 +28334,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
       </c>
       <c r="E30" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="F30" t="n">
-        <v>70.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="G30" t="n">
         <v>0.7</v>
@@ -27079,7 +28361,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -27088,7 +28370,7 @@
         <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>72.8</v>
+        <v>72.7</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -27106,7 +28388,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -27115,7 +28397,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>70.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -27133,7 +28415,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -27142,7 +28424,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>73.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -27160,7 +28442,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I694"/>
+  <dimension ref="A1:I727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26103,6 +26103,1227 @@
       <c r="I694" t="inlineStr">
         <is>
           <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D695" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E695" t="n">
+        <v>75</v>
+      </c>
+      <c r="F695" t="n">
+        <v>0</v>
+      </c>
+      <c r="G695" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="H695" t="n">
+        <v>3</v>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D696" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E696" t="n">
+        <v>93</v>
+      </c>
+      <c r="F696" t="n">
+        <v>0</v>
+      </c>
+      <c r="G696" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H696" t="n">
+        <v>3</v>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D697" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E697" t="n">
+        <v>73</v>
+      </c>
+      <c r="F697" t="n">
+        <v>0</v>
+      </c>
+      <c r="G697" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H697" t="n">
+        <v>3</v>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D698" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E698" t="n">
+        <v>65</v>
+      </c>
+      <c r="F698" t="n">
+        <v>0</v>
+      </c>
+      <c r="G698" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H698" t="n">
+        <v>3</v>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E699" t="n">
+        <v>74</v>
+      </c>
+      <c r="F699" t="n">
+        <v>0</v>
+      </c>
+      <c r="G699" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H699" t="n">
+        <v>3</v>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D700" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E700" t="n">
+        <v>68</v>
+      </c>
+      <c r="F700" t="n">
+        <v>0</v>
+      </c>
+      <c r="G700" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="H700" t="n">
+        <v>3</v>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E701" t="n">
+        <v>94</v>
+      </c>
+      <c r="F701" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G701" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H701" t="n">
+        <v>51</v>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D702" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E702" t="n">
+        <v>73</v>
+      </c>
+      <c r="F702" t="n">
+        <v>0</v>
+      </c>
+      <c r="G702" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H702" t="n">
+        <v>2</v>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D703" t="n">
+        <v>25</v>
+      </c>
+      <c r="E703" t="n">
+        <v>70</v>
+      </c>
+      <c r="F703" t="n">
+        <v>0</v>
+      </c>
+      <c r="G703" t="n">
+        <v>24</v>
+      </c>
+      <c r="H703" t="n">
+        <v>3</v>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D704" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E704" t="n">
+        <v>72</v>
+      </c>
+      <c r="F704" t="n">
+        <v>0</v>
+      </c>
+      <c r="G704" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H704" t="n">
+        <v>3</v>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D705" t="n">
+        <v>28</v>
+      </c>
+      <c r="E705" t="n">
+        <v>71</v>
+      </c>
+      <c r="F705" t="n">
+        <v>0</v>
+      </c>
+      <c r="G705" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H705" t="n">
+        <v>3</v>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D706" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E706" t="n">
+        <v>81</v>
+      </c>
+      <c r="F706" t="n">
+        <v>0</v>
+      </c>
+      <c r="G706" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H706" t="n">
+        <v>3</v>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D707" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E707" t="n">
+        <v>72</v>
+      </c>
+      <c r="F707" t="n">
+        <v>0</v>
+      </c>
+      <c r="G707" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H707" t="n">
+        <v>3</v>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D708" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E708" t="n">
+        <v>66</v>
+      </c>
+      <c r="F708" t="n">
+        <v>0</v>
+      </c>
+      <c r="G708" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H708" t="n">
+        <v>3</v>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D709" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E709" t="n">
+        <v>91</v>
+      </c>
+      <c r="F709" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G709" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H709" t="n">
+        <v>51</v>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D710" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E710" t="n">
+        <v>70</v>
+      </c>
+      <c r="F710" t="n">
+        <v>0</v>
+      </c>
+      <c r="G710" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H710" t="n">
+        <v>3</v>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D711" t="n">
+        <v>25</v>
+      </c>
+      <c r="E711" t="n">
+        <v>65</v>
+      </c>
+      <c r="F711" t="n">
+        <v>0</v>
+      </c>
+      <c r="G711" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H711" t="n">
+        <v>3</v>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D712" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E712" t="n">
+        <v>85</v>
+      </c>
+      <c r="F712" t="n">
+        <v>0</v>
+      </c>
+      <c r="G712" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H712" t="n">
+        <v>3</v>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D713" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E713" t="n">
+        <v>77</v>
+      </c>
+      <c r="F713" t="n">
+        <v>0</v>
+      </c>
+      <c r="G713" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H713" t="n">
+        <v>3</v>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D714" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E714" t="n">
+        <v>59</v>
+      </c>
+      <c r="F714" t="n">
+        <v>0</v>
+      </c>
+      <c r="G714" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H714" t="n">
+        <v>3</v>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D715" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E715" t="n">
+        <v>73</v>
+      </c>
+      <c r="F715" t="n">
+        <v>0</v>
+      </c>
+      <c r="G715" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H715" t="n">
+        <v>3</v>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D716" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E716" t="n">
+        <v>76</v>
+      </c>
+      <c r="F716" t="n">
+        <v>0</v>
+      </c>
+      <c r="G716" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H716" t="n">
+        <v>3</v>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D717" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E717" t="n">
+        <v>71</v>
+      </c>
+      <c r="F717" t="n">
+        <v>0</v>
+      </c>
+      <c r="G717" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H717" t="n">
+        <v>3</v>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D718" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E718" t="n">
+        <v>75</v>
+      </c>
+      <c r="F718" t="n">
+        <v>0</v>
+      </c>
+      <c r="G718" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H718" t="n">
+        <v>3</v>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D719" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E719" t="n">
+        <v>72</v>
+      </c>
+      <c r="F719" t="n">
+        <v>0</v>
+      </c>
+      <c r="G719" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H719" t="n">
+        <v>3</v>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D720" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E720" t="n">
+        <v>63</v>
+      </c>
+      <c r="F720" t="n">
+        <v>0</v>
+      </c>
+      <c r="G720" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H720" t="n">
+        <v>3</v>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D721" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E721" t="n">
+        <v>60</v>
+      </c>
+      <c r="F721" t="n">
+        <v>0</v>
+      </c>
+      <c r="G721" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H721" t="n">
+        <v>3</v>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D722" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E722" t="n">
+        <v>71</v>
+      </c>
+      <c r="F722" t="n">
+        <v>0</v>
+      </c>
+      <c r="G722" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="H722" t="n">
+        <v>3</v>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D723" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E723" t="n">
+        <v>65</v>
+      </c>
+      <c r="F723" t="n">
+        <v>0</v>
+      </c>
+      <c r="G723" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H723" t="n">
+        <v>3</v>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D724" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E724" t="n">
+        <v>67</v>
+      </c>
+      <c r="F724" t="n">
+        <v>0</v>
+      </c>
+      <c r="G724" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H724" t="n">
+        <v>3</v>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D725" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E725" t="n">
+        <v>77</v>
+      </c>
+      <c r="F725" t="n">
+        <v>0</v>
+      </c>
+      <c r="G725" t="n">
+        <v>20</v>
+      </c>
+      <c r="H725" t="n">
+        <v>3</v>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D726" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E726" t="n">
+        <v>73</v>
+      </c>
+      <c r="F726" t="n">
+        <v>0</v>
+      </c>
+      <c r="G726" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="H726" t="n">
+        <v>3</v>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D727" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E727" t="n">
+        <v>62</v>
+      </c>
+      <c r="F727" t="n">
+        <v>0</v>
+      </c>
+      <c r="G727" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H727" t="n">
+        <v>3</v>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
         </is>
       </c>
     </row>
@@ -26117,7 +27338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27512,6 +28733,67 @@
       <c r="O23" t="inlineStr">
         <is>
           <t>2026-09-24T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>33</v>
+      </c>
+      <c r="D24" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-09-25T03:30</t>
         </is>
       </c>
     </row>
@@ -27587,7 +28869,7 @@
         <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>81.3</v>
+        <v>81</v>
       </c>
       <c r="G2" t="n">
         <v>0.7</v>
@@ -27605,7 +28887,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -27614,7 +28896,7 @@
         <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>82.7</v>
+        <v>83.2</v>
       </c>
       <c r="G3" t="n">
         <v>2.9</v>
@@ -27641,7 +28923,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>76.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="G4" t="n">
         <v>0.8</v>
@@ -27659,7 +28941,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -27668,7 +28950,7 @@
         <v>24.7</v>
       </c>
       <c r="F5" t="n">
-        <v>66.8</v>
+        <v>66.7</v>
       </c>
       <c r="G5" t="n">
         <v>0.9</v>
@@ -27686,7 +28968,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -27695,7 +28977,7 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>82.7</v>
+        <v>82.3</v>
       </c>
       <c r="G6" t="n">
         <v>0.2</v>
@@ -27713,7 +28995,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -27722,7 +29004,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>74.7</v>
       </c>
       <c r="G7" t="n">
         <v>0.3</v>
@@ -27740,7 +29022,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -27749,10 +29031,10 @@
         <v>24.4</v>
       </c>
       <c r="F8" t="n">
-        <v>83.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -27767,7 +29049,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -27776,7 +29058,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>69.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -27794,7 +29076,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -27803,7 +29085,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>80.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>2.3</v>
@@ -27821,7 +29103,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -27830,7 +29112,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>79.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0.5</v>
@@ -27848,7 +29130,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -27857,7 +29139,7 @@
         <v>25.3</v>
       </c>
       <c r="F12" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>1.2</v>
@@ -27875,7 +29157,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -27884,7 +29166,7 @@
         <v>24.8</v>
       </c>
       <c r="F13" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="G13" t="n">
         <v>0.9</v>
@@ -27911,7 +29193,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>79.5</v>
+        <v>79.2</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -27929,7 +29211,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -27938,7 +29220,7 @@
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="G15" t="n">
         <v>1.6</v>
@@ -27956,7 +29238,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -27965,10 +29247,10 @@
         <v>25</v>
       </c>
       <c r="F16" t="n">
-        <v>80.5</v>
+        <v>81</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="17">
@@ -27983,7 +29265,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
@@ -27992,7 +29274,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>80.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="G17" t="n">
         <v>1.1</v>
@@ -28010,7 +29292,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -28019,7 +29301,7 @@
         <v>23.7</v>
       </c>
       <c r="F18" t="n">
-        <v>75.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>1.9</v>
@@ -28037,7 +29319,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -28046,7 +29328,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="G19" t="n">
         <v>1.5</v>
@@ -28064,7 +29346,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -28073,7 +29355,7 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>72.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
@@ -28091,7 +29373,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -28100,7 +29382,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>67</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0.7</v>
@@ -28118,7 +29400,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -28145,7 +29427,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -28154,7 +29436,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="G23" t="n">
         <v>0.2</v>
@@ -28172,7 +29454,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -28181,7 +29463,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>80.8</v>
+        <v>80.3</v>
       </c>
       <c r="G24" t="n">
         <v>0.4</v>
@@ -28199,7 +29481,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -28208,7 +29490,7 @@
         <v>25</v>
       </c>
       <c r="F25" t="n">
-        <v>82.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="G25" t="n">
         <v>0.8</v>
@@ -28235,7 +29517,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>79.5</v>
+        <v>79.2</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -28253,7 +29535,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -28262,7 +29544,7 @@
         <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>72</v>
+        <v>71.5</v>
       </c>
       <c r="G27" t="n">
         <v>0.3</v>
@@ -28280,7 +29562,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -28289,7 +29571,7 @@
         <v>23.3</v>
       </c>
       <c r="F28" t="n">
-        <v>70.2</v>
+        <v>69.8</v>
       </c>
       <c r="G28" t="n">
         <v>0.9</v>
@@ -28307,7 +29589,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
@@ -28316,7 +29598,7 @@
         <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>79.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0.2</v>
@@ -28334,7 +29616,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -28343,7 +29625,7 @@
         <v>24.5</v>
       </c>
       <c r="F30" t="n">
-        <v>72</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G30" t="n">
         <v>0.7</v>
@@ -28361,7 +29643,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -28370,7 +29652,7 @@
         <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>72.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -28388,7 +29670,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -28397,7 +29679,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>70.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -28415,7 +29697,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -28451,7 +29733,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>73.8</v>
+        <v>73.2</v>
       </c>
       <c r="G34" t="n">
         <v>0.5</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I727"/>
+  <dimension ref="A1:I760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27324,6 +27324,1227 @@
       <c r="I727" t="inlineStr">
         <is>
           <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D728" t="n">
+        <v>26</v>
+      </c>
+      <c r="E728" t="n">
+        <v>78</v>
+      </c>
+      <c r="F728" t="n">
+        <v>0</v>
+      </c>
+      <c r="G728" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H728" t="n">
+        <v>3</v>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D729" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E729" t="n">
+        <v>93</v>
+      </c>
+      <c r="F729" t="n">
+        <v>0</v>
+      </c>
+      <c r="G729" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H729" t="n">
+        <v>3</v>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D730" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E730" t="n">
+        <v>78</v>
+      </c>
+      <c r="F730" t="n">
+        <v>0</v>
+      </c>
+      <c r="G730" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H730" t="n">
+        <v>3</v>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D731" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E731" t="n">
+        <v>72</v>
+      </c>
+      <c r="F731" t="n">
+        <v>0</v>
+      </c>
+      <c r="G731" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H731" t="n">
+        <v>3</v>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D732" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E732" t="n">
+        <v>82</v>
+      </c>
+      <c r="F732" t="n">
+        <v>0</v>
+      </c>
+      <c r="G732" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H732" t="n">
+        <v>3</v>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D733" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E733" t="n">
+        <v>70</v>
+      </c>
+      <c r="F733" t="n">
+        <v>0</v>
+      </c>
+      <c r="G733" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="H733" t="n">
+        <v>3</v>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D734" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E734" t="n">
+        <v>96</v>
+      </c>
+      <c r="F734" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G734" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H734" t="n">
+        <v>53</v>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D735" t="n">
+        <v>26</v>
+      </c>
+      <c r="E735" t="n">
+        <v>75</v>
+      </c>
+      <c r="F735" t="n">
+        <v>0</v>
+      </c>
+      <c r="G735" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H735" t="n">
+        <v>2</v>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D736" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E736" t="n">
+        <v>75</v>
+      </c>
+      <c r="F736" t="n">
+        <v>0</v>
+      </c>
+      <c r="G736" t="n">
+        <v>24</v>
+      </c>
+      <c r="H736" t="n">
+        <v>3</v>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D737" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E737" t="n">
+        <v>77</v>
+      </c>
+      <c r="F737" t="n">
+        <v>0</v>
+      </c>
+      <c r="G737" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H737" t="n">
+        <v>3</v>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D738" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E738" t="n">
+        <v>73</v>
+      </c>
+      <c r="F738" t="n">
+        <v>0</v>
+      </c>
+      <c r="G738" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H738" t="n">
+        <v>3</v>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D739" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E739" t="n">
+        <v>91</v>
+      </c>
+      <c r="F739" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G739" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H739" t="n">
+        <v>51</v>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D740" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E740" t="n">
+        <v>77</v>
+      </c>
+      <c r="F740" t="n">
+        <v>0</v>
+      </c>
+      <c r="G740" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H740" t="n">
+        <v>3</v>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D741" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E741" t="n">
+        <v>80</v>
+      </c>
+      <c r="F741" t="n">
+        <v>0</v>
+      </c>
+      <c r="G741" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H741" t="n">
+        <v>3</v>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D742" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E742" t="n">
+        <v>93</v>
+      </c>
+      <c r="F742" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G742" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H742" t="n">
+        <v>55</v>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D743" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E743" t="n">
+        <v>73</v>
+      </c>
+      <c r="F743" t="n">
+        <v>0</v>
+      </c>
+      <c r="G743" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H743" t="n">
+        <v>3</v>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D744" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E744" t="n">
+        <v>72</v>
+      </c>
+      <c r="F744" t="n">
+        <v>0</v>
+      </c>
+      <c r="G744" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="H744" t="n">
+        <v>3</v>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D745" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E745" t="n">
+        <v>95</v>
+      </c>
+      <c r="F745" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G745" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H745" t="n">
+        <v>53</v>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D746" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E746" t="n">
+        <v>80</v>
+      </c>
+      <c r="F746" t="n">
+        <v>0</v>
+      </c>
+      <c r="G746" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H746" t="n">
+        <v>3</v>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D747" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E747" t="n">
+        <v>61</v>
+      </c>
+      <c r="F747" t="n">
+        <v>0</v>
+      </c>
+      <c r="G747" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H747" t="n">
+        <v>3</v>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D748" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E748" t="n">
+        <v>82</v>
+      </c>
+      <c r="F748" t="n">
+        <v>0</v>
+      </c>
+      <c r="G748" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H748" t="n">
+        <v>3</v>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D749" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E749" t="n">
+        <v>79</v>
+      </c>
+      <c r="F749" t="n">
+        <v>0</v>
+      </c>
+      <c r="G749" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H749" t="n">
+        <v>3</v>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D750" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E750" t="n">
+        <v>74</v>
+      </c>
+      <c r="F750" t="n">
+        <v>0</v>
+      </c>
+      <c r="G750" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="H750" t="n">
+        <v>3</v>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D751" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E751" t="n">
+        <v>92</v>
+      </c>
+      <c r="F751" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G751" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="H751" t="n">
+        <v>53</v>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D752" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E752" t="n">
+        <v>76</v>
+      </c>
+      <c r="F752" t="n">
+        <v>0</v>
+      </c>
+      <c r="G752" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="H752" t="n">
+        <v>3</v>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D753" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E753" t="n">
+        <v>72</v>
+      </c>
+      <c r="F753" t="n">
+        <v>0</v>
+      </c>
+      <c r="G753" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="H753" t="n">
+        <v>3</v>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D754" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E754" t="n">
+        <v>72</v>
+      </c>
+      <c r="F754" t="n">
+        <v>0</v>
+      </c>
+      <c r="G754" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H754" t="n">
+        <v>3</v>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D755" t="n">
+        <v>25</v>
+      </c>
+      <c r="E755" t="n">
+        <v>74</v>
+      </c>
+      <c r="F755" t="n">
+        <v>0</v>
+      </c>
+      <c r="G755" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H755" t="n">
+        <v>3</v>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D756" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E756" t="n">
+        <v>63</v>
+      </c>
+      <c r="F756" t="n">
+        <v>0</v>
+      </c>
+      <c r="G756" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H756" t="n">
+        <v>3</v>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D757" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E757" t="n">
+        <v>78</v>
+      </c>
+      <c r="F757" t="n">
+        <v>0</v>
+      </c>
+      <c r="G757" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H757" t="n">
+        <v>3</v>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D758" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E758" t="n">
+        <v>80</v>
+      </c>
+      <c r="F758" t="n">
+        <v>0</v>
+      </c>
+      <c r="G758" t="n">
+        <v>20</v>
+      </c>
+      <c r="H758" t="n">
+        <v>3</v>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D759" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E759" t="n">
+        <v>75</v>
+      </c>
+      <c r="F759" t="n">
+        <v>0</v>
+      </c>
+      <c r="G759" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="H759" t="n">
+        <v>3</v>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D760" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E760" t="n">
+        <v>67</v>
+      </c>
+      <c r="F760" t="n">
+        <v>0</v>
+      </c>
+      <c r="G760" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H760" t="n">
+        <v>3</v>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
         </is>
       </c>
     </row>
@@ -27338,7 +28559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28794,6 +30015,67 @@
       <c r="O24" t="inlineStr">
         <is>
           <t>2026-09-25T03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>33</v>
+      </c>
+      <c r="D25" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="I25" t="n">
+        <v>78</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-09-25T06:30</t>
         </is>
       </c>
     </row>
@@ -28860,7 +30142,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -28869,7 +30151,7 @@
         <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0.7</v>
@@ -28887,16 +30169,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="F3" t="n">
-        <v>83.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>2.9</v>
@@ -28914,7 +30196,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -28923,7 +30205,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>76.2</v>
+        <v>76.3</v>
       </c>
       <c r="G4" t="n">
         <v>0.8</v>
@@ -28941,16 +30223,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
       </c>
       <c r="E5" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="F5" t="n">
-        <v>66.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>0.9</v>
@@ -28968,7 +30250,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -29004,7 +30286,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>74.7</v>
+        <v>74.5</v>
       </c>
       <c r="G7" t="n">
         <v>0.3</v>
@@ -29022,19 +30304,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="F8" t="n">
-        <v>84.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -29049,7 +30331,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -29058,7 +30340,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>69.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -29076,7 +30358,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -29085,7 +30367,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>79.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="G10" t="n">
         <v>2.3</v>
@@ -29112,7 +30394,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="G11" t="n">
         <v>0.5</v>
@@ -29130,7 +30412,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -29139,7 +30421,7 @@
         <v>25.3</v>
       </c>
       <c r="F12" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="G12" t="n">
         <v>1.2</v>
@@ -29157,19 +30439,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
       </c>
       <c r="E13" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="F13" t="n">
-        <v>82.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -29184,7 +30466,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -29193,7 +30475,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>79.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -29211,7 +30493,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -29220,7 +30502,7 @@
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>73.2</v>
+        <v>73.5</v>
       </c>
       <c r="G15" t="n">
         <v>1.6</v>
@@ -29238,19 +30520,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="F16" t="n">
-        <v>81</v>
+        <v>81.5</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -29265,7 +30547,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
@@ -29274,7 +30556,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>80</v>
+        <v>79.7</v>
       </c>
       <c r="G17" t="n">
         <v>1.1</v>
@@ -29292,7 +30574,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -29301,7 +30583,7 @@
         <v>23.7</v>
       </c>
       <c r="F18" t="n">
-        <v>75.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="G18" t="n">
         <v>1.9</v>
@@ -29319,7 +30601,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -29328,10 +30610,10 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>83.8</v>
+        <v>84.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="20">
@@ -29346,7 +30628,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -29355,7 +30637,7 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>72.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
@@ -29373,7 +30655,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -29382,7 +30664,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>66.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0.7</v>
@@ -29400,7 +30682,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -29409,7 +30691,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>72</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>2.7</v>
@@ -29427,7 +30709,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -29454,7 +30736,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -29463,7 +30745,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>80.3</v>
+        <v>80</v>
       </c>
       <c r="G24" t="n">
         <v>0.4</v>
@@ -29481,19 +30763,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="F25" t="n">
-        <v>82</v>
+        <v>82.5</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -29508,7 +30790,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
@@ -29517,7 +30799,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -29535,7 +30817,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -29544,7 +30826,7 @@
         <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0.3</v>
@@ -29562,7 +30844,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -29571,7 +30853,7 @@
         <v>23.3</v>
       </c>
       <c r="F28" t="n">
-        <v>69.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G28" t="n">
         <v>0.9</v>
@@ -29598,7 +30880,7 @@
         <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>79.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="G29" t="n">
         <v>0.2</v>
@@ -29625,7 +30907,7 @@
         <v>24.5</v>
       </c>
       <c r="F30" t="n">
-        <v>71.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="G30" t="n">
         <v>0.7</v>
@@ -29643,7 +30925,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -29652,7 +30934,7 @@
         <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>72.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -29670,7 +30952,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -29679,7 +30961,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>70.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -29697,7 +30979,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -29724,7 +31006,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -29733,7 +31015,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="G34" t="n">
         <v>0.5</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I760"/>
+  <dimension ref="A1:I793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28545,6 +28545,1227 @@
       <c r="I760" t="inlineStr">
         <is>
           <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D761" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E761" t="n">
+        <v>65</v>
+      </c>
+      <c r="F761" t="n">
+        <v>0</v>
+      </c>
+      <c r="G761" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="H761" t="n">
+        <v>3</v>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D762" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E762" t="n">
+        <v>71</v>
+      </c>
+      <c r="F762" t="n">
+        <v>0</v>
+      </c>
+      <c r="G762" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H762" t="n">
+        <v>3</v>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D763" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E763" t="n">
+        <v>78</v>
+      </c>
+      <c r="F763" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G763" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H763" t="n">
+        <v>51</v>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D764" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E764" t="n">
+        <v>56</v>
+      </c>
+      <c r="F764" t="n">
+        <v>0</v>
+      </c>
+      <c r="G764" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H764" t="n">
+        <v>3</v>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D765" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E765" t="n">
+        <v>71</v>
+      </c>
+      <c r="F765" t="n">
+        <v>0</v>
+      </c>
+      <c r="G765" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H765" t="n">
+        <v>3</v>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D766" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E766" t="n">
+        <v>62</v>
+      </c>
+      <c r="F766" t="n">
+        <v>0</v>
+      </c>
+      <c r="G766" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="H766" t="n">
+        <v>3</v>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D767" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E767" t="n">
+        <v>95</v>
+      </c>
+      <c r="F767" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G767" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H767" t="n">
+        <v>53</v>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D768" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E768" t="n">
+        <v>45</v>
+      </c>
+      <c r="F768" t="n">
+        <v>0</v>
+      </c>
+      <c r="G768" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="H768" t="n">
+        <v>3</v>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D769" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E769" t="n">
+        <v>63</v>
+      </c>
+      <c r="F769" t="n">
+        <v>0</v>
+      </c>
+      <c r="G769" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="H769" t="n">
+        <v>3</v>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D770" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E770" t="n">
+        <v>70</v>
+      </c>
+      <c r="F770" t="n">
+        <v>0</v>
+      </c>
+      <c r="G770" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H770" t="n">
+        <v>3</v>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D771" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E771" t="n">
+        <v>59</v>
+      </c>
+      <c r="F771" t="n">
+        <v>0</v>
+      </c>
+      <c r="G771" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H771" t="n">
+        <v>3</v>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D772" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E772" t="n">
+        <v>78</v>
+      </c>
+      <c r="F772" t="n">
+        <v>0</v>
+      </c>
+      <c r="G772" t="n">
+        <v>20</v>
+      </c>
+      <c r="H772" t="n">
+        <v>3</v>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D773" t="n">
+        <v>29</v>
+      </c>
+      <c r="E773" t="n">
+        <v>69</v>
+      </c>
+      <c r="F773" t="n">
+        <v>0</v>
+      </c>
+      <c r="G773" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="H773" t="n">
+        <v>3</v>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D774" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E774" t="n">
+        <v>60</v>
+      </c>
+      <c r="F774" t="n">
+        <v>0</v>
+      </c>
+      <c r="G774" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H774" t="n">
+        <v>3</v>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D775" t="n">
+        <v>27</v>
+      </c>
+      <c r="E775" t="n">
+        <v>89</v>
+      </c>
+      <c r="F775" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G775" t="n">
+        <v>18</v>
+      </c>
+      <c r="H775" t="n">
+        <v>51</v>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D776" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E776" t="n">
+        <v>66</v>
+      </c>
+      <c r="F776" t="n">
+        <v>0</v>
+      </c>
+      <c r="G776" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H776" t="n">
+        <v>3</v>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D777" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E777" t="n">
+        <v>59</v>
+      </c>
+      <c r="F777" t="n">
+        <v>0</v>
+      </c>
+      <c r="G777" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="H777" t="n">
+        <v>3</v>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D778" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E778" t="n">
+        <v>90</v>
+      </c>
+      <c r="F778" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G778" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H778" t="n">
+        <v>51</v>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D779" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E779" t="n">
+        <v>54</v>
+      </c>
+      <c r="F779" t="n">
+        <v>0</v>
+      </c>
+      <c r="G779" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H779" t="n">
+        <v>3</v>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D780" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E780" t="n">
+        <v>54</v>
+      </c>
+      <c r="F780" t="n">
+        <v>0</v>
+      </c>
+      <c r="G780" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="H780" t="n">
+        <v>3</v>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D781" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E781" t="n">
+        <v>57</v>
+      </c>
+      <c r="F781" t="n">
+        <v>0</v>
+      </c>
+      <c r="G781" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="H781" t="n">
+        <v>3</v>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D782" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E782" t="n">
+        <v>57</v>
+      </c>
+      <c r="F782" t="n">
+        <v>0</v>
+      </c>
+      <c r="G782" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="H782" t="n">
+        <v>3</v>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D783" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E783" t="n">
+        <v>59</v>
+      </c>
+      <c r="F783" t="n">
+        <v>0</v>
+      </c>
+      <c r="G783" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H783" t="n">
+        <v>3</v>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D784" t="n">
+        <v>27</v>
+      </c>
+      <c r="E784" t="n">
+        <v>83</v>
+      </c>
+      <c r="F784" t="n">
+        <v>0</v>
+      </c>
+      <c r="G784" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H784" t="n">
+        <v>3</v>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D785" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E785" t="n">
+        <v>67</v>
+      </c>
+      <c r="F785" t="n">
+        <v>0</v>
+      </c>
+      <c r="G785" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="H785" t="n">
+        <v>3</v>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D786" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E786" t="n">
+        <v>53</v>
+      </c>
+      <c r="F786" t="n">
+        <v>0</v>
+      </c>
+      <c r="G786" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H786" t="n">
+        <v>3</v>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D787" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E787" t="n">
+        <v>53</v>
+      </c>
+      <c r="F787" t="n">
+        <v>0</v>
+      </c>
+      <c r="G787" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H787" t="n">
+        <v>3</v>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D788" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E788" t="n">
+        <v>64</v>
+      </c>
+      <c r="F788" t="n">
+        <v>0</v>
+      </c>
+      <c r="G788" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="H788" t="n">
+        <v>3</v>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D789" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E789" t="n">
+        <v>57</v>
+      </c>
+      <c r="F789" t="n">
+        <v>0</v>
+      </c>
+      <c r="G789" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="H789" t="n">
+        <v>3</v>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D790" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E790" t="n">
+        <v>60</v>
+      </c>
+      <c r="F790" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G790" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H790" t="n">
+        <v>51</v>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D791" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E791" t="n">
+        <v>53</v>
+      </c>
+      <c r="F791" t="n">
+        <v>0</v>
+      </c>
+      <c r="G791" t="n">
+        <v>25</v>
+      </c>
+      <c r="H791" t="n">
+        <v>3</v>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D792" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E792" t="n">
+        <v>73</v>
+      </c>
+      <c r="F792" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G792" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H792" t="n">
+        <v>51</v>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D793" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E793" t="n">
+        <v>60</v>
+      </c>
+      <c r="F793" t="n">
+        <v>0</v>
+      </c>
+      <c r="G793" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="H793" t="n">
+        <v>3</v>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
         </is>
       </c>
     </row>
@@ -28559,7 +29780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30076,6 +31297,67 @@
       <c r="O25" t="inlineStr">
         <is>
           <t>2026-09-25T06:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>33</v>
+      </c>
+      <c r="D26" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:30</t>
         </is>
       </c>
     </row>
@@ -30151,7 +31433,7 @@
         <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>80.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="G2" t="n">
         <v>0.7</v>
@@ -30178,7 +31460,7 @@
         <v>24.9</v>
       </c>
       <c r="F3" t="n">
-        <v>83.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>2.9</v>
@@ -30196,7 +31478,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -30205,10 +31487,10 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>76.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5">
@@ -30223,7 +31505,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -30232,7 +31514,7 @@
         <v>24.5</v>
       </c>
       <c r="F5" t="n">
-        <v>66.90000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="G5" t="n">
         <v>0.9</v>
@@ -30259,7 +31541,7 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>82.3</v>
+        <v>81.8</v>
       </c>
       <c r="G6" t="n">
         <v>0.2</v>
@@ -30286,7 +31568,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>74.5</v>
+        <v>74</v>
       </c>
       <c r="G7" t="n">
         <v>0.3</v>
@@ -30304,7 +31586,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -30313,10 +31595,10 @@
         <v>24.1</v>
       </c>
       <c r="F8" t="n">
-        <v>84.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -30331,7 +31613,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.4</v>
+        <v>28.6</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -30340,7 +31622,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>69.8</v>
+        <v>68.8</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -30358,7 +31640,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -30367,7 +31649,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>79.7</v>
+        <v>79</v>
       </c>
       <c r="G10" t="n">
         <v>2.3</v>
@@ -30394,7 +31676,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>79.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0.5</v>
@@ -30412,7 +31694,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -30421,7 +31703,7 @@
         <v>25.3</v>
       </c>
       <c r="F12" t="n">
-        <v>75.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>1.2</v>
@@ -30448,7 +31730,7 @@
         <v>24.4</v>
       </c>
       <c r="F13" t="n">
-        <v>82.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -30475,7 +31757,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>79.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -30493,7 +31775,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -30502,7 +31784,7 @@
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>73.5</v>
+        <v>73</v>
       </c>
       <c r="G15" t="n">
         <v>1.6</v>
@@ -30520,7 +31802,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -30529,10 +31811,10 @@
         <v>24.5</v>
       </c>
       <c r="F16" t="n">
-        <v>81.5</v>
+        <v>81.8</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -30547,7 +31829,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
@@ -30556,7 +31838,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>79.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>1.1</v>
@@ -30574,7 +31856,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -30583,7 +31865,7 @@
         <v>23.7</v>
       </c>
       <c r="F18" t="n">
-        <v>75</v>
+        <v>74.3</v>
       </c>
       <c r="G18" t="n">
         <v>1.9</v>
@@ -30601,7 +31883,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -30610,10 +31892,10 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>84.3</v>
+        <v>84.5</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="20">
@@ -30628,7 +31910,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -30637,7 +31919,7 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>73</v>
+        <v>72.2</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
@@ -30655,7 +31937,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -30664,7 +31946,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>66.40000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0.7</v>
@@ -30682,7 +31964,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -30691,7 +31973,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>72.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="G22" t="n">
         <v>2.7</v>
@@ -30709,7 +31991,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -30718,7 +32000,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>77.8</v>
+        <v>77</v>
       </c>
       <c r="G23" t="n">
         <v>0.2</v>
@@ -30736,7 +32018,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -30745,7 +32027,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>80</v>
+        <v>79.2</v>
       </c>
       <c r="G24" t="n">
         <v>0.4</v>
@@ -30763,7 +32045,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -30799,7 +32081,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>79</v>
+        <v>78.5</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -30817,7 +32099,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -30826,7 +32108,7 @@
         <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>71.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="G27" t="n">
         <v>0.3</v>
@@ -30844,7 +32126,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -30853,7 +32135,7 @@
         <v>23.3</v>
       </c>
       <c r="F28" t="n">
-        <v>69.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="G28" t="n">
         <v>0.9</v>
@@ -30880,7 +32162,7 @@
         <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>79.2</v>
+        <v>78.5</v>
       </c>
       <c r="G29" t="n">
         <v>0.2</v>
@@ -30907,7 +32189,7 @@
         <v>24.5</v>
       </c>
       <c r="F30" t="n">
-        <v>71.3</v>
+        <v>70.7</v>
       </c>
       <c r="G30" t="n">
         <v>0.7</v>
@@ -30925,7 +32207,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -30934,10 +32216,10 @@
         <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>72.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="32">
@@ -30952,7 +32234,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -30961,7 +32243,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>71.3</v>
+        <v>70.5</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -30988,10 +32270,10 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="34">
@@ -31015,7 +32297,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>73</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G34" t="n">
         <v>0.5</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I793"/>
+  <dimension ref="A1:I826"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29766,6 +29766,1227 @@
       <c r="I793" t="inlineStr">
         <is>
           <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D794" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E794" t="n">
+        <v>66</v>
+      </c>
+      <c r="F794" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G794" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H794" t="n">
+        <v>1</v>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D795" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E795" t="n">
+        <v>60</v>
+      </c>
+      <c r="F795" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G795" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H795" t="n">
+        <v>1</v>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D796" t="n">
+        <v>28</v>
+      </c>
+      <c r="E796" t="n">
+        <v>63</v>
+      </c>
+      <c r="F796" t="n">
+        <v>0</v>
+      </c>
+      <c r="G796" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H796" t="n">
+        <v>3</v>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D797" t="n">
+        <v>27</v>
+      </c>
+      <c r="E797" t="n">
+        <v>64</v>
+      </c>
+      <c r="F797" t="n">
+        <v>0</v>
+      </c>
+      <c r="G797" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H797" t="n">
+        <v>3</v>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D798" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E798" t="n">
+        <v>64</v>
+      </c>
+      <c r="F798" t="n">
+        <v>0</v>
+      </c>
+      <c r="G798" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H798" t="n">
+        <v>3</v>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D799" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E799" t="n">
+        <v>63</v>
+      </c>
+      <c r="F799" t="n">
+        <v>0</v>
+      </c>
+      <c r="G799" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H799" t="n">
+        <v>3</v>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D800" t="n">
+        <v>27</v>
+      </c>
+      <c r="E800" t="n">
+        <v>71</v>
+      </c>
+      <c r="F800" t="n">
+        <v>0</v>
+      </c>
+      <c r="G800" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H800" t="n">
+        <v>3</v>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D801" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E801" t="n">
+        <v>48</v>
+      </c>
+      <c r="F801" t="n">
+        <v>0</v>
+      </c>
+      <c r="G801" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H801" t="n">
+        <v>3</v>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D802" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E802" t="n">
+        <v>59</v>
+      </c>
+      <c r="F802" t="n">
+        <v>0</v>
+      </c>
+      <c r="G802" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H802" t="n">
+        <v>3</v>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D803" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E803" t="n">
+        <v>64</v>
+      </c>
+      <c r="F803" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G803" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H803" t="n">
+        <v>1</v>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D804" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E804" t="n">
+        <v>71</v>
+      </c>
+      <c r="F804" t="n">
+        <v>0</v>
+      </c>
+      <c r="G804" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H804" t="n">
+        <v>3</v>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D805" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E805" t="n">
+        <v>59</v>
+      </c>
+      <c r="F805" t="n">
+        <v>0</v>
+      </c>
+      <c r="G805" t="n">
+        <v>13</v>
+      </c>
+      <c r="H805" t="n">
+        <v>3</v>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D806" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E806" t="n">
+        <v>64</v>
+      </c>
+      <c r="F806" t="n">
+        <v>0</v>
+      </c>
+      <c r="G806" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H806" t="n">
+        <v>3</v>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D807" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E807" t="n">
+        <v>62</v>
+      </c>
+      <c r="F807" t="n">
+        <v>0</v>
+      </c>
+      <c r="G807" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H807" t="n">
+        <v>3</v>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D808" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E808" t="n">
+        <v>70</v>
+      </c>
+      <c r="F808" t="n">
+        <v>0</v>
+      </c>
+      <c r="G808" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H808" t="n">
+        <v>3</v>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D809" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E809" t="n">
+        <v>61</v>
+      </c>
+      <c r="F809" t="n">
+        <v>0</v>
+      </c>
+      <c r="G809" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H809" t="n">
+        <v>3</v>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D810" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E810" t="n">
+        <v>63</v>
+      </c>
+      <c r="F810" t="n">
+        <v>0</v>
+      </c>
+      <c r="G810" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H810" t="n">
+        <v>3</v>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D811" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E811" t="n">
+        <v>70</v>
+      </c>
+      <c r="F811" t="n">
+        <v>0</v>
+      </c>
+      <c r="G811" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H811" t="n">
+        <v>3</v>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D812" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E812" t="n">
+        <v>64</v>
+      </c>
+      <c r="F812" t="n">
+        <v>0</v>
+      </c>
+      <c r="G812" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H812" t="n">
+        <v>3</v>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D813" t="n">
+        <v>29</v>
+      </c>
+      <c r="E813" t="n">
+        <v>59</v>
+      </c>
+      <c r="F813" t="n">
+        <v>0</v>
+      </c>
+      <c r="G813" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H813" t="n">
+        <v>3</v>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D814" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E814" t="n">
+        <v>58</v>
+      </c>
+      <c r="F814" t="n">
+        <v>0</v>
+      </c>
+      <c r="G814" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H814" t="n">
+        <v>3</v>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D815" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E815" t="n">
+        <v>61</v>
+      </c>
+      <c r="F815" t="n">
+        <v>0</v>
+      </c>
+      <c r="G815" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H815" t="n">
+        <v>3</v>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D816" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E816" t="n">
+        <v>60</v>
+      </c>
+      <c r="F816" t="n">
+        <v>0</v>
+      </c>
+      <c r="G816" t="n">
+        <v>17</v>
+      </c>
+      <c r="H816" t="n">
+        <v>3</v>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D817" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E817" t="n">
+        <v>64</v>
+      </c>
+      <c r="F817" t="n">
+        <v>0</v>
+      </c>
+      <c r="G817" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H817" t="n">
+        <v>3</v>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D818" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E818" t="n">
+        <v>60</v>
+      </c>
+      <c r="F818" t="n">
+        <v>0</v>
+      </c>
+      <c r="G818" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H818" t="n">
+        <v>3</v>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D819" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E819" t="n">
+        <v>60</v>
+      </c>
+      <c r="F819" t="n">
+        <v>0</v>
+      </c>
+      <c r="G819" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H819" t="n">
+        <v>3</v>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D820" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E820" t="n">
+        <v>60</v>
+      </c>
+      <c r="F820" t="n">
+        <v>0</v>
+      </c>
+      <c r="G820" t="n">
+        <v>16</v>
+      </c>
+      <c r="H820" t="n">
+        <v>3</v>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D821" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E821" t="n">
+        <v>59</v>
+      </c>
+      <c r="F821" t="n">
+        <v>0</v>
+      </c>
+      <c r="G821" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H821" t="n">
+        <v>3</v>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D822" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E822" t="n">
+        <v>66</v>
+      </c>
+      <c r="F822" t="n">
+        <v>0</v>
+      </c>
+      <c r="G822" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H822" t="n">
+        <v>3</v>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D823" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E823" t="n">
+        <v>64</v>
+      </c>
+      <c r="F823" t="n">
+        <v>0</v>
+      </c>
+      <c r="G823" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H823" t="n">
+        <v>3</v>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D824" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E824" t="n">
+        <v>59</v>
+      </c>
+      <c r="F824" t="n">
+        <v>0</v>
+      </c>
+      <c r="G824" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H824" t="n">
+        <v>3</v>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D825" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E825" t="n">
+        <v>65</v>
+      </c>
+      <c r="F825" t="n">
+        <v>0</v>
+      </c>
+      <c r="G825" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H825" t="n">
+        <v>3</v>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D826" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E826" t="n">
+        <v>61</v>
+      </c>
+      <c r="F826" t="n">
+        <v>0</v>
+      </c>
+      <c r="G826" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H826" t="n">
+        <v>3</v>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>2026-09-25T18:45</t>
         </is>
       </c>
     </row>
@@ -29780,7 +31001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31358,6 +32579,67 @@
       <c r="O26" t="inlineStr">
         <is>
           <t>2026-09-25T12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>33</v>
+      </c>
+      <c r="D27" t="n">
+        <v>28</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:00</t>
         </is>
       </c>
     </row>
@@ -31424,7 +32706,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -31433,10 +32715,10 @@
         <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>80.2</v>
+        <v>79.7</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="3">
@@ -31451,7 +32733,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -31460,10 +32742,10 @@
         <v>24.9</v>
       </c>
       <c r="F3" t="n">
-        <v>83.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="4">
@@ -31487,7 +32769,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>76.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="G4" t="n">
         <v>0.9</v>
@@ -31505,7 +32787,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -31514,7 +32796,7 @@
         <v>24.5</v>
       </c>
       <c r="F5" t="n">
-        <v>66.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>0.9</v>
@@ -31541,7 +32823,7 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>81.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.2</v>
@@ -31568,7 +32850,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>0.3</v>
@@ -31595,7 +32877,7 @@
         <v>24.1</v>
       </c>
       <c r="F8" t="n">
-        <v>85.09999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="G8" t="n">
         <v>2.2</v>
@@ -31622,7 +32904,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>68.8</v>
+        <v>68</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -31649,7 +32931,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>79</v>
+        <v>78.2</v>
       </c>
       <c r="G10" t="n">
         <v>2.3</v>
@@ -31667,7 +32949,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -31676,10 +32958,10 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>78.90000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="12">
@@ -31703,7 +32985,7 @@
         <v>25.3</v>
       </c>
       <c r="F12" t="n">
-        <v>75.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>1.2</v>
@@ -31721,7 +33003,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -31730,7 +33012,7 @@
         <v>24.4</v>
       </c>
       <c r="F13" t="n">
-        <v>82.7</v>
+        <v>81.8</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -31757,7 +33039,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>78.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -31784,7 +33066,7 @@
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>73</v>
+        <v>72.5</v>
       </c>
       <c r="G15" t="n">
         <v>1.6</v>
@@ -31811,7 +33093,7 @@
         <v>24.5</v>
       </c>
       <c r="F16" t="n">
-        <v>81.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -31838,7 +33120,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>79.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>1.1</v>
@@ -31865,7 +33147,7 @@
         <v>23.7</v>
       </c>
       <c r="F18" t="n">
-        <v>74.3</v>
+        <v>73.8</v>
       </c>
       <c r="G18" t="n">
         <v>1.9</v>
@@ -31892,7 +33174,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>84.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>1.8</v>
@@ -31919,7 +33201,7 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>72.2</v>
+        <v>71.8</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
@@ -31946,7 +33228,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>65.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0.7</v>
@@ -31973,7 +33255,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>71.8</v>
+        <v>71.2</v>
       </c>
       <c r="G22" t="n">
         <v>2.7</v>
@@ -32000,7 +33282,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>77</v>
+        <v>76.3</v>
       </c>
       <c r="G23" t="n">
         <v>0.2</v>
@@ -32018,7 +33300,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -32027,7 +33309,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>79.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0.4</v>
@@ -32054,7 +33336,7 @@
         <v>24.5</v>
       </c>
       <c r="F25" t="n">
-        <v>82.5</v>
+        <v>81.8</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -32072,7 +33354,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
@@ -32081,7 +33363,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>78.5</v>
+        <v>77.8</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -32108,7 +33390,7 @@
         <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>70.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>0.3</v>
@@ -32135,7 +33417,7 @@
         <v>23.3</v>
       </c>
       <c r="F28" t="n">
-        <v>69.2</v>
+        <v>68.8</v>
       </c>
       <c r="G28" t="n">
         <v>0.9</v>
@@ -32162,7 +33444,7 @@
         <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>78.5</v>
+        <v>77.8</v>
       </c>
       <c r="G29" t="n">
         <v>0.2</v>
@@ -32189,7 +33471,7 @@
         <v>24.5</v>
       </c>
       <c r="F30" t="n">
-        <v>70.7</v>
+        <v>70.5</v>
       </c>
       <c r="G30" t="n">
         <v>0.7</v>
@@ -32216,7 +33498,7 @@
         <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>72.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="G31" t="n">
         <v>1.1</v>
@@ -32243,7 +33525,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>70.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -32261,7 +33543,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -32270,7 +33552,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>74.3</v>
+        <v>74</v>
       </c>
       <c r="G33" t="n">
         <v>1.1</v>
@@ -32297,7 +33579,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>72.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="G34" t="n">
         <v>0.5</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I826"/>
+  <dimension ref="A1:I859"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30987,6 +30987,1227 @@
       <c r="I826" t="inlineStr">
         <is>
           <t>2026-09-25T18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D827" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E827" t="n">
+        <v>66</v>
+      </c>
+      <c r="F827" t="n">
+        <v>0</v>
+      </c>
+      <c r="G827" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H827" t="n">
+        <v>1</v>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D828" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E828" t="n">
+        <v>70</v>
+      </c>
+      <c r="F828" t="n">
+        <v>0</v>
+      </c>
+      <c r="G828" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H828" t="n">
+        <v>3</v>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D829" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E829" t="n">
+        <v>66</v>
+      </c>
+      <c r="F829" t="n">
+        <v>0</v>
+      </c>
+      <c r="G829" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H829" t="n">
+        <v>3</v>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D830" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E830" t="n">
+        <v>68</v>
+      </c>
+      <c r="F830" t="n">
+        <v>0</v>
+      </c>
+      <c r="G830" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H830" t="n">
+        <v>3</v>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D831" t="n">
+        <v>30</v>
+      </c>
+      <c r="E831" t="n">
+        <v>65</v>
+      </c>
+      <c r="F831" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G831" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H831" t="n">
+        <v>1</v>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D832" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E832" t="n">
+        <v>58</v>
+      </c>
+      <c r="F832" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G832" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H832" t="n">
+        <v>1</v>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D833" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E833" t="n">
+        <v>70</v>
+      </c>
+      <c r="F833" t="n">
+        <v>0</v>
+      </c>
+      <c r="G833" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H833" t="n">
+        <v>3</v>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D834" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E834" t="n">
+        <v>65</v>
+      </c>
+      <c r="F834" t="n">
+        <v>0</v>
+      </c>
+      <c r="G834" t="n">
+        <v>17</v>
+      </c>
+      <c r="H834" t="n">
+        <v>3</v>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D835" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E835" t="n">
+        <v>68</v>
+      </c>
+      <c r="F835" t="n">
+        <v>0</v>
+      </c>
+      <c r="G835" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H835" t="n">
+        <v>3</v>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D836" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E836" t="n">
+        <v>66</v>
+      </c>
+      <c r="F836" t="n">
+        <v>0</v>
+      </c>
+      <c r="G836" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H836" t="n">
+        <v>3</v>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D837" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E837" t="n">
+        <v>66</v>
+      </c>
+      <c r="F837" t="n">
+        <v>0</v>
+      </c>
+      <c r="G837" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H837" t="n">
+        <v>3</v>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D838" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E838" t="n">
+        <v>68</v>
+      </c>
+      <c r="F838" t="n">
+        <v>0</v>
+      </c>
+      <c r="G838" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H838" t="n">
+        <v>2</v>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D839" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E839" t="n">
+        <v>66</v>
+      </c>
+      <c r="F839" t="n">
+        <v>0</v>
+      </c>
+      <c r="G839" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H839" t="n">
+        <v>3</v>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D840" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E840" t="n">
+        <v>62</v>
+      </c>
+      <c r="F840" t="n">
+        <v>0</v>
+      </c>
+      <c r="G840" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H840" t="n">
+        <v>3</v>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D841" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E841" t="n">
+        <v>73</v>
+      </c>
+      <c r="F841" t="n">
+        <v>0</v>
+      </c>
+      <c r="G841" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H841" t="n">
+        <v>3</v>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D842" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E842" t="n">
+        <v>60</v>
+      </c>
+      <c r="F842" t="n">
+        <v>0</v>
+      </c>
+      <c r="G842" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H842" t="n">
+        <v>3</v>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D843" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E843" t="n">
+        <v>67</v>
+      </c>
+      <c r="F843" t="n">
+        <v>0</v>
+      </c>
+      <c r="G843" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H843" t="n">
+        <v>3</v>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D844" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E844" t="n">
+        <v>67</v>
+      </c>
+      <c r="F844" t="n">
+        <v>0</v>
+      </c>
+      <c r="G844" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H844" t="n">
+        <v>3</v>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D845" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E845" t="n">
+        <v>64</v>
+      </c>
+      <c r="F845" t="n">
+        <v>0</v>
+      </c>
+      <c r="G845" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H845" t="n">
+        <v>3</v>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D846" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E846" t="n">
+        <v>61</v>
+      </c>
+      <c r="F846" t="n">
+        <v>0</v>
+      </c>
+      <c r="G846" t="n">
+        <v>15</v>
+      </c>
+      <c r="H846" t="n">
+        <v>3</v>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D847" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E847" t="n">
+        <v>61</v>
+      </c>
+      <c r="F847" t="n">
+        <v>0</v>
+      </c>
+      <c r="G847" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H847" t="n">
+        <v>2</v>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D848" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E848" t="n">
+        <v>66</v>
+      </c>
+      <c r="F848" t="n">
+        <v>0</v>
+      </c>
+      <c r="G848" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H848" t="n">
+        <v>3</v>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D849" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E849" t="n">
+        <v>67</v>
+      </c>
+      <c r="F849" t="n">
+        <v>0</v>
+      </c>
+      <c r="G849" t="n">
+        <v>15</v>
+      </c>
+      <c r="H849" t="n">
+        <v>3</v>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D850" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E850" t="n">
+        <v>68</v>
+      </c>
+      <c r="F850" t="n">
+        <v>0</v>
+      </c>
+      <c r="G850" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H850" t="n">
+        <v>3</v>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D851" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E851" t="n">
+        <v>65</v>
+      </c>
+      <c r="F851" t="n">
+        <v>0</v>
+      </c>
+      <c r="G851" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H851" t="n">
+        <v>3</v>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D852" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E852" t="n">
+        <v>65</v>
+      </c>
+      <c r="F852" t="n">
+        <v>0</v>
+      </c>
+      <c r="G852" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="H852" t="n">
+        <v>3</v>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D853" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E853" t="n">
+        <v>63</v>
+      </c>
+      <c r="F853" t="n">
+        <v>0</v>
+      </c>
+      <c r="G853" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H853" t="n">
+        <v>3</v>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D854" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E854" t="n">
+        <v>68</v>
+      </c>
+      <c r="F854" t="n">
+        <v>0</v>
+      </c>
+      <c r="G854" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H854" t="n">
+        <v>3</v>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D855" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E855" t="n">
+        <v>64</v>
+      </c>
+      <c r="F855" t="n">
+        <v>0</v>
+      </c>
+      <c r="G855" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H855" t="n">
+        <v>3</v>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D856" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E856" t="n">
+        <v>69</v>
+      </c>
+      <c r="F856" t="n">
+        <v>0</v>
+      </c>
+      <c r="G856" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H856" t="n">
+        <v>3</v>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D857" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E857" t="n">
+        <v>66</v>
+      </c>
+      <c r="F857" t="n">
+        <v>0</v>
+      </c>
+      <c r="G857" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H857" t="n">
+        <v>3</v>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D858" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E858" t="n">
+        <v>66</v>
+      </c>
+      <c r="F858" t="n">
+        <v>0</v>
+      </c>
+      <c r="G858" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H858" t="n">
+        <v>3</v>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D859" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E859" t="n">
+        <v>60</v>
+      </c>
+      <c r="F859" t="n">
+        <v>0</v>
+      </c>
+      <c r="G859" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="H859" t="n">
+        <v>3</v>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
         </is>
       </c>
     </row>
@@ -31001,7 +32222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32640,6 +33861,67 @@
       <c r="O27" t="inlineStr">
         <is>
           <t>2026-09-25T12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>33</v>
+      </c>
+      <c r="D28" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I28" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-09-25T23:45</t>
         </is>
       </c>
     </row>
@@ -32715,7 +33997,7 @@
         <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>79.7</v>
+        <v>79.2</v>
       </c>
       <c r="G2" t="n">
         <v>1.8</v>
@@ -32742,7 +34024,7 @@
         <v>24.9</v>
       </c>
       <c r="F3" t="n">
-        <v>82.2</v>
+        <v>81.7</v>
       </c>
       <c r="G3" t="n">
         <v>3.4</v>
@@ -32760,7 +34042,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -32769,7 +34051,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>75.8</v>
+        <v>75.5</v>
       </c>
       <c r="G4" t="n">
         <v>0.9</v>
@@ -32787,7 +34069,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -32814,7 +34096,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -32823,10 +34105,10 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>81.09999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -32841,7 +34123,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -32850,10 +34132,10 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>73.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -32868,7 +34150,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -32877,7 +34159,7 @@
         <v>24.1</v>
       </c>
       <c r="F8" t="n">
-        <v>84.5</v>
+        <v>84</v>
       </c>
       <c r="G8" t="n">
         <v>2.2</v>
@@ -32904,7 +34186,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>67.8</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -32931,7 +34213,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>78.2</v>
+        <v>77.8</v>
       </c>
       <c r="G10" t="n">
         <v>2.3</v>
@@ -32949,7 +34231,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -32958,7 +34240,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>78.3</v>
+        <v>77.8</v>
       </c>
       <c r="G11" t="n">
         <v>1.3</v>
@@ -32976,7 +34258,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -32985,7 +34267,7 @@
         <v>25.3</v>
       </c>
       <c r="F12" t="n">
-        <v>74.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>1.2</v>
@@ -33003,7 +34285,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -33012,7 +34294,7 @@
         <v>24.4</v>
       </c>
       <c r="F13" t="n">
-        <v>81.8</v>
+        <v>81.2</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -33030,7 +34312,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -33039,7 +34321,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>78.09999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -33066,7 +34348,7 @@
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>72.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>1.6</v>
@@ -33093,7 +34375,7 @@
         <v>24.5</v>
       </c>
       <c r="F16" t="n">
-        <v>81.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -33120,7 +34402,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>78.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="G17" t="n">
         <v>1.1</v>
@@ -33138,7 +34420,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -33147,7 +34429,7 @@
         <v>23.7</v>
       </c>
       <c r="F18" t="n">
-        <v>73.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>1.9</v>
@@ -33165,7 +34447,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -33174,7 +34456,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>83.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="G19" t="n">
         <v>1.8</v>
@@ -33192,7 +34474,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -33201,7 +34483,7 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>71.8</v>
+        <v>71.5</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
@@ -33219,7 +34501,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -33228,7 +34510,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>65.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0.7</v>
@@ -33255,7 +34537,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>71.2</v>
+        <v>70.8</v>
       </c>
       <c r="G22" t="n">
         <v>2.7</v>
@@ -33282,7 +34564,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>76.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0.2</v>
@@ -33300,7 +34582,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -33309,7 +34591,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>78.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="G24" t="n">
         <v>0.4</v>
@@ -33336,7 +34618,7 @@
         <v>24.5</v>
       </c>
       <c r="F25" t="n">
-        <v>81.8</v>
+        <v>81.2</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -33354,7 +34636,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
@@ -33363,7 +34645,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>77.8</v>
+        <v>77.3</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -33381,7 +34663,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -33390,7 +34672,7 @@
         <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>70.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="G27" t="n">
         <v>0.3</v>
@@ -33408,7 +34690,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -33417,7 +34699,7 @@
         <v>23.3</v>
       </c>
       <c r="F28" t="n">
-        <v>68.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G28" t="n">
         <v>0.9</v>
@@ -33444,7 +34726,7 @@
         <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>77.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0.2</v>
@@ -33462,7 +34744,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -33471,7 +34753,7 @@
         <v>24.5</v>
       </c>
       <c r="F30" t="n">
-        <v>70.5</v>
+        <v>70.2</v>
       </c>
       <c r="G30" t="n">
         <v>0.7</v>
@@ -33489,7 +34771,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -33498,7 +34780,7 @@
         <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>71.8</v>
+        <v>71.7</v>
       </c>
       <c r="G31" t="n">
         <v>1.1</v>
@@ -33516,7 +34798,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -33525,7 +34807,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>70.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -33543,7 +34825,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -33552,7 +34834,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>74</v>
+        <v>73.7</v>
       </c>
       <c r="G33" t="n">
         <v>1.1</v>
@@ -33579,7 +34861,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>72</v>
+        <v>71.5</v>
       </c>
       <c r="G34" t="n">
         <v>0.5</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I859"/>
+  <dimension ref="A1:I892"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32208,6 +32208,1227 @@
       <c r="I859" t="inlineStr">
         <is>
           <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D860" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E860" t="n">
+        <v>68</v>
+      </c>
+      <c r="F860" t="n">
+        <v>0</v>
+      </c>
+      <c r="G860" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H860" t="n">
+        <v>2</v>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D861" t="n">
+        <v>26</v>
+      </c>
+      <c r="E861" t="n">
+        <v>74</v>
+      </c>
+      <c r="F861" t="n">
+        <v>0</v>
+      </c>
+      <c r="G861" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H861" t="n">
+        <v>3</v>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D862" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E862" t="n">
+        <v>64</v>
+      </c>
+      <c r="F862" t="n">
+        <v>0</v>
+      </c>
+      <c r="G862" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H862" t="n">
+        <v>2</v>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D863" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E863" t="n">
+        <v>72</v>
+      </c>
+      <c r="F863" t="n">
+        <v>0</v>
+      </c>
+      <c r="G863" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H863" t="n">
+        <v>2</v>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D864" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E864" t="n">
+        <v>62</v>
+      </c>
+      <c r="F864" t="n">
+        <v>0</v>
+      </c>
+      <c r="G864" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H864" t="n">
+        <v>3</v>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D865" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E865" t="n">
+        <v>59</v>
+      </c>
+      <c r="F865" t="n">
+        <v>0</v>
+      </c>
+      <c r="G865" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H865" t="n">
+        <v>2</v>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D866" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E866" t="n">
+        <v>70</v>
+      </c>
+      <c r="F866" t="n">
+        <v>0</v>
+      </c>
+      <c r="G866" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H866" t="n">
+        <v>2</v>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D867" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E867" t="n">
+        <v>68</v>
+      </c>
+      <c r="F867" t="n">
+        <v>0</v>
+      </c>
+      <c r="G867" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H867" t="n">
+        <v>3</v>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D868" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E868" t="n">
+        <v>65</v>
+      </c>
+      <c r="F868" t="n">
+        <v>0</v>
+      </c>
+      <c r="G868" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H868" t="n">
+        <v>3</v>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D869" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E869" t="n">
+        <v>64</v>
+      </c>
+      <c r="F869" t="n">
+        <v>0</v>
+      </c>
+      <c r="G869" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H869" t="n">
+        <v>3</v>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D870" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E870" t="n">
+        <v>69</v>
+      </c>
+      <c r="F870" t="n">
+        <v>0</v>
+      </c>
+      <c r="G870" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H870" t="n">
+        <v>3</v>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D871" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E871" t="n">
+        <v>64</v>
+      </c>
+      <c r="F871" t="n">
+        <v>0</v>
+      </c>
+      <c r="G871" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H871" t="n">
+        <v>3</v>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D872" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E872" t="n">
+        <v>70</v>
+      </c>
+      <c r="F872" t="n">
+        <v>0</v>
+      </c>
+      <c r="G872" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H872" t="n">
+        <v>3</v>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D873" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E873" t="n">
+        <v>71</v>
+      </c>
+      <c r="F873" t="n">
+        <v>0</v>
+      </c>
+      <c r="G873" t="n">
+        <v>18</v>
+      </c>
+      <c r="H873" t="n">
+        <v>3</v>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D874" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E874" t="n">
+        <v>66</v>
+      </c>
+      <c r="F874" t="n">
+        <v>0</v>
+      </c>
+      <c r="G874" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H874" t="n">
+        <v>3</v>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D875" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E875" t="n">
+        <v>67</v>
+      </c>
+      <c r="F875" t="n">
+        <v>0</v>
+      </c>
+      <c r="G875" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H875" t="n">
+        <v>3</v>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D876" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E876" t="n">
+        <v>70</v>
+      </c>
+      <c r="F876" t="n">
+        <v>0</v>
+      </c>
+      <c r="G876" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H876" t="n">
+        <v>0</v>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D877" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E877" t="n">
+        <v>69</v>
+      </c>
+      <c r="F877" t="n">
+        <v>0</v>
+      </c>
+      <c r="G877" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H877" t="n">
+        <v>3</v>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D878" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E878" t="n">
+        <v>66</v>
+      </c>
+      <c r="F878" t="n">
+        <v>0</v>
+      </c>
+      <c r="G878" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H878" t="n">
+        <v>3</v>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D879" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E879" t="n">
+        <v>60</v>
+      </c>
+      <c r="F879" t="n">
+        <v>0</v>
+      </c>
+      <c r="G879" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H879" t="n">
+        <v>3</v>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D880" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E880" t="n">
+        <v>73</v>
+      </c>
+      <c r="F880" t="n">
+        <v>0</v>
+      </c>
+      <c r="G880" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H880" t="n">
+        <v>3</v>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D881" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E881" t="n">
+        <v>64</v>
+      </c>
+      <c r="F881" t="n">
+        <v>0</v>
+      </c>
+      <c r="G881" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H881" t="n">
+        <v>3</v>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D882" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E882" t="n">
+        <v>65</v>
+      </c>
+      <c r="F882" t="n">
+        <v>0</v>
+      </c>
+      <c r="G882" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H882" t="n">
+        <v>3</v>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D883" t="n">
+        <v>27</v>
+      </c>
+      <c r="E883" t="n">
+        <v>62</v>
+      </c>
+      <c r="F883" t="n">
+        <v>0</v>
+      </c>
+      <c r="G883" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H883" t="n">
+        <v>3</v>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D884" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E884" t="n">
+        <v>60</v>
+      </c>
+      <c r="F884" t="n">
+        <v>0</v>
+      </c>
+      <c r="G884" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H884" t="n">
+        <v>3</v>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D885" t="n">
+        <v>24</v>
+      </c>
+      <c r="E885" t="n">
+        <v>72</v>
+      </c>
+      <c r="F885" t="n">
+        <v>0</v>
+      </c>
+      <c r="G885" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H885" t="n">
+        <v>3</v>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D886" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E886" t="n">
+        <v>69</v>
+      </c>
+      <c r="F886" t="n">
+        <v>0</v>
+      </c>
+      <c r="G886" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H886" t="n">
+        <v>2</v>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D887" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E887" t="n">
+        <v>62</v>
+      </c>
+      <c r="F887" t="n">
+        <v>0</v>
+      </c>
+      <c r="G887" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H887" t="n">
+        <v>2</v>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D888" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E888" t="n">
+        <v>62</v>
+      </c>
+      <c r="F888" t="n">
+        <v>0</v>
+      </c>
+      <c r="G888" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H888" t="n">
+        <v>3</v>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D889" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E889" t="n">
+        <v>77</v>
+      </c>
+      <c r="F889" t="n">
+        <v>0</v>
+      </c>
+      <c r="G889" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H889" t="n">
+        <v>3</v>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D890" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E890" t="n">
+        <v>69</v>
+      </c>
+      <c r="F890" t="n">
+        <v>0</v>
+      </c>
+      <c r="G890" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H890" t="n">
+        <v>3</v>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D891" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E891" t="n">
+        <v>64</v>
+      </c>
+      <c r="F891" t="n">
+        <v>0</v>
+      </c>
+      <c r="G891" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H891" t="n">
+        <v>2</v>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D892" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E892" t="n">
+        <v>63</v>
+      </c>
+      <c r="F892" t="n">
+        <v>0</v>
+      </c>
+      <c r="G892" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H892" t="n">
+        <v>1</v>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
         </is>
       </c>
     </row>
@@ -32222,7 +33443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33922,6 +35143,67 @@
       <c r="O28" t="inlineStr">
         <is>
           <t>2026-09-25T23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>33</v>
+      </c>
+      <c r="D29" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-09-26T03:15</t>
         </is>
       </c>
     </row>
@@ -33988,7 +35270,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -33997,7 +35279,7 @@
         <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>79.2</v>
+        <v>78.7</v>
       </c>
       <c r="G2" t="n">
         <v>1.8</v>
@@ -34015,7 +35297,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -34024,7 +35306,7 @@
         <v>24.9</v>
       </c>
       <c r="F3" t="n">
-        <v>81.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>3.4</v>
@@ -34051,7 +35333,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>75.5</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
         <v>0.9</v>
@@ -34069,16 +35351,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
       </c>
       <c r="E5" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="F5" t="n">
-        <v>66.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>0.9</v>
@@ -34105,7 +35387,7 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>80.5</v>
+        <v>79.8</v>
       </c>
       <c r="G6" t="n">
         <v>0.9</v>
@@ -34123,7 +35405,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -34132,7 +35414,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>73</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>0.8</v>
@@ -34159,7 +35441,7 @@
         <v>24.1</v>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>2.2</v>
@@ -34177,7 +35459,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -34186,7 +35468,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>67.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -34204,7 +35486,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -34213,7 +35495,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>77.8</v>
+        <v>77.3</v>
       </c>
       <c r="G10" t="n">
         <v>2.3</v>
@@ -34240,7 +35522,7 @@
         <v>25.8</v>
       </c>
       <c r="F11" t="n">
-        <v>77.8</v>
+        <v>77.3</v>
       </c>
       <c r="G11" t="n">
         <v>1.3</v>
@@ -34258,7 +35540,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -34267,7 +35549,7 @@
         <v>25.3</v>
       </c>
       <c r="F12" t="n">
-        <v>74.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>1.2</v>
@@ -34294,7 +35576,7 @@
         <v>24.4</v>
       </c>
       <c r="F13" t="n">
-        <v>81.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -34321,7 +35603,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>77.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -34339,7 +35621,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -34366,7 +35648,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -34375,7 +35657,7 @@
         <v>24.5</v>
       </c>
       <c r="F16" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -34393,7 +35675,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
@@ -34402,7 +35684,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>77.7</v>
+        <v>77.3</v>
       </c>
       <c r="G17" t="n">
         <v>1.1</v>
@@ -34420,7 +35702,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -34429,7 +35711,7 @@
         <v>23.7</v>
       </c>
       <c r="F18" t="n">
-        <v>73.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>1.9</v>
@@ -34456,7 +35738,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>83.3</v>
+        <v>82.7</v>
       </c>
       <c r="G19" t="n">
         <v>1.8</v>
@@ -34474,7 +35756,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -34483,7 +35765,7 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>71.5</v>
+        <v>71.3</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
@@ -34501,7 +35783,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -34510,7 +35792,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>65.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="G21" t="n">
         <v>0.7</v>
@@ -34528,7 +35810,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -34537,7 +35819,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>70.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>2.7</v>
@@ -34555,7 +35837,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -34564,7 +35846,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>75.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="G23" t="n">
         <v>0.2</v>
@@ -34591,7 +35873,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>78</v>
+        <v>77.5</v>
       </c>
       <c r="G24" t="n">
         <v>0.4</v>
@@ -34618,7 +35900,7 @@
         <v>24.5</v>
       </c>
       <c r="F25" t="n">
-        <v>81.2</v>
+        <v>80.5</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -34645,7 +35927,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>77.3</v>
+        <v>76.7</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -34663,7 +35945,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -34690,7 +35972,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -34717,7 +35999,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
@@ -34726,7 +36008,7 @@
         <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>77.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="G29" t="n">
         <v>0.2</v>
@@ -34744,7 +36026,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -34753,7 +36035,7 @@
         <v>24.5</v>
       </c>
       <c r="F30" t="n">
-        <v>70.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G30" t="n">
         <v>0.7</v>
@@ -34771,7 +36053,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -34780,7 +36062,7 @@
         <v>22.6</v>
       </c>
       <c r="F31" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>1.1</v>
@@ -34798,7 +36080,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -34825,7 +36107,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -34834,7 +36116,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>73.7</v>
+        <v>73.3</v>
       </c>
       <c r="G33" t="n">
         <v>1.1</v>
@@ -34852,7 +36134,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
@@ -34861,7 +36143,7 @@
         <v>24.5</v>
       </c>
       <c r="F34" t="n">
-        <v>71.5</v>
+        <v>71.2</v>
       </c>
       <c r="G34" t="n">
         <v>0.5</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I892"/>
+  <dimension ref="A1:I925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33429,6 +33429,1227 @@
       <c r="I892" t="inlineStr">
         <is>
           <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D893" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E893" t="n">
+        <v>74</v>
+      </c>
+      <c r="F893" t="n">
+        <v>0</v>
+      </c>
+      <c r="G893" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H893" t="n">
+        <v>3</v>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D894" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E894" t="n">
+        <v>73</v>
+      </c>
+      <c r="F894" t="n">
+        <v>0</v>
+      </c>
+      <c r="G894" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H894" t="n">
+        <v>3</v>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D895" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E895" t="n">
+        <v>63</v>
+      </c>
+      <c r="F895" t="n">
+        <v>0</v>
+      </c>
+      <c r="G895" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H895" t="n">
+        <v>2</v>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D896" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E896" t="n">
+        <v>78</v>
+      </c>
+      <c r="F896" t="n">
+        <v>0</v>
+      </c>
+      <c r="G896" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H896" t="n">
+        <v>3</v>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D897" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E897" t="n">
+        <v>67</v>
+      </c>
+      <c r="F897" t="n">
+        <v>0</v>
+      </c>
+      <c r="G897" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H897" t="n">
+        <v>3</v>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D898" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E898" t="n">
+        <v>67</v>
+      </c>
+      <c r="F898" t="n">
+        <v>0</v>
+      </c>
+      <c r="G898" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H898" t="n">
+        <v>3</v>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D899" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E899" t="n">
+        <v>68</v>
+      </c>
+      <c r="F899" t="n">
+        <v>0</v>
+      </c>
+      <c r="G899" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H899" t="n">
+        <v>3</v>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D900" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E900" t="n">
+        <v>74</v>
+      </c>
+      <c r="F900" t="n">
+        <v>0</v>
+      </c>
+      <c r="G900" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H900" t="n">
+        <v>2</v>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D901" t="n">
+        <v>23</v>
+      </c>
+      <c r="E901" t="n">
+        <v>71</v>
+      </c>
+      <c r="F901" t="n">
+        <v>0</v>
+      </c>
+      <c r="G901" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H901" t="n">
+        <v>1</v>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D902" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E902" t="n">
+        <v>65</v>
+      </c>
+      <c r="F902" t="n">
+        <v>0</v>
+      </c>
+      <c r="G902" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H902" t="n">
+        <v>3</v>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D903" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E903" t="n">
+        <v>65</v>
+      </c>
+      <c r="F903" t="n">
+        <v>0</v>
+      </c>
+      <c r="G903" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H903" t="n">
+        <v>3</v>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D904" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E904" t="n">
+        <v>69</v>
+      </c>
+      <c r="F904" t="n">
+        <v>0</v>
+      </c>
+      <c r="G904" t="n">
+        <v>16</v>
+      </c>
+      <c r="H904" t="n">
+        <v>3</v>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D905" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E905" t="n">
+        <v>68</v>
+      </c>
+      <c r="F905" t="n">
+        <v>0</v>
+      </c>
+      <c r="G905" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H905" t="n">
+        <v>3</v>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D906" t="n">
+        <v>23</v>
+      </c>
+      <c r="E906" t="n">
+        <v>80</v>
+      </c>
+      <c r="F906" t="n">
+        <v>0</v>
+      </c>
+      <c r="G906" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H906" t="n">
+        <v>2</v>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D907" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E907" t="n">
+        <v>66</v>
+      </c>
+      <c r="F907" t="n">
+        <v>0</v>
+      </c>
+      <c r="G907" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H907" t="n">
+        <v>3</v>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D908" t="n">
+        <v>23</v>
+      </c>
+      <c r="E908" t="n">
+        <v>76</v>
+      </c>
+      <c r="F908" t="n">
+        <v>0</v>
+      </c>
+      <c r="G908" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H908" t="n">
+        <v>2</v>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D909" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E909" t="n">
+        <v>77</v>
+      </c>
+      <c r="F909" t="n">
+        <v>0</v>
+      </c>
+      <c r="G909" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H909" t="n">
+        <v>3</v>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D910" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E910" t="n">
+        <v>65</v>
+      </c>
+      <c r="F910" t="n">
+        <v>0</v>
+      </c>
+      <c r="G910" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H910" t="n">
+        <v>2</v>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D911" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E911" t="n">
+        <v>79</v>
+      </c>
+      <c r="F911" t="n">
+        <v>0</v>
+      </c>
+      <c r="G911" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H911" t="n">
+        <v>3</v>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D912" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E912" t="n">
+        <v>66</v>
+      </c>
+      <c r="F912" t="n">
+        <v>0</v>
+      </c>
+      <c r="G912" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H912" t="n">
+        <v>3</v>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D913" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E913" t="n">
+        <v>79</v>
+      </c>
+      <c r="F913" t="n">
+        <v>0</v>
+      </c>
+      <c r="G913" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H913" t="n">
+        <v>3</v>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D914" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E914" t="n">
+        <v>70</v>
+      </c>
+      <c r="F914" t="n">
+        <v>0</v>
+      </c>
+      <c r="G914" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H914" t="n">
+        <v>3</v>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D915" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E915" t="n">
+        <v>73</v>
+      </c>
+      <c r="F915" t="n">
+        <v>0</v>
+      </c>
+      <c r="G915" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H915" t="n">
+        <v>2</v>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D916" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E916" t="n">
+        <v>67</v>
+      </c>
+      <c r="F916" t="n">
+        <v>0</v>
+      </c>
+      <c r="G916" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H916" t="n">
+        <v>3</v>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D917" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E917" t="n">
+        <v>65</v>
+      </c>
+      <c r="F917" t="n">
+        <v>0</v>
+      </c>
+      <c r="G917" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H917" t="n">
+        <v>3</v>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D918" t="n">
+        <v>23</v>
+      </c>
+      <c r="E918" t="n">
+        <v>76</v>
+      </c>
+      <c r="F918" t="n">
+        <v>0</v>
+      </c>
+      <c r="G918" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H918" t="n">
+        <v>3</v>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D919" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E919" t="n">
+        <v>78</v>
+      </c>
+      <c r="F919" t="n">
+        <v>0</v>
+      </c>
+      <c r="G919" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H919" t="n">
+        <v>3</v>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D920" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E920" t="n">
+        <v>70</v>
+      </c>
+      <c r="F920" t="n">
+        <v>0</v>
+      </c>
+      <c r="G920" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H920" t="n">
+        <v>3</v>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D921" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E921" t="n">
+        <v>66</v>
+      </c>
+      <c r="F921" t="n">
+        <v>0</v>
+      </c>
+      <c r="G921" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H921" t="n">
+        <v>3</v>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D922" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E922" t="n">
+        <v>81</v>
+      </c>
+      <c r="F922" t="n">
+        <v>0</v>
+      </c>
+      <c r="G922" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H922" t="n">
+        <v>3</v>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D923" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E923" t="n">
+        <v>79</v>
+      </c>
+      <c r="F923" t="n">
+        <v>0</v>
+      </c>
+      <c r="G923" t="n">
+        <v>14</v>
+      </c>
+      <c r="H923" t="n">
+        <v>3</v>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D924" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E924" t="n">
+        <v>63</v>
+      </c>
+      <c r="F924" t="n">
+        <v>0</v>
+      </c>
+      <c r="G924" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H924" t="n">
+        <v>2</v>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D925" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E925" t="n">
+        <v>69</v>
+      </c>
+      <c r="F925" t="n">
+        <v>0</v>
+      </c>
+      <c r="G925" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="H925" t="n">
+        <v>3</v>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
         </is>
       </c>
     </row>
@@ -33443,7 +34664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35204,6 +36425,67 @@
       <c r="O29" t="inlineStr">
         <is>
           <t>2026-09-26T03:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>33</v>
+      </c>
+      <c r="D30" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="I30" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-09-26T06:00</t>
         </is>
       </c>
     </row>
@@ -35279,7 +36561,7 @@
         <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>1.8</v>
@@ -35297,7 +36579,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -35306,7 +36588,7 @@
         <v>24.9</v>
       </c>
       <c r="F3" t="n">
-        <v>81.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.4</v>
@@ -35324,7 +36606,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -35333,7 +36615,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0.9</v>
@@ -35351,16 +36633,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
       </c>
       <c r="E5" t="n">
-        <v>24.3</v>
+        <v>23.2</v>
       </c>
       <c r="F5" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="G5" t="n">
         <v>0.9</v>
@@ -35378,7 +36660,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -35387,7 +36669,7 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>79.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>0.9</v>
@@ -35405,7 +36687,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -35414,7 +36696,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="G7" t="n">
         <v>0.8</v>
@@ -35432,7 +36714,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -35441,7 +36723,7 @@
         <v>24.1</v>
       </c>
       <c r="F8" t="n">
-        <v>83.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>2.2</v>
@@ -35459,7 +36741,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -35468,7 +36750,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>67.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -35486,7 +36768,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -35495,7 +36777,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>77.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>2.3</v>
@@ -35513,16 +36795,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="F11" t="n">
-        <v>77.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>1.3</v>
@@ -35540,7 +36822,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -35549,7 +36831,7 @@
         <v>25.3</v>
       </c>
       <c r="F12" t="n">
-        <v>74.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="G12" t="n">
         <v>1.2</v>
@@ -35576,7 +36858,7 @@
         <v>24.4</v>
       </c>
       <c r="F13" t="n">
-        <v>80.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -35594,7 +36876,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -35603,7 +36885,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>77.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -35621,7 +36903,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -35630,7 +36912,7 @@
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>72.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>1.6</v>
@@ -35657,7 +36939,7 @@
         <v>24.5</v>
       </c>
       <c r="F16" t="n">
-        <v>80.5</v>
+        <v>80</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -35675,16 +36957,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F17" t="n">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
       <c r="G17" t="n">
         <v>1.1</v>
@@ -35702,16 +36984,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
       </c>
       <c r="E18" t="n">
-        <v>23.7</v>
+        <v>22.7</v>
       </c>
       <c r="F18" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>1.9</v>
@@ -35729,7 +37011,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -35738,7 +37020,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>82.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>1.8</v>
@@ -35756,7 +37038,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -35765,7 +37047,7 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>71.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
@@ -35783,7 +37065,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -35810,7 +37092,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -35819,7 +37101,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>70.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="G22" t="n">
         <v>2.7</v>
@@ -35837,7 +37119,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -35846,7 +37128,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>75.5</v>
+        <v>75.3</v>
       </c>
       <c r="G23" t="n">
         <v>0.2</v>
@@ -35864,7 +37146,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -35873,7 +37155,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>77.5</v>
+        <v>77.3</v>
       </c>
       <c r="G24" t="n">
         <v>0.4</v>
@@ -35891,7 +37173,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -35900,7 +37182,7 @@
         <v>24.5</v>
       </c>
       <c r="F25" t="n">
-        <v>80.5</v>
+        <v>80</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -35918,7 +37200,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
@@ -35927,7 +37209,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>76.7</v>
+        <v>76.2</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -35945,7 +37227,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -35954,7 +37236,7 @@
         <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>70.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>0.3</v>
@@ -35972,16 +37254,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
       </c>
       <c r="E28" t="n">
-        <v>23.3</v>
+        <v>22.9</v>
       </c>
       <c r="F28" t="n">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G28" t="n">
         <v>0.9</v>
@@ -35999,16 +37281,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
       </c>
       <c r="E29" t="n">
-        <v>24.2</v>
+        <v>23.6</v>
       </c>
       <c r="F29" t="n">
-        <v>76.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>0.2</v>
@@ -36026,7 +37308,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -36035,7 +37317,7 @@
         <v>24.5</v>
       </c>
       <c r="F30" t="n">
-        <v>69.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="G30" t="n">
         <v>0.7</v>
@@ -36053,16 +37335,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
       </c>
       <c r="E31" t="n">
-        <v>22.6</v>
+        <v>21.9</v>
       </c>
       <c r="F31" t="n">
-        <v>71.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="G31" t="n">
         <v>1.1</v>
@@ -36080,7 +37362,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="D32" t="n">
         <v>32.1</v>
@@ -36089,7 +37371,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>69.90000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -36107,7 +37389,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -36116,7 +37398,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>73.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>1.1</v>
@@ -36134,16 +37416,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
       </c>
       <c r="E34" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="F34" t="n">
-        <v>71.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G34" t="n">
         <v>0.5</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I925"/>
+  <dimension ref="A1:I958"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34650,6 +34650,1227 @@
       <c r="I925" t="inlineStr">
         <is>
           <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D926" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E926" t="n">
+        <v>62</v>
+      </c>
+      <c r="F926" t="n">
+        <v>0</v>
+      </c>
+      <c r="G926" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="H926" t="n">
+        <v>1</v>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D927" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E927" t="n">
+        <v>60</v>
+      </c>
+      <c r="F927" t="n">
+        <v>0</v>
+      </c>
+      <c r="G927" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H927" t="n">
+        <v>1</v>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D928" t="n">
+        <v>30</v>
+      </c>
+      <c r="E928" t="n">
+        <v>61</v>
+      </c>
+      <c r="F928" t="n">
+        <v>0</v>
+      </c>
+      <c r="G928" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H928" t="n">
+        <v>3</v>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D929" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E929" t="n">
+        <v>60</v>
+      </c>
+      <c r="F929" t="n">
+        <v>0</v>
+      </c>
+      <c r="G929" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H929" t="n">
+        <v>3</v>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D930" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E930" t="n">
+        <v>67</v>
+      </c>
+      <c r="F930" t="n">
+        <v>0</v>
+      </c>
+      <c r="G930" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H930" t="n">
+        <v>2</v>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D931" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E931" t="n">
+        <v>60</v>
+      </c>
+      <c r="F931" t="n">
+        <v>0</v>
+      </c>
+      <c r="G931" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H931" t="n">
+        <v>3</v>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D932" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E932" t="n">
+        <v>61</v>
+      </c>
+      <c r="F932" t="n">
+        <v>0</v>
+      </c>
+      <c r="G932" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H932" t="n">
+        <v>3</v>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D933" t="n">
+        <v>31</v>
+      </c>
+      <c r="E933" t="n">
+        <v>51</v>
+      </c>
+      <c r="F933" t="n">
+        <v>0</v>
+      </c>
+      <c r="G933" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H933" t="n">
+        <v>3</v>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D934" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E934" t="n">
+        <v>65</v>
+      </c>
+      <c r="F934" t="n">
+        <v>0</v>
+      </c>
+      <c r="G934" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H934" t="n">
+        <v>3</v>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D935" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E935" t="n">
+        <v>64</v>
+      </c>
+      <c r="F935" t="n">
+        <v>0</v>
+      </c>
+      <c r="G935" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H935" t="n">
+        <v>3</v>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D936" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E936" t="n">
+        <v>58</v>
+      </c>
+      <c r="F936" t="n">
+        <v>0</v>
+      </c>
+      <c r="G936" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H936" t="n">
+        <v>2</v>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D937" t="n">
+        <v>31</v>
+      </c>
+      <c r="E937" t="n">
+        <v>61</v>
+      </c>
+      <c r="F937" t="n">
+        <v>0</v>
+      </c>
+      <c r="G937" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H937" t="n">
+        <v>3</v>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D938" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E938" t="n">
+        <v>61</v>
+      </c>
+      <c r="F938" t="n">
+        <v>0</v>
+      </c>
+      <c r="G938" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H938" t="n">
+        <v>2</v>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D939" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E939" t="n">
+        <v>59</v>
+      </c>
+      <c r="F939" t="n">
+        <v>0</v>
+      </c>
+      <c r="G939" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H939" t="n">
+        <v>3</v>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D940" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E940" t="n">
+        <v>64</v>
+      </c>
+      <c r="F940" t="n">
+        <v>0</v>
+      </c>
+      <c r="G940" t="n">
+        <v>19</v>
+      </c>
+      <c r="H940" t="n">
+        <v>3</v>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D941" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E941" t="n">
+        <v>66</v>
+      </c>
+      <c r="F941" t="n">
+        <v>0</v>
+      </c>
+      <c r="G941" t="n">
+        <v>19</v>
+      </c>
+      <c r="H941" t="n">
+        <v>3</v>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D942" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E942" t="n">
+        <v>60</v>
+      </c>
+      <c r="F942" t="n">
+        <v>0</v>
+      </c>
+      <c r="G942" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H942" t="n">
+        <v>3</v>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D943" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E943" t="n">
+        <v>65</v>
+      </c>
+      <c r="F943" t="n">
+        <v>0</v>
+      </c>
+      <c r="G943" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H943" t="n">
+        <v>3</v>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D944" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E944" t="n">
+        <v>60</v>
+      </c>
+      <c r="F944" t="n">
+        <v>0</v>
+      </c>
+      <c r="G944" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H944" t="n">
+        <v>3</v>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D945" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E945" t="n">
+        <v>54</v>
+      </c>
+      <c r="F945" t="n">
+        <v>0</v>
+      </c>
+      <c r="G945" t="n">
+        <v>18</v>
+      </c>
+      <c r="H945" t="n">
+        <v>2</v>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D946" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E946" t="n">
+        <v>59</v>
+      </c>
+      <c r="F946" t="n">
+        <v>0</v>
+      </c>
+      <c r="G946" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H946" t="n">
+        <v>3</v>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D947" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E947" t="n">
+        <v>65</v>
+      </c>
+      <c r="F947" t="n">
+        <v>0</v>
+      </c>
+      <c r="G947" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H947" t="n">
+        <v>2</v>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D948" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E948" t="n">
+        <v>65</v>
+      </c>
+      <c r="F948" t="n">
+        <v>0</v>
+      </c>
+      <c r="G948" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H948" t="n">
+        <v>1</v>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D949" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E949" t="n">
+        <v>67</v>
+      </c>
+      <c r="F949" t="n">
+        <v>0</v>
+      </c>
+      <c r="G949" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H949" t="n">
+        <v>3</v>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D950" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E950" t="n">
+        <v>61</v>
+      </c>
+      <c r="F950" t="n">
+        <v>0</v>
+      </c>
+      <c r="G950" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H950" t="n">
+        <v>3</v>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D951" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E951" t="n">
+        <v>60</v>
+      </c>
+      <c r="F951" t="n">
+        <v>0</v>
+      </c>
+      <c r="G951" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H951" t="n">
+        <v>3</v>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D952" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E952" t="n">
+        <v>59</v>
+      </c>
+      <c r="F952" t="n">
+        <v>0</v>
+      </c>
+      <c r="G952" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H952" t="n">
+        <v>3</v>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D953" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E953" t="n">
+        <v>64</v>
+      </c>
+      <c r="F953" t="n">
+        <v>0</v>
+      </c>
+      <c r="G953" t="n">
+        <v>23</v>
+      </c>
+      <c r="H953" t="n">
+        <v>3</v>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D954" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E954" t="n">
+        <v>57</v>
+      </c>
+      <c r="F954" t="n">
+        <v>0</v>
+      </c>
+      <c r="G954" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H954" t="n">
+        <v>3</v>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D955" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E955" t="n">
+        <v>65</v>
+      </c>
+      <c r="F955" t="n">
+        <v>0</v>
+      </c>
+      <c r="G955" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H955" t="n">
+        <v>3</v>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D956" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E956" t="n">
+        <v>60</v>
+      </c>
+      <c r="F956" t="n">
+        <v>0</v>
+      </c>
+      <c r="G956" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H956" t="n">
+        <v>3</v>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D957" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E957" t="n">
+        <v>60</v>
+      </c>
+      <c r="F957" t="n">
+        <v>0</v>
+      </c>
+      <c r="G957" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H957" t="n">
+        <v>3</v>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D958" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E958" t="n">
+        <v>58</v>
+      </c>
+      <c r="F958" t="n">
+        <v>0</v>
+      </c>
+      <c r="G958" t="n">
+        <v>22</v>
+      </c>
+      <c r="H958" t="n">
+        <v>3</v>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
         </is>
       </c>
     </row>
@@ -34664,7 +35885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36486,6 +37707,67 @@
       <c r="O30" t="inlineStr">
         <is>
           <t>2026-09-26T06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>33</v>
+      </c>
+      <c r="D31" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>23</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:15</t>
         </is>
       </c>
     </row>
@@ -36561,7 +37843,7 @@
         <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>78.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="G2" t="n">
         <v>1.8</v>
@@ -36579,7 +37861,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -36588,7 +37870,7 @@
         <v>24.9</v>
       </c>
       <c r="F3" t="n">
-        <v>81.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>3.4</v>
@@ -36615,7 +37897,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>74.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0.9</v>
@@ -36642,7 +37924,7 @@
         <v>23.2</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>66.8</v>
       </c>
       <c r="G5" t="n">
         <v>0.9</v>
@@ -36660,7 +37942,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -36669,7 +37951,7 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>79.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>0.9</v>
@@ -36687,7 +37969,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -36696,7 +37978,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>72.2</v>
+        <v>71.8</v>
       </c>
       <c r="G7" t="n">
         <v>0.8</v>
@@ -36714,7 +37996,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -36723,7 +38005,7 @@
         <v>24.1</v>
       </c>
       <c r="F8" t="n">
-        <v>82.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>2.2</v>
@@ -36750,7 +38032,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>68.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -36777,7 +38059,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>77.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="G10" t="n">
         <v>2.3</v>
@@ -36804,7 +38086,7 @@
         <v>25.7</v>
       </c>
       <c r="F11" t="n">
-        <v>76.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>1.3</v>
@@ -36822,7 +38104,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -36831,7 +38113,7 @@
         <v>25.3</v>
       </c>
       <c r="F12" t="n">
-        <v>74</v>
+        <v>73.5</v>
       </c>
       <c r="G12" t="n">
         <v>1.2</v>
@@ -36849,7 +38131,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -36858,7 +38140,7 @@
         <v>24.4</v>
       </c>
       <c r="F13" t="n">
-        <v>80.2</v>
+        <v>79.5</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -36876,7 +38158,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -36885,7 +38167,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>77.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -36903,7 +38185,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -36912,7 +38194,7 @@
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>72.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>1.6</v>
@@ -36930,7 +38212,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="D16" t="n">
         <v>32.7</v>
@@ -36939,7 +38221,7 @@
         <v>24.5</v>
       </c>
       <c r="F16" t="n">
-        <v>80</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -36957,7 +38239,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
@@ -36966,7 +38248,7 @@
         <v>23</v>
       </c>
       <c r="F17" t="n">
-        <v>77.2</v>
+        <v>76.8</v>
       </c>
       <c r="G17" t="n">
         <v>1.1</v>
@@ -36993,7 +38275,7 @@
         <v>22.7</v>
       </c>
       <c r="F18" t="n">
-        <v>73.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>1.9</v>
@@ -37011,7 +38293,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -37020,7 +38302,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>82.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="G19" t="n">
         <v>1.8</v>
@@ -37038,7 +38320,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -37047,7 +38329,7 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>71.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
@@ -37074,7 +38356,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>65.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0.7</v>
@@ -37101,7 +38383,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>71.2</v>
+        <v>70.8</v>
       </c>
       <c r="G22" t="n">
         <v>2.7</v>
@@ -37119,7 +38401,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -37128,7 +38410,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>75.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0.2</v>
@@ -37155,7 +38437,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>77.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0.4</v>
@@ -37182,7 +38464,7 @@
         <v>24.5</v>
       </c>
       <c r="F25" t="n">
-        <v>80</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -37200,7 +38482,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
@@ -37209,7 +38491,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>76.2</v>
+        <v>75.7</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -37236,7 +38518,7 @@
         <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>70.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0.3</v>
@@ -37254,7 +38536,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -37263,7 +38545,7 @@
         <v>22.9</v>
       </c>
       <c r="F28" t="n">
-        <v>68.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G28" t="n">
         <v>0.9</v>
@@ -37290,7 +38572,7 @@
         <v>23.6</v>
       </c>
       <c r="F29" t="n">
-        <v>76.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>0.2</v>
@@ -37308,7 +38590,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="D30" t="n">
         <v>34.5</v>
@@ -37317,7 +38599,7 @@
         <v>24.5</v>
       </c>
       <c r="F30" t="n">
-        <v>69.8</v>
+        <v>69.3</v>
       </c>
       <c r="G30" t="n">
         <v>0.7</v>
@@ -37335,7 +38617,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="D31" t="n">
         <v>30.5</v>
@@ -37344,7 +38626,7 @@
         <v>21.9</v>
       </c>
       <c r="F31" t="n">
-        <v>72.2</v>
+        <v>72</v>
       </c>
       <c r="G31" t="n">
         <v>1.1</v>
@@ -37371,7 +38653,7 @@
         <v>23.9</v>
       </c>
       <c r="F32" t="n">
-        <v>70.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>3.3</v>
@@ -37389,7 +38671,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="D33" t="n">
         <v>34.4</v>
@@ -37398,7 +38680,7 @@
         <v>24.7</v>
       </c>
       <c r="F33" t="n">
-        <v>72.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="G33" t="n">
         <v>1.1</v>
@@ -37425,7 +38707,7 @@
         <v>24.3</v>
       </c>
       <c r="F34" t="n">
-        <v>71.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="G34" t="n">
         <v>0.5</v>

--- a/data/weather_data.xlsx
+++ b/data/weather_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I958"/>
+  <dimension ref="A1:I991"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35871,6 +35871,1227 @@
       <c r="I958" t="inlineStr">
         <is>
           <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Adilabad</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D959" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E959" t="n">
+        <v>59</v>
+      </c>
+      <c r="F959" t="n">
+        <v>0</v>
+      </c>
+      <c r="G959" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H959" t="n">
+        <v>3</v>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Bhadradri Kothagudem</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D960" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E960" t="n">
+        <v>66</v>
+      </c>
+      <c r="F960" t="n">
+        <v>0</v>
+      </c>
+      <c r="G960" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H960" t="n">
+        <v>2</v>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Hanumakonda</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D961" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E961" t="n">
+        <v>61</v>
+      </c>
+      <c r="F961" t="n">
+        <v>0</v>
+      </c>
+      <c r="G961" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H961" t="n">
+        <v>0</v>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D962" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E962" t="n">
+        <v>53</v>
+      </c>
+      <c r="F962" t="n">
+        <v>0</v>
+      </c>
+      <c r="G962" t="n">
+        <v>14</v>
+      </c>
+      <c r="H962" t="n">
+        <v>2</v>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Jagtial</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D963" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E963" t="n">
+        <v>65</v>
+      </c>
+      <c r="F963" t="n">
+        <v>0</v>
+      </c>
+      <c r="G963" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H963" t="n">
+        <v>2</v>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Jangaon</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D964" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E964" t="n">
+        <v>59</v>
+      </c>
+      <c r="F964" t="n">
+        <v>0</v>
+      </c>
+      <c r="G964" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H964" t="n">
+        <v>0</v>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Jayashankar Bhupalpally</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D965" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E965" t="n">
+        <v>65</v>
+      </c>
+      <c r="F965" t="n">
+        <v>0</v>
+      </c>
+      <c r="G965" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H965" t="n">
+        <v>1</v>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D966" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E966" t="n">
+        <v>40</v>
+      </c>
+      <c r="F966" t="n">
+        <v>0</v>
+      </c>
+      <c r="G966" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H966" t="n">
+        <v>3</v>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Kamareddy</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D967" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E967" t="n">
+        <v>60</v>
+      </c>
+      <c r="F967" t="n">
+        <v>0</v>
+      </c>
+      <c r="G967" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H967" t="n">
+        <v>3</v>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D968" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E968" t="n">
+        <v>63</v>
+      </c>
+      <c r="F968" t="n">
+        <v>0</v>
+      </c>
+      <c r="G968" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H968" t="n">
+        <v>1</v>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D969" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E969" t="n">
+        <v>58</v>
+      </c>
+      <c r="F969" t="n">
+        <v>0</v>
+      </c>
+      <c r="G969" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H969" t="n">
+        <v>3</v>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D970" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E970" t="n">
+        <v>65</v>
+      </c>
+      <c r="F970" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G970" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H970" t="n">
+        <v>51</v>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Mahabubabad</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D971" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E971" t="n">
+        <v>62</v>
+      </c>
+      <c r="F971" t="n">
+        <v>0</v>
+      </c>
+      <c r="G971" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H971" t="n">
+        <v>3</v>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Mahbubnagar</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D972" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E972" t="n">
+        <v>56</v>
+      </c>
+      <c r="F972" t="n">
+        <v>0</v>
+      </c>
+      <c r="G972" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H972" t="n">
+        <v>2</v>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Mancherial</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D973" t="n">
+        <v>31</v>
+      </c>
+      <c r="E973" t="n">
+        <v>68</v>
+      </c>
+      <c r="F973" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G973" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H973" t="n">
+        <v>51</v>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Medak</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D974" t="n">
+        <v>30</v>
+      </c>
+      <c r="E974" t="n">
+        <v>59</v>
+      </c>
+      <c r="F974" t="n">
+        <v>0</v>
+      </c>
+      <c r="G974" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H974" t="n">
+        <v>0</v>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Medchal-Malkajgiri</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D975" t="n">
+        <v>30</v>
+      </c>
+      <c r="E975" t="n">
+        <v>55</v>
+      </c>
+      <c r="F975" t="n">
+        <v>0</v>
+      </c>
+      <c r="G975" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H975" t="n">
+        <v>3</v>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Mulugu</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D976" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E976" t="n">
+        <v>67</v>
+      </c>
+      <c r="F976" t="n">
+        <v>0</v>
+      </c>
+      <c r="G976" t="n">
+        <v>12</v>
+      </c>
+      <c r="H976" t="n">
+        <v>1</v>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Nagarkurnool</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D977" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E977" t="n">
+        <v>55</v>
+      </c>
+      <c r="F977" t="n">
+        <v>0</v>
+      </c>
+      <c r="G977" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H977" t="n">
+        <v>1</v>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Nalgonda</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D978" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E978" t="n">
+        <v>52</v>
+      </c>
+      <c r="F978" t="n">
+        <v>0</v>
+      </c>
+      <c r="G978" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H978" t="n">
+        <v>1</v>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Narayanpet</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D979" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E979" t="n">
+        <v>50</v>
+      </c>
+      <c r="F979" t="n">
+        <v>0</v>
+      </c>
+      <c r="G979" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H979" t="n">
+        <v>3</v>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Nirmal</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D980" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E980" t="n">
+        <v>57</v>
+      </c>
+      <c r="F980" t="n">
+        <v>0</v>
+      </c>
+      <c r="G980" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H980" t="n">
+        <v>2</v>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D981" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E981" t="n">
+        <v>64</v>
+      </c>
+      <c r="F981" t="n">
+        <v>0</v>
+      </c>
+      <c r="G981" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H981" t="n">
+        <v>3</v>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Peddapalli</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D982" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E982" t="n">
+        <v>68</v>
+      </c>
+      <c r="F982" t="n">
+        <v>0</v>
+      </c>
+      <c r="G982" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H982" t="n">
+        <v>1</v>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Rajanna Sircilla</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D983" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E983" t="n">
+        <v>59</v>
+      </c>
+      <c r="F983" t="n">
+        <v>0</v>
+      </c>
+      <c r="G983" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H983" t="n">
+        <v>2</v>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Rangareddy</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D984" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E984" t="n">
+        <v>58</v>
+      </c>
+      <c r="F984" t="n">
+        <v>0</v>
+      </c>
+      <c r="G984" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H984" t="n">
+        <v>2</v>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Sangareddy</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D985" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E985" t="n">
+        <v>50</v>
+      </c>
+      <c r="F985" t="n">
+        <v>0</v>
+      </c>
+      <c r="G985" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H985" t="n">
+        <v>0</v>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D986" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E986" t="n">
+        <v>61</v>
+      </c>
+      <c r="F986" t="n">
+        <v>0</v>
+      </c>
+      <c r="G986" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="H986" t="n">
+        <v>0</v>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Suryapet</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D987" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E987" t="n">
+        <v>58</v>
+      </c>
+      <c r="F987" t="n">
+        <v>0</v>
+      </c>
+      <c r="G987" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H987" t="n">
+        <v>3</v>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D988" t="n">
+        <v>29</v>
+      </c>
+      <c r="E988" t="n">
+        <v>61</v>
+      </c>
+      <c r="F988" t="n">
+        <v>0</v>
+      </c>
+      <c r="G988" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H988" t="n">
+        <v>0</v>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Wanaparthy</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D989" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E989" t="n">
+        <v>51</v>
+      </c>
+      <c r="F989" t="n">
+        <v>0</v>
+      </c>
+      <c r="G989" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H989" t="n">
+        <v>2</v>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D990" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E990" t="n">
+        <v>57</v>
+      </c>
+      <c r="F990" t="n">
+        <v>0</v>
+      </c>
+      <c r="G990" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H990" t="n">
+        <v>1</v>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Yadadri Bhuvanagiri</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D991" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E991" t="n">
+        <v>56</v>
+      </c>
+      <c r="F991" t="n">
+        <v>0</v>
+      </c>
+      <c r="G991" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H991" t="n">
+        <v>3</v>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
         </is>
       </c>
     </row>
@@ -35885,7 +37106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37768,6 +38989,67 @@
       <c r="O31" t="inlineStr">
         <is>
           <t>2026-09-26T11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>33</v>
+      </c>
+      <c r="D32" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Jogulamba Gadwal</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Vikarabad</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>29</v>
+      </c>
+      <c r="I32" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Kumuram Bheem Asifabad</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Siddipet</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2026-09-26T16:15</t>
         </is>
       </c>
     </row>
@@ -37834,7 +39116,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
         <v>31.7</v>
@@ -37843,7 +39125,7 @@
         <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>78</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>1.8</v>
@@ -37861,7 +39143,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="D3" t="n">
         <v>34.1</v>
@@ -37870,7 +39152,7 @@
         <v>24.9</v>
       </c>
       <c r="F3" t="n">
-        <v>80.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>3.4</v>
@@ -37888,7 +39170,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="D4" t="n">
         <v>33.5</v>
@@ -37897,7 +39179,7 @@
         <v>24.9</v>
       </c>
       <c r="F4" t="n">
-        <v>74.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="G4" t="n">
         <v>0.9</v>
@@ -37915,7 +39197,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="D5" t="n">
         <v>32.2</v>
@@ -37924,7 +39206,7 @@
         <v>23.2</v>
       </c>
       <c r="F5" t="n">
-        <v>66.8</v>
+        <v>66.3</v>
       </c>
       <c r="G5" t="n">
         <v>0.9</v>
@@ -37942,7 +39224,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="D6" t="n">
         <v>31.4</v>
@@ -37951,7 +39233,7 @@
         <v>25.1</v>
       </c>
       <c r="F6" t="n">
-        <v>78.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="G6" t="n">
         <v>0.9</v>
@@ -37969,7 +39251,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="D7" t="n">
         <v>32</v>
@@ -37978,7 +39260,7 @@
         <v>24.4</v>
       </c>
       <c r="F7" t="n">
-        <v>71.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>0.8</v>
@@ -37996,7 +39278,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="D8" t="n">
         <v>33</v>
@@ -38005,7 +39287,7 @@
         <v>24.1</v>
       </c>
       <c r="F8" t="n">
-        <v>82.09999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>2.2</v>
@@ -38023,7 +39305,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.4</v>
+        <v>28.6</v>
       </c>
       <c r="D9" t="n">
         <v>34.2</v>
@@ -38032,7 +39314,7 @@
         <v>23.9</v>
       </c>
       <c r="F9" t="n">
-        <v>67.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -38050,7 +39332,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="D10" t="n">
         <v>30.1</v>
@@ -38059,7 +39341,7 @@
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>2.3</v>
@@ -38077,7 +39359,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="D11" t="n">
         <v>32</v>
@@ -38086,7 +39368,7 @@
         <v>25.7</v>
       </c>
       <c r="F11" t="n">
-        <v>76.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="G11" t="n">
         <v>1.3</v>
@@ -38104,7 +39386,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="D12" t="n">
         <v>35.2</v>
@@ -38113,7 +39395,7 @@
         <v>25.3</v>
       </c>
       <c r="F12" t="n">
-        <v>73.5</v>
+        <v>73</v>
       </c>
       <c r="G12" t="n">
         <v>1.2</v>
@@ -38131,7 +39413,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="D13" t="n">
         <v>32.8</v>
@@ -38140,10 +39422,10 @@
         <v>24.4</v>
       </c>
       <c r="F13" t="n">
-        <v>79.5</v>
+        <v>79</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="14">
@@ -38158,7 +39440,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="D14" t="n">
         <v>33.3</v>
@@ -38167,7 +39449,7 @@
         <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>76.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -38185,7 +39467,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="D15" t="n">
         <v>31.1</v>
@@ -38194,7 +39476,7 @@
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>71.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>1.6</v>
@@ -38221,10 +39503,10 @@
         <v>24.5</v>
       </c>
       <c r="F16" t="n">
-        <v>79.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="17">
@@ -38239,7 +39521,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="D17" t="n">
         <v>30.4</v>
@@ -38248,7 +39530,7 @@
         <v>23</v>
       </c>
       <c r="F17" t="n">
-        <v>76.8</v>
+        <v>76.2</v>
       </c>
       <c r="G17" t="n">
         <v>1.1</v>
@@ -38266,7 +39548,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="D18" t="n">
         <v>31.1</v>
@@ -38275,7 +39557,7 @@
         <v>22.7</v>
       </c>
       <c r="F18" t="n">
-        <v>73.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>1.9</v>
@@ -38293,7 +39575,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="D19" t="n">
         <v>32</v>
@@ -38302,7 +39584,7 @@
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>81.5</v>
+        <v>81</v>
       </c>
       <c r="G19" t="n">
         <v>1.8</v>
@@ -38320,7 +39602,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="D20" t="n">
         <v>32.2</v>
@@ -38329,7 +39611,7 @@
         <v>23.4</v>
       </c>
       <c r="F20" t="n">
-        <v>71.2</v>
+        <v>70.7</v>
       </c>
       <c r="G20" t="n">
         <v>2.1</v>
@@ -38347,7 +39629,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="D21" t="n">
         <v>36.2</v>
@@ -38356,7 +39638,7 @@
         <v>25.7</v>
       </c>
       <c r="F21" t="n">
-        <v>64.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0.7</v>
@@ -38374,7 +39656,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="D22" t="n">
         <v>31.4</v>
@@ -38383,7 +39665,7 @@
         <v>22.5</v>
       </c>
       <c r="F22" t="n">
-        <v>70.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>2.7</v>
@@ -38401,7 +39683,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="D23" t="n">
         <v>31.6</v>
@@ -38410,7 +39692,7 @@
         <v>24.4</v>
       </c>
       <c r="F23" t="n">
-        <v>74.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="G23" t="n">
         <v>0.2</v>
@@ -38428,7 +39710,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="D24" t="n">
         <v>30.6</v>
@@ -38437,7 +39719,7 @@
         <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>76.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="G24" t="n">
         <v>0.4</v>
@@ -38455,7 +39737,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="D25" t="n">
         <v>32</v>
@@ -38464,7 +39746,7 @@
         <v>24.5</v>
       </c>
       <c r="F25" t="n">
-        <v>79.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -38482,7 +39764,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="D26" t="n">
         <v>31.2</v>
@@ -38491,7 +39773,7 @@
         <v>25.1</v>
       </c>
       <c r="F26" t="n">
-        <v>75.7</v>
+        <v>75.2</v>
       </c>
       <c r="G26" t="n">
         <v>0.1</v>
@@ -38509,7 +39791,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="D27" t="n">
         <v>30.8</v>
@@ -38518,7 +39800,7 @@
         <v>22.9</v>
       </c>
       <c r="F27" t="n">
-        <v>70.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="G27" t="n">
         <v>0.3</v>
@@ -38536,7 +39818,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="D28" t="n">
         <v>31.9</v>
@@ -38545,7 +39827,7 @@
         <v>22.9</v>
       </c>
       <c r="F28" t="n">
-        <v>68.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="G28" t="n">
         <v>0.9</v>
@@ -38563,7 +39845,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="D29" t="n">
         <v>30.2</v>
@@ -38572,7 +39854,7 @@
         <v>23.6</v>
       </c>
       <c r="F29" t="n">
-        <v>76.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>0.2</v>
@@ -38590,7 +39872,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>